--- a/mc2/result/excel/engram_diverse.xlsx
+++ b/mc2/result/excel/engram_diverse.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6210" uniqueCount="3300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6210" uniqueCount="3299">
   <si>
     <t>case_name</t>
   </si>
@@ -62,7 +62,7 @@
     <t>world_size</t>
   </si>
   <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_7_ID001</t>
+    <t>h256_ws4_inbf16_outbf16_ID001</t>
   </si>
   <si>
     <t>[[65536, 256], [[967], [14135], [9117], [40949]]]</t>
@@ -86,13 +86,13 @@
     <t>[967, 14135, 9117, 40949]</t>
   </si>
   <si>
-    <t>[[967], [14135], [7625, 1, 1, 1, 1, 1, 1487], [6524, 1663, 502, 32260]]</t>
+    <t>[436, 7928, 9009, 35826]</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>h256_ws4_infp16_outfp16_fetch_4_ID002</t>
+    <t>h256_ws4_infp16_outfp16_ID002</t>
   </si>
   <si>
     <t>[[65536, 256], [[256], [469], [30194], [4476]]]</t>
@@ -107,10 +107,10 @@
     <t>[256, 469, 30194, 4476]</t>
   </si>
   <si>
-    <t>[[199, 57], [1, 1, 1, 466], [10065, 10065, 10064], [198, 992, 462, 2824]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outfp32_fetch_8_ID003</t>
+    <t>[216, 410, 27694, 764]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outfp32_ID003</t>
   </si>
   <si>
     <t>[[65536, 256], [[9916], [718], [2073], [40751]]]</t>
@@ -125,10 +125,10 @@
     <t>[9916, 718, 2073, 40751]</t>
   </si>
   <si>
-    <t>[[2950, 908, 2958, 949, 915, 553, 233, 450], [180, 180, 179, 179], [1037, 1036], [14789, 8235, 1440, 16287]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_inbf16_outbf16_fetch_2_ID004</t>
+    <t>[9496, 29, 1979, 29712]</t>
+  </si>
+  <si>
+    <t>h64_ws4_inbf16_outbf16_ID004</t>
   </si>
   <si>
     <t>[[65536, 64], [[2690], [41383], [168], [80]]]</t>
@@ -140,10 +140,10 @@
     <t>[2690, 41383, 168, 80]</t>
   </si>
   <si>
-    <t>[[1345, 1345], [22682, 18701], [168], [40, 40]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_inbf16_outbf16_fetch_4_ID005</t>
+    <t>[2475, 35370, 164, 7]</t>
+  </si>
+  <si>
+    <t>h128_ws4_inbf16_outbf16_ID005</t>
   </si>
   <si>
     <t>[[65536, 128], [[33496], [44736], [69], [26321]]]</t>
@@ -155,10 +155,10 @@
     <t>[33496, 44736, 69, 26321]</t>
   </si>
   <si>
-    <t>[[16748, 16748], [20897, 4923, 5857, 13059], [54, 1, 14], [1, 26320]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_3_ID006</t>
+    <t>[33379, 44664, 66, 2252]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID006</t>
   </si>
   <si>
     <t>[[65536, 256], [[15280], [5286], [28], [40818]]]</t>
@@ -167,10 +167,10 @@
     <t>[15280, 5286, 28, 40818]</t>
   </si>
   <si>
-    <t>[[15280], [2643, 2643], [28], [13606, 13606, 13606]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_inbf16_outbf16_fetch_2_ID007</t>
+    <t>[115, 4648, 11, 22603]</t>
+  </si>
+  <si>
+    <t>h512_ws4_inbf16_outbf16_ID007</t>
   </si>
   <si>
     <t>[[65536, 512], [[3471], [1791], [648], [696]]]</t>
@@ -182,10 +182,10 @@
     <t>[3471, 1791, 648, 696]</t>
   </si>
   <si>
-    <t>[[3471], [1791], [1, 647], [696]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_inbf16_outbf16_fetch_5_ID008</t>
+    <t>[1995, 91, 15, 115]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_inbf16_outbf16_ID008</t>
   </si>
   <si>
     <t>[[65536, 1024], [[7150], [821], [27], [9296]]]</t>
@@ -197,10 +197,10 @@
     <t>[7150, 821, 27, 9296]</t>
   </si>
   <si>
-    <t>[[1, 714, 2860, 2145, 1430], [274, 274, 273], [27], [923, 2825, 5548]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_inbf16_outbf16_fetch_5_ID009</t>
+    <t>[3647, 11, 10, 1211]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_inbf16_outbf16_ID009</t>
   </si>
   <si>
     <t>[[65536, 2048], [[7116], [4049], [50421], [8597]]]</t>
@@ -212,10 +212,10 @@
     <t>[7116, 4049, 50421, 8597]</t>
   </si>
   <si>
-    <t>[[3558, 3558], [1013, 1012, 1012, 1012], [1, 5042, 20168, 15126, 10084], [1951, 877, 5769]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_inbf16_outbf16_fetch_4_ID010</t>
+    <t>[5850, 1960, 3902, 6941]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_inbf16_outbf16_ID010</t>
   </si>
   <si>
     <t>[[65536, 4096], [[8026], [1243], [9049], [20500]]]</t>
@@ -227,10 +227,10 @@
     <t>[8026, 1243, 9049, 20500]</t>
   </si>
   <si>
-    <t>[[341, 1683, 1779, 4223], [1243], [1509, 4524, 3016], [20500]]</t>
-  </si>
-  <si>
-    <t>h1225_ws4_inbf16_outbf16_fetch_6_ID011</t>
+    <t>[7017, 106, 8566, 18073]</t>
+  </si>
+  <si>
+    <t>h1225_ws4_inbf16_outbf16_ID011</t>
   </si>
   <si>
     <t>[[65536, 1225], [[8629], [4111], [624], [4050]]]</t>
@@ -242,10 +242,10 @@
     <t>[8629, 4111, 624, 4050]</t>
   </si>
   <si>
-    <t>[[1438, 2157, 2876, 3595, -1438, 1], [4111], [312, 312], [1, 1519, 1518, 1012]]</t>
-  </si>
-  <si>
-    <t>h1619_ws4_inbf16_outbf16_fetch_6_ID012</t>
+    <t>[260, 2067, 52, 3903]</t>
+  </si>
+  <si>
+    <t>h1619_ws4_inbf16_outbf16_ID012</t>
   </si>
   <si>
     <t>[[65536, 1619], [[9669], [19345], [7139], [8540]]]</t>
@@ -257,10 +257,10 @@
     <t>[9669, 19345, 7139, 8540]</t>
   </si>
   <si>
-    <t>[[6539, 1, 1, 1, 1, 3126], [19345], [1192, 3568, 2379], [4324, 1, 1, 4214]]</t>
-  </si>
-  <si>
-    <t>h865_ws4_inbf16_outbf16_fetch_4_ID013</t>
+    <t>[163, 17956, 3560, 667]</t>
+  </si>
+  <si>
+    <t>h865_ws4_inbf16_outbf16_ID013</t>
   </si>
   <si>
     <t>[[65536, 865], [[4042], [19644], [92005], [18533]]]</t>
@@ -272,10 +272,10 @@
     <t>[4042, 19644, 92005, 18533]</t>
   </si>
   <si>
-    <t>[[1010, 1515, 1516, 1], [19644], [92005], [18533]]</t>
-  </si>
-  <si>
-    <t>h3833_ws4_inbf16_outbf16_fetch_5_ID014</t>
+    <t>[4028, 1410, 890, 18451]</t>
+  </si>
+  <si>
+    <t>h3833_ws4_inbf16_outbf16_ID014</t>
   </si>
   <si>
     <t>[[65536, 3833], [[819], [44544], [67767], [29072]]]</t>
@@ -287,10 +287,10 @@
     <t>[819, 44544, 67767, 29072]</t>
   </si>
   <si>
-    <t>[[164, 164, 164, 164, 163], [22272, 22272], [67767], [10191, 18881]]</t>
-  </si>
-  <si>
-    <t>h4059_ws4_inbf16_outbf16_fetch_3_ID015</t>
+    <t>[6, 42552, 66527, 20381]</t>
+  </si>
+  <si>
+    <t>h4059_ws4_inbf16_outbf16_ID015</t>
   </si>
   <si>
     <t>[[65536, 4059], [[256], [1592], [344], [97]]]</t>
@@ -302,10 +302,10 @@
     <t>[256, 1592, 344, 97]</t>
   </si>
   <si>
-    <t>[[256], [1592], [59, 171, 114], [49, 48]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outbf16_fetch_6_ID016</t>
+    <t>[150, 125, 206, 7]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outbf16_ID016</t>
   </si>
   <si>
     <t>[[65536, 256], [[8872], [4713]]]</t>
@@ -320,13 +320,13 @@
     <t>[8872, 4713]</t>
   </si>
   <si>
-    <t>[[1, -1475, 3695, 2956, 2217, 1478], [701, 1318, 2694]]</t>
+    <t>[748, 4520]</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_4_ID017</t>
+    <t>h256_ws4_inbf16_outbf16_ID017</t>
   </si>
   <si>
     <t>[[65536, 256], [[5971], [1024], [822], [28237]]]</t>
@@ -335,10 +335,10 @@
     <t>[5971, 1024, 822, 28237]</t>
   </si>
   <si>
-    <t>[[1, 2240, 2238, 1492], [1024], [274, 411, 137], [28237]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_inbf16_outbf16_fetch_7_ID018</t>
+    <t>[5810, 91, 14, 1115]</t>
+  </si>
+  <si>
+    <t>h256_ws8_inbf16_outbf16_ID018</t>
   </si>
   <si>
     <t>[[65536, 256], [[777], [4923], [601], [21991], [8509], [62852], [2933], [3856]]]</t>
@@ -353,13 +353,13 @@
     <t>[777, 4923, 601, 21991, 8509, 62852, 2933, 3856]</t>
   </si>
   <si>
-    <t>[[1, 291, 291, 194], [4923], [120, 180, 240, 60, 1], [21991], [1, 1, 1, 1, 1, 1, 8503], [62852], [2933], [644, 1927, 1285]]</t>
+    <t>[749, 2660, 41, 1531, 6736, 1856, 2914, 3478]</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_7_ID019</t>
+    <t>h256_ws16_inbf16_outbf16_ID019</t>
   </si>
   <si>
     <t>[[65536, 256], [[44109], [304], [9670], [3429], [2764], [6363], [256], [30385], [89], [2159], [57463], [7366], [54830], [37160], [84], [35956]]]</t>
@@ -374,13 +374,13 @@
     <t>[44109, 304, 9670, 3429, 2764, 6363, 256, 30385, 89, 2159, 57463, 7366, 54830, 37160, 84, 35956]</t>
   </si>
   <si>
-    <t>[[44109], [304], [1, 3627, 3625, 2417], [1388, 234, 1807], [1382, 1382], [1590, 2385, 2387, 1], [217, 39], [15193, 15192], [89], [1080, 1079], [14366, 14366, 14366, 14365], [1053, 1053, 1052, 1052, 1052, 1052, 1052], [1, 1, 1, 54827], [37160], [14, 42, 28], [17978, 17978]]</t>
+    <t>[23083, 258, 9327, 2775, 302, 6122, 9, 29655, 7, 957, 54078, 7298, 49706, 18912, 7, 26145]</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_3_ID020</t>
+    <t>h256_ws4_inbf16_outbf16_ID020</t>
   </si>
   <si>
     <t>[[4096, 256], [[94974], [19909], [2663], [87548]]]</t>
@@ -392,10 +392,10 @@
     <t>[94974, 19909, 2663, 87548]</t>
   </si>
   <si>
-    <t>[[47487, 47487], [19909], [2663], [17658, 23894, 45996]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_5_ID021</t>
+    <t>[38796, 19502, 2487, 2938]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID021</t>
   </si>
   <si>
     <t>[[8192, 256], [[806], [5608], [4539], [2048]]]</t>
@@ -410,10 +410,10 @@
     <t>[806, 5608, 4539, 2048]</t>
   </si>
   <si>
-    <t>[[92, 290, 63, 65, 296], [1, 564, 2241, 1681, 1121], [1, 1703, 1701, 1134], [1024, 1024]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_6_ID022</t>
+    <t>[521, 517, 3348, 1761]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID022</t>
   </si>
   <si>
     <t>[[16384, 256], [[512], [8325], [223], [32652]]]</t>
@@ -428,10 +428,10 @@
     <t>[512, 8325, 223, 32652]</t>
   </si>
   <si>
-    <t>[[256, 256], [1388, 1388, 1388, 1387, 1387, 1387], [86, 137], [10884, 10884, 10884]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_6_ID023</t>
+    <t>[485, 89, 217, 18960]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID023</t>
   </si>
   <si>
     <t>[[32768, 256], [[68999], [55475], [49], [9684]]]</t>
@@ -443,10 +443,10 @@
     <t>[68999, 55475, 49, 9684]</t>
   </si>
   <si>
-    <t>[[1, 25876, 25873, 17249], [27810, 1, 1, 27663], [9, 24, 16], [1614, 2421, 3228, 4035, -1615, 1]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_5_ID024</t>
+    <t>[67981, 53842, 39, 9068]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID024</t>
   </si>
   <si>
     <t>[[65536, 256], [[48192], [271], [786], [19915]]]</t>
@@ -455,10 +455,10 @@
     <t>[48192, 271, 786, 19915]</t>
   </si>
   <si>
-    <t>[[48192], [135, 136], [158, 157, 157, 157, 157], [19915]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_4_ID025</t>
+    <t>[27197, 253, 103, 18973]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID025</t>
   </si>
   <si>
     <t>[[48848, 256], [[1251], [5993], [12778], [99635]]]</t>
@@ -473,10 +473,10 @@
     <t>[1251, 5993, 12778, 99635]</t>
   </si>
   <si>
-    <t>[[1251], [5993], [12778], [1, 37364, 37362, 24908]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_5_ID026</t>
+    <t>[1052, 235, 11516, 95540]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID026</t>
   </si>
   <si>
     <t>[[871288, 256], [[23287], [38341], [13719], [882]]]</t>
@@ -491,10 +491,10 @@
     <t>[23287, 38341, 13719, 882]</t>
   </si>
   <si>
-    <t>[[23287], [19171, 19170], [13719], [1, 89, 352, 264, 176]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_3_ID027</t>
+    <t>[13196, 1589, 453, 841]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID027</t>
   </si>
   <si>
     <t>[[777015, 256], [[28167], [512], [360], [31827]]]</t>
@@ -509,10 +509,10 @@
     <t>[28167, 512, 360, 31827]</t>
   </si>
   <si>
-    <t>[[28167], [512], [332, 28], [5305, 15913, 10609]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_4_ID028</t>
+    <t>[12223, 273, 338, 17623]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID028</t>
   </si>
   <si>
     <t>[[397818, 256], [[233], [3917], [8603], [23822]]]</t>
@@ -527,10 +527,10 @@
     <t>[233, 3917, 8603, 23822]</t>
   </si>
   <si>
-    <t>[[51, 182], [1305, 1957, 655], [1, 3227, 3225, 2150], [6310, 17512]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_5_ID029</t>
+    <t>[228, 3847, 795, 23531]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID029</t>
   </si>
   <si>
     <t>[[791996, 256], [[6666], [5728], [452], [1305]]]</t>
@@ -545,10 +545,10 @@
     <t>[6666, 5728, 452, 1305]</t>
   </si>
   <si>
-    <t>[[1333, 1999, 2665, 668, 1], [665, 2189, 1147, 519, 1208], [113, 169, 169, 1], [1305]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_2_ID030</t>
+    <t>[2527, 4301, 72, 895]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID030</t>
   </si>
   <si>
     <t>[[65536, 256], [[5738], [23763], [256], [3196]]]</t>
@@ -557,10 +557,10 @@
     <t>[5738, 23763, 256, 3196]</t>
   </si>
   <si>
-    <t>[[5738], [23763], [121, 135], [1598, 1598]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_3_ID031</t>
+    <t>[3166, 5143, 29, 1617]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID031</t>
   </si>
   <si>
     <t>[[65536, 256], [[24], [19231], [19089], [4096]]]</t>
@@ -572,10 +572,10 @@
     <t>[24, 19231, 19089, 4096]</t>
   </si>
   <si>
-    <t>[[24], [19231], [19089], [684, 2047, 1365]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_4_ID032</t>
+    <t>[18, 7833, 653, 2019]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID032</t>
   </si>
   <si>
     <t>[[65536, 256], [[318], [815], [82522], [14]]]</t>
@@ -587,10 +587,10 @@
     <t>[318, 815, 82522, 14]</t>
   </si>
   <si>
-    <t>[[109, 209], [407, 408], [1, 30946, 30945, 20630], [14]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_2_ID033</t>
+    <t>[313, 769, 3482, 7]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID033</t>
   </si>
   <si>
     <t>[[65536, 256], [[4821], [28172], [9727], [62223]]]</t>
@@ -602,10 +602,10 @@
     <t>[4821, 28172, 9727, 62223]</t>
   </si>
   <si>
-    <t>[[2410, 2411], [14086, 14086], [7935, 1792], [36257, 25966]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_4_ID034</t>
+    <t>[469, 16479, 5238, 55922]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID034</t>
   </si>
   <si>
     <t>[[65536, 256], [[1453], [11960], [73900], [256]]]</t>
@@ -617,10 +617,10 @@
     <t>[1453, 11960, 73900, 256]</t>
   </si>
   <si>
-    <t>[[1453], [11960], [18475, 18475, 18475, 18475], [256]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_3_ID035</t>
+    <t>[626, 5173, 67128, 49]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID035</t>
   </si>
   <si>
     <t>[[65536, 256], [[3158], [20095], [5131], [9613]]]</t>
@@ -632,10 +632,10 @@
     <t>[3158, 20095, 5131, 9613]</t>
   </si>
   <si>
-    <t>[[528, 1578, 1052], [20095], [2566, 2565], [9613]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_2_ID036</t>
+    <t>[2913, 321, 2153, 8676]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID036</t>
   </si>
   <si>
     <t>[[65536, 256], [[1341], [1024], [50026], [3891]]]</t>
@@ -647,10 +647,10 @@
     <t>[1341, 1024, 50026, 3891]</t>
   </si>
   <si>
-    <t>[[1341], [1024], [50026], [2625, 1266]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outfp16_fetch_8_ID037</t>
+    <t>[1228, 418, 26023, 3573]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outfp16_ID037</t>
   </si>
   <si>
     <t>[[65536, 256], [[16003], [93609], [43752], [57]]]</t>
@@ -659,10 +659,10 @@
     <t>[16003, 93609, 43752, 57]</t>
   </si>
   <si>
-    <t>[[16003], [11702, 11701, 11701, 11701, 11701, 11701, 11701, 11701], [43752], [28, 29]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outfp32_fetch_1_ID038</t>
+    <t>[8202, 86031, 17802, 5]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outfp32_ID038</t>
   </si>
   <si>
     <t>[[65536, 256], [[38116], [16656], [814], [1715]]]</t>
@@ -671,10 +671,10 @@
     <t>[38116, 16656, 814, 1715]</t>
   </si>
   <si>
-    <t>[[38116], [16656], [814], [1715]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outbf16_fetch_6_ID039</t>
+    <t>[15829, 307, 420, 1555]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outbf16_ID039</t>
   </si>
   <si>
     <t>[[65536, 256], [[7314], [38], [1087], [26691]]]</t>
@@ -683,10 +683,10 @@
     <t>[7314, 38, 1087, 26691]</t>
   </si>
   <si>
-    <t>[[4064, 1, 1, 1, 1, 3246], [38], [1087], [26691]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp32_fetch_5_ID040</t>
+    <t>[6054, 18, 991, 193]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp32_ID040</t>
   </si>
   <si>
     <t>[[65536, 256], [[9584], [46], [23522], [456]]]</t>
@@ -695,10 +695,10 @@
     <t>[9584, 46, 23522, 456]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 1, 9580], [46], [11761, 11761], [81, 79, 296]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outbf16_fetch_6_ID041</t>
+    <t>[177, 46, 2233, 215]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outbf16_ID041</t>
   </si>
   <si>
     <t>[[65536, 256], [[4780], [2048], [5644], [7283]]]</t>
@@ -707,10 +707,10 @@
     <t>[4780, 2048, 5644, 7283]</t>
   </si>
   <si>
-    <t>[[2427, 1, 1, 2351], [2048], [2822, 2822], [1, -1206, 3031, 2425, 1819, 1213]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outfp16_fetch_4_ID042</t>
+    <t>[4384, 1940, 2689, 3335]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outfp16_ID042</t>
   </si>
   <si>
     <t>[[65536, 256], [[11639], [26049], [2679], [45741]]]</t>
@@ -719,10 +719,10 @@
     <t>[11639, 26049, 2679, 45741]</t>
   </si>
   <si>
-    <t>[[11639], [13025, 13024], [1339, 1340], [1, 17153, 17152, 11435]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_inbf16_outbf16_fetch_4_ID201</t>
+    <t>[9536, 1227, 2611, 1393]</t>
+  </si>
+  <si>
+    <t>h64_ws2_inbf16_outbf16_ID201</t>
   </si>
   <si>
     <t>[[65536, 64], [[433], [5633]]]</t>
@@ -731,10 +731,10 @@
     <t>[433, 5633]</t>
   </si>
   <si>
-    <t>[[315, 118], [1409, 1408, 1408, 1408]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_inbf16_outbf16_fetch_4_ID202</t>
+    <t>[363, 5528]</t>
+  </si>
+  <si>
+    <t>h64_ws4_inbf16_outbf16_ID202</t>
   </si>
   <si>
     <t>[[65536, 64], [[40732], [4245], [507], [2048]]]</t>
@@ -743,10 +743,10 @@
     <t>[40732, 4245, 507, 2048]</t>
   </si>
   <si>
-    <t>[[6790, 20365, 13577], [1, 1, 1, 4242], [507], [1024, 1024]]</t>
-  </si>
-  <si>
-    <t>h64_ws8_inbf16_outbf16_fetch_2_ID203</t>
+    <t>[3979, 4032, 8, 1921]</t>
+  </si>
+  <si>
+    <t>h64_ws8_inbf16_outbf16_ID203</t>
   </si>
   <si>
     <t>[[65536, 64], [[962], [4483], [86], [1024], [11454], [32551], [18634], [670]]]</t>
@@ -755,10 +755,10 @@
     <t>[962, 4483, 86, 1024, 11454, 32551, 18634, 670]</t>
   </si>
   <si>
-    <t>[[481, 481], [2241, 2242], [43, 43], [1024], [11454], [4433, 28118], [18634], [335, 335]]</t>
-  </si>
-  <si>
-    <t>h64_ws16_inbf16_outbf16_fetch_6_ID204</t>
+    <t>[946, 177, 85, 994, 420, 31563, 276, 224]</t>
+  </si>
+  <si>
+    <t>h64_ws16_inbf16_outbf16_ID204</t>
   </si>
   <si>
     <t>[[65536, 64], [[2400], [63725], [593], [56981], [20351], [7767], [169], [9592], [59915], [64916], [4884], [5989], [4366], [5384], [634], [49564]]]</t>
@@ -767,10 +767,10 @@
     <t>[2400, 63725, 593, 56981, 20351, 7767, 169, 9592, 59915, 64916, 4884, 5989, 4366, 5384, 634, 49564]</t>
   </si>
   <si>
-    <t>[[1200, 1200], [12745, 19117, 25489, 6373, 1], [297, 296], [56981], [10176, 10175], [1, -1292, 3235, 2588, 1941, 1294], [169], [3198, 3197, 3197], [59915], [32458, 32458], [4884], [5989], [4366], [5384], [317, 317], [1, 18586, 18586, 12391]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_inbf16_outbf16_fetch_8_ID205</t>
+    <t>[2324, 61779, 16, 52193, 20087, 126, 161, 335, 23997, 9873, 11, 4919, 54, 5058, 379, 47059]</t>
+  </si>
+  <si>
+    <t>h128_ws2_inbf16_outbf16_ID205</t>
   </si>
   <si>
     <t>[[65536, 128], [[2614], [9141]]]</t>
@@ -779,10 +779,10 @@
     <t>[2614, 9141]</t>
   </si>
   <si>
-    <t>[[1307, 1307], [1142, 1713, 2284, 2855, 3426, 3997, -6277, 1]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_inbf16_outbf16_fetch_3_ID206</t>
+    <t>[2557, 8598]</t>
+  </si>
+  <si>
+    <t>h128_ws4_inbf16_outbf16_ID206</t>
   </si>
   <si>
     <t>[[65536, 128], [[49], [512], [24364], [512]]]</t>
@@ -791,10 +791,10 @@
     <t>[49, 512, 24364, 512]</t>
   </si>
   <si>
-    <t>[[25, 24], [170, 255, 87], [24364], [512]]</t>
-  </si>
-  <si>
-    <t>h128_ws8_inbf16_outbf16_fetch_7_ID207</t>
+    <t>[8, 19, 13882, 226]</t>
+  </si>
+  <si>
+    <t>h128_ws8_inbf16_outbf16_ID207</t>
   </si>
   <si>
     <t>[[65536, 128], [[4633], [11589], [32715], [596], [13889], [3109], [432], [8545]]]</t>
@@ -803,10 +803,10 @@
     <t>[4633, 11589, 32715, 596, 13889, 3109, 432, 8545]</t>
   </si>
   <si>
-    <t>[[4633], [11589], [32715], [1, 61, 237, 178, 119], [13889], [3109], [216, 216], [1221, 1221, 1221, 1221, 1221, 1220, 1220]]</t>
-  </si>
-  <si>
-    <t>h128_ws16_inbf16_outbf16_fetch_8_ID208</t>
+    <t>[1914, 480, 18782, 543, 12896, 972, 246, 6865]</t>
+  </si>
+  <si>
+    <t>h128_ws16_inbf16_outbf16_ID208</t>
   </si>
   <si>
     <t>[[65536, 128], [[4214], [916], [8496], [8527], [3910], [332], [3474], [69943], [4370], [9790], [511], [8955], [4693], [97149], [8192], [20162]]]</t>
@@ -815,10 +815,10 @@
     <t>[4214, 916, 8496, 8527, 3910, 332, 3474, 69943, 4370, 9790, 511, 8955, 4693, 97149, 8192, 20162]</t>
   </si>
   <si>
-    <t>[[4214], [1, 343, 343, 229], [1213, 1819, 2425, 3031, 3637, -3630, 1], [1, -5844, 3725, 3193, 2661, 2129, 1597, 1065], [1, 1, 3908], [110, 165, 57], [3474], [1, 6996, 27976, 20982, 13988], [1, 4369], [2807, 1426, 2447, 3110], [171, 170, 170], [8955], [4693], [48575, 48574], [1, 820, 3276, 2457, 1638], [20162]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outbf16_fetch_3_ID209</t>
+    <t>[1753, 886, 7931, 8160, 3874, 42, 1762, 54339, 215, 9033, 472, 357, 2076, 39169, 3330, 3843]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outbf16_ID209</t>
   </si>
   <si>
     <t>[[65536, 256], [[1382], [689]]]</t>
@@ -827,10 +827,10 @@
     <t>[1382, 689]</t>
   </si>
   <si>
-    <t>[[1382], [117, 343, 229]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_8_ID210</t>
+    <t>[36, 43]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID210</t>
   </si>
   <si>
     <t>[[65536, 256], [[7641], [95197], [47], [3223]]]</t>
@@ -839,10 +839,10 @@
     <t>[7641, 95197, 47, 3223]</t>
   </si>
   <si>
-    <t>[[7641], [4025, 1794, 28144, 26683, 2300, 13494, 1342, 17415], [47], [1074, 1611, 538]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_inbf16_outbf16_fetch_5_ID211</t>
+    <t>[4083, 86683, 24, 1371]</t>
+  </si>
+  <si>
+    <t>h256_ws8_inbf16_outbf16_ID211</t>
   </si>
   <si>
     <t>[[65536, 256], [[4966], [90], [6618], [3164], [7971], [3918], [9436], [33410]]]</t>
@@ -851,10 +851,10 @@
     <t>[4966, 90, 6618, 3164, 7971, 3918, 9436, 33410]</t>
   </si>
   <si>
-    <t>[[829, 2482, 1655], [17, 73], [2206, 2206, 2206], [3164], [2657, 2657, 2657], [3918], [1, 945, 3773, 2830, 1887], [1, 1, 33408]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_7_ID212</t>
+    <t>[477, 88, 2102, 49, 4315, 61, 4505, 1565]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outbf16_ID212</t>
   </si>
   <si>
     <t>[[65536, 256], [[1675], [13899], [3138], [146], [4027], [4096], [3221], [37652], [2144], [1733], [577], [5565], [449], [8542], [9591], [20546]]]</t>
@@ -863,10 +863,10 @@
     <t>[1675, 13899, 3138, 146, 4027, 4096, 3221, 37652, 2144, 1733, 577, 5565, 449, 8542, 9591, 20546]</t>
   </si>
   <si>
-    <t>[[1675], [13899], [1109, 145, 1884], [146], [1343, 1342, 1342], [4096], [1073, 1609, 539], [18646, 19006], [2144], [1733], [193, 192, 192], [1, 1, 1, 5562], [449], [4271, 4271], [8975, 1, 1, 1, 1, 1, 611], [20546]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_inbf16_outbf16_fetch_3_ID213</t>
+    <t>[74, 6605, 526, 37, 218, 376, 1293, 36357, 98, 1404, 124, 5055, 22, 4346, 96, 3850]</t>
+  </si>
+  <si>
+    <t>h512_ws2_inbf16_outbf16_ID213</t>
   </si>
   <si>
     <t>[[65536, 512], [[325], [4094]]]</t>
@@ -875,10 +875,10 @@
     <t>[325, 4094]</t>
   </si>
   <si>
-    <t>[[55, 162, 108], [2047, 2047]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_inbf16_outbf16_fetch_5_ID214</t>
+    <t>[253, 637]</t>
+  </si>
+  <si>
+    <t>h512_ws4_inbf16_outbf16_ID214</t>
   </si>
   <si>
     <t>[[65536, 512], [[6822], [9845], [24431], [5121]]]</t>
@@ -887,10 +887,10 @@
     <t>[6822, 9845, 24431, 5121]</t>
   </si>
   <si>
-    <t>[[2274, 2274, 2274], [4923, 4922], [12216, 12215], [1, 512, 2048, 1536, 1024]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_inbf16_outbf16_fetch_4_ID215</t>
+    <t>[666, 4117, 23748, 5121]</t>
+  </si>
+  <si>
+    <t>h512_ws8_inbf16_outbf16_ID215</t>
   </si>
   <si>
     <t>[[65536, 512], [[52], [393], [1653], [5853], [17515], [3965], [2963], [8431]]]</t>
@@ -899,10 +899,10 @@
     <t>[52, 393, 1653, 5853, 17515, 3965, 2963, 8431]</t>
   </si>
   <si>
-    <t>[[13, 39], [393], [1653], [1, 2195, 2194, 1463], [17515], [663, 1981, 1321], [2963], [1, 3163, 3160, 2107]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outbf16_fetch_9_ID216</t>
+    <t>[51, 204, 823, 3472, 16634, 2301, 230, 7770]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outbf16_ID216</t>
   </si>
   <si>
     <t>[[65536, 512], [[92071], [592], [7184], [125], [9857], [3452], [5587], [1614], [594], [4096], [109], [5408], [7359], [256], [29007], [5730]]]</t>
@@ -911,10 +911,10 @@
     <t>[92071, 592, 7184, 125, 9857, 3452, 5587, 1614, 594, 4096, 109, 5408, 7359, 256, 29007, 5730]</t>
   </si>
   <si>
-    <t>[[10231, 10230, 10230, 10230, 10230, 10230, 10230, 10230, 10230], [592], [7184], [125], [2465, 2464, 2464, 2464], [3452], [925, 977, 796, 2889], [1614], [99, 297, 198], [1365, 2047, 684], [109], [5408], [1227, 3679, 2453], [256], [29007], [2053, 3677]]</t>
-  </si>
-  <si>
-    <t>h1024_ws2_inbf16_outbf16_fetch_2_ID217</t>
+    <t>[16237, 260, 3754, 13, 5702, 2955, 3680, 463, 522, 1907, 103, 534, 2573, 24, 13635, 396]</t>
+  </si>
+  <si>
+    <t>h1024_ws2_inbf16_outbf16_ID217</t>
   </si>
   <si>
     <t>[[65536, 1024], [[512], [812]]]</t>
@@ -923,10 +923,10 @@
     <t>[512, 812]</t>
   </si>
   <si>
-    <t>[[512], [1, 811]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_inbf16_outbf16_fetch_1_ID218</t>
+    <t>[270, 113]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_inbf16_outbf16_ID218</t>
   </si>
   <si>
     <t>[[65536, 1024], [[2782], [49361], [4373], [53208]]]</t>
@@ -935,10 +935,10 @@
     <t>[2782, 49361, 4373, 53208]</t>
   </si>
   <si>
-    <t>[[2782], [49361], [4373], [53208]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outbf16_fetch_4_ID219</t>
+    <t>[580, 27938, 2131, 29617]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outbf16_ID219</t>
   </si>
   <si>
     <t>[[65536, 1024], [[32298], [6385], [16772], [38617], [8744], [17], [38674], [3237]]]</t>
@@ -947,10 +947,10 @@
     <t>[32298, 6385, 16772, 38617, 8744, 17, 38674, 3237]</t>
   </si>
   <si>
-    <t>[[5383, 16149, 10766], [3192, 3193], [16772], [12873, 12872, 12872], [2186, 2186, 2186, 2186], [17], [22760, 1, 15913], [1618, 1619]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_inbf16_outbf16_fetch_8_ID220</t>
+    <t>[31089, 5964, 1102, 17472, 148, 8, 20274, 315]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_inbf16_outbf16_ID220</t>
   </si>
   <si>
     <t>[[65536, 1024], [[25270], [39802], [7586], [4581], [25450], [3685], [7316], [1395], [2260], [9644], [1117], [2387], [61936], [8192], [31215], [31260]]]</t>
@@ -959,10 +959,10 @@
     <t>[25270, 39802, 7586, 4581, 25450, 3685, 7316, 1395, 2260, 9644, 1117, 2387, 61936, 8192, 31215, 31260]</t>
   </si>
   <si>
-    <t>[[12635, 12635], [39802], [3793, 3793], [1145, 1717, 1718, 1], [25450], [1843, 1842], [1, 733, 2925, 2194, 1463], [1395], [1130, 1130], [3964, 2381, 460, 1385, 1454], [1117], [1460, 927], [61936], [1024, 1536, 2048, 2560, 3072, 3584, -5633, 1], [31215], [15630, 15630]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_inbf16_outbf16_fetch_3_ID221</t>
+    <t>[1262, 18440, 532, 4309, 3510, 3319, 7197, 58, 1376, 309, 991, 919, 53062, 162, 28876, 12]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_inbf16_outbf16_ID221</t>
   </si>
   <si>
     <t>[[65536, 2048], [[2533], [4790]]]</t>
@@ -971,10 +971,10 @@
     <t>[2533, 4790]</t>
   </si>
   <si>
-    <t>[[2533], [441, 1313, 3036]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_inbf16_outbf16_fetch_5_ID222</t>
+    <t>[1510, 4731]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_inbf16_outbf16_ID222</t>
   </si>
   <si>
     <t>[[65536, 2048], [[25417], [1516], [38], [8230]]]</t>
@@ -983,10 +983,10 @@
     <t>[25417, 1516, 38, 8230]</t>
   </si>
   <si>
-    <t>[[12709, 12708], [1516], [8, 18, 12], [1946, 1601, 1588, 490, 2605]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_inbf16_outbf16_fetch_8_ID223</t>
+    <t>[16087, 1513, 20, 8038]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_inbf16_outbf16_ID223</t>
   </si>
   <si>
     <t>[[65536, 2048], [[8205], [970], [9231], [17858], [45029], [10219], [32286], [8192]]]</t>
@@ -995,10 +995,10 @@
     <t>[8205, 970, 9231, 17858, 45029, 10219, 32286, 8192]</t>
   </si>
   <si>
-    <t>[[3964, 807, 646, 1232, 253, 260, 479, 564], [485, 485], [5386, 1, 1, 3843], [17858], [11258, 11257, 11257, 11257], [10219], [10762, 10762, 10762], [2048, 2048, 2048, 2048]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_inbf16_outbf16_fetch_7_ID224</t>
+    <t>[7909, 496, 1479, 8080, 3829, 1139, 6127, 6745]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_inbf16_outbf16_ID224</t>
   </si>
   <si>
     <t>[[65536, 2048], [[294], [9768], [256], [9656], [435], [5028], [942], [33128], [883], [7483], [2617], [37176], [76307], [43528], [15956], [152]]]</t>
@@ -1007,10 +1007,10 @@
     <t>[294, 9768, 256, 9656, 435, 5028, 942, 33128, 883, 7483, 2617, 37176, 76307, 43528, 15956, 152]</t>
   </si>
   <si>
-    <t>[[294], [1396, 1396, 1396, 1395, 1395, 1395, 1395], [128, 128], [1610, 1610, 1609, 1609, 1609, 1609], [145, 217, 73], [5028], [236, 236, 235, 235], [33128], [207, 142, 236, 298], [1248, 1247, 1247, 1247, 1247, 1247], [2617], [18588, 18588], [15262, 15262, 15261, 15261, 15261], [10882, 10882, 10882, 10882], [15956], [152]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_inbf16_outbf16_fetch_5_ID225</t>
+    <t>[125, 8826, 243, 6088, 208, 19, 55, 14501, 467, 3308, 236, 14938, 37286, 4194, 8663, 137]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_inbf16_outbf16_ID225</t>
   </si>
   <si>
     <t>[[65536, 4096], [[25694], [808]]]</t>
@@ -1019,10 +1019,10 @@
     <t>[25694, 808]</t>
   </si>
   <si>
-    <t>[[12847, 12847], [1, 84, 321, 241, 161]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_inbf16_outbf16_fetch_5_ID226</t>
+    <t>[24450, 501]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_inbf16_outbf16_ID226</t>
   </si>
   <si>
     <t>[[65536, 4096], [[1820], [451], [75227], [8475]]]</t>
@@ -1031,10 +1031,10 @@
     <t>[1820, 451, 75227, 8475]</t>
   </si>
   <si>
-    <t>[[1820], [150, 225, 76], [29942, 15825, 10584, 18876], [1390, 1291, 2125, 529, 3140]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_inbf16_outbf16_fetch_7_ID227</t>
+    <t>[1691, 19, 71909, 8121]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_inbf16_outbf16_ID227</t>
   </si>
   <si>
     <t>[[65536, 4096], [[7054], [933], [7802], [2542], [4965], [341], [1505], [6720]]]</t>
@@ -1043,10 +1043,10 @@
     <t>[7054, 933, 7802, 2542, 4965, 341, 1505, 6720]</t>
   </si>
   <si>
-    <t>[[1411, 1411, 1411, 1411, 1410], [628, 305], [1114, 1671, 2228, 2785, 3342, -3339, 1], [1271, 1271], [2095, 704, 531, 1635], [225, 116], [1505], [3057, 1270, 2393]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_inbf16_outbf16_fetch_8_ID228</t>
+    <t>[255, 82, 2599, 147, 4605, 338, 67, 6203]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_inbf16_outbf16_ID228</t>
   </si>
   <si>
     <t>[[65536, 4096], [[95575], [47608], [8648], [8467], [19629], [256], [58519], [36791], [1024], [7596], [2453], [9600], [42362], [49773], [5161], [4996]]]</t>
@@ -1055,10 +1055,10 @@
     <t>[95575, 47608, 8648, 8467, 19629, 256, 58519, 36791, 1024, 7596, 2453, 9600, 42362, 49773, 5161, 4996]</t>
   </si>
   <si>
-    <t>[[47787, 47788], [23804, 23804], [1235, 1852, 2469, 3086, 3703, -3698, 1], [1059, 1059, 1059, 1058, 1058, 1058, 1058, 1058], [19629], [9, 247], [58519], [36791], [1024], [1085, 1627, 2169, 2711, 3253, -3250, 1], [2453], [1, 1, 1, 1, 9596], [33299, 9063], [49773], [1, 5160], [4996]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_inbf16_outbf16_fetch_5_ID229</t>
+    <t>[48815, 43842, 7842, 3548, 18892, 103, 1386, 2471, 15, 2276, 110, 8437, 23351, 40532, 2197, 2112]</t>
+  </si>
+  <si>
+    <t>h64_ws4_inbf16_outbf16_ID229</t>
   </si>
   <si>
     <t>[[65536, 64], [[4689], [78165], [23804], [46573]]]</t>
@@ -1067,10 +1067,10 @@
     <t>[4689, 78165, 23804, 46573]</t>
   </si>
   <si>
-    <t>[[2345, 2344], [15633, 15633, 15633, 15633, 15633], [11902, 11902], [34807, 11766]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp16_outfp16_fetch_3_ID230</t>
+    <t>[4474, 35402, 652, 43018]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp16_outfp16_ID230</t>
   </si>
   <si>
     <t>[[65536, 64], [[29787], [45194], [65], [41921]]]</t>
@@ -1079,10 +1079,10 @@
     <t>[29787, 45194, 65, 41921]</t>
   </si>
   <si>
-    <t>[[14894, 14893], [7534, 22596, 15064], [21, 6, 38], [13974, 13974, 13973]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp32_outfp32_fetch_4_ID231</t>
+    <t>[26248, 41673, 35, 39197]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp32_outfp32_ID231</t>
   </si>
   <si>
     <t>[[65536, 64], [[58218], [30981], [47329], [6056]]]</t>
@@ -1091,10 +1091,10 @@
     <t>[58218, 30981, 47329, 6056]</t>
   </si>
   <si>
-    <t>[[8407, 1107, 13623, 35081], [5164, 15490, 10327], [5977, 41352], [2018, 3027, 1011]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_6_ID232</t>
+    <t>[57106, 139, 45823, 374]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID232</t>
   </si>
   <si>
     <t>[[65536, 256], [[4820], [54853], [67813], [20501]]]</t>
@@ -1103,10 +1103,10 @@
     <t>[4820, 54853, 67813, 20501]</t>
   </si>
   <si>
-    <t>[[2410, 2410], [1, 1, 1, 54850], [11302, 16953, 22604, 28255, -11302, 1], [20501]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp16_fetch_5_ID233</t>
+    <t>[1025, 3272, 11945, 409]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp16_ID233</t>
   </si>
   <si>
     <t>[[65536, 256], [[21426], [8931], [2364], [27607]]]</t>
@@ -1115,10 +1115,10 @@
     <t>[21426, 8931, 2364, 27607]</t>
   </si>
   <si>
-    <t>[[10713, 10713], [1, 1, 1, 1, 8927], [2364], [27607]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outfp32_fetch_1_ID234</t>
+    <t>[1234, 4949, 337, 14481]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outfp32_ID234</t>
   </si>
   <si>
     <t>[[65536, 256], [[1943], [76952], [8872], [65021]]]</t>
@@ -1127,10 +1127,10 @@
     <t>[1943, 76952, 8872, 65021]</t>
   </si>
   <si>
-    <t>[[1943], [76952], [8872], [65021]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_inbf16_outbf16_fetch_7_ID235</t>
+    <t>[1777, 32265, 573, 27619]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_inbf16_outbf16_ID235</t>
   </si>
   <si>
     <t>[[65536, 1024], [[9432], [26312], [122], [3591]]]</t>
@@ -1139,10 +1139,10 @@
     <t>[9432, 26312, 122, 3591]</t>
   </si>
   <si>
-    <t>[[3851, 1603, 306, 1450, 715, 739, 768], [1, 26311], [122], [1795, 1796]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp16_outfp16_fetch_4_ID236</t>
+    <t>[9036, 15402, 111, 331]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp16_outfp16_ID236</t>
   </si>
   <si>
     <t>[[65536, 1024], [[42460], [1024], [825], [699]]]</t>
@@ -1151,10 +1151,10 @@
     <t>[42460, 1024, 825, 699]</t>
   </si>
   <si>
-    <t>[[1, 15922, 15922, 10615], [1024], [55, 278, 492], [155, 10, 96, 438]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp32_outfp32_fetch_6_ID237</t>
+    <t>[31295, 954, 339, 110]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp32_outfp32_ID237</t>
   </si>
   <si>
     <t>[[65536, 1024], [[21046], [2048], [281], [7937]]]</t>
@@ -1163,10 +1163,10 @@
     <t>[21046, 2048, 281, 7937]</t>
   </si>
   <si>
-    <t>[[21046], [1, 2047], [91, 190], [1, -1318, 3305, 2644, 1983, 1322]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_inbf16_outbf16_fetch_6_ID238</t>
+    <t>[2535, 180, 182, 7567]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_inbf16_outbf16_ID238</t>
   </si>
   <si>
     <t>[[65536, 4096], [[15893], [2076], [929], [60882]]]</t>
@@ -1175,10 +1175,10 @@
     <t>[15893, 2076, 929, 60882]</t>
   </si>
   <si>
-    <t>[[15893], [2076], [310, 310, 309], [11387, 9908, 8630, 12194, 3712, 15051]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp16_outfp16_fetch_2_ID239</t>
+    <t>[8372, 2054, 13, 22774]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp16_outfp16_ID239</t>
   </si>
   <si>
     <t>[[65536, 4096], [[947], [37323], [163], [2048]]]</t>
@@ -1187,10 +1187,10 @@
     <t>[947, 37323, 163, 2048]</t>
   </si>
   <si>
-    <t>[[947], [18662, 18661], [163], [1024, 1024]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp32_outfp32_fetch_4_ID240</t>
+    <t>[449, 37249, 67, 1063]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp32_outfp32_ID240</t>
   </si>
   <si>
     <t>[[65536, 4096], [[53844], [50], [879], [6253]]]</t>
@@ -1199,10 +1199,10 @@
     <t>[53844, 50, 879, 6253]</t>
   </si>
   <si>
-    <t>[[13461, 20191, 20191, 1], [17, 2, 31], [1, 331, 328, 219], [1043, 3126, 2084]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outbf16_fetch_2_ID241</t>
+    <t>[51371, 34, 47, 6047]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outbf16_ID241</t>
   </si>
   <si>
     <t>[[4096, 256], [[16797], [2054]]]</t>
@@ -1214,10 +1214,10 @@
     <t>[16797, 2054]</t>
   </si>
   <si>
-    <t>[[16797], [1027, 1027]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_7_ID242</t>
+    <t>[16251, 1742]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID242</t>
   </si>
   <si>
     <t>[[4096, 256], [[9128], [8956], [3815], [42]]]</t>
@@ -1226,10 +1226,10 @@
     <t>[9128, 8956, 3815, 42]</t>
   </si>
   <si>
-    <t>[[2634, 6494], [1280, 1280, 1280, 1279, 1279, 1279, 1279], [638, 1906, 1271], [42]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_inbf16_outbf16_fetch_3_ID243</t>
+    <t>[4747, 852, 3493, 28]</t>
+  </si>
+  <si>
+    <t>h256_ws8_inbf16_outbf16_ID243</t>
   </si>
   <si>
     <t>[[4096, 256], [[4096], [1860], [6018], [225], [56], [47625], [23857], [1562]]]</t>
@@ -1238,10 +1238,10 @@
     <t>[4096, 1860, 6018, 225, 56, 47625, 23857, 1562]</t>
   </si>
   <si>
-    <t>[[40, 878, 3178], [1860], [2538, 3480], [225], [56], [7938, 23812, 15875], [23857], [1562]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_7_ID244</t>
+    <t>[3004, 40, 5994, 119, 3, 40597, 9847, 752]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outbf16_ID244</t>
   </si>
   <si>
     <t>[[4096, 256], [[94570], [8644], [203], [512], [28003], [68072], [18664], [8036], [6704], [55], [2574], [8539], [178], [9313], [66139], [6562]]]</t>
@@ -1250,10 +1250,10 @@
     <t>[94570, 8644, 203, 512, 28003, 68072, 18664, 8036, 6704, 55, 2574, 8539, 178, 9313, 66139, 6562]</t>
   </si>
   <si>
-    <t>[[35969, 3976, 15883, 17976, 20766], [1234, 1851, 2468, 3085, 3702, -3697, 1], [102, 101], [170, 255, 87], [22988, 5015], [40519, 1, 1, 1, 1, 27549], [18664], [1676, 2249, 4111], [6704], [16, 39], [1, 2573], [1424, 4269, 2846], [178], [1, 1, 1, 1, 1, 9308], [66139], [176, 980, 2699, 2707]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outbf16_fetch_5_ID245</t>
+    <t>[9337, 1988, 199, 483, 8752, 64118, 736, 7551, 5565, 9, 2375, 4836, 124, 5183, 2448, 6292]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outbf16_ID245</t>
   </si>
   <si>
     <t>[[16384, 256], [[582], [437]]]</t>
@@ -1262,10 +1262,10 @@
     <t>[582, 437]</t>
   </si>
   <si>
-    <t>[[81, 10, 160, 33, 298], [145, 217, 75]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_5_ID246</t>
+    <t>[540, 365]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID246</t>
   </si>
   <si>
     <t>[[16384, 256], [[83860], [6842], [551], [282]]]</t>
@@ -1274,10 +1274,10 @@
     <t>[83860, 6842, 551, 282]</t>
   </si>
   <si>
-    <t>[[27954, 27953, 27953], [1, 1, 1, 1, 6838], [184, 184, 183], [282]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_inbf16_outbf16_fetch_6_ID247</t>
+    <t>[71214, 2559, 327, 37]</t>
+  </si>
+  <si>
+    <t>h256_ws8_inbf16_outbf16_ID247</t>
   </si>
   <si>
     <t>[[16384, 256], [[1346], [8743], [53426], [19040], [3778], [769], [7911], [3115]]]</t>
@@ -1286,10 +1286,10 @@
     <t>[1346, 8743, 53426, 19040, 3778, 769, 7911, 3115]</t>
   </si>
   <si>
-    <t>[[1346], [3785, 1562, 113, 1608, 232, 1443], [8906, 26712, 17808], [19040], [1, 3777], [193, 192, 192, 192], [513, 2544, 1163, 1784, 782, 1125], [1038, 1557, 520]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_8_ID248</t>
+    <t>[578, 780, 30274, 12496, 1742, 52, 151, 81]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outbf16_ID248</t>
   </si>
   <si>
     <t>[[16384, 256], [[41295], [40272], [31275], [8212], [2414], [8552], [767], [82756], [9008], [26066], [8352], [5250], [3663], [8514], [76773], [2856]]]</t>
@@ -1298,10 +1298,10 @@
     <t>[41295, 40272, 31275, 8212, 2414, 8552, 767, 82756, 9008, 26066, 8352, 5250, 3663, 8514, 76773, 2856]</t>
   </si>
   <si>
-    <t>[[20647, 20648], [10068, 15102, 15101, 1], [12097, 19178], [4106, 4106], [1207, 1207], [798, 1981, 5773], [130, 382, 255], [1, 8277, 33101, 24826, 16551], [3001, 2064, 735, 814, 264, 972, 362, 796], [13033, 13033], [3015, 2214, 121, 1469, 168, 1365], [5250], [3643, 20], [1703, 1703, 1703, 1703, 1702], [34490, 1884, 8344, 1352, 30703], [1, 2855]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outbf16_fetch_5_ID249</t>
+    <t>[33199, 15834, 2910, 8202, 90, 1283, 40, 2576, 1595, 24828, 7795, 5227, 1501, 5878, 70149, 2750]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outbf16_ID249</t>
   </si>
   <si>
     <t>[[65536, 256], [[5559], [8192]]]</t>
@@ -1310,10 +1310,10 @@
     <t>[5559, 8192]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 1, 5555], [1367, 4095, 2730]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_3_ID250</t>
+    <t>[1886, 7345]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID250</t>
   </si>
   <si>
     <t>[[65536, 256], [[3574], [2118], [46651], [3723]]]</t>
@@ -1322,10 +1322,10 @@
     <t>[3574, 2118, 46651, 3723]</t>
   </si>
   <si>
-    <t>[[3574], [2118], [15550, 23325, 7776], [1862, 1861]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_inbf16_outbf16_fetch_7_ID251</t>
+    <t>[3021, 83, 2130, 3363]</t>
+  </si>
+  <si>
+    <t>h256_ws8_inbf16_outbf16_ID251</t>
   </si>
   <si>
     <t>[[65536, 256], [[7265], [48451], [7721], [16115], [8467], [9392], [20558], [4096]]]</t>
@@ -1334,10 +1334,10 @@
     <t>[7265, 48451, 7721, 16115, 8467, 9392, 20558, 4096]</t>
   </si>
   <si>
-    <t>[[3442, 17, 648, 753, 494, 1911], [1, 18170, 18168, 12112], [1103, 1654, 2205, 2756, 3307, -3305, 1], [16115], [5228, 1, 1, 1, 1, 1, 3234], [1565, 2347, 3129, 3911, -1561, 1], [7623, 12935], [1366, 1365, 1365]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_8_ID252</t>
+    <t>[6884, 24557, 247, 15431, 138, 757, 19309, 125]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outbf16_ID252</t>
   </si>
   <si>
     <t>[[65536, 256], [[11063], [1024], [4183], [8464], [1291], [16836], [4096], [9064], [15329], [12571], [5430], [48704], [57], [27599], [95072], [25729]]]</t>
@@ -1346,10 +1346,10 @@
     <t>[11063, 1024, 4183, 8464, 1291, 16836, 4096, 9064, 15329, 12571, 5430, 48704, 57, 27599, 95072, 25729]</t>
   </si>
   <si>
-    <t>[[11063], [1024], [1395, 1394, 1394], [1058, 1587, 2116, 2645, 3174, 3703, -5820, 1], [1291], [16836], [1234, 749, 645, 1468], [2703, 1224, 1696, 3441], [15329], [12571], [1357, 2035, 2037, 1], [15963, 32741], [28, 29], [13800, 13799], [27565, 1368, 24991, 3217, 37931], [25729]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outbf16_fetch_6_ID253</t>
+    <t>[962, 589, 340, 4891, 1235, 382, 3897, 8868, 9869, 645, 676, 3392, 52, 26618, 90721, 3450]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outbf16_ID253</t>
   </si>
   <si>
     <t>[[262144, 256], [[7252], [3390]]]</t>
@@ -1361,10 +1361,10 @@
     <t>[7252, 3390]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 1, 1, 7247], [1, 3389]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_8_ID254</t>
+    <t>[887, 3]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID254</t>
   </si>
   <si>
     <t>[[262144, 256], [[5111], [6569], [9196], [31263]]]</t>
@@ -1373,10 +1373,10 @@
     <t>[5111, 6569, 9196, 31263]</t>
   </si>
   <si>
-    <t>[[4657, 1, 1, 452], [1, -1090, 2735, 2188, 1641, 1094], [1, 1, 1, 1, 1, 1, 1, 9189], [6578, 24685]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_inbf16_outbf16_fetch_5_ID255</t>
+    <t>[4839, 526, 8991, 28837]</t>
+  </si>
+  <si>
+    <t>h256_ws8_inbf16_outbf16_ID255</t>
   </si>
   <si>
     <t>[[262144, 256], [[755], [48331], [57], [18297], [9850], [7295], [88329], [4025]]]</t>
@@ -1388,10 +1388,10 @@
     <t>[755, 48331, 57, 18297, 9850, 7295, 88329, 4025]</t>
   </si>
   <si>
-    <t>[[188, 282, 284, 1], [24166, 24165], [57], [18297], [4925, 4925], [2431, 3646, 1218], [17666, 17666, 17666, 17666, 17665], [1, 1509, 1509, 1006]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_6_ID256</t>
+    <t>[725, 40609, 54, 492, 9184, 298, 48318, 3709]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outbf16_ID256</t>
   </si>
   <si>
     <t>[[262144, 256], [[8082], [1653], [8086], [9384], [783], [6281], [89450], [657], [3642], [13278], [80702], [8192], [64191], [19226], [11541], [10761]]]</t>
@@ -1403,10 +1403,10 @@
     <t>[8082, 1653, 8086, 9384, 783, 6281, 89450, 657, 3642, 13278, 80702, 8192, 64191, 19226, 11541, 10761]</t>
   </si>
   <si>
-    <t>[[4041, 4041], [1653], [1617, 2425, 3233, 810, 1], [4692, 4692], [783], [1047, 1047, 1047, 1047, 1047, 1046], [44725, 44725], [657], [1821, 1821], [13278], [80702], [8192], [1, -10696, 26745, 21396, 16047, 10698], [19226], [11541], [10761]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_inbf16_outbf16_fetch_6_ID257</t>
+    <t>[966, 938, 8002, 9201, 46, 526, 1601, 15, 2152, 237, 75477, 231, 57973, 18322, 10618, 712]</t>
+  </si>
+  <si>
+    <t>h64_ws4_inbf16_outbf16_ID257</t>
   </si>
   <si>
     <t>[[4096, 64], [[2663], [9725], [1198], [10303]]]</t>
@@ -1415,10 +1415,10 @@
     <t>[2663, 9725, 1198, 10303]</t>
   </si>
   <si>
-    <t>[[2309, 354], [1620, 2430, 3240, 4050, -1616, 1], [1198], [10303]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_inbf16_outbf16_fetch_4_ID258</t>
+    <t>[1623, 8758, 767, 980]</t>
+  </si>
+  <si>
+    <t>h64_ws4_inbf16_outbf16_ID258</t>
   </si>
   <si>
     <t>[[65536, 64], [[14776], [644], [3299], [48782]]]</t>
@@ -1427,10 +1427,10 @@
     <t>[14776, 644, 3299, 48782]</t>
   </si>
   <si>
-    <t>[[14776], [161, 241, 241, 1], [1, 1, 3297], [16260, 24390, 8132]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_inbf16_outbf16_fetch_9_ID259</t>
+    <t>[1536, 621, 529, 36921]</t>
+  </si>
+  <si>
+    <t>h64_ws4_inbf16_outbf16_ID259</t>
   </si>
   <si>
     <t>[[262144, 64], [[80], [710], [92905], [15330]]]</t>
@@ -1439,10 +1439,10 @@
     <t>[80, 710, 92905, 15330]</t>
   </si>
   <si>
-    <t>[[1, 79], [178, 178, 177, 177], [1, -87731, 41288, 36127, 30966, 25805, 20644, 15483, 10322], [15330]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_6_ID260</t>
+    <t>[74, 471, 53614, 14236]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID260</t>
   </si>
   <si>
     <t>[[4096, 256], [[7674], [8900], [1975], [28394]]]</t>
@@ -1451,10 +1451,10 @@
     <t>[7674, 8900, 1975, 28394]</t>
   </si>
   <si>
-    <t>[[7674], [1, -1479, 3706, 2965, 2224, 1483], [1975], [28394]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_1_ID261</t>
+    <t>[3375, 445, 1884, 12727]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID261</t>
   </si>
   <si>
     <t>[[65536, 256], [[1496], [138], [5312], [27208]]]</t>
@@ -1463,10 +1463,10 @@
     <t>[1496, 138, 5312, 27208]</t>
   </si>
   <si>
-    <t>[[1496], [138], [5312], [27208]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_4_ID262</t>
+    <t>[759, 56, 2616, 24352]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID262</t>
   </si>
   <si>
     <t>[[262144, 256], [[9754], [6621], [6471], [10390]]]</t>
@@ -1475,10 +1475,10 @@
     <t>[9754, 6621, 6471, 10390]</t>
   </si>
   <si>
-    <t>[[2438, 3657, 3658, 1], [3311, 3310], [6471], [10390]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_inbf16_outbf16_fetch_3_ID263</t>
+    <t>[9740, 5960, 6209, 10232]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_inbf16_outbf16_ID263</t>
   </si>
   <si>
     <t>[[4096, 1024], [[38013], [7181], [18827], [1013]]]</t>
@@ -1487,10 +1487,10 @@
     <t>[38013, 7181, 18827, 1013]</t>
   </si>
   <si>
-    <t>[[38013], [2394, 2394, 2393], [18827], [1013]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_inbf16_outbf16_fetch_7_ID264</t>
+    <t>[36665, 4159, 3320, 989]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_inbf16_outbf16_ID264</t>
   </si>
   <si>
     <t>[[65536, 1024], [[29164], [9484], [325], [99617]]]</t>
@@ -1499,10 +1499,10 @@
     <t>[29164, 9484, 325, 99617]</t>
   </si>
   <si>
-    <t>[[29164], [1, -4057, 4062, 3385, 2708, 2031, 1354], [163, 162], [19924, 19924, 19923, 19923, 19923]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_inbf16_outbf16_fetch_4_ID265</t>
+    <t>[15572, 9044, 318, 1430]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_inbf16_outbf16_ID265</t>
   </si>
   <si>
     <t>[[262144, 1024], [[41330], [41708], [6137], [4694]]]</t>
@@ -1511,10 +1511,10 @@
     <t>[41330, 41708, 6137, 4694]</t>
   </si>
   <si>
-    <t>[[41330], [13902, 20853, 6953], [1535, 1534, 1534, 1534], [4694]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_7_ID266</t>
+    <t>[18370, 24377, 444, 2742]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID266</t>
   </si>
   <si>
     <t>[[65536, 256], [[4096], [16579], [4193], [7842]]]</t>
@@ -1523,10 +1523,10 @@
     <t>[4096, 16579, 4193, 7842]</t>
   </si>
   <si>
-    <t>[[2048, 2048], [16579], [4193], [1643, 2372, 1892, 796, 85, 160, 894]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_3_ID267</t>
+    <t>[315, 1002, 2467, 7733]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID267</t>
   </si>
   <si>
     <t>[[65536, 256], [[555], [256], [70], [90]]]</t>
@@ -1535,10 +1535,10 @@
     <t>[555, 256, 70, 90]</t>
   </si>
   <si>
-    <t>[[555], [207, 49], [1, 1, 68], [90]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_4_ID268</t>
+    <t>[285, 25, 67, 9]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID268</t>
   </si>
   <si>
     <t>[[65536, 256], [[45023], [1676], [17941], [47705]]]</t>
@@ -1547,10 +1547,10 @@
     <t>[45023, 1676, 17941, 47705]</t>
   </si>
   <si>
-    <t>[[45023], [1676], [17941], [11927, 11926, 11926, 11926]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_1_ID269</t>
+    <t>[19110, 308, 2454, 43481]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID269</t>
   </si>
   <si>
     <t>[[65536, 256], [[18], [30378], [512], [9205]]]</t>
@@ -1559,10 +1559,10 @@
     <t>[18, 30378, 512, 9205]</t>
   </si>
   <si>
-    <t>[[18], [30378], [512], [9205]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp16_fetch_4_ID270</t>
+    <t>[4, 27806, 244, 672]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp16_ID270</t>
   </si>
   <si>
     <t>[[65536, 256], [[33452], [48986], [11269], [3295]]]</t>
@@ -1571,10 +1571,10 @@
     <t>[33452, 48986, 11269, 3295]</t>
   </si>
   <si>
-    <t>[[28544, 1, 4907], [12247, 12247, 12246, 12246], [11269], [3295]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp16_fetch_3_ID271</t>
+    <t>[15133, 44332, 1101, 2995]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp16_ID271</t>
   </si>
   <si>
     <t>[[65536, 256], [[6824], [3864], [8857], [15107]]]</t>
@@ -1583,10 +1583,10 @@
     <t>[6824, 3864, 8857, 15107]</t>
   </si>
   <si>
-    <t>[[2275, 2275, 2274], [1288, 1288, 1288], [8857], [15107]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp16_fetch_5_ID272</t>
+    <t>[103, 501, 152, 158]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp16_ID272</t>
   </si>
   <si>
     <t>[[65536, 256], [[1024], [998], [7029], [4096]]]</t>
@@ -1595,10 +1595,10 @@
     <t>[1024, 998, 7029, 4096]</t>
   </si>
   <si>
-    <t>[[1024], [998], [1, 707, 2809, 2107, 1405], [1, 1, 1, 4093]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp16_fetch_5_ID273</t>
+    <t>[45, 421, 6562, 3695]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp16_ID273</t>
   </si>
   <si>
     <t>[[65536, 256], [[748], [5999], [48104], [4598]]]</t>
@@ -1607,10 +1607,10 @@
     <t>[748, 5999, 48104, 4598]</t>
   </si>
   <si>
-    <t>[[11, 235, 190, 132, 180], [1, 1, 1, 1, 5995], [48104], [768, 2298, 1532]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outfp32_fetch_4_ID274</t>
+    <t>[713, 174, 47491, 1794]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outfp32_ID274</t>
   </si>
   <si>
     <t>[[65536, 256], [[478], [4438], [44], [4561]]]</t>
@@ -1619,10 +1619,10 @@
     <t>[478, 4438, 44, 4561]</t>
   </si>
   <si>
-    <t>[[478], [1, 1, 1, 4435], [44], [4561]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outfp32_fetch_6_ID275</t>
+    <t>[283, 237, 1, 13]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outfp32_ID275</t>
   </si>
   <si>
     <t>[[65536, 256], [[18135], [7083], [6243], [440]]]</t>
@@ -1631,10 +1631,10 @@
     <t>[18135, 7083, 6243, 440]</t>
   </si>
   <si>
-    <t>[[18135], [1180, 1770, 2360, 2950, -1178, 1], [325, 1354, 1996, 538, 2030], [440]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outfp32_fetch_5_ID276</t>
+    <t>[8224, 5347, 547, 41]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outfp32_ID276</t>
   </si>
   <si>
     <t>[[65536, 256], [[4248], [70935], [1064], [19411]]]</t>
@@ -1643,10 +1643,10 @@
     <t>[4248, 70935, 1064, 19411]</t>
   </si>
   <si>
-    <t>[[2686, 1562], [14187, 14187, 14187, 14187, 14187], [1064], [19411]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outfp32_fetch_3_ID277</t>
+    <t>[184, 4786, 26, 1420]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outfp32_ID277</t>
   </si>
   <si>
     <t>[[65536, 256], [[62255], [1651], [879], [8705]]]</t>
@@ -1655,10 +1655,10 @@
     <t>[62255, 1651, 879, 8705]</t>
   </si>
   <si>
-    <t>[[31128, 31127], [1651], [277, 131, 471], [4352, 4353]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_infp32_outbf16_fetch_3_ID278</t>
+    <t>[11247, 1592, 524, 613]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_infp32_outbf16_ID278</t>
   </si>
   <si>
     <t>[[65536, 2048], [[82616], [8933], [40972], [8501]]]</t>
@@ -1667,10 +1667,10 @@
     <t>[82616, 8933, 40972, 8501]</t>
   </si>
   <si>
-    <t>[[82616], [3686, 1958, 3289], [40972], [3164, 5337]]</t>
-  </si>
-  <si>
-    <t>h64_ws16_inbf16_outbf16_fetch_7_ID279</t>
+    <t>[36152, 1460, 37513, 1190]</t>
+  </si>
+  <si>
+    <t>h64_ws16_inbf16_outbf16_ID279</t>
   </si>
   <si>
     <t>[[292548, 64], [[1854], [4038], [5947], [4475], [2539], [36126], [3893], [8750], [512], [9708], [91698], [29014], [363], [40651], [7742], [22339]]]</t>
@@ -1685,10 +1685,10 @@
     <t>[1854, 4038, 5947, 4475, 2539, 36126, 3893, 8750, 512, 9708, 91698, 29014, 363, 40651, 7742, 22339]</t>
   </si>
   <si>
-    <t>[[1854], [1346, 2019, 673], [1983, 1982, 1982], [4475], [1270, 1269], [7180, 6520, 22426], [1947, 1946], [1499, 1877, 524, 2172, 2678], [199, 3, 150, 160], [1, -4153, 4158, 3465, 2772, 2079, 1386], [13100, 13100, 13100, 13100, 13100, 13099, 13099], [29014], [363], [40651], [7742], [22339]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_infp32_outfp32_fetch_5_ID280</t>
+    <t>[1827, 179, 115, 2193, 161, 18654, 898, 8706, 46, 9052, 23984, 26635, 249, 721, 3218, 21772]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_infp32_outfp32_ID280</t>
   </si>
   <si>
     <t>[[16384, 4096], [[2351], [27121], [6496], [1301], [1741], [93012], [8880], [7313], [92579], [32802], [5877], [1024], [86], [499], [95740], [7798]]]</t>
@@ -1700,10 +1700,10 @@
     <t>[2351, 27121, 6496, 1301, 1741, 93012, 8880, 7313, 92579, 32802, 5877, 1024, 86, 499, 95740, 7798]</t>
   </si>
   <si>
-    <t>[[1175, 1176], [13561, 13560], [1624, 2436, 2435, 1], [1301], [1741], [79008, 14004], [4440, 4440], [1462, 2193, 2924, 733, 1], [88592, 1, 3986], [10934, 10934, 10934], [1959, 1959, 1959], [1024], [86], [499], [47870, 47870], [2350, 15, 1983, 3450]]</t>
-  </si>
-  <si>
-    <t>h3457_ws8_inbf16_outbf16_fetch_4_ID281</t>
+    <t>[198, 1854, 3454, 106, 103, 1910, 8119, 2982, 47527, 31528, 2881, 516, 6, 42, 47335, 7571]</t>
+  </si>
+  <si>
+    <t>h3457_ws8_inbf16_outbf16_ID281</t>
   </si>
   <si>
     <t>[[970123, 3457], [[42], [554], [512], [12275], [28309], [2218], [3309], [909]]]</t>
@@ -1721,10 +1721,10 @@
     <t>[42, 554, 512, 12275, 28309, 2218, 3309, 909]</t>
   </si>
   <si>
-    <t>[[42], [429, 1, 1, 123], [87, 255, 170], [12275], [14154, 14155], [2218], [1103, 1654, 552], [1, 1, 1, 906]]</t>
-  </si>
-  <si>
-    <t>h5015_ws2_inbf16_outfp16_fetch_1_ID282</t>
+    <t>[40, 481, 41, 11744, 25389, 935, 236, 92]</t>
+  </si>
+  <si>
+    <t>h5015_ws2_inbf16_outfp16_ID282</t>
   </si>
   <si>
     <t>[[425618, 5015], [[41455], [34711]]]</t>
@@ -1742,10 +1742,10 @@
     <t>[41455, 34711]</t>
   </si>
   <si>
-    <t>[[41455], [34711]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp32_outbf16_fetch_7_ID283</t>
+    <t>[19015, 1692]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp32_outbf16_ID283</t>
   </si>
   <si>
     <t>[[262144, 4096], [[18949], [67235], [2048], [8192]]]</t>
@@ -1757,10 +1757,10 @@
     <t>[18949, 67235, 2048, 8192]</t>
   </si>
   <si>
-    <t>[[18949], [41344, 1, 1, 25889], [2048], [1171, 1171, 1170, 1170, 1170, 1170, 1170]]</t>
-  </si>
-  <si>
-    <t>h2645_ws4_infp32_outfp16_fetch_4_ID284</t>
+    <t>[20, 66597, 1698, 4858]</t>
+  </si>
+  <si>
+    <t>h2645_ws4_infp32_outfp16_ID284</t>
   </si>
   <si>
     <t>[[131072, 2645], [[45], [8451], [9233], [40966]]]</t>
@@ -1775,10 +1775,10 @@
     <t>[45, 8451, 9233, 40966]</t>
   </si>
   <si>
-    <t>[[16, 29], [4769, 1, 3681], [9233], [10242, 10242, 10241, 10241]]</t>
-  </si>
-  <si>
-    <t>h2462_ws8_infp32_outfp16_fetch_4_ID285</t>
+    <t>[44, 7760, 8894, 17406]</t>
+  </si>
+  <si>
+    <t>h2462_ws8_infp32_outfp16_ID285</t>
   </si>
   <si>
     <t>[[327550, 2462], [[7350], [8512], [455], [8446], [71], [22197], [1042], [859]]]</t>
@@ -1799,10 +1799,10 @@
     <t>[7350, 8512, 455, 8446, 71, 22197, 1042, 859]</t>
   </si>
   <si>
-    <t>[[1225, 3675, 2450], [1, 1, 1, 8509], [228, 227], [8446], [71], [21889, 308], [1042], [429, 430]]</t>
-  </si>
-  <si>
-    <t>h584_ws4_infp16_outfp32_fetch_3_ID286</t>
+    <t>[725, 7909, 25, 7633, 64, 20986, 85, 89]</t>
+  </si>
+  <si>
+    <t>h584_ws4_infp16_outfp32_ID286</t>
   </si>
   <si>
     <t>[[270700, 584], [[6189], [15169], [36731], [3380]]]</t>
@@ -1820,10 +1820,10 @@
     <t>[6189, 15169, 36731, 3380]</t>
   </si>
   <si>
-    <t>[[2063, 2063, 2063], [15169], [36731], [1690, 1690]]</t>
-  </si>
-  <si>
-    <t>h3094_ws8_infp16_outfp32_fetch_5_ID287</t>
+    <t>[15, 8248, 2233, 3081]</t>
+  </si>
+  <si>
+    <t>h3094_ws8_infp16_outfp32_ID287</t>
   </si>
   <si>
     <t>[[276655, 3094], [[6137], [3728], [9419], [3399], [32021], [7475], [12465], [31585]]]</t>
@@ -1844,10 +1844,10 @@
     <t>[6137, 3728, 9419, 3399, 32021, 7475, 12465, 31585]</t>
   </si>
   <si>
-    <t>[[1535, 1534, 1534, 1534], [3728], [1, 1, 9417], [3399], [16338, 1, 15682], [1, 748, 2989, 2242, 1495], [12465], [31585]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_inbf16_outfp32_fetch_8_ID288</t>
+    <t>[5587, 1734, 1634, 3125, 31858, 6021, 11469, 29228]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_inbf16_outfp32_ID288</t>
   </si>
   <si>
     <t>[[131072, 1024], [[68432], [98228], [1781], [1477], [8507], [588], [805], [48547], [17794], [1024], [7489], [1024], [2048], [7838], [23287], [9008]]]</t>
@@ -1859,10 +1859,10 @@
     <t>[68432, 98228, 1781, 1477, 8507, 588, 805, 48547, 17794, 1024, 7489, 1024, 2048, 7838, 23287, 9008]</t>
   </si>
   <si>
-    <t>[[11406, 11406, 11405, 11405, 11405, 11405], [12278, 18417, 24556, 30695, 36834, 42973, -67526, 1], [1781], [1477], [1417, 2125, 2833, 3541, -1410, 1], [588], [161, 241, 321, 81, 1], [27931, 1, 20615], [17794], [1024], [1249, 1248, 1248, 1248, 1248, 1248], [1024], [1024, 1024], [2613, 2613, 2612], [5631, 17656], [1, 1, 1, 9005]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_inbf16_outfp32_fetch_6_ID289</t>
+    <t>[39840, 94490, 114, 1411, 660, 1, 791, 3059, 14692, 435, 7433, 585, 897, 7502, 11795, 5129]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_inbf16_outfp32_ID289</t>
   </si>
   <si>
     <t>[[8192, 2048], [[27841], [22187], [105], [34646], [11858], [2957], [7845], [8192]]]</t>
@@ -1874,10 +1874,10 @@
     <t>[27841, 22187, 105, 34646, 11858, 2957, 7845, 8192]</t>
   </si>
   <si>
-    <t>[[14319, 13522], [22187], [105], [17323, 17323], [11858], [269, 2688], [1307, 1960, 2613, 3266, -1302, 1], [1, 1, 1, 1, 8188]]</t>
-  </si>
-  <si>
-    <t>h4410_ws2_infp32_outbf16_fetch_4_ID290</t>
+    <t>[15427, 17948, 5, 30780, 10703, 2927, 1438, 274]</t>
+  </si>
+  <si>
+    <t>h4410_ws2_infp32_outbf16_ID290</t>
   </si>
   <si>
     <t>[[835733, 4410], [[6542], [88870]]]</t>
@@ -1898,10 +1898,10 @@
     <t>[6542, 88870]</t>
   </si>
   <si>
-    <t>[[2180, 3270, 1092], [1, 33327, 33325, 22217]]</t>
-  </si>
-  <si>
-    <t>h1367_ws16_inbf16_outbf16_fetch_5_ID291</t>
+    <t>[301, 80530]</t>
+  </si>
+  <si>
+    <t>h1367_ws16_inbf16_outbf16_ID291</t>
   </si>
   <si>
     <t>[[954024, 1367], [[42917], [35575], [45767], [5360], [23347], [5303], [2783], [972], [24258], [6316], [560], [305], [925], [1059], [44989], [21930]]]</t>
@@ -1919,10 +1919,10 @@
     <t>[42917, 35575, 45767, 5360, 23347, 5303, 2783, 972, 24258, 6316, 560, 305, 925, 1059, 44989, 21930]</t>
   </si>
   <si>
-    <t>[[4945, 13874, 2746, 21352], [15102, 20473], [45767], [1340, 1340, 1340, 1340], [23347], [2652, 2651], [1, 2782], [972], [24258], [3728, 2588], [267, 29, 58, 98, 108], [63, 242], [309, 308, 308], [1059], [33806, 1, 11182], [21930]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_infp32_outbf16_fetch_5_ID292</t>
+    <t>[25399, 9889, 42562, 5295, 12525, 2545, 2582, 930, 132, 2853, 15, 252, 746, 231, 8488, 2936]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_infp32_outbf16_ID292</t>
   </si>
   <si>
     <t>[[384675, 2048], [[29158], [957]]]</t>
@@ -1937,10 +1937,10 @@
     <t>[29158, 957]</t>
   </si>
   <si>
-    <t>[[2324, 26834], [1, 98, 381, 286, 191]]</t>
-  </si>
-  <si>
-    <t>h2917_ws16_infp32_outfp16_fetch_8_ID293</t>
+    <t>[28452, 128]</t>
+  </si>
+  <si>
+    <t>h2917_ws16_infp32_outfp16_ID293</t>
   </si>
   <si>
     <t>[[34864, 2917], [[2871], [9547], [8232], [4359], [950], [9039], [141], [43108], [62683], [21184], [2335], [6463], [4492], [35887], [695], [233]]]</t>
@@ -1958,10 +1958,10 @@
     <t>[2871, 9547, 8232, 4359, 950, 9039, 141, 43108, 62683, 21184, 2335, 6463, 4492, 35887, 695, 233]</t>
   </si>
   <si>
-    <t>[[1436, 1435], [1, -6552, 4173, 3577, 2981, 2385, 1789, 1193], [559, 743, 820, 1104, 5006], [4359], [238, 238, 237, 237], [3013, 4519, 1507], [141], [2309, 40799], [1, 1, 1, 62680], [10592, 10592], [2335], [1, 6462], [4074, 418], [11962, 17943, 5982], [139, 208, 277, 70, 1], [233]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_inbf16_outfp32_fetch_9_ID294</t>
+    <t>[28, 9192, 7891, 317, 426, 7475, 128, 6465, 1803, 2309, 2163, 3029, 4141, 957, 63, 224]</t>
+  </si>
+  <si>
+    <t>h256_ws8_inbf16_outfp32_ID294</t>
   </si>
   <si>
     <t>[[16384, 256], [[595], [98290], [831], [36244], [8352], [4813], [1024], [9555]]]</t>
@@ -1973,10 +1973,10 @@
     <t>[595, 98290, 831, 36244, 8352, 4813, 1024, 9555]</t>
   </si>
   <si>
-    <t>[[119, 10, 466], [63653, 1, 1, 1, 1, 1, 1, 1, 34630], [831], [48, 36196], [1392, 1392, 1392, 1392, 1392, 1392], [4813], [1024], [4778, 4777]]</t>
-  </si>
-  <si>
-    <t>h208_ws4_inbf16_outfp32_fetch_4_ID295</t>
+    <t>[38, 96561, 720, 14962, 8047, 2520, 667, 3840]</t>
+  </si>
+  <si>
+    <t>h208_ws4_inbf16_outfp32_ID295</t>
   </si>
   <si>
     <t>[[895157, 208], [[68492], [40804], [8814], [364]]]</t>
@@ -1994,10 +1994,10 @@
     <t>[68492, 40804, 8814, 364]</t>
   </si>
   <si>
-    <t>[[68492], [20402, 20402], [2204, 2204, 2203, 2203], [182, 182]]</t>
-  </si>
-  <si>
-    <t>h1468_ws16_infp16_outfp32_fetch_7_ID296</t>
+    <t>[35336, 40198, 4404, 347]</t>
+  </si>
+  <si>
+    <t>h1468_ws16_infp16_outfp32_ID296</t>
   </si>
   <si>
     <t>[[524288, 1468], [[359], [1756], [47429], [3697], [52799], [3775], [25247], [256], [7084], [736], [2982], [731], [7853], [9723], [22545], [9728]]]</t>
@@ -2018,10 +2018,10 @@
     <t>[359, 1756, 47429, 3697, 52799, 3775, 25247, 256, 7084, 736, 2982, 731, 7853, 9723, 22545, 9728]</t>
   </si>
   <si>
-    <t>[[179, 180], [1756], [1, 17786, 17785, 11857], [1233, 1232, 1232], [10560, 10560, 10560, 10560, 10559], [2643, 1, 1131], [25247], [256], [2575, 2042, 791, 270, 1406], [736], [1666, 1316], [101, 104, 105, 14, 407], [1121, 1681, 2241, 2801, 3361, -3353, 1], [1, 1, 1, 9720], [22545], [1, 1, 1, 1, 1, 9723]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_infp16_outbf16_fetch_4_ID297</t>
+    <t>[346, 723, 28989, 3657, 29741, 2197, 23223, 121, 6988, 33, 278, 706, 123, 8403, 20641, 9057]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_infp16_outbf16_ID297</t>
   </si>
   <si>
     <t>[[16384, 2048], [[7598], [51], [16286], [274]]]</t>
@@ -2033,10 +2033,10 @@
     <t>[7598, 51, 16286, 274]</t>
   </si>
   <si>
-    <t>[[1899, 2848, 2850, 1], [9, 25, 17], [16286], [274]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp32_outbf16_fetch_6_ID298</t>
+    <t>[7147, 46, 14946, 160]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp32_outbf16_ID298</t>
   </si>
   <si>
     <t>[[603555, 512], [[9666], [282], [8503], [8600], [46746], [27960], [8267], [580]]]</t>
@@ -2051,10 +2051,10 @@
     <t>[9666, 282, 8503, 8600, 46746, 27960, 8267, 580]</t>
   </si>
   <si>
-    <t>[[2416, 3624, 3625, 1], [1, 281], [1, 1, 1, 1, 1, 8498], [2677, 1635, 1681, 2607], [10064, 7908, 1381, 27393], [13980, 13980], [8267], [116, 116, 116, 116, 116]]</t>
-  </si>
-  <si>
-    <t>h977_ws16_inbf16_outbf16_fetch_8_ID299</t>
+    <t>[9279, 279, 672, 386, 21410, 26844, 8031, 16]</t>
+  </si>
+  <si>
+    <t>h977_ws16_inbf16_outbf16_ID299</t>
   </si>
   <si>
     <t>[[61041, 977], [[4072], [76], [48811], [6408], [1799], [8701], [6603], [77293], [6210], [26318], [2048], [62993], [73682], [256], [18749], [21066]]]</t>
@@ -2072,10 +2072,10 @@
     <t>[4072, 76, 48811, 6408, 1799, 8701, 6603, 77293, 6210, 26318, 2048, 62993, 73682, 256, 18749, 21066]</t>
   </si>
   <si>
-    <t>[[680, 2035, 1357], [57, 1, 18], [16270, 24405, 8136], [1248, 1470, 1099, 233, 530, 1828], [1799], [8555, 1, 1, 1, 1, 1, 1, 140], [6603], [1, -12882, 32205, 25764, 19323, 12882], [1035, 1035, 1035, 1035, 1035, 1035], [26318], [1, 2047], [10501, 31495, 20997], [1, 1, 1, 1, 1, 1, 73676], [256], [18749], [10533, 10533]]</t>
-  </si>
-  <si>
-    <t>h4068_ws16_inbf16_outbf16_fetch_6_ID300</t>
+    <t>[234, 69, 23527, 621, 92, 1862, 394, 73627, 6019, 11094, 2011, 35032, 38863, 234, 568, 19911]</t>
+  </si>
+  <si>
+    <t>h4068_ws16_inbf16_outbf16_ID300</t>
   </si>
   <si>
     <t>[[53091, 4068], [[6647], [2048], [7937], [3715], [537], [3270], [16181], [89176], [9441], [53128], [29450], [2172], [1024], [1312], [923], [308]]]</t>
@@ -2093,10 +2093,10 @@
     <t>[6647, 2048, 7937, 3715, 537, 3270, 16181, 89176, 9441, 53128, 29450, 2172, 1024, 1312, 923, 308]</t>
   </si>
   <si>
-    <t>[[2215, 3322, 1110], [1024, 1024], [19, 3089, 1508, 827, 203, 2291], [750, 1109, 1856], [268, 269], [545, 1635, 1090], [16181], [24257, 116, 11462, 11934, 14420, 26987], [2361, 2360, 2360, 2360], [13282, 19923, 19922, 1], [29450], [1086, 1086], [1024], [1312], [462, 461], [308]]</t>
-  </si>
-  <si>
-    <t>h128_ws16_infp32_outfp32_fetch_7_ID301</t>
+    <t>[290, 1846, 38, 207, 283, 1499, 10299, 85606, 853, 48566, 14645, 113, 932, 49, 382, 3]</t>
+  </si>
+  <si>
+    <t>h128_ws16_infp32_outfp32_ID301</t>
   </si>
   <si>
     <t>[[650014, 128], [[9083], [4867], [90713], [4985], [3148], [556], [8192], [1024], [95], [61466], [6238], [512], [39987], [51038], [11145], [54668]]]</t>
@@ -2111,10 +2111,10 @@
     <t>[9083, 4867, 90713, 4985, 3148, 556, 8192, 1024, 95, 61466, 6238, 512, 39987, 51038, 11145, 54668]</t>
   </si>
   <si>
-    <t>[[1, -3883, 3889, 3241, 2593, 1945, 1297], [1623, 1622, 1622], [90713], [1247, 1246, 1246, 1246], [1574, 1574], [556], [1, 3071, 3072, 2048], [1024], [48, 47], [12294, 12293, 12293, 12293, 12293], [2291, 663, 1206, 2078], [256, 256], [34603, 5384], [25519, 25519], [11145], [18223, 18223, 18222]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_infp16_outfp16_fetch_5_ID302</t>
+    <t>[8684, 380, 36857, 450, 2894, 521, 4399, 406, 89, 58889, 3552, 265, 36641, 4822, 9687, 1624]</t>
+  </si>
+  <si>
+    <t>h64_ws2_infp16_outfp16_ID302</t>
   </si>
   <si>
     <t>[[97475, 64], [[4096], [76675]]]</t>
@@ -2132,10 +2132,10 @@
     <t>[4096, 76675]</t>
   </si>
   <si>
-    <t>[[1024, 1024, 1024, 1024], [29446, 15351, 8543, 8814, 14521]]</t>
-  </si>
-  <si>
-    <t>h2802_ws8_infp32_outfp32_fetch_7_ID303</t>
+    <t>[3749, 66570]</t>
+  </si>
+  <si>
+    <t>h2802_ws8_infp32_outfp32_ID303</t>
   </si>
   <si>
     <t>[[131072, 2802], [[34], [679], [66952], [7525], [584], [15785], [9911], [12109]]]</t>
@@ -2150,10 +2150,10 @@
     <t>[34, 679, 66952, 7525, 584, 15785, 9911, 12109]</t>
   </si>
   <si>
-    <t>[[17, 17], [130, 14, 56, 232, 247], [1, 1, 1, 1, 1, 66947], [1075, 1075, 1075, 1075, 1075, 1075, 1075], [292, 292], [15785], [1, -1644, 4126, 3301, 2476, 1651], [12109]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_infp32_outfp16_fetch_4_ID304</t>
+    <t>[5, 613, 6215, 3230, 108, 7278, 4818, 739]</t>
+  </si>
+  <si>
+    <t>h128_ws4_infp32_outfp16_ID304</t>
   </si>
   <si>
     <t>[[176847, 128], [[537], [8395], [912], [30052]]]</t>
@@ -2168,10 +2168,10 @@
     <t>[537, 8395, 912, 30052]</t>
   </si>
   <si>
-    <t>[[134, 201, 201, 1], [8395], [304, 456, 152], [30052]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outfp16_fetch_5_ID305</t>
+    <t>[500, 84, 911, 1087]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outfp16_ID305</t>
   </si>
   <si>
     <t>[[8192, 512], [[680], [5641], [3758], [680], [4143], [13897], [8192], [9083], [4894], [3419], [4096], [1560], [5596], [66353], [3553], [2072]]]</t>
@@ -2180,10 +2180,10 @@
     <t>[680, 5641, 3758, 680, 4143, 13897, 8192, 9083, 4894, 3419, 4096, 1560, 5596, 66353, 3553, 2072]</t>
   </si>
   <si>
-    <t>[[340, 340], [1410, 2115, 2115, 1], [1879, 1879], [1, 67, 272, 204, 136], [1381, 1381, 1381], [13897], [6401, 1, 1790], [9083], [1127, 1531, 651, 1585], [1710, 1709], [2024, 807, 1265], [1560], [1, 1, 1, 1, 5592], [13270, 19905, 26540, 6637, 1], [1777, 1776], [1036, 1036]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_infp16_outfp16_fetch_8_ID306</t>
+    <t>[608, 5563, 3092, 657, 2445, 6665, 8085, 9031, 160, 3307, 2254, 88, 5320, 51639, 31, 681]</t>
+  </si>
+  <si>
+    <t>h64_ws2_infp16_outfp16_ID306</t>
   </si>
   <si>
     <t>[[524288, 64], [[9598], [28224]]]</t>
@@ -2192,10 +2192,10 @@
     <t>[9598, 28224]</t>
   </si>
   <si>
-    <t>[[802, 1378, 1232, 1932, 674, 668, 761, 2151], [14112, 14112]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp16_outfp32_fetch_2_ID307</t>
+    <t>[9204, 12666]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp16_outfp32_ID307</t>
   </si>
   <si>
     <t>[[590301, 4096], [[29701], [29420]]]</t>
@@ -2210,10 +2210,10 @@
     <t>[29701, 29420]</t>
   </si>
   <si>
-    <t>[[29701], [14710, 14710]]</t>
-  </si>
-  <si>
-    <t>h4525_ws16_inbf16_outfp16_fetch_8_ID308</t>
+    <t>[4188, 26264]</t>
+  </si>
+  <si>
+    <t>h4525_ws16_inbf16_outfp16_ID308</t>
   </si>
   <si>
     <t>[[32768, 4525], [[508], [9215], [8142], [8035], [78225], [3800], [2432], [567], [8760], [60], [5300], [1607], [7571], [7418], [5503], [23911]]]</t>
@@ -2225,10 +2225,10 @@
     <t>[508, 9215, 8142, 8035, 78225, 3800, 2432, 567, 8760, 60, 5300, 1607, 7571, 7418, 5503, 23911]</t>
   </si>
   <si>
-    <t>[[47, 181, 35, 245], [2304, 2304, 2304, 2303], [6084, 1, 1, 1, 1, 1, 1, 2052], [1, 3014, 3012, 2008], [1, 1, 1, 1, 1, 1, 78219], [1900, 1900], [2432], [288, 279], [1752, 1752, 1752, 1752, 1752], [60], [2650, 2650], [1607], [1, -1254, 3151, 2521, 1891, 1261], [1, 1, 1, 7415], [918, 2751, 1834], [23911]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_infp16_outbf16_fetch_8_ID309</t>
+    <t>[494, 1313, 1014, 7434, 14066, 469, 27, 251, 8543, 28, 2330, 44, 2526, 7406, 5410, 2477]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_infp16_outbf16_ID309</t>
   </si>
   <si>
     <t>[[4096, 4096], [[100], [1000], [63337], [9129], [954], [27280], [9900], [1397], [2421], [5266], [92], [43255], [227], [571], [7299], [38754]]]</t>
@@ -2240,10 +2240,10 @@
     <t>[100, 1000, 63337, 9129, 954, 27280, 9900, 1397, 2421, 5266, 92, 43255, 227, 571, 7299, 38754]</t>
   </si>
   <si>
-    <t>[[100], [1000], [12668, 12668, 12667, 12667, 12667], [1, 1, 1, 1, 1, 1, 1, 9122], [1, 98, 380, 285, 190], [13640, 13640], [1, 1, 1, 1, 1, 9895], [1397], [2421], [1053, 1579, 2105, 528, 1], [92], [14419, 14418, 14418], [227], [571], [4620, 1, 1, 1, 2676], [38754]]</t>
-  </si>
-  <si>
-    <t>h1234_ws2_infp16_outfp32_fetch_2_ID310</t>
+    <t>[97, 30, 1617, 9069, 881, 2271, 9688, 1384, 41, 498, 12, 21654, 226, 4, 3040, 19378]</t>
+  </si>
+  <si>
+    <t>h1234_ws2_infp16_outfp32_ID310</t>
   </si>
   <si>
     <t>[[813523, 1234], [[4096], [20697]]]</t>
@@ -2261,10 +2261,10 @@
     <t>[4096, 20697]</t>
   </si>
   <si>
-    <t>[[1360, 2736], [10349, 10348]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_inbf16_outfp16_fetch_6_ID311</t>
+    <t>[573, 88]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_inbf16_outfp16_ID311</t>
   </si>
   <si>
     <t>[[981366, 2048], [[26854], [38565], [3532], [1704], [4717], [30218], [256], [28943], [256], [5287], [8322], [52347], [2992], [11761], [2682], [3116]]]</t>
@@ -2279,10 +2279,10 @@
     <t>[26854, 38565, 3532, 1704, 4717, 30218, 256, 28943, 256, 5287, 8322, 52347, 2992, 11761, 2682, 3116]</t>
   </si>
   <si>
-    <t>[[26854], [19283, 19282], [1766, 1766], [1704], [1, 1, 4715], [15109, 15109], [128, 128], [10792, 18151], [128, 128], [2163, 683, 974, 464, 1003], [1387, 2080, 2773, 3466, -1385, 1], [10469, 15703, 20937, 5237, 1], [1496, 1496], [11761], [1341, 1341], [1039, 1039, 1038]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_infp16_outbf16_fetch_4_ID312</t>
+    <t>[22245, 37984, 1613, 827, 445, 15661, 138, 17792, 255, 3886, 580, 34598, 244, 11239, 186, 1609]</t>
+  </si>
+  <si>
+    <t>h512_ws4_infp16_outbf16_ID312</t>
   </si>
   <si>
     <t>[[777133, 512], [[35026], [28], [4796], [803]]]</t>
@@ -2297,10 +2297,10 @@
     <t>[35026, 28, 4796, 803]</t>
   </si>
   <si>
-    <t>[[9015, 12824, 13187], [28], [2398, 2398], [200, 300, 302, 1]]</t>
-  </si>
-  <si>
-    <t>h4027_ws4_infp32_outfp16_fetch_5_ID313</t>
+    <t>[33206, 9, 811, 123]</t>
+  </si>
+  <si>
+    <t>h4027_ws4_infp32_outfp16_ID313</t>
   </si>
   <si>
     <t>[[131072, 4027], [[7991], [1287], [243], [436]]]</t>
@@ -2315,10 +2315,10 @@
     <t>[7991, 1287, 243, 436]</t>
   </si>
   <si>
-    <t>[[1, 799, 3196, 2397, 1598], [1287], [121, 122], [144, 96, 196]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_infp32_outbf16_fetch_4_ID314</t>
+    <t>[7222, 1211, 95, 19]</t>
+  </si>
+  <si>
+    <t>h512_ws2_infp32_outbf16_ID314</t>
   </si>
   <si>
     <t>[[262144, 512], [[214], [745]]]</t>
@@ -2327,10 +2327,10 @@
     <t>[214, 745]</t>
   </si>
   <si>
-    <t>[[107, 107], [367, 106, 49, 223]]</t>
-  </si>
-  <si>
-    <t>h2021_ws16_inbf16_outbf16_fetch_8_ID315</t>
+    <t>[193, 741]</t>
+  </si>
+  <si>
+    <t>h2021_ws16_inbf16_outbf16_ID315</t>
   </si>
   <si>
     <t>[[524288, 2021], [[7781], [7126], [1818], [859], [5232], [125], [82928], [613], [256], [29174], [35701], [462], [68], [50], [12751], [304]]]</t>
@@ -2345,10 +2345,10 @@
     <t>[7781, 7126, 1818, 859, 5232, 125, 82928, 613, 256, 29174, 35701, 462, 68, 50, 12751, 304]</t>
   </si>
   <si>
-    <t>[[1945, 2917, 2918, 1], [5336, 1, 1, 1788], [1818], [55, 82, 48, 674], [1808, 195, 483, 661, 2085], [125], [30184, 25377, 7790, 9027, 2740, 434, 3008, 4368], [172, 27, 62, 171, 181], [104, 152], [29174], [11901, 11900, 11900], [115, 172, 174, 1], [8, 23, 37], [50], [12751], [1, 303]]</t>
-  </si>
-  <si>
-    <t>h2648_ws8_inbf16_outbf16_fetch_3_ID316</t>
+    <t>[7261, 7086, 1675, 355, 4816, 119, 57838, 274, 2, 1809, 30184, 450, 2, 35, 5494, 136]</t>
+  </si>
+  <si>
+    <t>h2648_ws8_inbf16_outbf16_ID316</t>
   </si>
   <si>
     <t>[[720944, 2648], [[11], [10720], [24783], [1175], [2044], [9199], [25118], [29]]]</t>
@@ -2366,10 +2366,10 @@
     <t>[11, 10720, 24783, 1175, 2044, 9199, 25118, 29]</t>
   </si>
   <si>
-    <t>[[11], [10720], [24783], [1175], [2044], [727, 1039, 7433], [25118], [29]]</t>
-  </si>
-  <si>
-    <t>h410_ws16_inbf16_outbf16_fetch_6_ID317</t>
+    <t>[1, 4403, 22356, 2, 196, 2739, 2905, 5]</t>
+  </si>
+  <si>
+    <t>h410_ws16_inbf16_outbf16_ID317</t>
   </si>
   <si>
     <t>[[52880, 410], [[7311], [41], [8773], [5673], [67353], [8996], [32987], [57743], [612], [7046], [299], [121], [47], [39530], [137], [90585]]]</t>
@@ -2387,10 +2387,10 @@
     <t>[7311, 41, 8773, 5673, 67353, 8996, 32987, 57743, 612, 7046, 299, 121, 47, 39530, 137, 90585]</t>
   </si>
   <si>
-    <t>[[1462, 2193, 2924, 731, 1], [21, 20], [4086, 375, 4312], [2680, 2993], [34829, 32524], [1, 1, 8994], [32987], [26229, 31514], [306, 306], [1761, 2641, 2643, 1], [299], [121], [15, 22, 10], [39530], [137], [14482, 25098, 15796, 8512, 3265, 23432]]</t>
-  </si>
-  <si>
-    <t>h64_ws8_infp32_outfp32_fetch_5_ID318</t>
+    <t>[2590, 2, 1022, 2563, 25081, 8832, 18255, 51419, 246, 283, 144, 11, 23, 37534, 77, 39940]</t>
+  </si>
+  <si>
+    <t>h64_ws8_infp32_outfp32_ID318</t>
   </si>
   <si>
     <t>[[824395, 64], [[13074], [7878], [951], [37415], [34635], [4181], [20797], [100]]]</t>
@@ -2405,10 +2405,10 @@
     <t>[13074, 7878, 951, 37415, 34635, 4181, 20797, 100]</t>
   </si>
   <si>
-    <t>[[13074], [1575, 2362, 3149, 791, 1], [388, 180, 106, 117, 160], [37415], [11545, 17317, 5773], [1134, 1353, 1694], [20797], [100]]</t>
-  </si>
-  <si>
-    <t>h3533_ws8_infp32_outbf16_fetch_4_ID319</t>
+    <t>[925, 5819, 69, 23027, 33039, 2429, 2421, 86]</t>
+  </si>
+  <si>
+    <t>h3533_ws8_infp32_outbf16_ID319</t>
   </si>
   <si>
     <t>[[796870, 3533], [[141], [45256], [49282], [2050], [5609], [797], [921], [91203]]]</t>
@@ -2426,10 +2426,10 @@
     <t>[141, 45256, 49282, 2050, 5609, 797, 921, 91203]</t>
   </si>
   <si>
-    <t>[[141], [11314, 11314, 11314, 11314], [12321, 12321, 12320, 12320], [1025, 1025], [937, 2803, 1869], [399, 398], [231, 230, 230, 230], [1, 91202]]</t>
-  </si>
-  <si>
-    <t>h2112_ws16_infp16_outfp16_fetch_7_ID320</t>
+    <t>[135, 41325, 44441, 86, 415, 126, 388, 15867]</t>
+  </si>
+  <si>
+    <t>h2112_ws16_infp16_outfp16_ID320</t>
   </si>
   <si>
     <t>[[8192, 2112], [[2458], [6279], [378], [624], [33368], [25466], [8860], [82544], [9147], [8764], [98317], [307], [6979], [1688], [520], [4096]]]</t>
@@ -2444,10 +2444,10 @@
     <t>[2458, 6279, 378, 624, 33368, 25466, 8860, 82544, 9147, 8764, 98317, 307, 6979, 1688, 520, 4096]</t>
   </si>
   <si>
-    <t>[[2458], [1, 1, 1, 1, 6275], [63, 189, 126], [624], [33368], [761, 24705], [1, -3786, 3793, 3161, 2529, 1897, 1265], [1, 1, 1, 82541], [1, -1522, 3810, 3048, 2286, 1524], [1, -3757, 3756, 3130, 2504, 1878, 1252], [1, 9834, 39325, 29494, 19663], [154, 153], [6979], [1688], [520], [1, 4095]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp32_fetch_4_ID321</t>
+    <t>[2035, 5670, 8, 566, 33316, 23747, 694, 80761, 8498, 8243, 89626, 6, 18, 1563, 82, 4076]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp32_ID321</t>
   </si>
   <si>
     <t>[[292585, 256], [[3057], [8242], [5030], [79814]]]</t>
@@ -2462,10 +2462,10 @@
     <t>[3057, 8242, 5030, 79814]</t>
   </si>
   <si>
-    <t>[[510, 1528, 1019], [1, 1, 1, 8239], [2515, 2515], [39907, 39907]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_inbf16_outbf16_fetch_4_ID322</t>
+    <t>[1818, 7194, 206, 77441]</t>
+  </si>
+  <si>
+    <t>h64_ws2_inbf16_outbf16_ID322</t>
   </si>
   <si>
     <t>[[16384, 64], [[77517], [342]]]</t>
@@ -2477,10 +2477,10 @@
     <t>[77517, 342]</t>
   </si>
   <si>
-    <t>[[19379, 29068, 29069, 1], [190, 152]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp16_outfp32_fetch_5_ID323</t>
+    <t>[76330, 22]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp16_outfp32_ID323</t>
   </si>
   <si>
     <t>[[131072, 256], [[17314], [415], [781], [39113], [1024], [7868], [8982], [42], [33755], [525], [17471], [122], [681], [7656], [867], [94345]]]</t>
@@ -2492,10 +2492,10 @@
     <t>[17314, 415, 781, 39113, 1024, 7868, 8982, 42, 33755, 525, 17471, 122, 681, 7656, 867, 94345]</t>
   </si>
   <si>
-    <t>[[17314], [139, 138, 138], [128, 98, 175, 380], [13037, 19555, 6521], [1024], [3934, 3934], [1975, 493, 1892, 1172, 3450], [8, 34], [1, 33754], [525], [17471], [122], [307, 374], [1532, 1531, 1531, 1531, 1531], [1, 326, 324, 216], [47172, 47173]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp16_fetch_8_ID324</t>
+    <t>[16487, 3, 772, 37617, 17, 3479, 8379, 16, 17283, 24, 7678, 4, 53, 142, 854, 86082]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp16_ID324</t>
   </si>
   <si>
     <t>[[32768, 256], [[8716], [535], [14730], [74]]]</t>
@@ -2507,10 +2507,10 @@
     <t>[8716, 535, 14730, 74]</t>
   </si>
   <si>
-    <t>[[1, -5979, 3809, 3265, 2721, 2177, 1633, 1089], [133, 199, 202, 1], [14730], [74]]</t>
-  </si>
-  <si>
-    <t>h2388_ws4_inbf16_outfp16_fetch_3_ID325</t>
+    <t>[8300, 534, 1328, 5]</t>
+  </si>
+  <si>
+    <t>h2388_ws4_inbf16_outfp16_ID325</t>
   </si>
   <si>
     <t>[[505285, 2388], [[3058], [2215], [349], [2970]]]</t>
@@ -2528,10 +2528,10 @@
     <t>[3058, 2215, 349, 2970]</t>
   </si>
   <si>
-    <t>[[2436, 1, 621], [1, 2214], [120, 229], [2970]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp32_outbf16_fetch_5_ID326</t>
+    <t>[769, 64, 343, 453]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp32_outbf16_ID326</t>
   </si>
   <si>
     <t>[[524288, 256], [[416], [69], [2595], [31399], [3768], [168], [2826], [10089], [5658], [8893], [576], [39221], [34757], [46392], [8981], [4564]]]</t>
@@ -2543,10 +2543,10 @@
     <t>[416, 69, 2595, 31399, 3768, 168, 2826, 10089, 5658, 8893, 576, 39221, 34757, 46392, 8981, 4564]</t>
   </si>
   <si>
-    <t>[[104, 104, 104, 104], [69], [2595], [3422, 7710, 20267], [1738, 518, 1512], [168], [760, 2066], [10089], [5658], [781, 3663, 1920, 2529], [544, 1, 1, 1, 29], [6539, 19609, 13073], [5795, 17377, 11585], [46392], [2245, 3367, 3368, 1], [2279, 2285]]</t>
-  </si>
-  <si>
-    <t>h2617_ws4_infp16_outbf16_fetch_4_ID327</t>
+    <t>[380, 37, 2289, 30954, 3476, 30, 254, 6076, 5182, 3933, 13, 37764, 31913, 45568, 4764, 4187]</t>
+  </si>
+  <si>
+    <t>h2617_ws4_infp16_outbf16_ID327</t>
   </si>
   <si>
     <t>[[4096, 2617], [[83908], [3082], [910], [4356]]]</t>
@@ -2561,10 +2561,10 @@
     <t>[83908, 3082, 910, 4356]</t>
   </si>
   <si>
-    <t>[[34424, 10647, 3990, 34847], [3082], [304, 303, 303], [2178, 2178]]</t>
-  </si>
-  <si>
-    <t>h4017_ws8_inbf16_outfp32_fetch_4_ID328</t>
+    <t>[10647, 499, 390, 5]</t>
+  </si>
+  <si>
+    <t>h4017_ws8_inbf16_outfp32_ID328</t>
   </si>
   <si>
     <t>[[131898, 4017], [[31489], [2303], [38833], [35985], [453], [45223], [66764], [27860]]]</t>
@@ -2582,10 +2582,10 @@
     <t>[31489, 2303, 38833, 35985, 453, 45223, 66764, 27860]</t>
   </si>
   <si>
-    <t>[[31489], [1151, 1152], [9971, 28862], [27564, 8421], [1, 170, 169, 113], [7538, 22611, 15074], [22254, 33381, 11129], [13930, 13930]]</t>
-  </si>
-  <si>
-    <t>h3132_ws16_infp16_outbf16_fetch_7_ID329</t>
+    <t>[3684, 119, 19942, 33396, 57, 43492, 62777, 1029]</t>
+  </si>
+  <si>
+    <t>h3132_ws16_infp16_outbf16_ID329</t>
   </si>
   <si>
     <t>[[524288, 3132], [[30238], [4636], [4335], [54576], [9585], [2565], [4109], [8297], [2544], [4308], [3136], [26240], [461], [457], [9783], [81798]]]</t>
@@ -2597,10 +2597,10 @@
     <t>[30238, 4636, 4335, 54576, 9585, 2565, 4109, 8297, 2544, 4308, 3136, 26240, 461, 457, 9783, 81798]</t>
   </si>
   <si>
-    <t>[[15119, 15119], [1682, 2954], [4335], [18192, 18192, 18192], [1370, 1370, 1369, 1369, 1369, 1369, 1369], [1283, 1282], [1027, 1540, 1541, 1], [8297], [1272, 1272], [2685, 1623], [3136], [26240], [115, 172, 173, 1], [1, 456], [7381, 1, 1, 1, 2399], [27266, 40899, 13633]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_infp16_outfp16_fetch_6_ID330</t>
+    <t>[29202, 868, 662, 51693, 4666, 1326, 2441, 7769, 1388, 798, 2922, 22055, 187, 63, 799, 2233]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_infp16_outfp16_ID330</t>
   </si>
   <si>
     <t>[[788242, 1024], [[4096], [150], [1266], [9404], [4958], [187], [77812], [9229], [83], [666], [507], [24878], [586], [84073], [9333], [86430]]]</t>
@@ -2615,10 +2615,10 @@
     <t>[4096, 150, 1266, 9404, 4958, 187, 77812, 9229, 83, 666, 507, 24878, 586, 84073, 9333, 86430]</t>
   </si>
   <si>
-    <t>[[3040, 1, 1055], [150], [1266], [1955, 3042, 368, 1127, 2912], [42, 1663, 3253], [187], [1, 77811], [1811, 3006, 1309, 914, 667, 1522], [42, 41], [18, 56, 260, 332], [1, 1, 1, 504], [24878], [586], [42037, 42036], [1556, 1556, 1556, 1555, 1555, 1555], [14405, 14405, 14405, 14405, 14405, 14405]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_infp16_outbf16_fetch_8_ID331</t>
+    <t>[127, 133, 1178, 8557, 761, 109, 33791, 165, 75, 617, 88, 2456, 41, 80997, 860, 50223]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_infp16_outbf16_ID331</t>
   </si>
   <si>
     <t>[[131072, 2048], [[31044], [66248], [91411], [587], [6507], [7821], [78317], [37470], [79], [9616], [31653], [45473], [93533], [3363], [3762], [696]]]</t>
@@ -2630,10 +2630,10 @@
     <t>[31044, 66248, 91411, 587, 6507, 7821, 78317, 37470, 79, 9616, 31653, 45473, 93533, 3363, 3762, 696]</t>
   </si>
   <si>
-    <t>[[7949, 6212, 16883], [23395, 42853], [23310, 27656, 9154, 13795, 1189, 4189, 979, 11139], [62, 525], [1626, 2439, 2441, 1], [1409, 6412], [25722, 52595], [12490, 12490, 12490], [40, 39], [9616], [1, 31652], [1, 45472], [13361, 20041, 26721, 33401, 40081, -40073, 1], [1914, 1, 1448], [2925, 837], [153, 92, 68, 81, 302]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outfp32_fetch_1_ID332</t>
+    <t>[17325, 62728, 15908, 365, 6142, 4809, 39703, 20898, 7, 163, 11265, 6431, 46352, 3042, 3597, 42]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outfp32_ID332</t>
   </si>
   <si>
     <t>[[111314, 256], [[9660], [37460]]]</t>
@@ -2648,10 +2648,10 @@
     <t>[9660, 37460]</t>
   </si>
   <si>
-    <t>[[9660], [37460]]</t>
-  </si>
-  <si>
-    <t>h3123_ws16_infp32_outfp32_fetch_6_ID333</t>
+    <t>[5556, 34476]</t>
+  </si>
+  <si>
+    <t>h3123_ws16_infp32_outfp32_ID333</t>
   </si>
   <si>
     <t>[[8192, 3123], [[6785], [7625], [650], [7876], [6411], [4914], [56061], [5235], [41543], [5173], [25196], [5489], [32], [2745], [256], [13400]]]</t>
@@ -2666,10 +2666,10 @@
     <t>[6785, 7625, 650, 7876, 6411, 4914, 56061, 5235, 41543, 5173, 25196, 5489, 32, 2745, 256, 13400]</t>
   </si>
   <si>
-    <t>[[1696, 2544, 2544, 1], [1271, 1271, 1271, 1271, 1271, 1270], [325, 325], [1312, 1968, 2624, 3280, -1309, 1], [302, 2165, 1905, 565, 144, 1330], [1, 1843, 1842, 1228], [28030, 28031], [873, 2617, 1745], [10386, 10386, 10386, 10385], [5173], [7442, 17754], [5489], [32], [858, 1887], [256], [13400]]</t>
-  </si>
-  <si>
-    <t>h4798_ws4_infp16_outbf16_fetch_8_ID334</t>
+    <t>[6472, 3557, 618, 603, 4520, 4686, 5450, 5106, 17792, 5100, 14883, 2431, 31, 1469, 137, 1475]</t>
+  </si>
+  <si>
+    <t>h4798_ws4_infp16_outbf16_ID334</t>
   </si>
   <si>
     <t>[[262144, 4798], [[86356], [35017], [6893], [34488]]]</t>
@@ -2681,10 +2681,10 @@
     <t>[86356, 35017, 6893, 34488]</t>
   </si>
   <si>
-    <t>[[10795, 10795, 10795, 10795, 10794, 10794, 10794, 10794], [35017], [3447, 3446], [1, 34487]]</t>
-  </si>
-  <si>
-    <t>h3358_ws2_inbf16_outbf16_fetch_5_ID335</t>
+    <t>[78912, 20521, 6394, 32445]</t>
+  </si>
+  <si>
+    <t>h3358_ws2_inbf16_outbf16_ID335</t>
   </si>
   <si>
     <t>[[16384, 3358], [[890], [7670]]]</t>
@@ -2696,10 +2696,10 @@
     <t>[890, 7670]</t>
   </si>
   <si>
-    <t>[[38, 70, 146, 310, 326], [7670]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp16_outfp32_fetch_9_ID336</t>
+    <t>[578, 3346]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp16_outfp32_ID336</t>
   </si>
   <si>
     <t>[[205297, 512], [[78], [59423], [3995], [97202], [78], [8010], [542], [5991]]]</t>
@@ -2714,10 +2714,10 @@
     <t>[78, 59423, 3995, 97202, 78, 8010, 542, 5991]</t>
   </si>
   <si>
-    <t>[[26, 26, 26], [1, 1, 59421], [3995], [10801, 10801, 10800, 10800, 10800, 10800, 10800, 10800, 10800], [26, 26, 26], [646, 1821, 2232, 3311], [92, 270, 180], [1424, 277, 41, 763, 3486]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_inbf16_outfp32_fetch_6_ID337</t>
+    <t>[14, 1305, 2306, 43277, 66, 4238, 241, 1292]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_inbf16_outfp32_ID337</t>
   </si>
   <si>
     <t>[[747403, 4096], [[9515], [1199], [6906], [8182], [91], [96203], [46], [131]]]</t>
@@ -2732,10 +2732,10 @@
     <t>[9515, 1199, 6906, 8182, 91, 96203, 46, 131]</t>
   </si>
   <si>
-    <t>[[1358, 3176, 1364, 786, 1301, 1530], [1199], [1, 1, 1, 6903], [1364, 1364, 1364, 1364, 1363, 1363], [46, 45], [45824, 50379], [15, 22, 9], [131]]</t>
-  </si>
-  <si>
-    <t>h4389_ws16_infp32_outbf16_fetch_5_ID338</t>
+    <t>[8738, 74, 5996, 682, 91, 5041, 46, 12]</t>
+  </si>
+  <si>
+    <t>h4389_ws16_infp32_outbf16_ID338</t>
   </si>
   <si>
     <t>[[131072, 4389], [[387], [4272], [49572], [398], [35650], [4161], [206], [80], [2140], [4002], [3684], [1024], [4096], [70161], [36385], [691]]]</t>
@@ -2747,10 +2747,10 @@
     <t>[387, 4272, 49572, 398, 35650, 4161, 206, 80, 2140, 4002, 3684, 1024, 4096, 70161, 36385, 691]</t>
   </si>
   <si>
-    <t>[[129, 193, 65], [712, 2136, 1424], [17511, 4454, 10541, 17066], [32, 70, 296], [35650], [4161], [206], [80], [2140], [1, 1501, 1500, 1000], [869, 752, 2063], [1024], [1, 4095], [35081, 35080], [12128, 18192, 6065], [138, 207, 276, 69, 1]]</t>
-  </si>
-  <si>
-    <t>h2025_ws2_inbf16_outbf16_fetch_2_ID339</t>
+    <t>[18, 4068, 35022, 37, 8072, 7, 193, 9, 394, 1799, 3584, 869, 132, 64558, 1699, 405]</t>
+  </si>
+  <si>
+    <t>h2025_ws2_inbf16_outbf16_ID339</t>
   </si>
   <si>
     <t>[[32768, 2025], [[942], [39482]]]</t>
@@ -2765,10 +2765,10 @@
     <t>[942, 39482]</t>
   </si>
   <si>
-    <t>[[471, 471], [39482]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outfp32_fetch_5_ID340</t>
+    <t>[763, 875]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outfp32_ID340</t>
   </si>
   <si>
     <t>[[56507, 1024], [[2554], [4096], [382], [324], [45887], [3537], [8459], [28045]]]</t>
@@ -2783,10 +2783,10 @@
     <t>[2554, 4096, 382, 324, 45887, 3537, 8459, 28045]</t>
   </si>
   <si>
-    <t>[[349, 2205], [1366, 1365, 1365], [382], [324], [15295, 22942, 7650], [590, 1768, 1179], [1692, 1692, 1692, 1692, 1691], [28045]]</t>
-  </si>
-  <si>
-    <t>h4502_ws4_infp32_outfp16_fetch_5_ID341</t>
+    <t>[221, 1395, 1, 141, 22709, 276, 7875, 12571]</t>
+  </si>
+  <si>
+    <t>h4502_ws4_infp32_outfp16_ID341</t>
   </si>
   <si>
     <t>[[817108, 4502], [[3462], [52326], [27055], [26466]]]</t>
@@ -2804,10 +2804,10 @@
     <t>[3462, 52326, 27055, 26466]</t>
   </si>
   <si>
-    <t>[[1731, 1731], [10465, 15697, 20929, 5234, 1], [13528, 13527], [26466]]</t>
-  </si>
-  <si>
-    <t>h4432_ws16_infp16_outfp32_fetch_6_ID342</t>
+    <t>[3300, 19511, 141, 22659]</t>
+  </si>
+  <si>
+    <t>h4432_ws16_infp16_outfp32_ID342</t>
   </si>
   <si>
     <t>[[347266, 4432], [[697], [173], [2499], [4096], [1616], [45679], [9103], [26], [16410], [62108], [38014], [8238], [11122], [66715], [7141], [4993]]]</t>
@@ -2825,10 +2825,10 @@
     <t>[697, 173, 2499, 4096, 1616, 45679, 9103, 26, 16410, 62108, 38014, 8238, 11122, 66715, 7141, 4993]</t>
   </si>
   <si>
-    <t>[[697], [173], [2499], [4096], [1616], [1693, 43986], [9103], [26], [16410], [39791, 22317], [1, 38013], [1648, 1648, 1648, 1647, 1647], [11122], [11119, 16678, 22237, 27796, -11116, 1], [1190, 1785, 2380, 2975, -1190, 1], [1927, 3066]]</t>
-  </si>
-  <si>
-    <t>h3858_ws2_infp16_outbf16_fetch_3_ID343</t>
+    <t>[371, 111, 2332, 384, 116, 42805, 847, 13, 14891, 1561, 32595, 7574, 6555, 5504, 2950, 924]</t>
+  </si>
+  <si>
+    <t>h3858_ws2_infp16_outbf16_ID343</t>
   </si>
   <si>
     <t>[[381776, 3858], [[878], [512]]]</t>
@@ -2846,10 +2846,10 @@
     <t>[878, 512]</t>
   </si>
   <si>
-    <t>[[292, 438, 148], [424, 88]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_inbf16_outfp16_fetch_7_ID344</t>
+    <t>[45, 471]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_inbf16_outfp16_ID344</t>
   </si>
   <si>
     <t>[[12474, 4096], [[2676], [9593], [94573], [31494]]]</t>
@@ -2864,10 +2864,10 @@
     <t>[2676, 9593, 94573, 31494]</t>
   </si>
   <si>
-    <t>[[1338, 1338], [1, 1, 1, 1, 1, 1, 9587], [94385, 1, 187], [18239, 1, 13254]]</t>
-  </si>
-  <si>
-    <t>h1564_ws2_inbf16_outfp16_fetch_5_ID345</t>
+    <t>[2657, 9542, 4642, 31082]</t>
+  </si>
+  <si>
+    <t>h1564_ws2_inbf16_outfp16_ID345</t>
   </si>
   <si>
     <t>[[262144, 1564], [[10378], [519]]]</t>
@@ -2879,10 +2879,10 @@
     <t>[10378, 519]</t>
   </si>
   <si>
-    <t>[[10378], [112, 183, 43, 14, 167]]</t>
-  </si>
-  <si>
-    <t>h365_ws2_infp16_outfp32_fetch_5_ID346</t>
+    <t>[5976, 224]</t>
+  </si>
+  <si>
+    <t>h365_ws2_infp16_outfp32_ID346</t>
   </si>
   <si>
     <t>[[4096, 365], [[9499], [942]]]</t>
@@ -2894,10 +2894,10 @@
     <t>[9499, 942]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 1, 9495], [942]]</t>
-  </si>
-  <si>
-    <t>h4970_ws2_infp16_outfp16_fetch_8_ID347</t>
+    <t>[718, 18]</t>
+  </si>
+  <si>
+    <t>h4970_ws2_infp16_outfp16_ID347</t>
   </si>
   <si>
     <t>[[931889, 4970], [[8692], [28429]]]</t>
@@ -2915,10 +2915,10 @@
     <t>[8692, 28429]</t>
   </si>
   <si>
-    <t>[[1816, 179, 1745, 959, 1994, 232, 123, 1644], [28429]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_inbf16_outbf16_fetch_5_ID348</t>
+    <t>[8565, 7263]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_inbf16_outbf16_ID348</t>
   </si>
   <si>
     <t>[[262144, 1024], [[62004], [8463], [15838], [4087], [50648], [1024], [33549], [666], [2551], [24439], [40483], [65976], [39905], [22595], [3883], [33731]]]</t>
@@ -2930,10 +2930,10 @@
     <t>[62004, 8463, 15838, 4087, 50648, 1024, 33549, 666, 2551, 24439, 40483, 65976, 39905, 22595, 3883, 33731]</t>
   </si>
   <si>
-    <t>[[38505, 1, 1, 23497], [976, 7487], [15838], [1362, 2043, 682], [1, 1, 1, 50645], [1024], [33549], [666], [2551], [24439], [20343, 1, 20139], [13196, 13195, 13195, 13195, 13195], [9141, 30764], [14128, 8467], [3883], [5624, 16864, 11243]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outbf16_fetch_5_ID349</t>
+    <t>[57016, 6962, 1951, 381, 3623, 21, 15056, 4, 38, 17059, 2509, 63971, 20655, 12600, 1143, 31065]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outbf16_ID349</t>
   </si>
   <si>
     <t>[[957022, 1024], [[8014], [7402], [5702], [9556], [51], [26], [9312], [5282]]]</t>
@@ -2948,10 +2948,10 @@
     <t>[8014, 7402, 5702, 9556, 51, 26, 9312, 5282]</t>
   </si>
   <si>
-    <t>[[8014], [1480, 2220, 2960, 741, 1], [1900, 2850, 952], [3132, 796, 2178, 251, 3199], [51], [26], [1377, 2140, 5795], [1321, 1321, 1320, 1320]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp16_outfp32_fetch_4_ID350</t>
+    <t>[3807, 2953, 374, 851, 25, 5, 3966, 4847]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp16_outfp32_ID350</t>
   </si>
   <si>
     <t>[[276457, 128], [[61779], [6130]]]</t>
@@ -2966,10 +2966,10 @@
     <t>[61779, 6130]</t>
   </si>
   <si>
-    <t>[[15445, 15445, 15445, 15444], [649, 5481]]</t>
-  </si>
-  <si>
-    <t>h976_ws8_inbf16_outfp32_fetch_5_ID351</t>
+    <t>[61617, 2921]</t>
+  </si>
+  <si>
+    <t>h976_ws8_inbf16_outfp32_ID351</t>
   </si>
   <si>
     <t>[[16384, 976], [[87727], [5450], [5844], [35480], [8664], [27981], [26568], [99866]]]</t>
@@ -2981,10 +2981,10 @@
     <t>[87727, 5450, 5844, 35480, 8664, 27981, 26568, 99866]</t>
   </si>
   <si>
-    <t>[[29243, 29242, 29242], [5450], [1, 587, 2336, 1752, 1168], [11826, 17739, 5915], [1, 1, 1, 1, 8660], [27981], [13284, 13284], [33288, 49932, 16646]]</t>
-  </si>
-  <si>
-    <t>h3235_ws2_infp32_outfp32_fetch_3_ID352</t>
+    <t>[85272, 265, 1111, 18268, 859, 27590, 22111, 28953]</t>
+  </si>
+  <si>
+    <t>h3235_ws2_infp32_outfp32_ID352</t>
   </si>
   <si>
     <t>[[65536, 3235], [[59392], [27770]]]</t>
@@ -2996,10 +2996,10 @@
     <t>[59392, 27770]</t>
   </si>
   <si>
-    <t>[[9900, 29695, 19797], [27770]]</t>
-  </si>
-  <si>
-    <t>h545_ws2_infp16_outbf16_fetch_2_ID353</t>
+    <t>[3618, 15464]</t>
+  </si>
+  <si>
+    <t>h545_ws2_infp16_outbf16_ID353</t>
   </si>
   <si>
     <t>[[131072, 545], [[486], [15816]]]</t>
@@ -3011,10 +3011,10 @@
     <t>[486, 15816]</t>
   </si>
   <si>
-    <t>[[176, 310], [15816]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_inbf16_outfp16_fetch_8_ID354</t>
+    <t>[88, 15264]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_inbf16_outfp16_ID354</t>
   </si>
   <si>
     <t>[[296464, 4096], [[2419], [19894], [49], [8192], [37921], [5621], [28727], [8860], [695], [95599], [9095], [25799], [41307], [9724], [21044], [10718]]]</t>
@@ -3029,10 +3029,10 @@
     <t>[2419, 19894, 49, 8192, 37921, 5621, 28727, 8860, 695, 95599, 9095, 25799, 41307, 9724, 21044, 10718]</t>
   </si>
   <si>
-    <t>[[2419], [19894], [39, 10], [1859, 168, 6165], [37921], [1, 2108, 2107, 1405], [1, 28726], [8860], [1, 262, 259, 173], [11950, 11950, 11950, 11950, 11950, 11950, 11950, 11949], [4548, 4547], [25799], [41307], [1122, 8602], [21044], [10718]]</t>
-  </si>
-  <si>
-    <t>h4668_ws4_infp16_outbf16_fetch_3_ID355</t>
+    <t>[496, 849, 3, 7977, 36307, 1141, 14869, 4045, 120, 91152, 1638, 11490, 40260, 8826, 12361, 8841]</t>
+  </si>
+  <si>
+    <t>h4668_ws4_infp16_outbf16_ID355</t>
   </si>
   <si>
     <t>[[134489, 4668], [[730], [1832], [722], [2708]]]</t>
@@ -3050,10 +3050,10 @@
     <t>[730, 1832, 722, 2708]</t>
   </si>
   <si>
-    <t>[[424, 1, 305], [1832], [1, 1, 720], [1354, 1354]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp16_outfp16_fetch_6_ID356</t>
+    <t>[19, 280, 288, 102]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp16_outfp16_ID356</t>
   </si>
   <si>
     <t>[[331648, 512], [[40893], [76871], [8324], [7662], [445], [2048], [36618], [7716]]]</t>
@@ -3068,10 +3068,10 @@
     <t>[40893, 76871, 8324, 7662, 445, 2048, 36618, 7716]</t>
   </si>
   <si>
-    <t>[[20447, 20446], [15374, 23061, 30748, 7687, 1], [1, 8323], [2554, 2554, 2554], [240, 1, 204], [1024, 1024], [36618], [1286, 1286, 1286, 1286, 1286, 1286]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outbf16_fetch_5_ID357</t>
+    <t>[8, 40978, 1902, 666, 245, 53, 2226, 3765]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outbf16_ID357</t>
   </si>
   <si>
     <t>[[32768, 1024], [[816], [347], [9820], [36588], [20435], [32731], [8927], [29098]]]</t>
@@ -3080,10 +3080,10 @@
     <t>[816, 347, 9820, 36588, 20435, 32731, 8927, 29098]</t>
   </si>
   <si>
-    <t>[[1, 83, 325, 244, 163], [1, 346], [2455, 3682, 3682, 1], [36588], [4460, 15975], [32731], [8927], [17525, 11573]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_inbf16_outfp32_fetch_6_ID358</t>
+    <t>[436, 321, 1882, 33114, 8919, 30105, 8255, 1489]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_inbf16_outfp32_ID358</t>
   </si>
   <si>
     <t>[[65536, 4096], [[25705], [6099], [51071], [248], [13414], [8294], [3682], [3272]]]</t>
@@ -3092,10 +3092,10 @@
     <t>[25705, 6099, 51071, 248, 13414, 8294, 3682, 3272]</t>
   </si>
   <si>
-    <t>[[25705], [237, 1411, 967, 3484], [10214, 15321, 20428, 5107, 1], [1, 247], [13414], [1, -1381, 3455, 2764, 2073, 1382], [1841, 1841], [3272]]</t>
-  </si>
-  <si>
-    <t>h2591_ws8_inbf16_outbf16_fetch_4_ID359</t>
+    <t>[10992, 6055, 26069, 166, 1753, 1220, 378, 3127]</t>
+  </si>
+  <si>
+    <t>h2591_ws8_inbf16_outbf16_ID359</t>
   </si>
   <si>
     <t>[[475916, 2591], [[617], [9031], [69359], [11502], [2635], [52178], [8192], [54017]]]</t>
@@ -3113,10 +3113,10 @@
     <t>[617, 9031, 69359, 11502, 2635, 52178, 8192, 54017]</t>
   </si>
   <si>
-    <t>[[365, 1, 1, 250], [4516, 4515], [11562, 34678, 23119], [11502], [1, 2634], [14952, 7389, 486, 29351], [1367, 4095, 2730], [27008, 27009]]</t>
-  </si>
-  <si>
-    <t>h128_ws8_infp16_outbf16_fetch_8_ID360</t>
+    <t>[570, 3840, 34649, 975, 115, 1434, 7994, 50462]</t>
+  </si>
+  <si>
+    <t>h128_ws8_infp16_outbf16_ID360</t>
   </si>
   <si>
     <t>[[452745, 128], [[70088], [2396], [8192], [290], [942], [2949], [31359], [9865]]]</t>
@@ -3131,10 +3131,10 @@
     <t>[70088, 2396, 8192, 290, 942, 2949, 31359, 9865]</t>
   </si>
   <si>
-    <t>[[50337, 1, 1, 1, 1, 1, 19746], [1198, 1198], [8192], [290], [314, 471, 157], [1475, 1474], [29229, 1, 2129], [1233, 1849, 2465, 3081, 3697, 4313, -6774, 1]]</t>
-  </si>
-  <si>
-    <t>h128_ws16_infp16_outbf16_fetch_6_ID361</t>
+    <t>[59893, 18, 4691, 33, 40, 182, 31236, 9585]</t>
+  </si>
+  <si>
+    <t>h128_ws16_infp16_outbf16_ID361</t>
   </si>
   <si>
     <t>[[325169, 128], [[58542], [36126], [1317], [98026], [90500], [729], [2048], [6055], [8657], [2112], [1779], [22025], [2048], [5947], [42646], [4525]]]</t>
@@ -3149,10 +3149,10 @@
     <t>[58542, 36126, 1317, 98026, 90500, 729, 2048, 6055, 8657, 2112, 1779, 22025, 2048, 5947, 42646, 4525]</t>
   </si>
   <si>
-    <t>[[58542], [18063, 18063], [1317], [30523, 67503], [15083, 22624, 30165, 37706, -15079, 1], [364, 365], [2048], [1, 2272, 2269, 1513], [1442, 2163, 2884, 3605, -1438, 1], [2112], [1779], [22025], [1024, 1024], [5947], [42646], [2208, 24, 2293]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_inbf16_outfp16_fetch_3_ID362</t>
+    <t>[27619, 1867, 111, 56373, 87393, 22, 141, 788, 8454, 1985, 40, 538, 1882, 4912, 42159, 2116]</t>
+  </si>
+  <si>
+    <t>h512_ws8_inbf16_outfp16_ID362</t>
   </si>
   <si>
     <t>[[524288, 512], [[44377], [6972], [83205], [49812], [6107], [5270], [4804], [4653]]]</t>
@@ -3164,10 +3164,10 @@
     <t>[44377, 6972, 83205, 49812, 6107, 5270, 4804, 4653]</t>
   </si>
   <si>
-    <t>[[44377], [3777, 3195], [83205], [24906, 24906], [6107], [465, 1083, 3722], [802, 2401, 1601], [4653]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp32_outbf16_fetch_4_ID363</t>
+    <t>[21527, 5722, 81536, 28712, 1525, 2139, 594, 2598]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp32_outbf16_ID363</t>
   </si>
   <si>
     <t>[[833489, 64], [[12338], [5891], [640], [77005]]]</t>
@@ -3182,10 +3182,10 @@
     <t>[12338, 5891, 640, 77005]</t>
   </si>
   <si>
-    <t>[[12338], [1472, 2208, 2210, 1], [640], [1, 28877, 28876, 19251]]</t>
-  </si>
-  <si>
-    <t>h224_ws16_infp32_outbf16_fetch_7_ID364</t>
+    <t>[1539, 52, 618, 38440]</t>
+  </si>
+  <si>
+    <t>h224_ws16_infp32_outbf16_ID364</t>
   </si>
   <si>
     <t>[[8192, 224], [[16027], [1131], [61752], [3524], [4147], [95068], [13026], [27589], [248], [37], [9730], [8309], [60470], [149], [30168], [8083]]]</t>
@@ -3197,10 +3197,10 @@
     <t>[16027, 1131, 61752, 3524, 4147, 95068, 13026, 27589, 248, 37, 9730, 8309, 60470, 149, 30168, 8083]</t>
   </si>
   <si>
-    <t>[[16027], [1131], [10292, 30876, 20584], [1762, 1762], [1, 1556, 1554, 1036], [31690, 31689, 31689], [13026], [13795, 13794], [218, 30], [2, 35], [1390, 2085, 2780, 3475, 4170, -4171, 1], [2770, 2770, 2769], [60470], [149], [20094, 10074], [8083]]</t>
-  </si>
-  <si>
-    <t>h3398_ws8_infp16_outbf16_fetch_6_ID365</t>
+    <t>[15072, 103, 58233, 296, 4054, 88294, 5555, 26385, 244, 34, 8309, 1011, 59887, 9, 24654, 7763]</t>
+  </si>
+  <si>
+    <t>h3398_ws8_infp16_outbf16_ID365</t>
   </si>
   <si>
     <t>[[262144, 3398], [[19740], [4169], [7346], [21713], [22], [66], [68711], [441]]]</t>
@@ -3215,10 +3215,10 @@
     <t>[19740, 4169, 7346, 21713, 22, 66, 68711, 441]</t>
   </si>
   <si>
-    <t>[[19740], [1042, 1563, 1563, 1], [3244, 1969, 496, 133, 574, 930], [21713], [1, 21], [1, 1, 64], [13742, 20613, 27484, 6871, 1], [111, 110, 110, 110]]</t>
-  </si>
-  <si>
-    <t>h2593_ws2_inbf16_outbf16_fetch_5_ID366</t>
+    <t>[18284, 3907, 6488, 20532, 1, 62, 24014, 240]</t>
+  </si>
+  <si>
+    <t>h2593_ws2_inbf16_outbf16_ID366</t>
   </si>
   <si>
     <t>[[131072, 2593], [[840], [19561]]]</t>
@@ -3230,10 +3230,10 @@
     <t>[840, 19561]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 1, 836], [19561]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_infp32_outfp32_fetch_2_ID367</t>
+    <t>[244, 13736]</t>
+  </si>
+  <si>
+    <t>h128_ws4_infp32_outfp32_ID367</t>
   </si>
   <si>
     <t>[[131072, 128], [[77], [41988], [54], [256]]]</t>
@@ -3245,10 +3245,10 @@
     <t>[77, 41988, 54, 256]</t>
   </si>
   <si>
-    <t>[[7, 70], [41988], [27, 27], [256]]</t>
-  </si>
-  <si>
-    <t>h64_ws16_infp32_outbf16_fetch_5_ID368</t>
+    <t>[70, 22541, 51, 37]</t>
+  </si>
+  <si>
+    <t>h64_ws16_infp32_outbf16_ID368</t>
   </si>
   <si>
     <t>[[16384, 64], [[88127], [304], [56738], [5564], [996], [7279], [202], [37620], [9691], [41592], [40], [58910], [306], [8757], [5251], [53356]]]</t>
@@ -3257,10 +3257,10 @@
     <t>[88127, 304, 56738, 5564, 996, 7279, 202, 37620, 9691, 41592, 40, 58910, 306, 8757, 5251, 53356]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 88124], [304], [14874, 13293, 4247, 1129, 23195], [2782, 2782], [1, 1, 994], [7279], [202], [37620], [4846, 4845], [5823, 15467, 20302], [40], [9820, 29454, 19636], [83, 223], [1, 8756], [1851, 1607, 303, 583, 907], [53356]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_infp32_outfp32_fetch_3_ID369</t>
+    <t>[78503, 35, 38199, 5422, 9, 6445, 2, 33530, 55, 1024, 36, 55177, 91, 8693, 2792, 50257]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_infp32_outfp32_ID369</t>
   </si>
   <si>
     <t>[[405118, 2048], [[30427], [65668], [10940], [9583]]]</t>
@@ -3275,10 +3275,10 @@
     <t>[30427, 65668, 10940, 9583]</t>
   </si>
   <si>
-    <t>[[10142, 15213, 5072], [21890, 21889, 21889], [10940], [9583]]</t>
-  </si>
-  <si>
-    <t>h4606_ws2_inbf16_outfp32_fetch_5_ID370</t>
+    <t>[22802, 2439, 5520, 8634]</t>
+  </si>
+  <si>
+    <t>h4606_ws2_inbf16_outfp32_ID370</t>
   </si>
   <si>
     <t>[[702305, 4606], [[950], [68858]]]</t>
@@ -3296,10 +3296,10 @@
     <t>[950, 68858]</t>
   </si>
   <si>
-    <t>[[190, 285, 380, 94, 1], [68858]]</t>
-  </si>
-  <si>
-    <t>h1951_ws16_infp32_outbf16_fetch_6_ID371</t>
+    <t>[266, 33907]</t>
+  </si>
+  <si>
+    <t>h1951_ws16_infp32_outbf16_ID371</t>
   </si>
   <si>
     <t>[[262144, 1951], [[7790], [2577], [1024], [13230], [4511], [35804], [2950], [305], [41721], [48329], [4910], [2251], [25253], [38905], [33848], [810]]]</t>
@@ -3311,10 +3311,10 @@
     <t>[7790, 2577, 1024, 13230, 4511, 35804, 2950, 305, 41721, 48329, 4910, 2251, 25253, 38905, 33848, 810]</t>
   </si>
   <si>
-    <t>[[1, -1297, 3245, 2596, 1947, 1298], [242, 2335], [1024], [13230], [1504, 1504, 1503], [21007, 1, 14796], [2950], [101, 151, 53], [41721], [48329], [605, 4305], [1125, 1126], [17596, 7657], [35778, 1, 3126], [33848], [405, 405]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp16_outfp32_fetch_4_ID372</t>
+    <t>[7351, 484, 937, 747, 33, 15718, 1642, 132, 22360, 28023, 2666, 701, 4837, 3074, 2463, 26]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp16_outfp32_ID372</t>
   </si>
   <si>
     <t>[[65536, 4096], [[959], [25880], [313], [40394]]]</t>
@@ -3323,10 +3323,10 @@
     <t>[959, 25880, 313, 40394]</t>
   </si>
   <si>
-    <t>[[959], [8294, 17586], [66, 247], [10098, 15147, 15148, 1]]</t>
-  </si>
-  <si>
-    <t>h2124_ws2_infp16_outfp32_fetch_1_ID373</t>
+    <t>[557, 2437, 26, 33175]</t>
+  </si>
+  <si>
+    <t>h2124_ws2_infp16_outfp32_ID373</t>
   </si>
   <si>
     <t>[[877922, 2124], [[94], [17809]]]</t>
@@ -3344,10 +3344,10 @@
     <t>[94, 17809]</t>
   </si>
   <si>
-    <t>[[94], [17809]]</t>
-  </si>
-  <si>
-    <t>h4391_ws4_infp16_outfp16_fetch_2_ID374</t>
+    <t>[42, 16733]</t>
+  </si>
+  <si>
+    <t>h4391_ws4_infp16_outfp16_ID374</t>
   </si>
   <si>
     <t>[[135682, 4391], [[9283], [18600], [848], [43333]]]</t>
@@ -3365,10 +3365,10 @@
     <t>[9283, 18600, 848, 43333]</t>
   </si>
   <si>
-    <t>[[9283], [18600], [424, 424], [43333]]</t>
-  </si>
-  <si>
-    <t>h128_ws16_infp16_outfp32_fetch_5_ID375</t>
+    <t>[5017, 17955, 50, 1683]</t>
+  </si>
+  <si>
+    <t>h128_ws16_infp16_outfp32_ID375</t>
   </si>
   <si>
     <t>[[227942, 128], [[5087], [21704], [27401], [420], [4096], [38165], [3830], [36241], [10], [5898], [2359], [4627], [174], [9705], [262], [7847]]]</t>
@@ -3383,10 +3383,10 @@
     <t>[5087, 21704, 27401, 420, 4096, 38165, 3830, 36241, 10, 5898, 2359, 4627, 174, 9705, 262, 7847]</t>
   </si>
   <si>
-    <t>[[5087], [21704], [13700, 13701], [105, 157, 157, 1], [4096], [19083, 19082], [3830], [36241], [10], [1180, 1180, 1180, 1179, 1179], [1334, 1025], [4627], [174], [8669, 1, 1, 1, 1033], [131, 131], [1, 7846]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_inbf16_outfp16_fetch_2_ID376</t>
+    <t>[2458, 12335, 2241, 395, 1744, 1736, 1630, 16524, 3, 295, 1340, 3778, 77, 1988, 147, 240]</t>
+  </si>
+  <si>
+    <t>h128_ws4_inbf16_outfp16_ID376</t>
   </si>
   <si>
     <t>[[658431, 128], [[36549], [3659], [16624], [3975]]]</t>
@@ -3401,10 +3401,10 @@
     <t>[36549, 3659, 16624, 3975]</t>
   </si>
   <si>
-    <t>[[18275, 18274], [1830, 1829], [16624], [2513, 1462]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_inbf16_outfp32_fetch_2_ID377</t>
+    <t>[34768, 248, 666, 3962]</t>
+  </si>
+  <si>
+    <t>h64_ws2_inbf16_outfp32_ID377</t>
   </si>
   <si>
     <t>[[695209, 64], [[2546], [25949]]]</t>
@@ -3419,10 +3419,10 @@
     <t>[2546, 25949]</t>
   </si>
   <si>
-    <t>[[2546], [12975, 12974]]</t>
-  </si>
-  <si>
-    <t>h2170_ws4_inbf16_outfp32_fetch_8_ID378</t>
+    <t>[246, 14430]</t>
+  </si>
+  <si>
+    <t>h2170_ws4_inbf16_outfp32_ID378</t>
   </si>
   <si>
     <t>[[880513, 2170], [[100], [8431], [838], [1422]]]</t>
@@ -3440,10 +3440,10 @@
     <t>[100, 8431, 838, 1422]</t>
   </si>
   <si>
-    <t>[[100], [1, -5778, 3683, 3157, 2631, 2105, 1579, 1053], [1, 837], [1422]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_infp32_outbf16_fetch_7_ID379</t>
+    <t>[45, 7990, 688, 75]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_infp32_outbf16_ID379</t>
   </si>
   <si>
     <t>[[230811, 4096], [[78], [6390], [30549], [47388], [8192], [91211], [256], [9955], [396], [1024], [6799], [8192], [17635], [7109], [4996], [699]]]</t>
@@ -3458,10 +3458,10 @@
     <t>[78, 6390, 30549, 47388, 8192, 91211, 256, 9955, 396, 1024, 6799, 8192, 17635, 7109, 4996, 699]</t>
   </si>
   <si>
-    <t>[[26, 39, 13], [3195, 3195], [28534, 1, 2014], [23694, 23694], [8192], [13031, 13030, 13030, 13030, 13030, 13030, 13030], [208, 48], [4977, 4978], [66, 198, 132], [1024], [1, 1, 1, 1, 6795], [8192], [17635], [4107, 1, 3001], [1666, 1665, 1665], [1, 1, 1, 696]]</t>
-  </si>
-  <si>
-    <t>h64_ws8_infp32_outfp16_fetch_9_ID380</t>
+    <t>[4, 6360, 29613, 8333, 3483, 82652, 236, 688, 6, 93, 6712, 1097, 17144, 1342, 2008, 616]</t>
+  </si>
+  <si>
+    <t>h64_ws8_infp32_outfp16_ID380</t>
   </si>
   <si>
     <t>[[32768, 64], [[71622], [36671], [8170], [4316], [27224], [93774], [27235], [3519]]]</t>
@@ -3470,10 +3470,10 @@
     <t>[71622, 36671, 8170, 4316, 27224, 93774, 27235, 3519]</t>
   </si>
   <si>
-    <t>[[30766, 2452, 5641, 12508, 4051, 16204], [18335, 18336], [5516, 1, 2653], [1104, 767, 501, 1944], [13612, 13612], [10419, 15628, 20837, 26046, 31255, 36464, 41673, -88549, 1], [27235], [1760, 1759]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_infp32_outfp32_fetch_7_ID381</t>
+    <t>[61532, 16077, 540, 3695, 1649, 35306, 1002, 3197]</t>
+  </si>
+  <si>
+    <t>h512_ws16_infp32_outfp32_ID381</t>
   </si>
   <si>
     <t>[[505526, 512], [[1453], [2733], [4490], [90590], [5405], [35457], [40504], [1314], [63], [48824], [50728], [38502], [36282], [9945], [1815], [4137]]]</t>
@@ -3488,10 +3488,10 @@
     <t>[1453, 2733, 4490, 90590, 5405, 35457, 40504, 1314, 63, 48824, 50728, 38502, 36282, 9945, 1815, 4137]</t>
   </si>
   <si>
-    <t>[[1453], [1592, 1141], [1497, 1497, 1496], [90590], [5405], [35457], [1, 40503], [1314], [63], [48824], [12682, 19023, 19022, 1], [5135, 1004, 32363], [2362, 7724, 26196], [5504, 1, 1, 1, 1, 1, 4436], [1815], [4137]]</t>
-  </si>
-  <si>
-    <t>h1024_ws2_infp16_outfp16_fetch_6_ID382</t>
+    <t>[188, 1754, 4350, 46895, 2274, 264, 1016, 1233, 7, 11348, 758, 36191, 2929, 2568, 996, 591]</t>
+  </si>
+  <si>
+    <t>h1024_ws2_infp16_outfp16_ID382</t>
   </si>
   <si>
     <t>[[524288, 1024], [[241], [9433]]]</t>
@@ -3503,10 +3503,10 @@
     <t>[241, 9433]</t>
   </si>
   <si>
-    <t>[[132, 109], [5103, 1, 1, 1, 1, 4326]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outbf16_fetch_7_ID383</t>
+    <t>[237, 7747]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outbf16_ID383</t>
   </si>
   <si>
     <t>[[352254, 512], [[9703], [4804], [7043], [4288], [256], [27910], [2804], [29760], [49426], [8555], [6476], [1171], [9149], [23573], [882], [5933]]]</t>
@@ -3521,10 +3521,10 @@
     <t>[9703, 4804, 7043, 4288, 256, 27910, 2804, 29760, 49426, 8555, 6476, 1171, 9149, 23573, 882, 5933]</t>
   </si>
   <si>
-    <t>[[4851, 4852], [1602, 1601, 1601], [975, 376, 2638, 1465, 237, 393, 959], [1072, 1608, 1607, 1], [1, 255], [13955, 13955], [2804], [19331, 10429], [16476, 16475, 16475], [4277, 4278], [1080, 1080, 1079, 1079, 1079, 1079], [1171], [1902, 1432, 2525, 1298, 751, 485, 756], [23573], [294, 441, 147], [1827, 1600, 1036, 568, 902]]</t>
-  </si>
-  <si>
-    <t>h2262_ws8_infp32_outfp32_fetch_5_ID384</t>
+    <t>[5720, 358, 12, 1950, 143, 25149, 2601, 11674, 30035, 90, 6233, 1005, 69, 2312, 83, 3399]</t>
+  </si>
+  <si>
+    <t>h2262_ws8_infp32_outfp32_ID384</t>
   </si>
   <si>
     <t>[[881943, 2262], [[35145], [78], [11628], [1024], [5042], [671], [5650], [503]]]</t>
@@ -3542,10 +3542,10 @@
     <t>[35145, 78, 11628, 1024, 5042, 671, 5650, 503]</t>
   </si>
   <si>
-    <t>[[17573, 17572], [13, 39, 26], [11628], [1024], [1260, 1890, 1891, 1], [134, 201, 268, 67, 1], [2880, 2770], [126, 126, 126, 125]]</t>
-  </si>
-  <si>
-    <t>h3817_ws8_inbf16_outfp16_fetch_7_ID385</t>
+    <t>[199, 71, 10000, 956, 2451, 632, 3071, 282]</t>
+  </si>
+  <si>
+    <t>h3817_ws8_inbf16_outfp16_ID385</t>
   </si>
   <si>
     <t>[[36869, 3817], [[82586], [6053], [58], [7168], [74465], [3466], [36771], [60390]]]</t>
@@ -3563,10 +3563,10 @@
     <t>[82586, 6053, 58, 7168, 74465, 3466, 36771, 60390]</t>
   </si>
   <si>
-    <t>[[27529, 27529, 27528], [1, 6052], [11, 28, 19], [2390, 2389, 2389], [1, 1, 1, 1, 1, 1, 74459], [1156, 1155, 1155], [36771], [15097, 22645, 22647, 1]]</t>
-  </si>
-  <si>
-    <t>h2075_ws16_infp32_outbf16_fetch_8_ID386</t>
+    <t>[71535, 4867, 54, 3242, 4056, 3366, 3611, 50603]</t>
+  </si>
+  <si>
+    <t>h2075_ws16_infp32_outbf16_ID386</t>
   </si>
   <si>
     <t>[[32768, 2075], [[36375], [7837], [77], [41], [5143], [25622], [29221], [6470], [542], [824], [11577], [18602], [18498], [39198], [8462], [9575]]]</t>
@@ -3578,10 +3578,10 @@
     <t>[36375, 7837, 77, 41, 5143, 25622, 29221, 6470, 542, 824, 11577, 18602, 18498, 39198, 8462, 9575]</t>
   </si>
   <si>
-    <t>[[19837, 1, 16537], [6568, 1, 1268], [77], [41], [1029, 1029, 1029, 1028, 1028], [25622], [29221], [1, 6469], [181, 181, 180], [242, 243, 339], [11577], [18602], [18498], [19599, 19599], [1058, 1058, 1058, 1058, 1058, 1058, 1057, 1057], [3395, 117, 1205, 702, 1615, 699, 1842]]</t>
-  </si>
-  <si>
-    <t>h4375_ws16_infp16_outbf16_fetch_6_ID387</t>
+    <t>[11836, 622, 39, 32, 2305, 2056, 13607, 2927, 317, 822, 85, 1136, 17619, 35614, 83, 4571]</t>
+  </si>
+  <si>
+    <t>h4375_ws16_infp16_outbf16_ID387</t>
   </si>
   <si>
     <t>[[131072, 4375], [[1655], [62065], [22568], [9310], [17177], [24954], [351], [5822], [41], [19457], [4096], [26], [614], [2935], [28], [4052]]]</t>
@@ -3596,10 +3596,10 @@
     <t>[1655, 62065, 22568, 9310, 17177, 24954, 351, 5822, 41, 19457, 4096, 26, 614, 2935, 28, 4052]</t>
   </si>
   <si>
-    <t>[[1655], [10344, 15516, 20688, 25860, -10344, 1], [22568], [1, 1, 1, 1, 9306], [17177], [23882, 1072], [176, 175], [1899, 1230, 789, 1904], [21, 20], [19457], [392, 1559, 2145], [26], [614], [1468, 1467], [28], [134, 970, 704, 2244]]</t>
-  </si>
-  <si>
-    <t>h4041_ws4_inbf16_outfp32_fetch_5_ID388</t>
+    <t>[986, 62006, 190, 9177, 385, 21010, 348, 5406, 9, 18306, 4003, 26, 554, 2916, 2, 2345]</t>
+  </si>
+  <si>
+    <t>h4041_ws4_inbf16_outfp32_ID388</t>
   </si>
   <si>
     <t>[[514334, 4041], [[34170], [3949], [39036], [7021]]]</t>
@@ -3617,10 +3617,10 @@
     <t>[34170, 3949, 39036, 7021]</t>
   </si>
   <si>
-    <t>[[17663, 1, 16506], [3949], [19518, 19518], [1404, 2106, 2808, 702, 1]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_infp32_outfp32_fetch_7_ID389</t>
+    <t>[12452, 3177, 36430, 6870]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_infp32_outfp32_ID389</t>
   </si>
   <si>
     <t>[[932408, 1024], [[33073], [7798], [4988], [7395], [299], [14762], [1837], [32727]]]</t>
@@ -3635,10 +3635,10 @@
     <t>[33073, 7798, 4988, 7395, 299, 14762, 1837, 32727]</t>
   </si>
   <si>
-    <t>[[33073], [3899, 3899], [2494, 2494], [1056, 1584, 2112, 2640, 3168, -3166, 1], [299], [14762], [1837], [16364, 16363]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outfp16_fetch_5_ID390</t>
+    <t>[19653, 7390, 433, 6655, 141, 7979, 1011, 30372]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outfp16_ID390</t>
   </si>
   <si>
     <t>[[524288, 256], [[2452], [85307], [83614], [4555]]]</t>
@@ -3647,10 +3647,10 @@
     <t>[2452, 85307, 83614, 4555]</t>
   </si>
   <si>
-    <t>[[2452], [37480, 47827], [81796, 1, 1, 1, 1815], [1, 1709, 1707, 1138]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp32_outbf16_fetch_4_ID391</t>
+    <t>[1035, 42630, 81401, 4247]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp32_outbf16_ID391</t>
   </si>
   <si>
     <t>[[8192, 1024], [[4966], [19639], [596], [73]]]</t>
@@ -3662,10 +3662,10 @@
     <t>[4966, 19639, 596, 73]</t>
   </si>
   <si>
-    <t>[[2436, 2530], [19639], [149, 223, 223, 1], [73]]</t>
-  </si>
-  <si>
-    <t>h497_ws8_inbf16_outfp16_fetch_4_ID392</t>
+    <t>[609, 1453, 51, 4]</t>
+  </si>
+  <si>
+    <t>h497_ws8_inbf16_outfp16_ID392</t>
   </si>
   <si>
     <t>[[524288, 497], [[39720], [4356], [6220], [2027], [70223], [29806], [3302], [18]]]</t>
@@ -3677,10 +3677,10 @@
     <t>[39720, 4356, 6220, 2027, 70223, 29806, 3302, 18]</t>
   </si>
   <si>
-    <t>[[19860, 19860], [4356], [1, 6219], [1014, 1013], [1, 26335, 26332, 17555], [14903, 14903], [1475, 692, 1135], [18]]</t>
-  </si>
-  <si>
-    <t>h4614_ws4_infp16_outbf16_fetch_5_ID393</t>
+    <t>[3684, 3981, 5762, 398, 4027, 28527, 3226, 8]</t>
+  </si>
+  <si>
+    <t>h4614_ws4_infp16_outbf16_ID393</t>
   </si>
   <si>
     <t>[[131072, 4614], [[3764], [99221], [3242], [349]]]</t>
@@ -3695,10 +3695,10 @@
     <t>[3764, 99221, 3242, 349]</t>
   </si>
   <si>
-    <t>[[1882, 1882], [59985, 1, 1, 1, 39233], [1621, 1621], [175, 174]]</t>
-  </si>
-  <si>
-    <t>h622_ws4_infp16_outfp16_fetch_4_ID394</t>
+    <t>[3564, 2143, 1458, 4]</t>
+  </si>
+  <si>
+    <t>h622_ws4_infp16_outfp16_ID394</t>
   </si>
   <si>
     <t>[[262144, 622], [[512], [4574], [6388], [3954]]]</t>
@@ -3710,10 +3710,10 @@
     <t>[512, 4574, 6388, 3954]</t>
   </si>
   <si>
-    <t>[[450, 1, 1, 60], [1525, 1525, 1524], [6388], [1977, 1977]]</t>
-  </si>
-  <si>
-    <t>h4142_ws16_infp16_outfp32_fetch_9_ID395</t>
+    <t>[471, 4272, 42, 1958]</t>
+  </si>
+  <si>
+    <t>h4142_ws16_infp16_outfp32_ID395</t>
   </si>
   <si>
     <t>[[768340, 4142], [[1344], [93671], [17752], [6954], [77254], [941], [9709], [4612], [20962], [5704], [35430], [9790], [26805], [4448], [3795], [92]]]</t>
@@ -3731,10 +3731,10 @@
     <t>[1344, 93671, 17752, 6954, 77254, 941, 9709, 4612, 20962, 5704, 35430, 9790, 26805, 4448, 3795, 92]</t>
   </si>
   <si>
-    <t>[[1344], [83821, 1, 1, 1, 1, 1, 1, 1, 9843], [17752], [1391, 1391, 1391, 1391, 1390], [1, 1, 1, 77251], [118, 203, 24, 596], [1213, 1819, 2425, 3031, 3637, 4243, -6660, 1], [1538, 1537, 1537], [20962], [357, 2268, 216, 713, 2150], [35430], [9790], [26805], [731, 3717], [1265, 1265, 1265], [82, 1, 9]]</t>
-  </si>
-  <si>
-    <t>h370_ws4_inbf16_outbf16_fetch_6_ID396</t>
+    <t>[666, 81019, 6939, 6857, 73298, 45, 1722, 4508, 3555, 1877, 32078, 9129, 181, 2241, 2264, 53]</t>
+  </si>
+  <si>
+    <t>h370_ws4_inbf16_outbf16_ID396</t>
   </si>
   <si>
     <t>[[485808, 370], [[771], [3345], [2336], [9347]]]</t>
@@ -3752,10 +3752,10 @@
     <t>[771, 3345, 2336, 9347]</t>
   </si>
   <si>
-    <t>[[771], [1, 1, 3343], [1168, 1168], [1, -1550, 3891, 3113, 2335, 1557]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_infp32_outbf16_fetch_6_ID397</t>
+    <t>[433, 259, 2231, 452]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_infp32_outbf16_ID397</t>
   </si>
   <si>
     <t>[[131072, 2048], [[504], [1020], [48365], [25506], [36392], [433], [84369], [4096], [1837], [40201], [33565], [32744], [68], [12822], [46458], [22899]]]</t>
@@ -3767,10 +3767,10 @@
     <t>[504, 1020, 48365, 25506, 36392, 433, 84369, 4096, 1837, 40201, 33565, 32744, 68, 12822, 46458, 22899]</t>
   </si>
   <si>
-    <t>[[504], [1020], [1, 1, 1, 48362], [12753, 12753], [18196, 18196], [217, 216], [14062, 14062, 14062, 14061, 14061, 14061], [4096], [1837], [20101, 20100], [33565], [1, 1, 32742], [34, 34], [12822], [23229, 23229], [22899]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp16_outfp16_fetch_6_ID398</t>
+    <t>[241, 188, 45164, 20798, 32894, 5, 79332, 2428, 852, 4288, 8743, 30397, 39, 2763, 32, 631]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp16_outfp16_ID398</t>
   </si>
   <si>
     <t>[[696323, 1024], [[78040], [8344], [3794], [12637]]]</t>
@@ -3785,10 +3785,10 @@
     <t>[78040, 8344, 3794, 12637]</t>
   </si>
   <si>
-    <t>[[26013, 39019, 13008], [1391, 1391, 1391, 1391, 1390, 1390], [1897, 1897], [12637]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_infp32_outfp32_fetch_3_ID399</t>
+    <t>[2579, 64, 255, 12509]</t>
+  </si>
+  <si>
+    <t>h512_ws4_infp32_outfp32_ID399</t>
   </si>
   <si>
     <t>[[299043, 512], [[88], [39], [797], [157]]]</t>
@@ -3803,10 +3803,10 @@
     <t>[88, 39, 797, 157]</t>
   </si>
   <si>
-    <t>[[1, 1, 86], [2, 37], [399, 398], [157]]</t>
-  </si>
-  <si>
-    <t>h4037_ws16_infp32_outfp16_fetch_7_ID400</t>
+    <t>[32, 39, 365, 152]</t>
+  </si>
+  <si>
+    <t>h4037_ws16_infp32_outfp16_ID400</t>
   </si>
   <si>
     <t>[[524288, 4037], [[5158], [16081], [8510], [7927], [5667], [8054], [8192], [512], [10410], [4749], [4586], [194], [2075], [2234], [47219], [8192]]]</t>
@@ -3821,10 +3821,10 @@
     <t>[5158, 16081, 8510, 7927, 5667, 8054, 8192, 512, 10410, 4749, 4586, 194, 2075, 2234, 47219, 8192]</t>
   </si>
   <si>
-    <t>[[1292, 3866], [16081], [1, -3636, 3643, 3036, 2429, 1822, 1215], [271, 1577, 2623, 1616, 1840], [2428, 3239], [8054], [4564, 1, 1, 1, 1, 3624], [1, 191, 192, 128], [10410], [4749], [1528, 2292, 766], [194], [1038, 1037], [1117, 1117], [3554, 3617, 8672, 31376], [1, 820, 3276, 2457, 1638]]</t>
-  </si>
-  <si>
-    <t>h4593_ws8_infp32_outfp32_fetch_8_ID401</t>
+    <t>[646, 482, 6923, 7773, 541, 7903, 28, 480, 8796, 4491, 3679, 146, 1257, 13, 17100, 7671]</t>
+  </si>
+  <si>
+    <t>h4593_ws8_infp32_outfp32_ID401</t>
   </si>
   <si>
     <t>[[936856, 4593], [[8007], [28355], [35714], [6233], [910], [78749], [831], [14841]]]</t>
@@ -3842,10 +3842,10 @@
     <t>[8007, 28355, 35714, 6233, 910, 78749, 831, 14841]</t>
   </si>
   <si>
-    <t>[[1001, 1001, 1001, 1001, 1001, 1001, 1001, 1000], [28355], [5595, 30119], [1041, 3115, 2077], [227, 340, 342, 1], [11249, 16873, 22497, 28121, 33745, -33737, 1], [167, 166, 166, 166, 166], [14841]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_infp32_outbf16_fetch_4_ID402</t>
+    <t>[7250, 27351, 3992, 5979, 84, 12852, 30, 14436]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_infp32_outbf16_ID402</t>
   </si>
   <si>
     <t>[[16384, 2048], [[16377], [37365], [8464], [7641], [21226], [70], [41298], [280]]]</t>
@@ -3854,10 +3854,10 @@
     <t>[16377, 37365, 8464, 7641, 21226, 70, 41298, 280]</t>
   </si>
   <si>
-    <t>[[16377], [37365], [8464], [1910, 2865, 2865, 1], [21226], [24, 23, 23], [41298], [280]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_inbf16_outfp16_fetch_3_ID403</t>
+    <t>[10636, 19081, 4108, 6953, 10638, 67, 782, 152]</t>
+  </si>
+  <si>
+    <t>h128_ws4_inbf16_outfp16_ID403</t>
   </si>
   <si>
     <t>[[84600, 128], [[6602], [30], [98015], [19808]]]</t>
@@ -3872,10 +3872,10 @@
     <t>[6602, 30, 98015, 19808]</t>
   </si>
   <si>
-    <t>[[1102, 3300, 2200], [30], [16338, 49006, 32671], [19808]]</t>
-  </si>
-  <si>
-    <t>h1301_ws2_infp32_outbf16_fetch_2_ID404</t>
+    <t>[460, 2, 94536, 601]</t>
+  </si>
+  <si>
+    <t>h1301_ws2_infp32_outbf16_ID404</t>
   </si>
   <si>
     <t>[[972122, 1301], [[515], [83934]]]</t>
@@ -3893,10 +3893,10 @@
     <t>[515, 83934]</t>
   </si>
   <si>
-    <t>[[515], [41967, 41967]]</t>
-  </si>
-  <si>
-    <t>h3869_ws8_infp16_outbf16_fetch_3_ID405</t>
+    <t>[224, 42371]</t>
+  </si>
+  <si>
+    <t>h3869_ws8_infp16_outbf16_ID405</t>
   </si>
   <si>
     <t>[[16384, 3869], [[68], [47429], [16502], [48802], [9702], [438], [36031], [9911]]]</t>
@@ -3911,10 +3911,10 @@
     <t>[68, 47429, 16502, 48802, 9702, 438, 36031, 9911]</t>
   </si>
   <si>
-    <t>[[1, 67], [37209, 10220], [16502], [48802], [9702], [146, 219, 73], [18016, 18015], [9911]]</t>
-  </si>
-  <si>
-    <t>h4242_ws2_infp16_outfp16_fetch_4_ID406</t>
+    <t>[64, 15476, 823, 43588, 351, 397, 33661, 316]</t>
+  </si>
+  <si>
+    <t>h4242_ws2_infp16_outfp16_ID406</t>
   </si>
   <si>
     <t>[[153950, 4242], [[7831], [47758]]]</t>
@@ -3932,10 +3932,10 @@
     <t>[7831, 47758]</t>
   </si>
   <si>
-    <t>[[2716, 5115], [1, 17910, 17908, 11939]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp16_outfp32_fetch_2_ID407</t>
+    <t>[975, 46879]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp16_outfp32_ID407</t>
   </si>
   <si>
     <t>[[16384, 64], [[16791], [28785], [6998], [40038]]]</t>
@@ -3944,10 +3944,10 @@
     <t>[16791, 28785, 6998, 40038]</t>
   </si>
   <si>
-    <t>[[16791], [28785], [3499, 3499], [40038]]</t>
-  </si>
-  <si>
-    <t>h128_ws16_inbf16_outfp32_fetch_5_ID408</t>
+    <t>[9567, 26307, 1985, 36060]</t>
+  </si>
+  <si>
+    <t>h128_ws16_inbf16_outfp32_ID408</t>
   </si>
   <si>
     <t>[[785730, 128], [[38863], [4874], [2552], [5146], [4096], [44780], [2759], [27173], [3283], [60117], [281], [594], [326], [30116], [7700], [2379]]]</t>
@@ -3962,10 +3962,10 @@
     <t>[38863, 4874, 2552, 5146, 4096, 44780, 2759, 27173, 3283, 60117, 281, 594, 326, 30116, 7700, 2379]</t>
   </si>
   <si>
-    <t>[[19431, 19432], [4874], [226, 2326], [2370, 396, 2380], [1, 1, 4094], [22390, 22390], [1380, 1379], [4130, 23043], [3283], [12024, 12024, 12023, 12023, 12023], [49, 232], [519, 1, 74], [326], [30116], [1, 1, 7698], [1190, 1189]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_infp32_outfp16_fetch_8_ID409</t>
+    <t>[36100, 2072, 131, 2755, 1582, 1720, 334, 13646, 1033, 29037, 15, 580, 97, 649, 4508, 2170]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_infp32_outfp16_ID409</t>
   </si>
   <si>
     <t>[[118866, 1024], [[45872], [9996], [91562], [995], [8192], [193], [4129], [3421]]]</t>
@@ -3980,10 +3980,10 @@
     <t>[45872, 9996, 91562, 995, 8192, 193, 4129, 3421]</t>
   </si>
   <si>
-    <t>[[45872], [9996], [1, -62939, 40055, 34333, 28611, 22889, 17167, 11445], [1, 100, 397, 298, 199], [1, -1361, 3411, 2729, 2047, 1365], [193], [1376, 2064, 689], [571, 1710, 1140]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp16_outfp32_fetch_4_ID410</t>
+    <t>[26925, 5141, 65362, 961, 7928, 14, 4079, 3225]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp16_outfp32_ID410</t>
   </si>
   <si>
     <t>[[131072, 64], [[418], [52], [407], [40348]]]</t>
@@ -3995,10 +3995,10 @@
     <t>[418, 52, 407, 40348]</t>
   </si>
   <si>
-    <t>[[139, 208, 71], [6, 46], [248, 159], [10087, 10087, 10087, 10087]]</t>
-  </si>
-  <si>
-    <t>h2253_ws4_infp16_outfp16_fetch_3_ID411</t>
+    <t>[23, 52, 86, 38542]</t>
+  </si>
+  <si>
+    <t>h2253_ws4_infp16_outfp16_ID411</t>
   </si>
   <si>
     <t>[[826718, 2253], [[6356], [301], [8790], [4432]]]</t>
@@ -4016,10 +4016,10 @@
     <t>[6356, 301, 8790, 4432]</t>
   </si>
   <si>
-    <t>[[6356], [151, 150], [1465, 4395, 2930], [301, 651, 3480]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_inbf16_outfp32_fetch_6_ID412</t>
+    <t>[2605, 273, 8099, 2310]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_inbf16_outfp32_ID412</t>
   </si>
   <si>
     <t>[[32768, 2048], [[1950], [302], [296], [8679], [2176], [3893], [9368], [5119]]]</t>
@@ -4028,10 +4028,10 @@
     <t>[1950, 302, 296, 8679, 2176, 3893, 9368, 5119]</t>
   </si>
   <si>
-    <t>[[1950], [100, 150, 52], [296], [2894, 1555, 4230], [1088, 1088], [3893], [3449, 2447, 660, 1334, 198, 1280], [1, 516, 2045, 1534, 1023]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_infp16_outfp16_fetch_5_ID413</t>
+    <t>[1762, 5, 270, 5788, 2080, 3585, 761, 4852]</t>
+  </si>
+  <si>
+    <t>h256_ws8_infp16_outfp16_ID413</t>
   </si>
   <si>
     <t>[[65536, 256], [[40674], [662], [29175], [675], [909], [2730], [5120], [6685]]]</t>
@@ -4040,10 +4040,10 @@
     <t>[40674, 662, 29175, 675, 909, 2730, 5120, 6685]</t>
   </si>
   <si>
-    <t>[[1, 15253, 15252, 10168], [662], [29175], [337, 338], [455, 454], [899, 1831], [1707, 1707, 1706], [1, 1, 1, 1, 6681]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_inbf16_outbf16_fetch_2_ID414</t>
+    <t>[38528, 377, 14300, 641, 573, 271, 4905, 3863]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_inbf16_outbf16_ID414</t>
   </si>
   <si>
     <t>[[262144, 4096], [[6710], [49896], [25335], [29234]]]</t>
@@ -4055,10 +4055,10 @@
     <t>[6710, 49896, 25335, 29234]</t>
   </si>
   <si>
-    <t>[[3697, 3013], [24948, 24948], [12667, 12668], [14617, 14617]]</t>
-  </si>
-  <si>
-    <t>h1641_ws2_inbf16_outfp16_fetch_2_ID415</t>
+    <t>[192, 45590, 23242, 1958]</t>
+  </si>
+  <si>
+    <t>h1641_ws2_inbf16_outfp16_ID415</t>
   </si>
   <si>
     <t>[[8192, 1641], [[26164], [22720]]]</t>
@@ -4073,10 +4073,10 @@
     <t>[26164, 22720]</t>
   </si>
   <si>
-    <t>[[5258, 20906], [22720]]</t>
-  </si>
-  <si>
-    <t>h3195_ws4_infp16_outfp16_fetch_8_ID416</t>
+    <t>[24292, 22625]</t>
+  </si>
+  <si>
+    <t>h3195_ws4_infp16_outfp16_ID416</t>
   </si>
   <si>
     <t>[[65536, 3195], [[1127], [5804], [8255], [90764]]]</t>
@@ -4088,10 +4088,10 @@
     <t>[1127, 5804, 8255, 90764]</t>
   </si>
   <si>
-    <t>[[1127], [5804], [1, -5657, 3606, 3091, 2576, 2061, 1546, 1031], [33555, 2510, 25368, 12783, 6324, 389, 9835]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_infp32_outfp32_fetch_7_ID417</t>
+    <t>[614, 5331, 7937, 88066]</t>
+  </si>
+  <si>
+    <t>h128_ws4_infp32_outfp32_ID417</t>
   </si>
   <si>
     <t>[[131072, 128], [[97385], [862], [1750], [8572]]]</t>
@@ -4103,10 +4103,10 @@
     <t>[97385, 862, 1750, 8572]</t>
   </si>
   <si>
-    <t>[[16231, 16231, 16231, 16231, 16231, 16230], [68, 359, 185, 250], [1750], [1, -3669, 3672, 3060, 2448, 1836, 1224]]</t>
-  </si>
-  <si>
-    <t>h1467_ws16_inbf16_outfp32_fetch_5_ID418</t>
+    <t>[1475, 855, 271, 323]</t>
+  </si>
+  <si>
+    <t>h1467_ws16_inbf16_outfp32_ID418</t>
   </si>
   <si>
     <t>[[443402, 1467], [[2851], [5530], [25316], [1690], [431], [48732], [5781], [45595], [418], [576], [54713], [1938], [29], [812], [27469], [25867]]]</t>
@@ -4124,10 +4124,10 @@
     <t>[2851, 5530, 25316, 1690, 431, 48732, 5781, 45595, 418, 576, 54713, 1938, 29, 812, 27469, 25867]</t>
   </si>
   <si>
-    <t>[[2851], [1412, 1495, 848, 1775], [25316], [1690], [400, 1, 1, 29], [24366, 24366], [1156, 1734, 2312, 578, 1], [45595], [140, 139, 139], [288, 288], [54713], [1938], [14, 15], [1, 82, 324, 243, 162], [27469], [25867]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp32_outbf16_fetch_1_ID419</t>
+    <t>[1404, 5329, 1695, 1565, 397, 9046, 1085, 867, 398, 254, 23714, 322, 7, 80, 27338, 702]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp32_outbf16_ID419</t>
   </si>
   <si>
     <t>[[561837, 64], [[18319], [389], [9449], [115]]]</t>
@@ -4142,10 +4142,10 @@
     <t>[18319, 389, 9449, 115]</t>
   </si>
   <si>
-    <t>[[18319], [389], [9449], [115]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_inbf16_outfp16_fetch_8_ID420</t>
+    <t>[16819, 177, 8743, 113]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_inbf16_outfp16_ID420</t>
   </si>
   <si>
     <t>[[509260, 4096], [[56], [2566], [17487], [51], [1302], [18355], [8068], [6506], [3399], [27127], [8888], [26212], [7461], [256], [1150], [43202]]]</t>
@@ -4160,10 +4160,10 @@
     <t>[56, 2566, 17487, 51, 1302, 18355, 8068, 6506, 3399, 27127, 8888, 26212, 7461, 256, 1150, 43202]</t>
   </si>
   <si>
-    <t>[[11, 27, 18], [1283, 1283], [17487], [17, 25, 9], [1302], [18355], [3173, 2146, 1171, 1578], [1511, 962, 1393, 2640], [1632, 1767], [13563, 13564], [1, -6104, 3886, 3331, 2776, 2221, 1666, 1111], [26212], [7223, 1, 1, 1, 1, 1, 233], [17, 239], [1150], [21601, 21601]]</t>
-  </si>
-  <si>
-    <t>h2308_ws8_inbf16_outbf16_fetch_5_ID421</t>
+    <t>[56, 10, 2932, 3, 1156, 17164, 3930, 3021, 272, 26097, 8308, 25629, 4272, 126, 47, 39911]</t>
+  </si>
+  <si>
+    <t>h2308_ws8_inbf16_outbf16_ID421</t>
   </si>
   <si>
     <t>[[771600, 2308], [[26674], [82372], [28328], [8354], [5060], [3039], [1429], [9091]]]</t>
@@ -4181,10 +4181,10 @@
     <t>[26674, 82372, 28328, 8354, 5060, 3039, 1429, 9091]</t>
   </si>
   <si>
-    <t>[[26674], [53647, 1, 28724], [28328], [1, 1, 1, 1, 8350], [2530, 2530], [1816, 1223], [1429], [1, 3410, 3408, 2272]]</t>
-  </si>
-  <si>
-    <t>h2659_ws2_infp16_outfp32_fetch_8_ID422</t>
+    <t>[15236, 72127, 16011, 4414, 209, 1490, 1217, 535]</t>
+  </si>
+  <si>
+    <t>h2659_ws2_infp16_outfp32_ID422</t>
   </si>
   <si>
     <t>[[222094, 2659], [[1101], [9254]]]</t>
@@ -4202,10 +4202,10 @@
     <t>[1101, 9254]</t>
   </si>
   <si>
-    <t>[[1101], [1, -6353, 4046, 3468, 2890, 2312, 1734, 1156]]</t>
-  </si>
-  <si>
-    <t>h4461_ws2_infp16_outfp32_fetch_8_ID423</t>
+    <t>[1085, 8341]</t>
+  </si>
+  <si>
+    <t>h4461_ws2_infp16_outfp32_ID423</t>
   </si>
   <si>
     <t>[[566528, 4461], [[9850], [47404]]]</t>
@@ -4223,10 +4223,10 @@
     <t>[9850, 47404]</t>
   </si>
   <si>
-    <t>[[1, -6762, 4306, 3691, 3076, 2461, 1846, 1231], [47404]]</t>
-  </si>
-  <si>
-    <t>h4899_ws16_infp32_outbf16_fetch_8_ID424</t>
+    <t>[9374, 27707]</t>
+  </si>
+  <si>
+    <t>h4899_ws16_infp32_outbf16_ID424</t>
   </si>
   <si>
     <t>[[524288, 4899], [[3274], [806], [14531], [3583], [33], [44868], [297], [337], [27938], [972], [7230], [40219], [9323], [33235], [37785], [39717]]]</t>
@@ -4238,10 +4238,10 @@
     <t>[3274, 806, 14531, 3583, 33, 44868, 297, 337, 27938, 972, 7230, 40219, 9323, 33235, 37785, 39717]</t>
   </si>
   <si>
-    <t>[[3274], [161, 241, 321, 82, 1], [14531], [1194, 1791, 598], [17, 16], [9168, 35700], [120, 177], [337], [18410, 9528], [1, 98, 388, 291, 194], [3383, 1224, 877, 1746], [40219], [1504, 3015, 1304, 591, 13, 821, 405, 1670], [11078, 16617, 5540], [12595, 12595, 12595], [39717]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_infp32_outfp16_fetch_4_ID425</t>
+    <t>[1811, 269, 8363, 1448, 2, 7858, 240, 329, 24570, 442, 7082, 28060, 2000, 32202, 37019, 37972]</t>
+  </si>
+  <si>
+    <t>h256_ws2_infp32_outfp16_ID425</t>
   </si>
   <si>
     <t>[[32768, 256], [[3815], [4663]]]</t>
@@ -4250,10 +4250,10 @@
     <t>[3815, 4663]</t>
   </si>
   <si>
-    <t>[[1908, 1907], [3946, 1, 1, 715]]</t>
-  </si>
-  <si>
-    <t>h2761_ws8_infp16_outfp32_fetch_6_ID426</t>
+    <t>[2, 4291]</t>
+  </si>
+  <si>
+    <t>h2761_ws8_infp16_outfp32_ID426</t>
   </si>
   <si>
     <t>[[16384, 2761], [[848], [15100], [3024], [9611], [6400], [90330], [35608], [30472]]]</t>
@@ -4265,10 +4265,10 @@
     <t>[848, 15100, 3024, 9611, 6400, 90330, 35608, 30472]</t>
   </si>
   <si>
-    <t>[[848], [15100], [3024], [7420, 1, 1, 1, 1, 2187], [2447, 111, 1591, 27, 205, 2019], [45165, 45165], [17804, 17804], [5080, 15235, 10157]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_inbf16_outfp16_fetch_7_ID427</t>
+    <t>[499, 3563, 1222, 8899, 234, 45254, 2674, 19573]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_inbf16_outfp16_ID427</t>
   </si>
   <si>
     <t>[[303263, 2048], [[935], [6918], [47], [816], [82875], [41657], [2048], [37871], [6529], [10345], [3712], [45660], [60486], [3721], [8299], [2748]]]</t>
@@ -4283,10 +4283,10 @@
     <t>[935, 6918, 47, 816, 82875, 41657, 2048, 37871, 6529, 10345, 3712, 45660, 60486, 3721, 8299, 2748]</t>
   </si>
   <si>
-    <t>[[935], [1619, 2481, 378, 2440], [47], [702, 1, 1, 1, 111], [13813, 13813, 13813, 13812, 13812, 13812], [41657], [1024, 1024], [37871], [1850, 986, 1189, 433, 2071], [10345], [3712], [45660], [30243, 30243], [3721], [1186, 1186, 1186, 1186, 1185, 1185, 1185], [2748]]</t>
-  </si>
-  <si>
-    <t>h2753_ws4_infp16_outfp32_fetch_7_ID428</t>
+    <t>[432, 6916, 26, 189, 43087, 8932, 296, 168, 5351, 791, 3675, 44955, 26127, 3286, 7400, 217]</t>
+  </si>
+  <si>
+    <t>h2753_ws4_infp16_outfp32_ID428</t>
   </si>
   <si>
     <t>[[357147, 2753], [[1846], [2618], [66433], [85596]]]</t>
@@ -4304,10 +4304,10 @@
     <t>[1846, 2618, 66433, 85596]</t>
   </si>
   <si>
-    <t>[[1846], [1309, 1309], [66433], [1, -36685, 36684, 30570, 24456, 18342, 12228]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp32_outfp32_fetch_1_ID429</t>
+    <t>[1045, 2490, 35689, 83664]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp32_outfp32_ID429</t>
   </si>
   <si>
     <t>[[16384, 4096], [[3011], [1024]]]</t>
@@ -4316,10 +4316,10 @@
     <t>[3011, 1024]</t>
   </si>
   <si>
-    <t>[[3011], [1024]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp32_outfp32_fetch_6_ID430</t>
+    <t>[1726, 899]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp32_outfp32_ID430</t>
   </si>
   <si>
     <t>[[242568, 512], [[3254], [37], [6029], [297], [4096], [76543], [3308], [6426]]]</t>
@@ -4334,10 +4334,10 @@
     <t>[3254, 37, 6029, 297, 4096, 76543, 3308, 6426]</t>
   </si>
   <si>
-    <t>[[1213, 2041], [7, 18, 12], [639, 1874, 1129, 258, 791, 1338], [297], [684, 2047, 1365], [1, 7656, 30616, 22962, 15308], [1102, 1653, 553], [3213, 3213]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_infp16_outbf16_fetch_4_ID431</t>
+    <t>[263, 27, 1277, 284, 1032, 70230, 143, 6295]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_infp16_outbf16_ID431</t>
   </si>
   <si>
     <t>[[32768, 1024], [[256], [52263], [64], [24314], [4275], [5065], [5817], [2260]]]</t>
@@ -4346,10 +4346,10 @@
     <t>[256, 52263, 64, 24314, 4275, 5065, 5817, 2260]</t>
   </si>
   <si>
-    <t>[[256], [1, 1, 1, 52260], [64], [9406, 14908], [3084, 1191], [1267, 1266, 1266, 1266], [1, 2181, 2181, 1454], [1130, 1130]]</t>
-  </si>
-  <si>
-    <t>h111_ws8_inbf16_outfp32_fetch_8_ID432</t>
+    <t>[86, 3996, 1, 24153, 3451, 806, 5271, 2136]</t>
+  </si>
+  <si>
+    <t>h111_ws8_inbf16_outfp32_ID432</t>
   </si>
   <si>
     <t>[[65536, 111], [[8982], [924], [41077], [21952], [9457], [41866], [1018], [6545]]]</t>
@@ -4361,10 +4361,10 @@
     <t>[8982, 924, 41077, 21952, 9457, 41866, 1018, 6545]</t>
   </si>
   <si>
-    <t>[[1123, 1123, 1123, 1123, 1123, 1123, 1122, 1122], [788, 1, 135], [1, 41076], [21952], [6057, 1, 1, 1, 3397], [41866], [1018], [6364, 1, 1, 1, 1, 177]]</t>
-  </si>
-  <si>
-    <t>h1246_ws16_infp32_outfp32_fetch_5_ID433</t>
+    <t>[8152, 20, 2756, 17893, 9427, 1141, 930, 226]</t>
+  </si>
+  <si>
+    <t>h1246_ws16_infp32_outfp32_ID433</t>
   </si>
   <si>
     <t>[[816717, 1246], [[608], [601], [30057], [94888], [335], [7980], [30705], [12785], [239], [2623], [23506], [698], [8620], [87101], [28487], [16583]]]</t>
@@ -4382,10 +4382,10 @@
     <t>[608, 601, 30057, 94888, 335, 7980, 30705, 12785, 239, 2623, 23506, 698, 8620, 87101, 28487, 16583]</t>
   </si>
   <si>
-    <t>[[608], [601], [15028, 15029], [94888], [335], [5860, 1, 1, 2118], [30705], [12785], [239], [2623], [23506], [140, 140, 140, 139, 139], [7795, 1, 1, 1, 822], [29033, 43549, 14519], [28487], [16583]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_inbf16_outfp16_fetch_2_ID434</t>
+    <t>[287, 268, 1515, 40271, 181, 7319, 5091, 6999, 117, 960, 1291, 71, 7767, 7762, 26203, 9925]</t>
+  </si>
+  <si>
+    <t>h64_ws2_inbf16_outfp16_ID434</t>
   </si>
   <si>
     <t>[[16384, 64], [[9525], [618]]]</t>
@@ -4397,10 +4397,10 @@
     <t>[9525, 618]</t>
   </si>
   <si>
-    <t>[[9525], [226, 392]]</t>
-  </si>
-  <si>
-    <t>h3022_ws4_infp16_outfp16_fetch_3_ID435</t>
+    <t>[4774, 57]</t>
+  </si>
+  <si>
+    <t>h3022_ws4_infp16_outfp16_ID435</t>
   </si>
   <si>
     <t>[[692300, 3022], [[512], [6092], [728], [41642]]]</t>
@@ -4418,10 +4418,10 @@
     <t>[512, 6092, 728, 41642]</t>
   </si>
   <si>
-    <t>[[170, 255, 87], [6092], [24, 173, 531], [41642]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_inbf16_outfp32_fetch_7_ID436</t>
+    <t>[42, 80, 693, 3051]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_inbf16_outfp32_ID436</t>
   </si>
   <si>
     <t>[[805807, 2048], [[7525], [7062]]]</t>
@@ -4436,10 +4436,10 @@
     <t>[7525, 7062]</t>
   </si>
   <si>
-    <t>[[1075, 1612, 2149, 2686, 3223, -3221, 1], [1413, 1413, 1412, 1412, 1412]]</t>
-  </si>
-  <si>
-    <t>h3339_ws16_infp16_outbf16_fetch_7_ID437</t>
+    <t>[575, 3684]</t>
+  </si>
+  <si>
+    <t>h3339_ws16_infp16_outbf16_ID437</t>
   </si>
   <si>
     <t>[[656232, 3339], [[2618], [58284], [42], [8770], [5451], [7913], [1333], [6782], [21289], [110], [9292], [43006], [31460], [8578], [16286], [6174]]]</t>
@@ -4457,10 +4457,10 @@
     <t>[2618, 58284, 42, 8770, 5451, 7913, 1333, 6782, 21289, 110, 9292, 43006, 31460, 8578, 16286, 6174]</t>
   </si>
   <si>
-    <t>[[2618], [29142, 29142], [21, 21], [1, -1455, 3651, 2921, 2191, 1461], [1, 545, 2180, 1635, 1090], [1, 793, 3164, 2373, 1582], [1333], [6782], [2257, 19032], [110], [1328, 1328, 1328, 1327, 1327, 1327, 1327], [43006], [15730, 15730], [1225, 1837, 2449, 3061, 3673, -3668, 1], [16286], [1, 1, 1, 6171]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp32_outbf16_fetch_8_ID438</t>
+    <t>[244, 55300, 6, 8452, 5413, 4004, 745, 6638, 1954, 110, 1910, 30246, 15969, 804, 2718, 398]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp32_outbf16_ID438</t>
   </si>
   <si>
     <t>[[16384, 512], [[9274], [98527], [85316], [1789], [19030], [4756], [357], [59340]]]</t>
@@ -4472,10 +4472,10 @@
     <t>[9274, 98527, 85316, 1789, 19030, 4756, 357, 59340]</t>
   </si>
   <si>
-    <t>[[1, -6366, 4054, 3475, 2896, 2317, 1738, 1159], [27793, 70734], [85316], [1789], [19030], [1, 1, 1, 4753], [179, 178], [11868, 17802, 23736, 5933, 1]]</t>
-  </si>
-  <si>
-    <t>h4013_ws16_inbf16_outbf16_fetch_6_ID439</t>
+    <t>[9112, 90429, 55585, 1039, 1282, 531, 330, 31447]</t>
+  </si>
+  <si>
+    <t>h4013_ws16_inbf16_outbf16_ID439</t>
   </si>
   <si>
     <t>[[814606, 4013], [[6101], [9336], [67244], [37187], [95511], [67978], [5906], [3187], [8192], [20], [10946], [24813], [41072], [743], [20513], [3561]]]</t>
@@ -4493,10 +4493,10 @@
     <t>[6101, 9336, 67244, 37187, 95511, 67978, 5906, 3187, 8192, 20, 10946, 24813, 41072, 743, 20513, 3561]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 1, 6097], [2334, 3501, 3500, 1], [29016, 16136, 1180, 834, 20078], [37187], [47755, 47756], [11329, 16993, 22657, 28321, -11323, 1], [1968, 2952, 986], [3187], [2730, 4095, 1367], [20], [10946], [24813], [41072], [743], [20513], [1187, 1780, 594]]</t>
-  </si>
-  <si>
-    <t>h2428_ws2_inbf16_outfp32_fetch_1_ID440</t>
+    <t>[1266, 1533, 4309, 29016, 87138, 27218, 2607, 160, 359, 17, 21, 14664, 38295, 428, 8583, 3240]</t>
+  </si>
+  <si>
+    <t>h2428_ws2_inbf16_outfp32_ID440</t>
   </si>
   <si>
     <t>[[16384, 2428], [[184], [29362]]]</t>
@@ -4508,10 +4508,10 @@
     <t>[184, 29362]</t>
   </si>
   <si>
-    <t>[[184], [29362]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_infp16_outbf16_fetch_8_ID441</t>
+    <t>[10, 28706]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_infp16_outbf16_ID441</t>
   </si>
   <si>
     <t>[[131072, 2048], [[922], [3501], [4576], [5877], [10171], [2590], [3271], [2276], [470], [99969], [29], [5562], [65], [350], [96887], [87878]]]</t>
@@ -4520,10 +4520,10 @@
     <t>[922, 3501, 4576, 5877, 10171, 2590, 3271, 2276, 470, 99969, 29, 5562, 65, 350, 96887, 87878]</t>
   </si>
   <si>
-    <t>[[184, 276, 368, 93, 1], [584, 1750, 1167], [2288, 2288], [5877], [10171], [2590], [345, 884, 2042], [1138, 1138], [118, 118, 117, 117], [24993, 24992, 24992, 24992], [29], [1854, 2781, 927], [33, 32], [330, 20], [12110, 18165, 24220, 30275, 36330, 42385, -66599, 1], [21970, 21970, 21969, 21969]]</t>
-  </si>
-  <si>
-    <t>h2185_ws8_infp16_outfp16_fetch_4_ID442</t>
+    <t>[283, 3477, 3756, 2396, 5619, 1407, 2492, 2061, 245, 47487, 15, 5062, 2, 327, 8042, 3136]</t>
+  </si>
+  <si>
+    <t>h2185_ws8_infp16_outfp16_ID442</t>
   </si>
   <si>
     <t>[[131072, 2185], [[8293], [37720], [7281], [878], [25989], [2382], [6421], [8199]]]</t>
@@ -4538,10 +4538,10 @@
     <t>[8293, 37720, 7281, 878, 25989, 2382, 6421, 8199]</t>
   </si>
   <si>
-    <t>[[8293], [12573, 18859, 6288], [7281], [439, 439], [25989], [2382], [1, 2408, 2407, 1605], [1, 3076, 3073, 2049]]</t>
-  </si>
-  <si>
-    <t>h3203_ws4_infp16_outfp32_fetch_2_ID443</t>
+    <t>[4402, 421, 6671, 474, 404, 247, 1702, 7957]</t>
+  </si>
+  <si>
+    <t>h3203_ws4_infp16_outfp32_ID443</t>
   </si>
   <si>
     <t>[[262144, 3203], [[11394], [27524], [2778], [1211]]]</t>
@@ -4553,10 +4553,10 @@
     <t>[11394, 27524, 2778, 1211]</t>
   </si>
   <si>
-    <t>[[11394], [27524], [1389, 1389], [1211]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outfp32_fetch_7_ID444</t>
+    <t>[9728, 23246, 2675, 125]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outfp32_ID444</t>
   </si>
   <si>
     <t>[[647263, 256], [[1216], [5525], [98669], [8241]]]</t>
@@ -4571,10 +4571,10 @@
     <t>[1216, 5525, 98669, 8241]</t>
   </si>
   <si>
-    <t>[[1216], [39, 1822, 1115, 2549], [27418, 15448, 13148, 11699, 30956], [1178, 1178, 1177, 1177, 1177, 1177, 1177]]</t>
-  </si>
-  <si>
-    <t>h3355_ws8_inbf16_outbf16_fetch_6_ID445</t>
+    <t>[175, 4981, 97718, 532]</t>
+  </si>
+  <si>
+    <t>h3355_ws8_inbf16_outbf16_ID445</t>
   </si>
   <si>
     <t>[[420508, 3355], [[5094], [793], [1024], [6100], [567], [37757], [27010], [9133]]]</t>
@@ -4592,10 +4592,10 @@
     <t>[5094, 793, 1024, 6100, 567, 37757, 27010, 9133]</t>
   </si>
   <si>
-    <t>[[1, 5093], [158, 237, 316, 81, 1], [1024], [177, 123, 1106, 617, 1610, 2467], [567], [37757], [27010], [4567, 4566]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp16_outbf16_fetch_3_ID446</t>
+    <t>[729, 457, 68, 556, 45, 17313, 3686, 5060]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp16_outbf16_ID446</t>
   </si>
   <si>
     <t>[[65536, 4096], [[45464], [24095]]]</t>
@@ -4604,10 +4604,10 @@
     <t>[45464, 24095]</t>
   </si>
   <si>
-    <t>[[15155, 15155, 15154], [24095]]</t>
-  </si>
-  <si>
-    <t>h4764_ws2_infp32_outfp16_fetch_3_ID447</t>
+    <t>[999, 24025]</t>
+  </si>
+  <si>
+    <t>h4764_ws2_infp32_outfp16_ID447</t>
   </si>
   <si>
     <t>[[161418, 4764], [[9606], [58]]]</t>
@@ -4625,10 +4625,10 @@
     <t>[9606, 58]</t>
   </si>
   <si>
-    <t>[[4803, 4803], [20, 19, 19]]</t>
-  </si>
-  <si>
-    <t>h64_ws16_inbf16_outbf16_fetch_8_ID448</t>
+    <t>[5396, 57]</t>
+  </si>
+  <si>
+    <t>h64_ws16_inbf16_outbf16_ID448</t>
   </si>
   <si>
     <t>[[362900, 64], [[2932], [60324], [84], [8004], [57689], [22630], [43307], [6812], [8692], [86178], [6850], [6643], [17762], [2006], [10386], [4126]]]</t>
@@ -4643,10 +4643,10 @@
     <t>[2932, 60324, 84, 8004, 57689, 22630, 43307, 6812, 8692, 86178, 6850, 6643, 17762, 2006, 10386, 4126]</t>
   </si>
   <si>
-    <t>[[1, 2931], [60324], [14, 42, 28], [4002, 4002], [57689], [22630], [14435, 21652, 7220], [6812], [1, -5970, 3801, 3258, 2715, 2172, 1629, 1086], [17236, 17236, 17236, 17235, 17235], [1, 1, 1, 1, 6846], [1, 1, 6641], [17762], [2006], [10386], [2063, 2063]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_inbf16_outfp16_fetch_1_ID449</t>
+    <t>[2740, 2665, 9, 7302, 52080, 10772, 4874, 3636, 8324, 728, 1333, 1066, 427, 1690, 10123, 538]</t>
+  </si>
+  <si>
+    <t>h64_ws2_inbf16_outfp16_ID449</t>
   </si>
   <si>
     <t>[[16384, 64], [[295], [18155]]]</t>
@@ -4655,10 +4655,10 @@
     <t>[295, 18155]</t>
   </si>
   <si>
-    <t>[[295], [18155]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp16_outbf16_fetch_5_ID450</t>
+    <t>[160, 7822]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp16_outbf16_ID450</t>
   </si>
   <si>
     <t>[[8192, 256], [[983], [19502], [1976], [4096], [1837], [25923], [2020], [434], [998], [1200], [3527], [323], [41918], [57738], [22064], [13273]]]</t>
@@ -4667,10 +4667,10 @@
     <t>[983, 19502, 1976, 4096, 1837, 25923, 2020, 434, 998, 1200, 3527, 323, 41918, 57738, 22064, 13273]</t>
   </si>
   <si>
-    <t>[[1, 100, 392, 294, 196], [19502], [1976], [684, 2047, 1365], [1837], [25923], [1010, 1010], [145, 145, 144], [526, 1, 1, 470], [1200], [1763, 1764], [88, 235], [41918], [28869, 28869], [22064], [13273]]</t>
-  </si>
-  <si>
-    <t>h3995_ws4_infp16_outbf16_fetch_3_ID451</t>
+    <t>[432, 19297, 1905, 238, 138, 12129, 1237, 370, 946, 722, 1871, 264, 34779, 32484, 1159, 13205]</t>
+  </si>
+  <si>
+    <t>h3995_ws4_infp16_outbf16_ID451</t>
   </si>
   <si>
     <t>[[32768, 3995], [[26], [6947], [22], [58061]]]</t>
@@ -4682,10 +4682,10 @@
     <t>[26, 6947, 22, 58061]</t>
   </si>
   <si>
-    <t>[[13, 13], [3474, 3473], [22], [9679, 29029, 19353]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_infp32_outfp32_fetch_7_ID452</t>
+    <t>[6, 5999, 7, 57568]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_infp32_outfp32_ID452</t>
   </si>
   <si>
     <t>[[406803, 1024], [[5994], [6091], [299], [4096], [43994], [90323], [13664], [2048], [709], [7552], [76227], [3439], [9924], [4096], [1024], [30427]]]</t>
@@ -4700,10 +4700,10 @@
     <t>[5994, 6091, 299, 4096, 43994, 90323, 13664, 2048, 709, 7552, 76227, 3439, 9924, 4096, 1024, 30427]</t>
   </si>
   <si>
-    <t>[[1998, 1998, 1998], [5225, 1, 1, 1, 1, 862], [149, 150], [684, 2047, 1365], [21997, 21997], [45162, 45161], [13664], [2048], [1, 180, 47, 481], [1078, 1617, 2156, 2695, 3234, -3229, 1], [42071, 1, 1, 34154], [1720, 1719], [4962, 4962], [4096], [1024], [10142, 15213, 5072]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outfp32_fetch_7_ID453</t>
+    <t>[98, 5962, 277, 2375, 41514, 1452, 7873, 915, 117, 13, 7513, 1659, 9695, 3337, 932, 15902]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outfp32_ID453</t>
   </si>
   <si>
     <t>[[131072, 256], [[9755], [7312], [4096], [8344]]]</t>
@@ -4712,10 +4712,10 @@
     <t>[9755, 7312, 4096, 8344]</t>
   </si>
   <si>
-    <t>[[1, 976, 3901, 2926, 1951], [1, -3129, 3132, 2610, 2088, 1566, 1044], [2048, 2048], [8344]]</t>
-  </si>
-  <si>
-    <t>h447_ws4_infp32_outfp32_fetch_5_ID454</t>
+    <t>[423, 6786, 17, 301]</t>
+  </si>
+  <si>
+    <t>h447_ws4_infp32_outfp32_ID454</t>
   </si>
   <si>
     <t>[[334471, 447], [[9802], [31361], [37817], [6478]]]</t>
@@ -4733,10 +4733,10 @@
     <t>[9802, 31361, 37817, 6478]</t>
   </si>
   <si>
-    <t>[[4534, 2171, 1379, 844, 874], [31361], [37817], [2159, 3238, 1081]]</t>
-  </si>
-  <si>
-    <t>h1343_ws8_infp32_outfp32_fetch_9_ID455</t>
+    <t>[659, 28748, 34726, 68]</t>
+  </si>
+  <si>
+    <t>h1343_ws8_infp32_outfp32_ID455</t>
   </si>
   <si>
     <t>[[724843, 1343], [[97578], [82], [25226], [21890], [512], [241], [488], [21011]]]</t>
@@ -4754,10 +4754,10 @@
     <t>[97578, 82, 25226, 21890, 512, 241, 488, 21011]</t>
   </si>
   <si>
-    <t>[[10842, 10842, 10842, 10842, 10842, 10842, 10842, 10842, 10842], [82], [25226], [21890], [188, 6, 96, 222], [241], [1, 182, 183, 122], [10506, 10505]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp16_outbf16_fetch_4_ID456</t>
+    <t>[385, 42, 320, 17681, 8, 230, 464, 20153]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp16_outbf16_ID456</t>
   </si>
   <si>
     <t>[[551839, 4096], [[40552], [1660], [44191], [71394]]]</t>
@@ -4772,10 +4772,10 @@
     <t>[40552, 1660, 44191, 71394]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 40549], [1660], [44191], [1971, 69423]]</t>
-  </si>
-  <si>
-    <t>h339_ws16_inbf16_outbf16_fetch_7_ID457</t>
+    <t>[40477, 214, 38315, 3941]</t>
+  </si>
+  <si>
+    <t>h339_ws16_inbf16_outbf16_ID457</t>
   </si>
   <si>
     <t>[[8192, 339], [[32440], [8538], [32360], [33], [23492], [3088], [7811], [38385], [737], [1587], [876], [9479], [17912], [4096], [5706], [24630]]]</t>
@@ -4787,10 +4787,10 @@
     <t>[32440, 8538, 32360, 33, 23492, 3088, 7811, 38385, 737, 1587, 876, 9479, 17912, 4096, 5706, 24630]</t>
   </si>
   <si>
-    <t>[[16220, 16220], [1, 1, 1, 8535], [10787, 10787, 10786], [11, 11, 11], [23492], [1544, 1544], [1116, 1116, 1116, 1116, 1116, 1116, 1115], [38385], [369, 368], [1587], [173, 90, 132, 481], [3159, 4738, 1582], [17912], [2048, 2048], [2853, 2853], [17543, 7087]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_inbf16_outfp32_fetch_6_ID458</t>
+    <t>[170, 3166, 5215, 12, 7617, 2972, 7797, 17252, 613, 1472, 345, 7865, 1179, 3761, 4907, 2154]</t>
+  </si>
+  <si>
+    <t>h256_ws8_inbf16_outfp32_ID458</t>
   </si>
   <si>
     <t>[[32768, 256], [[643], [2455], [4096], [41769], [9501], [11211], [69558], [1317]]]</t>
@@ -4799,10 +4799,10 @@
     <t>[643, 2455, 4096, 41769, 9501, 11211, 69558, 1317]</t>
   </si>
   <si>
-    <t>[[1, 642], [1228, 1227], [1412, 58, 860, 1766], [20884, 20885], [5961, 1, 1, 1, 1, 3536], [11211], [1, 6959, 27821, 20866, 13911], [1317]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_infp16_outbf16_fetch_7_ID459</t>
+    <t>[637, 2440, 3989, 23583, 7905, 5088, 34019, 908]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_infp16_outbf16_ID459</t>
   </si>
   <si>
     <t>[[781619, 1024], [[8192], [967], [21275], [76505], [70177], [467], [44973], [89354], [16076], [10507], [64931], [11183], [88], [592], [97984], [22796]]]</t>
@@ -4817,10 +4817,10 @@
     <t>[8192, 967, 21275, 76505, 70177, 467, 44973, 89354, 16076, 10507, 64931, 11183, 88, 592, 97984, 22796]</t>
   </si>
   <si>
-    <t>[[1171, 1171, 1170, 1170, 1170, 1170, 1170], [1, 364, 361, 241], [21275], [1, 1, 1, 76502], [70177], [467], [44973], [89354], [16076], [10507], [34235, 1, 1, 1, 30693], [11183], [29, 43, 16], [296, 296], [13997, 20995, 27993, 34991, 41989, -41982, 1], [22796]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp32_outfp32_fetch_7_ID460</t>
+    <t>[7471, 923, 18904, 10545, 6496, 188, 18164, 81375, 14525, 7907, 5007, 9167, 27, 332, 2362, 22129]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp32_outfp32_ID460</t>
   </si>
   <si>
     <t>[[573556, 1024], [[8889], [36073], [31393], [63]]]</t>
@@ -4835,10 +4835,10 @@
     <t>[8889, 36073, 31393, 63]</t>
   </si>
   <si>
-    <t>[[1269, 1903, 2537, 3171, 3805, -3797, 1], [18036, 18037], [10464, 15696, 5233], [63]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp16_outbf16_fetch_5_ID461</t>
+    <t>[8886, 1299, 2386, 4]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp16_outbf16_ID461</t>
   </si>
   <si>
     <t>[[8192, 64], [[14366], [9940], [7868], [21343]]]</t>
@@ -4847,10 +4847,10 @@
     <t>[14366, 9940, 7868, 21343]</t>
   </si>
   <si>
-    <t>[[14366], [2234, 363, 1435, 2596, 3312], [7868], [21164, 179]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_inbf16_outfp16_fetch_2_ID462</t>
+    <t>[8415, 4603, 7238, 363]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_inbf16_outfp16_ID462</t>
   </si>
   <si>
     <t>[[262144, 1024], [[2218], [2048], [22022], [10]]]</t>
@@ -4859,10 +4859,10 @@
     <t>[2218, 2048, 22022, 10]</t>
   </si>
   <si>
-    <t>[[1109, 1109], [2048], [11011, 11011], [10]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_inbf16_outbf16_fetch_6_ID463</t>
+    <t>[179, 923, 21634, 8]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_inbf16_outbf16_ID463</t>
   </si>
   <si>
     <t>[[471649, 2048], [[8724], [2347], [23994], [14577], [573], [25713], [9202], [69258]]]</t>
@@ -4877,10 +4877,10 @@
     <t>[8724, 2347, 23994, 14577, 573, 25713, 9202, 69258]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 1, 1, 8719], [2347], [20854, 3140], [14577], [114, 171, 228, 59, 1], [1, 25712], [1841, 1841, 1840, 1840, 1840], [69258]]</t>
-  </si>
-  <si>
-    <t>h4135_ws2_infp16_outfp32_fetch_6_ID464</t>
+    <t>[180, 337, 622, 13859, 560, 1570, 8574, 3447]</t>
+  </si>
+  <si>
+    <t>h4135_ws2_infp16_outfp32_ID464</t>
   </si>
   <si>
     <t>[[172069, 4135], [[9975], [65649]]]</t>
@@ -4898,10 +4898,10 @@
     <t>[9975, 65649]</t>
   </si>
   <si>
-    <t>[[1, -1660, 4155, 3324, 2493, 1662], [16412, 24618, 24618, 1]]</t>
-  </si>
-  <si>
-    <t>h3758_ws4_inbf16_outfp32_fetch_5_ID465</t>
+    <t>[468, 65112]</t>
+  </si>
+  <si>
+    <t>h3758_ws4_inbf16_outfp32_ID465</t>
   </si>
   <si>
     <t>[[480856, 3758], [[326], [763], [39], [21734]]]</t>
@@ -4919,10 +4919,10 @@
     <t>[326, 763, 39, 21734]</t>
   </si>
   <si>
-    <t>[[326], [1, 78, 304, 228, 152], [14, 25], [21734]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_inbf16_outbf16_fetch_5_ID466</t>
+    <t>[313, 763, 36, 1573]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_inbf16_outbf16_ID466</t>
   </si>
   <si>
     <t>[[813073, 2048], [[58044], [3446], [64800], [6763], [595], [2913], [5627], [2697], [9474], [635], [5139], [9026], [95843], [47004], [666], [1626]]]</t>
@@ -4937,10 +4937,10 @@
     <t>[58044, 3446, 64800, 6763, 595, 2913, 5627, 2697, 9474, 635, 5139, 9026, 95843, 47004, 666, 1626]</t>
   </si>
   <si>
-    <t>[[11608, 17412, 23216, 5807, 1], [1723, 1723], [1, 1, 1, 1, 64796], [3930, 1, 2832], [148, 222, 224, 1], [1, 2912], [1, 2111, 2109, 1406], [2697], [4737, 4737], [635], [1284, 1926, 1928, 1], [1, 904, 3609, 2707, 1805], [19169, 19169, 19169, 19168, 19168], [23243, 23761], [323, 32, 88, 223], [1626]]</t>
-  </si>
-  <si>
-    <t>h98_ws8_infp16_outbf16_fetch_6_ID467</t>
+    <t>[23733, 36, 46860, 555, 493, 2797, 196, 1994, 8570, 40, 3009, 4970, 6775, 2160, 632, 754]</t>
+  </si>
+  <si>
+    <t>h98_ws8_infp16_outbf16_ID467</t>
   </si>
   <si>
     <t>[[8192, 98], [[7606], [532], [86275], [67356], [2597], [62003], [411], [518]]]</t>
@@ -4952,10 +4952,10 @@
     <t>[7606, 532, 86275, 67356, 2597, 62003, 411, 518]</t>
   </si>
   <si>
-    <t>[[1267, 1900, 2533, 3166, -1261, 1], [178, 177, 177], [86275], [22452, 33678, 11226], [1299, 1298], [20668, 20668, 20667], [206, 205], [1, 517]]</t>
-  </si>
-  <si>
-    <t>h3003_ws4_infp32_outfp32_fetch_5_ID468</t>
+    <t>[369, 303, 34935, 2581, 11, 525, 12, 6]</t>
+  </si>
+  <si>
+    <t>h3003_ws4_infp32_outfp32_ID468</t>
   </si>
   <si>
     <t>[[262144, 3003], [[2048], [195], [758], [59901]]]</t>
@@ -4967,10 +4967,10 @@
     <t>[2048, 195, 758, 59901]</t>
   </si>
   <si>
-    <t>[[2048], [195], [12, 42, 24, 153, 527], [59901]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp32_outfp32_fetch_9_ID469</t>
+    <t>[1971, 50, 753, 53484]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp32_outfp32_ID469</t>
   </si>
   <si>
     <t>[[32768, 256], [[5892], [37350], [13765], [356], [76], [17137], [296], [95152], [7546], [37791], [6950], [2190], [5220], [97], [9378], [71]]]</t>
@@ -4979,10 +4979,10 @@
     <t>[5892, 37350, 13765, 356, 76, 17137, 296, 95152, 7546, 37791, 6950, 2190, 5220, 97, 9378, 71]</t>
   </si>
   <si>
-    <t>[[5892], [18675, 18675], [13765], [356], [16, 4, 56], [17137], [32, 264], [13949, 981, 31357, 13604, 7547, 7632, 5031, 1098, 13953], [1, -1251, 3141, 2513, 1885, 1257], [18896, 18895], [3170, 3780], [2190], [5220], [17, 48, 32], [1, -6445, 4102, 3516, 2930, 2344, 1758, 1172], [1, 70]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_infp32_outfp16_fetch_9_ID470</t>
+    <t>[2679, 35608, 537, 198, 32, 8301, 15, 16243, 4289, 34151, 6490, 2130, 138, 93, 8644, 2]</t>
+  </si>
+  <si>
+    <t>h128_ws4_infp32_outfp16_ID470</t>
   </si>
   <si>
     <t>[[8192, 128], [[54], [628], [92797], [81451]]]</t>
@@ -4994,10 +4994,10 @@
     <t>[54, 628, 92797, 81451]</t>
   </si>
   <si>
-    <t>[[9, 27, 18], [1, 627], [1, -87629, 41240, 36085, 30930, 25775, 20620, 15465, 10310], [81451]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_infp16_outbf16_fetch_6_ID471</t>
+    <t>[49, 122, 63476, 39305]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_infp16_outbf16_ID471</t>
   </si>
   <si>
     <t>[[728767, 1024], [[256], [40337], [33291], [6893], [42275], [9470], [8126], [76606], [6901], [26808], [63], [9069], [3303], [971], [5858], [471]]]</t>
@@ -5012,10 +5012,10 @@
     <t>[256, 40337, 33291, 6893, 42275, 9470, 8126, 76606, 6901, 26808, 63, 9069, 3303, 971, 5858, 471]</t>
   </si>
   <si>
-    <t>[[256], [22043, 18294], [33291], [1, 1, 6891], [42275], [1, -1577, 3945, 3156, 2367, 1578], [7853, 1, 1, 1, 270], [76606], [1, 2588, 2587, 1725], [26808], [63], [1, 1, 1, 1, 9065], [1101, 1101, 1101], [1, 970], [1464, 2196, 2197, 1], [1, 178, 175, 117]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp16_outfp16_fetch_2_ID472</t>
+    <t>[10, 32737, 19822, 6333, 23066, 5379, 7630, 76444, 3019, 25717, 5, 612, 106, 782, 5546, 447]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp16_outfp16_ID472</t>
   </si>
   <si>
     <t>[[262037, 4096], [[62810], [2048]]]</t>
@@ -5030,10 +5030,10 @@
     <t>[62810, 2048]</t>
   </si>
   <si>
-    <t>[[31405, 31405], [2048]]</t>
-  </si>
-  <si>
-    <t>h2211_ws2_infp32_outbf16_fetch_1_ID473</t>
+    <t>[61925, 432]</t>
+  </si>
+  <si>
+    <t>h2211_ws2_infp32_outbf16_ID473</t>
   </si>
   <si>
     <t>[[65536, 2211], [[1881], [24]]]</t>
@@ -5045,10 +5045,10 @@
     <t>[1881, 24]</t>
   </si>
   <si>
-    <t>[[1881], [24]]</t>
-  </si>
-  <si>
-    <t>h3145_ws8_infp32_outfp32_fetch_4_ID474</t>
+    <t>[1085, 3]</t>
+  </si>
+  <si>
+    <t>h3145_ws8_infp32_outfp32_ID474</t>
   </si>
   <si>
     <t>[[32768, 3145], [[150], [3288], [6934], [512], [476], [136], [970], [99864]]]</t>
@@ -5060,10 +5060,10 @@
     <t>[150, 3288, 6934, 512, 476, 136, 970, 99864]</t>
   </si>
   <si>
-    <t>[[150], [548, 1644, 1096], [2311, 3466, 1157], [128, 128, 128, 128], [1, 1, 1, 473], [136], [970], [47925, 51939]]</t>
-  </si>
-  <si>
-    <t>h3361_ws4_inbf16_outbf16_fetch_7_ID475</t>
+    <t>[74, 1738, 270, 460, 366, 132, 177, 12394]</t>
+  </si>
+  <si>
+    <t>h3361_ws4_inbf16_outbf16_ID475</t>
   </si>
   <si>
     <t>[[32768, 3361], [[256], [91], [8232], [31362]]]</t>
@@ -5075,10 +5075,10 @@
     <t>[256, 91, 8232, 31362]</t>
   </si>
   <si>
-    <t>[[256], [91], [1612, 1136, 2603, 590, 957, 169, 1165], [31362]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_infp32_outfp32_fetch_5_ID476</t>
+    <t>[140, 84, 3223, 2603]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_infp32_outfp32_ID476</t>
   </si>
   <si>
     <t>[[65536, 2048], [[5513], [4096], [8674], [25388], [38839], [11093], [534], [45324], [390], [434], [35860], [7195], [35316], [256], [2805], [3533]]]</t>
@@ -5087,10 +5087,10 @@
     <t>[5513, 4096, 8674, 25388, 38839, 11093, 534, 45324, 390, 434, 35860, 7195, 35316, 256, 2805, 3533]</t>
   </si>
   <si>
-    <t>[[1103, 1103, 1103, 1102, 1102], [2048, 2048], [1447, 4336, 2891], [25388], [38839], [11093], [411, 1, 122], [7554, 22662, 15108], [390], [434], [11953, 17929, 5978], [4480, 1, 1, 2713], [35316], [21, 235], [1402, 1403], [2847, 686]]</t>
-  </si>
-  <si>
-    <t>h3338_ws2_infp16_outbf16_fetch_1_ID477</t>
+    <t>[103, 4039, 7950, 3109, 2567, 7591, 93, 40884, 30, 193, 1272, 918, 30018, 117, 273, 3098]</t>
+  </si>
+  <si>
+    <t>h3338_ws2_infp16_outbf16_ID477</t>
   </si>
   <si>
     <t>[[65536, 3338], [[13535], [3789]]]</t>
@@ -5102,10 +5102,10 @@
     <t>[13535, 3789]</t>
   </si>
   <si>
-    <t>[[13535], [3789]]</t>
-  </si>
-  <si>
-    <t>h459_ws8_infp16_outfp32_fetch_6_ID478</t>
+    <t>[13034, 3501]</t>
+  </si>
+  <si>
+    <t>h459_ws8_infp16_outfp32_ID478</t>
   </si>
   <si>
     <t>[[4096, 459], [[512], [121], [6247], [670], [6098], [86631], [256], [6888]]]</t>
@@ -5117,10 +5117,10 @@
     <t>[512, 121, 6247, 670, 6098, 86631, 256, 6888]</t>
   </si>
   <si>
-    <t>[[422, 1, 1, 1, 87], [121], [1639, 2271, 650, 1687], [670], [1869, 1057, 1488, 148, 592, 944], [83569, 3062], [256], [2296, 2296, 2296]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp16_outbf16_fetch_8_ID479</t>
+    <t>[177, 2, 6146, 643, 3186, 59782, 24, 166]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp16_outbf16_ID479</t>
   </si>
   <si>
     <t>[[553430, 512], [[77140], [9330], [9787], [642], [22098], [998], [109], [20565]]]</t>
@@ -5135,10 +5135,10 @@
     <t>[77140, 9330, 9787, 642, 22098, 998, 109, 20565]</t>
   </si>
   <si>
-    <t>[[77140], [1866, 1866, 1866, 1866, 1866], [1223, 1834, 2445, 3056, 3667, 4278, -6717, 1], [378, 1, 1, 262], [11049, 11049], [1, 375, 373, 249], [109], [20565]]</t>
-  </si>
-  <si>
-    <t>h847_ws16_infp32_outfp32_fetch_7_ID480</t>
+    <t>[43927, 615, 34, 622, 20614, 914, 105, 19969]</t>
+  </si>
+  <si>
+    <t>h847_ws16_infp32_outfp32_ID480</t>
   </si>
   <si>
     <t>[[824961, 847], [[5766], [8471], [6065], [62872], [25363], [364], [6804], [1024], [19], [483], [50321], [95426], [941], [48173], [22532], [33158]]]</t>
@@ -5156,10 +5156,10 @@
     <t>[5766, 8471, 6065, 62872, 25363, 364, 6804, 1024, 19, 483, 50321, 95426, 941, 48173, 22532, 33158]</t>
   </si>
   <si>
-    <t>[[5766], [1, -3630, 3630, 3025, 2420, 1815, 1210], [3033, 3032], [1, 23576, 23577, 15718], [3623, 21740], [182, 182], [6804], [1024], [19], [242, 241], [43601, 1, 6719], [19085, 28627, 38169, 9544, 1], [159, 469, 313], [5981, 42192], [7052, 15480], [33158]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outfp32_fetch_3_ID481</t>
+    <t>[2827, 6758, 5690, 32254, 24067, 114, 319, 607, 8, 447, 22901, 46845, 896, 2191, 1727, 4262]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outfp32_ID481</t>
   </si>
   <si>
     <t>[[603823, 256], [[41015], [93161], [756], [4164], [1024], [6293], [353], [60], [3964], [1024], [70], [39404], [184], [26813], [15718], [33]]]</t>
@@ -5174,10 +5174,10 @@
     <t>[41015, 93161, 756, 4164, 1024, 6293, 353, 60, 3964, 1024, 70, 39404, 184, 26813, 15718, 33]</t>
   </si>
   <si>
-    <t>[[41015], [31053, 46579, 15529], [756], [2082, 2082], [1024], [6293], [1, 352], [30, 30], [1982, 1982], [1024], [70], [19702, 19702], [184], [1, 26812], [15718], [11, 11, 11]]</t>
-  </si>
-  <si>
-    <t>h1104_ws2_inbf16_outfp16_fetch_2_ID482</t>
+    <t>[23130, 86126, 738, 2177, 32, 2141, 338, 32, 1758, 907, 30, 700, 167, 15798, 3210, 10]</t>
+  </si>
+  <si>
+    <t>h1104_ws2_inbf16_outfp16_ID482</t>
   </si>
   <si>
     <t>[[293038, 1104], [[5924], [92126]]]</t>
@@ -5195,10 +5195,10 @@
     <t>[5924, 92126]</t>
   </si>
   <si>
-    <t>[[5924], [92006, 120]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_inbf16_outfp32_fetch_5_ID483</t>
+    <t>[3151, 42592]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_inbf16_outfp32_ID483</t>
   </si>
   <si>
     <t>[[171411, 4096], [[6155], [1125], [87], [4644]]]</t>
@@ -5213,10 +5213,10 @@
     <t>[6155, 1125, 87, 4644]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 1, 6151], [1125], [43, 44], [2322, 2322]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp16_outfp16_fetch_3_ID484</t>
+    <t>[1122, 685, 46, 89]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp16_outfp16_ID484</t>
   </si>
   <si>
     <t>[[131072, 128], [[8261], [2559]]]</t>
@@ -5225,10 +5225,10 @@
     <t>[8261, 2559]</t>
   </si>
   <si>
-    <t>[[3045, 1, 5215], [2559]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_infp16_outfp32_fetch_5_ID485</t>
+    <t>[1372, 1078]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_infp16_outfp32_ID485</t>
   </si>
   <si>
     <t>[[262144, 4096], [[878], [983], [7361], [9152], [6454], [4839], [347], [5174]]]</t>
@@ -5237,10 +5237,10 @@
     <t>[878, 983, 7361, 9152, 6454, 4839, 347, 5174]</t>
   </si>
   <si>
-    <t>[[345, 44, 489], [693, 1, 1, 1, 287], [464, 2838, 1428, 954, 1677], [1831, 1831, 1830, 1830, 1830], [6454], [1, 1, 4837], [174, 173], [1725, 1725, 1724]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_inbf16_outbf16_fetch_5_ID486</t>
+    <t>[73, 88, 6543, 8132, 4785, 2644, 331, 2106]</t>
+  </si>
+  <si>
+    <t>h512_ws4_inbf16_outbf16_ID486</t>
   </si>
   <si>
     <t>[[262144, 512], [[601], [4628], [69872], [9121]]]</t>
@@ -5252,10 +5252,10 @@
     <t>[601, 4628, 69872, 9121]</t>
   </si>
   <si>
-    <t>[[237, 109, 95, 160], [4628], [1, 6988, 27948, 20961, 13974], [8202, 919]]</t>
-  </si>
-  <si>
-    <t>h786_ws4_infp32_outfp16_fetch_2_ID487</t>
+    <t>[596, 3792, 68928, 89]</t>
+  </si>
+  <si>
+    <t>h786_ws4_infp32_outfp16_ID487</t>
   </si>
   <si>
     <t>[[782653, 786], [[49514], [1660], [869], [4770]]]</t>
@@ -5273,10 +5273,10 @@
     <t>[49514, 1660, 869, 4770]</t>
   </si>
   <si>
-    <t>[[16948, 32566], [1660], [435, 434], [4770]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_inbf16_outfp16_fetch_5_ID488</t>
+    <t>[5256, 768, 366, 3963]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_inbf16_outfp16_ID488</t>
   </si>
   <si>
     <t>[[728381, 4096], [[842], [30625], [9756], [9399]]]</t>
@@ -5291,10 +5291,10 @@
     <t>[842, 30625, 9756, 9399]</t>
   </si>
   <si>
-    <t>[[702, 1, 139], [4816, 25809], [1, 977, 3901, 2926, 1951], [1879, 2818, 3757, 944, 1]]</t>
-  </si>
-  <si>
-    <t>h420_ws4_inbf16_outfp32_fetch_6_ID489</t>
+    <t>[81, 28998, 9334, 779]</t>
+  </si>
+  <si>
+    <t>h420_ws4_inbf16_outfp32_ID489</t>
   </si>
   <si>
     <t>[[441130, 420], [[61775], [43177], [96495], [77877]]]</t>
@@ -5312,10 +5312,10 @@
     <t>[61775, 43177, 96495, 77877]</t>
   </si>
   <si>
-    <t>[[1, 23167, 23164, 15443], [43177], [69197, 27298], [12980, 12980, 12980, 12979, 12979, 12979]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp16_outfp16_fetch_7_ID490</t>
+    <t>[59311, 22767, 43721, 71065]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp16_outfp16_ID490</t>
   </si>
   <si>
     <t>[[262144, 4096], [[81031], [2244]]]</t>
@@ -5324,10 +5324,10 @@
     <t>[81031, 2244]</t>
   </si>
   <si>
-    <t>[[11576, 11576, 11576, 11576, 11576, 11576, 11575], [2244]]</t>
-  </si>
-  <si>
-    <t>h151_ws8_inbf16_outfp32_fetch_6_ID491</t>
+    <t>[55974, 1321]</t>
+  </si>
+  <si>
+    <t>h151_ws8_inbf16_outfp32_ID491</t>
   </si>
   <si>
     <t>[[489476, 151], [[7475], [9952], [8015], [8389], [8795], [456], [6967], [252]]]</t>
@@ -5345,10 +5345,10 @@
     <t>[7475, 9952, 8015, 8389, 8795, 456, 6967, 252]</t>
   </si>
   <si>
-    <t>[[3738, 3737], [1990, 2985, 3980, 996, 1], [2004, 2004, 2004, 2003], [1, 3146, 3145, 2097], [1759, 1759, 1759, 1759, 1759], [114, 114, 114, 114], [1, -1158, 2901, 2321, 1741, 1161], [126, 126]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outfp32_fetch_8_ID492</t>
+    <t>[6619, 222, 3671, 8290, 706, 243, 4149, 246]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outfp32_ID492</t>
   </si>
   <si>
     <t>[[590678, 512], [[16870], [68807], [91], [37], [216], [2323], [9077], [434], [1024], [65510], [14033], [256], [9613], [13131], [1384], [1438]]]</t>
@@ -5363,10 +5363,10 @@
     <t>[16870, 68807, 91, 37, 216, 2323, 9077, 434, 1024, 65510, 14033, 256, 9613, 13131, 1384, 1438]</t>
   </si>
   <si>
-    <t>[[16870], [13761, 20641, 27521, 6883, 1], [91], [18, 19], [216], [2323], [2269, 3403, 3404, 1], [217, 217], [1024], [28469, 4471, 15793, 16777], [14033], [256], [1202, 1202, 1202, 1202, 1202, 1201, 1201, 1201], [13131], [1384], [1438]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp32_outfp32_fetch_4_ID493</t>
+    <t>[4421, 68606, 36, 14, 203, 989, 8935, 216, 858, 60189, 6802, 70, 794, 11857, 963, 651]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp32_outfp32_ID493</t>
   </si>
   <si>
     <t>[[587591, 512], [[94783], [69743], [6809], [6572], [52821], [23892], [4096], [4926]]]</t>
@@ -5381,10 +5381,10 @@
     <t>[94783, 69743, 6809, 6572, 52821, 23892, 4096, 4926]</t>
   </si>
   <si>
-    <t>[[54348, 1, 1, 40433], [1, 1, 1, 69740], [3404, 3405], [1, 2464, 2464, 1643], [19027, 1747, 6095, 25952], [8910, 14982], [1024, 1536, 1535, 1], [3596, 1, 1, 1328]]</t>
-  </si>
-  <si>
-    <t>h3981_ws4_infp16_outfp16_fetch_4_ID494</t>
+    <t>[81490, 34509, 335, 417, 51529, 19027, 2018, 4724]</t>
+  </si>
+  <si>
+    <t>h3981_ws4_infp16_outfp16_ID494</t>
   </si>
   <si>
     <t>[[319392, 3981], [[19821], [92], [8151], [7443]]]</t>
@@ -5402,10 +5402,10 @@
     <t>[19821, 92, 8151, 7443]</t>
   </si>
   <si>
-    <t>[[19821], [1, 91], [8151], [1, 2792, 2790, 1860]]</t>
-  </si>
-  <si>
-    <t>h1386_ws8_infp16_outfp32_fetch_6_ID495</t>
+    <t>[16645, 21, 361, 396]</t>
+  </si>
+  <si>
+    <t>h1386_ws8_infp16_outfp32_ID495</t>
   </si>
   <si>
     <t>[[507813, 1386], [[22330], [56253], [512], [73061], [6935], [844], [290], [48889]]]</t>
@@ -5423,10 +5423,10 @@
     <t>[22330, 56253, 512, 73061, 6935, 844, 290, 48889]</t>
   </si>
   <si>
-    <t>[[3741, 18589], [28127, 28126], [256, 256], [36531, 36530], [2025, 1918, 954, 278, 301, 1459], [211, 211, 211, 211], [290], [4080, 44809]]</t>
-  </si>
-  <si>
-    <t>h1024_ws2_infp32_outbf16_fetch_4_ID496</t>
+    <t>[22215, 48076, 470, 71011, 4050, 818, 10, 44256]</t>
+  </si>
+  <si>
+    <t>h1024_ws2_infp32_outbf16_ID496</t>
   </si>
   <si>
     <t>[[582332, 1024], [[39587], [6209]]]</t>
@@ -5441,10 +5441,10 @@
     <t>[39587, 6209]</t>
   </si>
   <si>
-    <t>[[39587], [1552, 2328, 2328, 1]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp32_outfp16_fetch_3_ID497</t>
+    <t>[15841, 5874]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp32_outfp16_ID497</t>
   </si>
   <si>
     <t>[[65536, 4096], [[3583], [5652]]]</t>
@@ -5453,10 +5453,10 @@
     <t>[3583, 5652]</t>
   </si>
   <si>
-    <t>[[3583], [3993, 1, 1658]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_infp32_outfp16_fetch_5_ID498</t>
+    <t>[1556, 137]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_infp32_outfp16_ID498</t>
   </si>
   <si>
     <t>[[155294, 2048], [[5059], [7244], [71], [67271], [8192], [726], [39500], [3100]]]</t>
@@ -5471,10 +5471,10 @@
     <t>[5059, 7244, 71, 67271, 8192, 726, 39500, 3100]</t>
   </si>
   <si>
-    <t>[[2530, 2529], [7244], [29, 42], [16818, 16818, 16818, 16817], [1, 820, 3276, 2457, 1638], [1, 725], [39500], [1550, 1550]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_infp16_outfp16_fetch_3_ID499</t>
+    <t>[4733, 344, 57, 67123, 3892, 670, 915, 1602]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_infp16_outfp16_ID499</t>
   </si>
   <si>
     <t>[[101981, 2048], [[868], [69735]]]</t>
@@ -5489,10 +5489,10 @@
     <t>[868, 69735]</t>
   </si>
   <si>
-    <t>[[146, 433, 289], [34867, 34868]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_inbf16_outbf16_fetch_6_ID500</t>
+    <t>[61, 67903]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_inbf16_outbf16_ID500</t>
   </si>
   <si>
     <t>[[16384, 4096], [[44519], [5188], [34639], [2769], [2496], [52], [5831], [18], [6039], [8989], [295], [3657], [6499], [9605], [107], [965]]]</t>
@@ -5501,10 +5501,10 @@
     <t>[44519, 5188, 34639, 2769, 2496, 52, 5831, 18, 6039, 8989, 295, 3657, 6499, 9605, 107, 965]</t>
   </si>
   <si>
-    <t>[[14840, 14840, 14839], [1297, 1945, 1945, 1], [34639], [1384, 1385], [2496], [52], [2916, 2915], [18], [6039], [5974, 1, 1, 1, 3012], [147, 148], [1829, 1828], [2167, 2166, 2166], [1600, 2400, 3200, 4000, -1596, 1], [107], [483, 482]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outfp16_fetch_5_ID501</t>
+    <t>[463, 5015, 16519, 162, 454, 25, 4696, 10, 2130, 8550, 58, 260, 2469, 9484, 2, 48]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outfp16_ID501</t>
   </si>
   <si>
     <t>[[524288, 256], [[33177], [6372], [6962], [449]]]</t>
@@ -5513,10 +5513,10 @@
     <t>[33177, 6372, 6962, 449]</t>
   </si>
   <si>
-    <t>[[18387, 1, 14789], [1274, 1911, 2548, 638, 1], [2320, 3480, 1162], [449]]</t>
-  </si>
-  <si>
-    <t>h3477_ws16_infp32_outfp16_fetch_8_ID502</t>
+    <t>[26990, 6067, 321, 1]</t>
+  </si>
+  <si>
+    <t>h3477_ws16_infp32_outfp16_ID502</t>
   </si>
   <si>
     <t>[[8192, 3477], [[3760], [21123], [2048], [52683], [74839], [5047], [2774], [45271], [5032], [1618], [55946], [21378], [132], [88768], [203], [9308]]]</t>
@@ -5528,10 +5528,10 @@
     <t>[3760, 21123, 2048, 52683, 74839, 5047, 2774, 45271, 5032, 1618, 55946, 21378, 132, 88768, 203, 9308]</t>
   </si>
   <si>
-    <t>[[3760], [10561, 10562], [881, 1167], [1342, 19091, 32250], [18709, 28063, 28066, 1], [5047], [1, 2773], [45271], [1, 1, 5030], [1618], [1, 20980, 20979, 13986], [10689, 10689], [132], [1, -14791, 36985, 29588, 22191, 14794], [203], [1163, 1744, 2325, 2906, 3487, 4068, -6386, 1]]</t>
-  </si>
-  <si>
-    <t>h483_ws8_inbf16_outfp16_fetch_4_ID503</t>
+    <t>[491, 1762, 1436, 2683, 57546, 59, 2626, 769, 2997, 148, 6260, 19703, 29, 47699, 201, 8900]</t>
+  </si>
+  <si>
+    <t>h483_ws8_inbf16_outfp16_ID503</t>
   </si>
   <si>
     <t>[[4096, 483], [[462], [34739], [1308], [64], [11899], [46524], [40349], [1638]]]</t>
@@ -5543,10 +5543,10 @@
     <t>[462, 34739, 1308, 64, 11899, 46524, 40349, 1638]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 459], [11580, 11580, 11579], [1308], [7, 17, 40], [11899], [1, 1, 1, 46521], [40349], [1638]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outfp32_fetch_5_ID504</t>
+    <t>[423, 3968, 54, 14, 10204, 22878, 2205, 69]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outfp32_ID504</t>
   </si>
   <si>
     <t>[[524288, 512], [[7012], [22551], [288], [42880], [47859], [5916], [803], [40], [9422], [22187], [77232], [954], [28787], [787], [10998], [1954]]]</t>
@@ -5558,10 +5558,10 @@
     <t>[7012, 22551, 288, 42880, 47859, 5916, 803, 40, 9422, 22187, 77232, 954, 28787, 787, 10998, 1954]</t>
   </si>
   <si>
-    <t>[[3101, 1231, 290, 2390], [5267, 17284], [144, 144], [7148, 21439, 14293], [45545, 1, 1, 2312], [1, 5915], [378, 425], [40], [2355, 3532, 3534, 1], [22187], [77232], [487, 1, 1, 1, 464], [14393, 14394], [787], [10998], [1954]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_infp16_outfp16_fetch_7_ID505</t>
+    <t>[6872, 4631, 233, 21067, 35184, 5344, 58, 37, 8694, 17784, 331, 219, 589, 14, 8313, 1573]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_infp16_outfp16_ID505</t>
   </si>
   <si>
     <t>[[131072, 2048], [[964], [6538], [29260], [9741]]]</t>
@@ -5570,10 +5570,10 @@
     <t>[964, 6538, 29260, 9741]</t>
   </si>
   <si>
-    <t>[[964], [2043, 174, 1485, 1372, 1464], [29260], [1, 1, 1, 1, 1, 1, 9735]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_infp16_outbf16_fetch_6_ID506</t>
+    <t>[546, 3799, 16343, 4637]</t>
+  </si>
+  <si>
+    <t>h256_ws8_infp16_outbf16_ID506</t>
   </si>
   <si>
     <t>[[69880, 256], [[42137], [7793], [65465], [21345], [37936], [9052], [125], [34857]]]</t>
@@ -5588,10 +5588,10 @@
     <t>[42137, 7793, 65465, 21345, 37936, 9052, 125, 34857]</t>
   </si>
   <si>
-    <t>[[21069, 21068], [1559, 1559, 1559, 1558, 1558], [65465], [6619, 14726], [37936], [1509, 1509, 1509, 1509, 1508, 1508], [125], [17428, 17429]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp32_outfp32_fetch_2_ID507</t>
+    <t>[34731, 3502, 52597, 1655, 19371, 48, 11, 3162]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp32_outfp32_ID507</t>
   </si>
   <si>
     <t>[[763904, 4096], [[3336], [4968], [2739], [4417]]]</t>
@@ -5606,10 +5606,10 @@
     <t>[3336, 4968, 2739, 4417]</t>
   </si>
   <si>
-    <t>[[3336], [2484, 2484], [2739], [4417]]</t>
-  </si>
-  <si>
-    <t>h1757_ws4_infp32_outfp32_fetch_3_ID508</t>
+    <t>[1720, 4499, 2459, 2568]</t>
+  </si>
+  <si>
+    <t>h1757_ws4_infp32_outfp32_ID508</t>
   </si>
   <si>
     <t>[[65536, 1757], [[7874], [2651], [2323], [44585]]]</t>
@@ -5621,10 +5621,10 @@
     <t>[7874, 2651, 2323, 44585]</t>
   </si>
   <si>
-    <t>[[2175, 980, 4719], [2651], [2323], [20789, 23796]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp16_outbf16_fetch_3_ID509</t>
+    <t>[584, 980, 64, 36235]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp16_outbf16_ID509</t>
   </si>
   <si>
     <t>[[65536, 128], [[37558], [3695]]]</t>
@@ -5633,10 +5633,10 @@
     <t>[37558, 3695]</t>
   </si>
   <si>
-    <t>[[23656, 13902], [1232, 1232, 1231]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_infp32_outfp32_fetch_5_ID510</t>
+    <t>[3028, 3108]</t>
+  </si>
+  <si>
+    <t>h512_ws16_infp32_outfp32_ID510</t>
   </si>
   <si>
     <t>[[262144, 512], [[46140], [7874], [2232], [980], [4045], [3582], [5509], [2048], [28772], [43305], [1225], [2530], [55466], [76846], [25447], [38772]]]</t>
@@ -5645,10 +5645,10 @@
     <t>[46140, 7874, 2232, 980, 4045, 3582, 5509, 2048, 28772, 43305, 1225, 2530, 55466, 76846, 25447, 38772]</t>
   </si>
   <si>
-    <t>[[1, 17302, 17302, 11535], [2805, 1238, 275, 3556], [245, 1987], [194, 128, 121, 224, 313], [1, 1517, 1516, 1011], [1791, 1791], [5509], [2048], [28772], [2139, 5328, 35838], [1225], [1265, 1265], [1, 20800, 20799, 13866], [1, 28818, 28816, 19211], [12723, 12724], [12924, 12924, 12924]]</t>
-  </si>
-  <si>
-    <t>h64_ws16_infp16_outbf16_fetch_5_ID511</t>
+    <t>[45383, 7681, 35, 951, 2173, 1545, 5301, 1965, 27580, 23947, 730, 874, 39407, 6023, 2139, 76]</t>
+  </si>
+  <si>
+    <t>h64_ws16_infp16_outbf16_ID511</t>
   </si>
   <si>
     <t>[[219088, 64], [[224], [594], [23828], [48088], [18550], [1450], [2334], [777], [37024], [6821], [33], [18907], [49204], [15654], [14900], [23427]]]</t>
@@ -5663,10 +5663,10 @@
     <t>[224, 594, 23828, 48088, 18550, 1450, 2334, 777, 37024, 6821, 33, 18907, 49204, 15654, 14900, 23427]</t>
   </si>
   <si>
-    <t>[[224], [119, 119, 119, 119, 118], [11914, 11914], [48088], [18550], [1450], [1167, 1167], [133, 316, 78, 40, 210], [37024], [6446, 1, 374], [33], [18907], [24602, 24602], [15654], [14900], [1940, 21487]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_inbf16_outfp16_fetch_2_ID512</t>
+    <t>[33, 271, 9577, 47265, 70, 86, 132, 265, 19795, 209, 28, 1395, 19841, 225, 1185, 1176]</t>
+  </si>
+  <si>
+    <t>h128_ws2_inbf16_outfp16_ID512</t>
   </si>
   <si>
     <t>[[435045, 128], [[66], [521]]]</t>
@@ -5681,10 +5681,10 @@
     <t>[66, 521]</t>
   </si>
   <si>
-    <t>[[10, 56], [251, 270]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp32_outfp16_fetch_2_ID513</t>
+    <t>[61, 22]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp32_outfp16_ID513</t>
   </si>
   <si>
     <t>[[2718, 128], [[26], [512]]]</t>
@@ -5699,10 +5699,10 @@
     <t>[26, 512]</t>
   </si>
   <si>
-    <t>[[13, 13], [256, 256]]</t>
-  </si>
-  <si>
-    <t>h4021_ws8_infp32_outfp32_fetch_8_ID514</t>
+    <t>[23, 7]</t>
+  </si>
+  <si>
+    <t>h4021_ws8_infp32_outfp32_ID514</t>
   </si>
   <si>
     <t>[[626595, 4021], [[4409], [524], [38229], [6210], [6304], [5226], [96], [96132]]]</t>
@@ -5720,10 +5720,10 @@
     <t>[4409, 524, 38229, 6210, 6304, 5226, 96, 96132]</t>
   </si>
   <si>
-    <t>[[4409], [1, 55, 208, 156, 104], [19115, 19114], [1, 1, 1, 1, 6206], [1, 633, 2520, 1890, 1260], [1724, 1361, 2141], [85, 1, 10], [12017, 12017, 12017, 12017, 12016, 12016, 12016, 12016]]</t>
-  </si>
-  <si>
-    <t>h2058_ws16_inbf16_outfp32_fetch_8_ID515</t>
+    <t>[1909, 425, 1963, 6190, 1115, 5011, 85, 94833]</t>
+  </si>
+  <si>
+    <t>h2058_ws16_inbf16_outfp32_ID515</t>
   </si>
   <si>
     <t>[[16384, 2058], [[389], [56234], [10674], [5496], [1396], [12984], [40366], [6423], [4096], [40694], [2048], [3358], [42734], [91916], [1024], [6849]]]</t>
@@ -5735,10 +5735,10 @@
     <t>[389, 56234, 10674, 5496, 1396, 12984, 40366, 6423, 4096, 40694, 2048, 3358, 42734, 91916, 1024, 6849]</t>
   </si>
   <si>
-    <t>[[129, 193, 67], [56234], [10674], [916, 2748, 1832], [1396], [12984], [13455, 20182, 6729], [1947, 432, 4044], [1, 1535, 1536, 1024], [20347, 20347], [2048], [1, 1, 3356], [3855, 19256, 141, 19482], [11489, 17233, 22977, 28721, 34465, 40209, -63179, 1], [1024], [1142, 3424, 2283]]</t>
-  </si>
-  <si>
-    <t>h1802_ws4_infp16_outbf16_fetch_3_ID516</t>
+    <t>[5, 37650, 10337, 4975, 868, 12281, 1036, 3893, 2143, 37533, 38, 3332, 8163, 15419, 18, 6437]</t>
+  </si>
+  <si>
+    <t>h1802_ws4_infp16_outbf16_ID516</t>
   </si>
   <si>
     <t>[[4096, 1802], [[25601], [9659], [55], [123]]]</t>
@@ -5750,10 +5750,10 @@
     <t>[25601, 9659, 55, 123]</t>
   </si>
   <si>
-    <t>[[25601], [3219, 4828, 1612], [28, 27], [123]]</t>
-  </si>
-  <si>
-    <t>h4023_ws4_inbf16_outfp16_fetch_2_ID517</t>
+    <t>[23192, 9185, 54, 68]</t>
+  </si>
+  <si>
+    <t>h4023_ws4_inbf16_outfp16_ID517</t>
   </si>
   <si>
     <t>[[65536, 4023], [[36396], [99613], [3832], [42724]]]</t>
@@ -5765,10 +5765,10 @@
     <t>[36396, 99613, 3832, 42724]</t>
   </si>
   <si>
-    <t>[[18198, 18198], [99613], [3832], [42724]]</t>
-  </si>
-  <si>
-    <t>h385_ws8_infp16_outfp32_fetch_6_ID518</t>
+    <t>[34749, 50031, 132, 1772]</t>
+  </si>
+  <si>
+    <t>h385_ws8_infp16_outfp32_ID518</t>
   </si>
   <si>
     <t>[[498826, 385], [[74360], [5183], [9424], [42709], [46870], [11101], [87547], [72769]]]</t>
@@ -5786,10 +5786,10 @@
     <t>[74360, 5183, 9424, 42709, 46870, 11101, 87547, 72769]</t>
   </si>
   <si>
-    <t>[[37180, 37180], [2837, 1, 2345], [3541, 2393, 3490], [14236, 21354, 7119], [1, 46869], [11101], [14592, 14591, 14591, 14591, 14591, 14591], [25803, 46966]]</t>
-  </si>
-  <si>
-    <t>h3826_ws8_infp16_outfp16_fetch_5_ID519</t>
+    <t>[63586, 4269, 886, 19862, 1620, 634, 46575, 33065]</t>
+  </si>
+  <si>
+    <t>h3826_ws8_infp16_outfp16_ID519</t>
   </si>
   <si>
     <t>[[4096, 3826], [[11854], [512], [929], [1954], [23951], [860], [5863], [66]]]</t>
@@ -5801,10 +5801,10 @@
     <t>[11854, 512, 929, 1954, 23951, 860, 5863, 66]</t>
   </si>
   <si>
-    <t>[[11854], [1, 52, 204, 153, 102], [233, 232, 232, 232], [1954], [23951], [82, 187, 77, 514], [1173, 1173, 1173, 1172, 1172], [66]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_inbf16_outfp16_fetch_7_ID520</t>
+    <t>[11767, 484, 529, 973, 3077, 164, 154, 6]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_inbf16_outfp16_ID520</t>
   </si>
   <si>
     <t>[[458313, 4096], [[256], [75929], [3248], [7825]]]</t>
@@ -5819,10 +5819,10 @@
     <t>[256, 75929, 3248, 7825]</t>
   </si>
   <si>
-    <t>[[202, 54], [10847, 10847, 10847, 10847, 10847, 10847, 10847], [1624, 1624], [1, -1304, 3260, 2608, 1956, 1304]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outbf16_fetch_3_ID521</t>
+    <t>[237, 70624, 1190, 3803]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outbf16_ID521</t>
   </si>
   <si>
     <t>[[877895, 256], [[978], [7710], [21635], [33332]]]</t>
@@ -5837,10 +5837,10 @@
     <t>[978, 7710, 21635, 33332]</t>
   </si>
   <si>
-    <t>[[978], [980, 549, 6181], [10818, 10817], [16666, 16666]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_inbf16_outfp16_fetch_8_ID522</t>
+    <t>[482, 625, 18076, 30350]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_inbf16_outfp16_ID522</t>
   </si>
   <si>
     <t>[[16384, 2048], [[495], [11382], [192], [9487], [22299], [12744], [38898], [9266]]]</t>
@@ -5849,10 +5849,10 @@
     <t>[495, 11382, 192, 9487, 22299, 12744, 38898, 9266]</t>
   </si>
   <si>
-    <t>[[48, 447], [11382], [192], [9487], [22299], [12744], [38898], [591, 3648, 1784, 1092, 733, 666, 195, 557]]</t>
-  </si>
-  <si>
-    <t>h3619_ws16_inbf16_outbf16_fetch_6_ID523</t>
+    <t>[89, 3069, 186, 7649, 9183, 5528, 31153, 1182]</t>
+  </si>
+  <si>
+    <t>h3619_ws16_inbf16_outbf16_ID523</t>
   </si>
   <si>
     <t>[[604866, 3619], [[8192], [84390], [8703], [941], [90846], [1148], [7440], [33811], [8803], [26577], [8192], [5267], [61], [4473], [500], [13402]]]</t>
@@ -5870,10 +5870,10 @@
     <t>[8192, 84390, 8703, 941, 90846, 1148, 7440, 33811, 8803, 26577, 8192, 5267, 61, 4473, 500, 13402]</t>
   </si>
   <si>
-    <t>[[1367, 4095, 2730], [21098, 21098, 21097, 21097], [2176, 2176, 2176, 2175], [470, 471], [30282, 45423, 15141], [1148], [1240, 1240, 1240, 1240, 1240, 1240], [13391, 7061, 13359], [2200, 3300, 3302, 1], [13289, 13288], [1365, 2047, 2729, 3411, -1361, 1], [5267], [61], [2237, 2236], [500], [13402]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp32_outfp32_fetch_4_ID524</t>
+    <t>[7052, 40283, 3942, 20, 3321, 630, 4426, 26781, 8116, 1805, 7699, 27, 25, 1947, 450, 3042]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp32_outfp32_ID524</t>
   </si>
   <si>
     <t>[[65536, 4096], [[1180], [9048]]]</t>
@@ -5882,10 +5882,10 @@
     <t>[1180, 9048]</t>
   </si>
   <si>
-    <t>[[1180], [307, 56, 4320, 4365]]</t>
-  </si>
-  <si>
-    <t>h2335_ws8_infp16_outfp16_fetch_3_ID525</t>
+    <t>[542, 1090]</t>
+  </si>
+  <si>
+    <t>h2335_ws8_infp16_outfp16_ID525</t>
   </si>
   <si>
     <t>[[32768, 2335], [[17628], [3798], [49209], [724], [8215], [12224], [26074], [41055]]]</t>
@@ -5897,10 +5897,10 @@
     <t>[17628, 3798, 49209, 724, 8215, 12224, 26074, 41055]</t>
   </si>
   <si>
-    <t>[[17628], [1266, 1899, 633], [49209], [362, 362], [4108, 4107], [12224], [13037, 13037], [16860, 24195]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp32_outbf16_fetch_6_ID526</t>
+    <t>[1090, 37, 23092, 663, 4245, 12046, 9634, 20377]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp32_outbf16_ID526</t>
   </si>
   <si>
     <t>[[4096, 4096], [[512], [402], [7534], [9381]]]</t>
@@ -5912,10 +5912,10 @@
     <t>[512, 402, 7534, 9381]</t>
   </si>
   <si>
-    <t>[[60, 142, 9, 10, 291], [134, 134, 134], [1798, 2277, 549, 707, 444, 1759], [1, 938, 3752, 2814, 1876]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_infp32_outfp16_fetch_3_ID527</t>
+    <t>[240, 17, 3739, 5159]</t>
+  </si>
+  <si>
+    <t>h256_ws8_infp32_outfp16_ID527</t>
   </si>
   <si>
     <t>[[453260, 256], [[2048], [20591], [4959], [1528], [31], [41047], [34074], [16100]]]</t>
@@ -5930,10 +5930,10 @@
     <t>[2048, 20591, 4959, 1528, 31, 41047, 34074, 16100]</t>
   </si>
   <si>
-    <t>[[1024, 1024], [10295, 10296], [4959], [1528], [1, 1, 29], [41047], [11358, 17037, 5679], [16100]]</t>
-  </si>
-  <si>
-    <t>h1484_ws8_infp16_outfp16_fetch_4_ID528</t>
+    <t>[1410, 19581, 382, 816, 27, 869, 14184, 4145]</t>
+  </si>
+  <si>
+    <t>h1484_ws8_infp16_outfp16_ID528</t>
   </si>
   <si>
     <t>[[328109, 1484], [[47197], [8682], [3864], [26249], [4096], [4189], [477], [1381]]]</t>
@@ -5951,10 +5951,10 @@
     <t>[47197, 8682, 3864, 26249, 4096, 4189, 477, 1381]</t>
   </si>
   <si>
-    <t>[[7867, 23598, 15732], [1, 3256, 3255, 2170], [1288, 1932, 644], [26249], [1, 1535, 1536, 1024], [525, 3664], [239, 238], [1381]]</t>
-  </si>
-  <si>
-    <t>h3155_ws4_infp16_outbf16_fetch_8_ID529</t>
+    <t>[3967, 7532, 3862, 25453, 146, 4061, 44, 398]</t>
+  </si>
+  <si>
+    <t>h3155_ws4_infp16_outbf16_ID529</t>
   </si>
   <si>
     <t>[[131072, 3155], [[19976], [25515], [8192], [4342]]]</t>
@@ -5969,10 +5969,10 @@
     <t>[19976, 25515, 8192, 4342]</t>
   </si>
   <si>
-    <t>[[19976], [25515], [1, -5633, 3584, 3072, 2560, 2048, 1536, 1024], [1827, 1159, 1356]]</t>
-  </si>
-  <si>
-    <t>h64_ws8_infp32_outfp16_fetch_8_ID530</t>
+    <t>[237, 4830, 454, 4041]</t>
+  </si>
+  <si>
+    <t>h64_ws8_infp32_outfp16_ID530</t>
   </si>
   <si>
     <t>[[8192, 64], [[56926], [46525], [49758], [7444], [1550], [671], [83173], [29151]]]</t>
@@ -5981,10 +5981,10 @@
     <t>[56926, 46525, 49758, 7444, 1550, 671, 83173, 29151]</t>
   </si>
   <si>
-    <t>[[56926], [15508, 23262, 7755], [49758], [1, 1, 1, 1, 1, 1, 7438], [1550], [167, 250, 253, 1], [10396, 15594, 20792, 25990, 31188, 36386, -57174, 1], [14576, 14575]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outfp32_fetch_8_ID531</t>
+    <t>[30408, 2195, 25455, 1425, 797, 647, 79630, 28181]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outfp32_ID531</t>
   </si>
   <si>
     <t>[[4096, 256], [[94745], [854], [6755], [2470], [25], [4265], [16044], [19670], [9467], [38], [9070], [95813], [26505], [415], [368], [73090]]]</t>
@@ -5993,10 +5993,10 @@
     <t>[94745, 854, 6755, 2470, 25, 4265, 16044, 19670, 9467, 38, 9070, 95813, 26505, 415, 368, 73090]</t>
   </si>
   <si>
-    <t>[[94745], [1, 1, 1, 851], [1351, 1351, 1351, 1351, 1351], [1235, 1235], [25], [2219, 1, 1, 2044], [16044], [19670], [3698, 240, 2171, 1126, 586, 193, 556, 897], [19, 19], [9070], [47218, 18962, 719, 7629, 6844, 1135, 13306], [6239, 20266], [208, 207], [99, 269], [1, -12175, 30451, 24361, 18271, 12181]]</t>
-  </si>
-  <si>
-    <t>h3729_ws4_infp32_outfp32_fetch_3_ID532</t>
+    <t>[44675, 851, 1169, 1467, 24, 412, 15376, 15823, 588, 22, 7396, 55688, 9361, 52, 149, 51004]</t>
+  </si>
+  <si>
+    <t>h3729_ws4_infp32_outfp32_ID532</t>
   </si>
   <si>
     <t>[[524288, 3729], [[3406], [599], [1168], [92764]]]</t>
@@ -6008,10 +6008,10 @@
     <t>[3406, 599, 1168, 92764]</t>
   </si>
   <si>
-    <t>[[3406], [46, 207, 346], [1168], [23821, 68943]]</t>
-  </si>
-  <si>
-    <t>h128_ws8_infp32_outbf16_fetch_7_ID533</t>
+    <t>[3276, 321, 1103, 85164]</t>
+  </si>
+  <si>
+    <t>h128_ws8_infp32_outbf16_ID533</t>
   </si>
   <si>
     <t>[[262144, 128], [[7067], [7754], [42013], [4068], [19183], [2841], [1412], [2992]]]</t>
@@ -6020,10 +6020,10 @@
     <t>[7067, 7754, 42013, 4068, 19183, 2841, 1412, 2992]</t>
   </si>
   <si>
-    <t>[[2872, 789, 257, 231, 1280, 767, 871], [1, 1, 1, 7751], [42013], [1356, 2034, 678], [19183], [2841], [1412], [2992]]</t>
-  </si>
-  <si>
-    <t>h1020_ws8_inbf16_outfp32_fetch_6_ID534</t>
+    <t>[5744, 257, 23316, 70, 1036, 2303, 1355, 159]</t>
+  </si>
+  <si>
+    <t>h1020_ws8_inbf16_outfp32_ID534</t>
   </si>
   <si>
     <t>[[16384, 1020], [[4255], [3541], [8002], [17], [623], [2048], [512], [1024]]]</t>
@@ -6035,10 +6035,10 @@
     <t>[4255, 3541, 8002, 17, 623, 2048, 512, 1024]</t>
   </si>
   <si>
-    <t>[[631, 755, 2869], [526, 3015], [1333, 1999, 2665, 3331, -1327, 1], [17], [623], [2048], [256, 256], [1024]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_infp16_outbf16_fetch_7_ID535</t>
+    <t>[315, 391, 2101, 6, 586, 830, 251, 864]</t>
+  </si>
+  <si>
+    <t>h512_ws4_infp16_outbf16_ID535</t>
   </si>
   <si>
     <t>[[65536, 512], [[528], [7625], [945], [2769]]]</t>
@@ -6047,10 +6047,10 @@
     <t>[528, 7625, 945, 2769]</t>
   </si>
   <si>
-    <t>[[25, 248, 255], [6304, 1, 1, 1, 1, 1, 1316], [315, 315, 315], [1384, 1385]]</t>
-  </si>
-  <si>
-    <t>h128_ws8_infp16_outbf16_fetch_8_ID536</t>
+    <t>[52, 391, 911, 2]</t>
+  </si>
+  <si>
+    <t>h128_ws8_infp16_outbf16_ID536</t>
   </si>
   <si>
     <t>[[772212, 128], [[44902], [1020], [7164], [8059], [22203], [7576], [43], [3631]]]</t>
@@ -6065,10 +6065,10 @@
     <t>[44902, 1020, 7164, 8059, 22203, 7576, 43, 3631]</t>
   </si>
   <si>
-    <t>[[44902], [1020], [1, -1195, 2985, 2388, 1791, 1194], [1, 1, 1, 1, 1, 1, 1, 8052], [22203], [3788, 3788], [21, 22], [1210, 1815, 606]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp32_outbf16_fetch_7_ID537</t>
+    <t>[23627, 72, 6937, 297, 19916, 622, 2, 1676]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp32_outbf16_ID537</t>
   </si>
   <si>
     <t>[[65536, 128], [[26368], [8520]]]</t>
@@ -6077,10 +6077,10 @@
     <t>[26368, 8520]</t>
   </si>
   <si>
-    <t>[[7631, 18737], [1218, 1217, 1217, 1217, 1217, 1217, 1217]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outfp16_fetch_8_ID538</t>
+    <t>[2065, 8076]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outfp16_ID538</t>
   </si>
   <si>
     <t>[[914076, 1024], [[1787], [12680], [430], [2606], [91412], [35283], [45499], [7796]]]</t>
@@ -6095,10 +6095,10 @@
     <t>[1787, 12680, 430, 2606, 91412, 35283, 45499, 7796]</t>
   </si>
   <si>
-    <t>[[1787], [12680], [430], [2606], [1, -62840, 39991, 34278, 28565, 22852, 17139, 11426], [35283], [45499], [1299, 1948, 2597, 3246, -1295, 1]]</t>
-  </si>
-  <si>
-    <t>h3740_ws2_infp32_outfp16_fetch_3_ID539</t>
+    <t>[163, 7352, 95, 1073, 85829, 32155, 21037, 4034]</t>
+  </si>
+  <si>
+    <t>h3740_ws2_infp32_outfp16_ID539</t>
   </si>
   <si>
     <t>[[524288, 3740], [[1718], [34270]]]</t>
@@ -6110,10 +6110,10 @@
     <t>[1718, 34270]</t>
   </si>
   <si>
-    <t>[[1718], [15084, 6706, 12480]]</t>
-  </si>
-  <si>
-    <t>h3612_ws4_inbf16_outfp32_fetch_3_ID540</t>
+    <t>[867, 30168]</t>
+  </si>
+  <si>
+    <t>h3612_ws4_inbf16_outfp32_ID540</t>
   </si>
   <si>
     <t>[[167591, 3612], [[34341], [50], [48146], [5306]]]</t>
@@ -6131,10 +6131,10 @@
     <t>[34341, 50, 48146, 5306]</t>
   </si>
   <si>
-    <t>[[34341], [3, 5, 42], [48146], [5306]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_infp32_outfp32_fetch_6_ID541</t>
+    <t>[16695, 40, 21395, 2326]</t>
+  </si>
+  <si>
+    <t>h256_ws8_infp32_outfp32_ID541</t>
   </si>
   <si>
     <t>[[65536, 256], [[8670], [3851], [6194], [2488], [47991], [27317], [89], [16977]]]</t>
@@ -6143,10 +6143,10 @@
     <t>[8670, 3851, 6194, 2488, 47991, 27317, 89, 16977]</t>
   </si>
   <si>
-    <t>[[2969, 1039, 1511, 1437, 198, 1516], [3851], [3837, 1, 1, 1, 2354], [2488], [23995, 23996], [13658, 13659], [44, 45], [16977]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_inbf16_outfp32_fetch_3_ID542</t>
+    <t>[599, 130, 198, 995, 11740, 22614, 20, 1440]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_inbf16_outfp32_ID542</t>
   </si>
   <si>
     <t>[[745582, 2048], [[3656], [3700], [6980], [383]]]</t>
@@ -6161,10 +6161,10 @@
     <t>[3656, 3700, 6980, 383]</t>
   </si>
   <si>
-    <t>[[1, 3655], [1, 1, 3698], [6980], [191, 192]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_infp16_outfp32_fetch_5_ID543</t>
+    <t>[363, 157, 3146, 363]</t>
+  </si>
+  <si>
+    <t>h256_ws8_infp16_outfp32_ID543</t>
   </si>
   <si>
     <t>[[8192, 256], [[18262], [899], [22133], [55520], [9595], [90153], [7193], [97551]]]</t>
@@ -6173,10 +6173,10 @@
     <t>[18262, 899, 22133, 55520, 9595, 90153, 7193, 97551]</t>
   </si>
   <si>
-    <t>[[18262], [180, 180, 180, 180, 179], [11067, 11066], [13880, 13880, 13880, 13880], [1843, 2351, 2269, 1169, 1963], [22538, 33807, 33807, 1], [3597, 3596], [7089, 4690, 85772]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp32_outfp32_fetch_7_ID544</t>
+    <t>[8903, 39, 21654, 50148, 569, 7028, 255, 90597]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp32_outfp32_ID544</t>
   </si>
   <si>
     <t>[[65536, 256], [[28318], [726], [2100], [11385], [2048], [1773], [4772], [15686], [11268], [399], [54683], [1392], [2410], [6948], [7402], [90455]]]</t>
@@ -6185,10 +6185,10 @@
     <t>[28318, 726, 2100, 11385, 2048, 1773, 4772, 15686, 11268, 399, 54683, 1392, 2410, 6948, 7402, 90455]</t>
   </si>
   <si>
-    <t>[[28318], [363, 363], [2100], [11385], [2048], [1773], [1590, 2385, 797], [15686], [11268], [399], [10936, 16404, 21872, 5470, 1], [1392], [2410], [3474, 3474], [1057, 1585, 2113, 2641, 3169, -3164, 1], [11297, 3830, 8814, 66514]]</t>
-  </si>
-  <si>
-    <t>h4564_ws8_infp16_outbf16_fetch_4_ID545</t>
+    <t>[4674, 605, 2087, 1734, 69, 96, 1902, 899, 286, 39, 1017, 356, 37, 3415, 354, 40587]</t>
+  </si>
+  <si>
+    <t>h4564_ws8_infp16_outbf16_ID545</t>
   </si>
   <si>
     <t>[[65536, 4564], [[1899], [2277], [6551], [44961], [319], [17736], [39736], [22031]]]</t>
@@ -6200,10 +6200,10 @@
     <t>[1899, 2277, 6551, 44961, 319, 17736, 39736, 22031]</t>
   </si>
   <si>
-    <t>[[1899], [2277], [3276, 3275], [1, 16860, 16860, 11240], [1, 318], [17736], [5046, 893, 33797], [11015, 11016]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp32_outfp32_fetch_3_ID546</t>
+    <t>[1597, 2052, 6242, 1131, 146, 8740, 1191, 1643]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp32_outfp32_ID546</t>
   </si>
   <si>
     <t>[[855874, 512], [[60], [1746], [35083], [31382], [462], [1024], [13484], [26036]]]</t>
@@ -6218,10 +6218,10 @@
     <t>[60, 1746, 35083, 31382, 462, 1024, 13484, 26036]</t>
   </si>
   <si>
-    <t>[[60], [1746], [5930, 29153], [31382], [1, 1, 460], [1024], [13484], [13018, 13018]]</t>
-  </si>
-  <si>
-    <t>h2090_ws2_inbf16_outfp32_fetch_8_ID547</t>
+    <t>[54, 1706, 30191, 3586, 449, 947, 5696, 11268]</t>
+  </si>
+  <si>
+    <t>h2090_ws2_inbf16_outfp32_ID547</t>
   </si>
   <si>
     <t>[[524288, 2090], [[100], [8999]]]</t>
@@ -6233,10 +6233,10 @@
     <t>[100, 8999]</t>
   </si>
   <si>
-    <t>[[100], [8009, 1, 1, 1, 1, 1, 1, 984]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_infp16_outbf16_fetch_1_ID548</t>
+    <t>[51, 8339]</t>
+  </si>
+  <si>
+    <t>h64_ws2_infp16_outbf16_ID548</t>
   </si>
   <si>
     <t>[[16384, 64], [[256], [3425]]]</t>
@@ -6245,10 +6245,10 @@
     <t>[256, 3425]</t>
   </si>
   <si>
-    <t>[[256], [3425]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp32_outfp32_fetch_5_ID549</t>
+    <t>[11, 3412]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp32_outfp32_ID549</t>
   </si>
   <si>
     <t>[[908513, 64], [[63267], [9838], [5728], [54358]]]</t>
@@ -6263,10 +6263,10 @@
     <t>[63267, 9838, 5728, 54358]</t>
   </si>
   <si>
-    <t>[[5687, 3938, 25474, 8835, 19333], [9838], [2864, 2864], [10872, 10872, 10872, 10871, 10871]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_inbf16_outbf16_fetch_3_ID550</t>
+    <t>[48149, 2844, 3395, 30869]</t>
+  </si>
+  <si>
+    <t>h512_ws2_inbf16_outbf16_ID550</t>
   </si>
   <si>
     <t>[[32768, 512], [[40889], [7076]]]</t>
@@ -6275,10 +6275,10 @@
     <t>[40889, 7076]</t>
   </si>
   <si>
-    <t>[[40889], [2358, 3537, 1181]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_infp16_outbf16_fetch_2_ID551</t>
+    <t>[4949, 3411]</t>
+  </si>
+  <si>
+    <t>h256_ws2_infp16_outbf16_ID551</t>
   </si>
   <si>
     <t>[[654671, 256], [[4900], [41]]]</t>
@@ -6293,10 +6293,10 @@
     <t>[4900, 41]</t>
   </si>
   <si>
-    <t>[[1652, 3248], [41]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_inbf16_outfp32_fetch_2_ID552</t>
+    <t>[1238, 26]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_inbf16_outfp32_ID552</t>
   </si>
   <si>
     <t>[[8192, 2048], [[19], [35319], [25276], [47252]]]</t>
@@ -6305,10 +6305,10 @@
     <t>[19, 35319, 25276, 47252]</t>
   </si>
   <si>
-    <t>[[19], [35319], [25276], [23626, 23626]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_infp32_outfp16_fetch_5_ID553</t>
+    <t>[17, 6481, 23416, 19437]</t>
+  </si>
+  <si>
+    <t>h256_ws2_infp32_outfp16_ID553</t>
   </si>
   <si>
     <t>[[854419, 256], [[8449], [127]]]</t>
@@ -6323,10 +6323,10 @@
     <t>[8449, 127]</t>
   </si>
   <si>
-    <t>[[670, 774, 2567, 1500, 2938], [127]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp32_outfp16_fetch_3_ID554</t>
+    <t>[4973, 11]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp32_outfp16_ID554</t>
   </si>
   <si>
     <t>[[65536, 1024], [[3825], [63665], [3446], [46]]]</t>
@@ -6335,10 +6335,10 @@
     <t>[3825, 63665, 3446, 46]</t>
   </si>
   <si>
-    <t>[[1913, 1912], [63665], [2327, 1, 1118], [23, 23]]</t>
-  </si>
-  <si>
-    <t>h3713_ws16_inbf16_outfp16_fetch_5_ID555</t>
+    <t>[3477, 37674, 1984, 40]</t>
+  </si>
+  <si>
+    <t>h3713_ws16_inbf16_outfp16_ID555</t>
   </si>
   <si>
     <t>[[566221, 3713], [[264], [825], [60053], [4145], [5632], [1318], [48168], [72], [2730], [18188], [711], [7785], [6293], [832], [45212], [14060]]]</t>
@@ -6356,10 +6356,10 @@
     <t>[264, 825, 60053, 4145, 5632, 1318, 48168, 72, 2730, 18188, 711, 7785, 6293, 832, 45212, 14060]</t>
   </si>
   <si>
-    <t>[[132, 132], [732, 1, 1, 1, 90], [2228, 57825], [2101, 2044], [2280, 3352], [1318], [48168], [12, 36, 24], [1, 2729], [18188], [711], [7785], [2098, 2098, 2097], [208, 208, 208, 208], [11303, 16954, 16954, 1], [14060]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp16_outfp16_fetch_3_ID556</t>
+    <t>[24, 491, 9604, 1790, 140, 1057, 9572, 60, 261, 17186, 5, 7113, 629, 3, 40977, 13411]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp16_outfp16_ID556</t>
   </si>
   <si>
     <t>[[489914, 128], [[22317], [4096]]]</t>
@@ -6374,10 +6374,10 @@
     <t>[22317, 4096]</t>
   </si>
   <si>
-    <t>[[9153, 13164], [684, 2047, 1365]]</t>
-  </si>
-  <si>
-    <t>h2871_ws16_infp32_outbf16_fetch_4_ID557</t>
+    <t>[1049, 4083]</t>
+  </si>
+  <si>
+    <t>h2871_ws16_infp32_outbf16_ID557</t>
   </si>
   <si>
     <t>[[16384, 2871], [[23], [44910], [36548], [4132], [3890], [2998], [8192], [376], [46779], [574], [9366], [9206], [3401], [14995], [5694], [44263]]]</t>
@@ -6389,10 +6389,10 @@
     <t>[23, 44910, 36548, 4132, 3890, 2998, 8192, 376, 46779, 574, 9366, 9206, 3401, 14995, 5694, 44263]</t>
   </si>
   <si>
-    <t>[[23], [14970, 14970, 14970], [6093, 18273, 12182], [1, 1549, 1549, 1033], [3890], [2998], [2048, 3072, 3071, 1], [1, 375], [11695, 11695, 11695, 11694], [46, 12, 209, 307], [1, 3513, 3511, 2341], [4444, 1302, 3460], [1701, 1700], [14995], [3293, 2401], [44263]]</t>
-  </si>
-  <si>
-    <t>h1024_ws2_infp16_outbf16_fetch_6_ID558</t>
+    <t>[12, 1014, 34440, 3739, 1782, 791, 278, 57, 25845, 91, 4580, 8963, 2788, 5207, 63, 22093]</t>
+  </si>
+  <si>
+    <t>h1024_ws2_infp16_outbf16_ID558</t>
   </si>
   <si>
     <t>[[134218, 1024], [[1024], [9513]]]</t>
@@ -6407,10 +6407,10 @@
     <t>[1024, 9513]</t>
   </si>
   <si>
-    <t>[[1024], [1022, 3077, 1096, 1030, 430, 2858]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp16_outbf16_fetch_4_ID559</t>
+    <t>[969, 5325]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp16_outbf16_ID559</t>
   </si>
   <si>
     <t>[[405282, 256], [[65], [32305], [3280], [369], [6480], [104], [84582], [37440], [8192], [809], [14981], [73502], [33522], [230], [28688], [492]]]</t>
@@ -6425,10 +6425,10 @@
     <t>[65, 32305, 3280, 369, 6480, 104, 84582, 37440, 8192, 809, 14981, 73502, 33522, 230, 28688, 492]</t>
   </si>
   <si>
-    <t>[[13, 31, 21], [16152, 16153], [3280], [369], [1627, 1048, 1004, 2801], [104], [42291, 42291], [37440], [8192], [269, 403, 137], [14981], [73502], [33522], [115, 115], [28688], [164, 246, 82]]</t>
-  </si>
-  <si>
-    <t>h2399_ws4_infp16_outbf16_fetch_4_ID560</t>
+    <t>[63, 761, 5, 28, 3254, 104, 8028, 34578, 1087, 343, 14420, 2698, 31254, 134, 3712, 249]</t>
+  </si>
+  <si>
+    <t>h2399_ws4_infp16_outbf16_ID560</t>
   </si>
   <si>
     <t>[[845613, 2399], [[12902], [8571], [84], [73134]]]</t>
@@ -6446,10 +6446,10 @@
     <t>[12902, 8571, 84, 73134]</t>
   </si>
   <si>
-    <t>[[12902], [2143, 2143, 2143, 2142], [13, 71], [24378, 36567, 12189]]</t>
-  </si>
-  <si>
-    <t>h4752_ws16_inbf16_outfp16_fetch_8_ID561</t>
+    <t>[11924, 875, 25, 5137]</t>
+  </si>
+  <si>
+    <t>h4752_ws16_inbf16_outfp16_ID561</t>
   </si>
   <si>
     <t>[[274400, 4752], [[4220], [394], [330], [44891], [48131], [86431], [38426], [2221], [44922], [18516], [1301], [4313], [866], [2378], [180], [256]]]</t>
@@ -6467,10 +6467,10 @@
     <t>[4220, 394, 330, 44891, 48131, 86431, 38426, 2221, 44922, 18516, 1301, 4313, 866, 2378, 180, 256]</t>
   </si>
   <si>
-    <t>[[2110, 2110], [132, 131, 131], [165, 165], [13893, 6937, 24061], [16044, 16044, 16043], [2264, 7895, 20976, 17222, 4094, 13630, 3550, 16800], [6406, 19212, 12808], [2221], [23507, 1, 1, 21413], [18516], [1301], [1, 1617, 1617, 1078], [289, 289, 288], [1189, 1189], [180], [256]]</t>
-  </si>
-  <si>
-    <t>h1113_ws16_infp32_outfp32_fetch_7_ID562</t>
+    <t>[403, 204, 316, 27786, 47491, 79163, 326, 2172, 2264, 10387, 32, 3991, 506, 1077, 166, 25]</t>
+  </si>
+  <si>
+    <t>h1113_ws16_infp32_outfp32_ID562</t>
   </si>
   <si>
     <t>[[432385, 1113], [[17812], [219], [21937], [8407], [840], [1271], [5882], [81], [10245], [13225], [2983], [78214], [922], [1118], [4911], [28346]]]</t>
@@ -6488,10 +6488,10 @@
     <t>[17812, 219, 21937, 8407, 840, 1271, 5882, 81, 10245, 13225, 2983, 78214, 922, 1118, 4911, 28346]</t>
   </si>
   <si>
-    <t>[[17812], [1, 218], [21937], [1, 1, 1, 8404], [840], [1271], [302, 105, 815, 4660], [22, 59], [10245], [13225], [1, 2982], [4651, 23171, 14407, 10329, 1065, 9891, 14700], [461, 461], [1118], [2455, 2456], [11011, 17335]]</t>
-  </si>
-  <si>
-    <t>h806_ws4_inbf16_outbf16_fetch_5_ID563</t>
+    <t>[600, 203, 516, 2417, 43, 226, 2804, 7, 1206, 6103, 2978, 1638, 406, 517, 880, 2326]</t>
+  </si>
+  <si>
+    <t>h806_ws4_inbf16_outbf16_ID563</t>
   </si>
   <si>
     <t>[[849972, 806], [[5970], [21348], [54490], [73975]]]</t>
@@ -6509,10 +6509,10 @@
     <t>[5970, 21348, 54490, 73975]</t>
   </si>
   <si>
-    <t>[[1194, 1791, 2388, 596, 1], [10674, 10674], [18164, 18163, 18163], [1, 27742, 27739, 18493]]</t>
-  </si>
-  <si>
-    <t>h4128_ws4_inbf16_outfp32_fetch_2_ID564</t>
+    <t>[2614, 11800, 2724, 36301]</t>
+  </si>
+  <si>
+    <t>h4128_ws4_inbf16_outfp32_ID564</t>
   </si>
   <si>
     <t>[[308140, 4128], [[62910], [13629], [6837], [3884]]]</t>
@@ -6530,10 +6530,10 @@
     <t>[62910, 13629, 6837, 3884]</t>
   </si>
   <si>
-    <t>[[62910], [13629], [3419, 3418], [3884]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_infp32_outbf16_fetch_5_ID565</t>
+    <t>[26738, 2275, 5802, 1713]</t>
+  </si>
+  <si>
+    <t>h128_ws4_infp32_outbf16_ID565</t>
   </si>
   <si>
     <t>[[826330, 128], [[81008], [34751], [38038], [3539]]]</t>
@@ -6548,10 +6548,10 @@
     <t>[81008, 34751, 38038, 3539]</t>
   </si>
   <si>
-    <t>[[31684, 12841, 8452, 11846, 16185], [22659, 12092], [6341, 19018, 12679], [1180, 1180, 1179]]</t>
-  </si>
-  <si>
-    <t>h812_ws8_infp16_outfp32_fetch_3_ID566</t>
+    <t>[39832, 31684, 35290, 112]</t>
+  </si>
+  <si>
+    <t>h812_ws8_infp16_outfp32_ID566</t>
   </si>
   <si>
     <t>[[531677, 812], [[41822], [6060], [58341], [7504], [880], [2227], [303], [17241]]]</t>
@@ -6569,10 +6569,10 @@
     <t>[41822, 6060, 58341, 7504, 880, 2227, 303, 17241]</t>
   </si>
   <si>
-    <t>[[41822], [6060], [24267, 11588, 22486], [3752, 3752], [440, 440], [2227], [303], [17241]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_infp16_outbf16_fetch_9_ID567</t>
+    <t>[16955, 6024, 4940, 5772, 31, 1016, 272, 15659]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_infp16_outbf16_ID567</t>
   </si>
   <si>
     <t>[[523114, 4096], [[586], [937], [47968], [7459], [99065], [30], [71220], [1872]]]</t>
@@ -6587,10 +6587,10 @@
     <t>[586, 937, 47968, 7459, 99065, 30, 71220, 1872]</t>
   </si>
   <si>
-    <t>[[118, 117, 117, 117, 117], [734, 203], [47968], [3730, 3729], [70005, 1, 1, 1, 1, 1, 1, 1, 29053], [30], [10175, 10175, 10174, 10174, 10174, 10174, 10174], [1872]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp16_fetch_4_ID568</t>
+    <t>[121, 790, 130, 3349, 97758, 26, 13481, 1084]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp16_ID568</t>
   </si>
   <si>
     <t>[[131072, 256], [[650], [41861], [1024], [2036]]]</t>
@@ -6599,10 +6599,10 @@
     <t>[650, 41861, 1024, 2036]</t>
   </si>
   <si>
-    <t>[[1, 244, 243, 162], [41861], [1024], [1018, 1018]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outfp32_fetch_5_ID569</t>
+    <t>[645, 33597, 449, 1009]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outfp32_ID569</t>
   </si>
   <si>
     <t>[[274164, 1024], [[45223], [161], [5343], [9010], [9163], [6398], [11476], [9154]]]</t>
@@ -6617,10 +6617,10 @@
     <t>[45223, 161, 5343, 9010, 9163, 6398, 11476, 9154]</t>
   </si>
   <si>
-    <t>[[1, 16960, 16957, 11305], [161], [1336, 1336, 1336, 1335], [2356, 129, 417, 6108], [1528, 4581, 3054], [1068, 3198, 2132], [11476], [1, 918, 3660, 2745, 1830]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_inbf16_outbf16_fetch_1_ID570</t>
+    <t>[43902, 130, 589, 3812, 940, 472, 629, 756]</t>
+  </si>
+  <si>
+    <t>h512_ws4_inbf16_outbf16_ID570</t>
   </si>
   <si>
     <t>[[499621, 512], [[114], [1083], [1024], [4782]]]</t>
@@ -6635,10 +6635,10 @@
     <t>[114, 1083, 1024, 4782]</t>
   </si>
   <si>
-    <t>[[114], [1083], [1024], [4782]]</t>
-  </si>
-  <si>
-    <t>h1939_ws8_infp32_outbf16_fetch_4_ID571</t>
+    <t>[46, 506, 97, 2722]</t>
+  </si>
+  <si>
+    <t>h1939_ws8_infp32_outbf16_ID571</t>
   </si>
   <si>
     <t>[[25831, 1939], [[987], [906], [3060], [282], [3767], [659], [43], [2339]]]</t>
@@ -6656,10 +6656,10 @@
     <t>[987, 906, 3060, 282, 3767, 659, 43, 2339]</t>
   </si>
   <si>
-    <t>[[494, 493], [453, 453], [2088, 972], [282], [3767], [1, 248, 246, 164], [43], [1496, 843]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_infp32_outfp32_fetch_6_ID572</t>
+    <t>[896, 24, 1503, 151, 446, 594, 40, 2275]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_infp32_outfp32_ID572</t>
   </si>
   <si>
     <t>[[812451, 2048], [[76027], [68068]]]</t>
@@ -6674,10 +6674,10 @@
     <t>[76027, 68068]</t>
   </si>
   <si>
-    <t>[[12671, 19006, 25341, 31676, -12668, 1], [67873, 195]]</t>
-  </si>
-  <si>
-    <t>h4093_ws4_inbf16_outfp32_fetch_4_ID573</t>
+    <t>[7543, 3364]</t>
+  </si>
+  <si>
+    <t>h4093_ws4_inbf16_outfp32_ID573</t>
   </si>
   <si>
     <t>[[16384, 4093], [[27093], [54267], [9247], [3949]]]</t>
@@ -6692,10 +6692,10 @@
     <t>[27093, 54267, 9247, 3949]</t>
   </si>
   <si>
-    <t>[[13547, 13546], [54267], [2312, 2312, 2312, 2311], [1317, 1316, 1316]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_infp16_outbf16_fetch_8_ID574</t>
+    <t>[24856, 24147, 7549, 3571]</t>
+  </si>
+  <si>
+    <t>h128_ws4_infp16_outbf16_ID574</t>
   </si>
   <si>
     <t>[[443871, 128], [[9987], [1024], [9144], [7846]]]</t>
@@ -6710,10 +6710,10 @@
     <t>[9987, 1024, 9144, 7846]</t>
   </si>
   <si>
-    <t>[[9053, 1, 1, 1, 1, 1, 1, 928], [1024], [1524, 2286, 3048, 3810, -1525, 1], [1569, 2353, 3137, 786, 1]]</t>
-  </si>
-  <si>
-    <t>h3750_ws4_inbf16_outfp32_fetch_4_ID575</t>
+    <t>[9128, 945, 8948, 7573]</t>
+  </si>
+  <si>
+    <t>h3750_ws4_inbf16_outfp32_ID575</t>
   </si>
   <si>
     <t>[[32768, 3750], [[1691], [57246], [7970], [49986]]]</t>
@@ -6725,10 +6725,10 @@
     <t>[1691, 57246, 7970, 49986]</t>
   </si>
   <si>
-    <t>[[1691], [28623, 28623], [7970], [46975, 1, 1, 3009]]</t>
-  </si>
-  <si>
-    <t>h4276_ws2_infp32_outfp16_fetch_5_ID576</t>
+    <t>[1675, 837, 7652, 45232]</t>
+  </si>
+  <si>
+    <t>h4276_ws2_infp32_outfp16_ID576</t>
   </si>
   <si>
     <t>[[907796, 4276], [[48509], [62804]]]</t>
@@ -6746,10 +6746,10 @@
     <t>[48509, 62804]</t>
   </si>
   <si>
-    <t>[[16169, 24253, 8087], [12560, 18840, 25120, 6283, 1]]</t>
-  </si>
-  <si>
-    <t>h4460_ws8_inbf16_outfp32_fetch_4_ID577</t>
+    <t>[2807, 21625]</t>
+  </si>
+  <si>
+    <t>h4460_ws8_inbf16_outfp32_ID577</t>
   </si>
   <si>
     <t>[[93023, 4460], [[2311], [7809], [85389], [4985], [36121], [10215], [100], [8008]]]</t>
@@ -6767,10 +6767,10 @@
     <t>[2311, 7809, 85389, 4985, 36121, 10215, 100, 8008]</t>
   </si>
   <si>
-    <t>[[757, 1554], [4248, 3561], [4844, 34991, 45554], [1246, 1869, 1869, 1], [12040, 18060, 6021], [10215], [100], [3516, 364, 4128]]</t>
-  </si>
-  <si>
-    <t>h4357_ws2_inbf16_outfp16_fetch_3_ID578</t>
+    <t>[134, 179, 71070, 76, 35386, 9556, 3, 656]</t>
+  </si>
+  <si>
+    <t>h4357_ws2_inbf16_outfp16_ID578</t>
   </si>
   <si>
     <t>[[524288, 4357], [[20711], [36033]]]</t>
@@ -6782,10 +6782,10 @@
     <t>[20711, 36033]</t>
   </si>
   <si>
-    <t>[[10355, 10356], [6006, 18016, 12011]]</t>
-  </si>
-  <si>
-    <t>h128_ws8_infp16_outfp32_fetch_4_ID579</t>
+    <t>[20128, 34224]</t>
+  </si>
+  <si>
+    <t>h128_ws8_infp16_outfp32_ID579</t>
   </si>
   <si>
     <t>[[998241, 128], [[7564], [19230], [12106], [2639], [78415], [44595], [28291], [40246]]]</t>
@@ -6800,10 +6800,10 @@
     <t>[7564, 19230, 12106, 2639, 78415, 44595, 28291, 40246]</t>
   </si>
   <si>
-    <t>[[7564], [19230], [12106], [1320, 1319], [78415], [22298, 22297], [14146, 14145], [188, 8937, 11675, 19446]]</t>
-  </si>
-  <si>
-    <t>h3409_ws16_infp16_outfp16_fetch_6_ID580</t>
+    <t>[4534, 988, 7083, 2522, 41007, 8044, 27192, 375]</t>
+  </si>
+  <si>
+    <t>h3409_ws16_infp16_outfp16_ID580</t>
   </si>
   <si>
     <t>[[406744, 3409], [[5825], [256], [8192], [3375], [5647], [4119], [512], [5404], [7799], [45295], [9445], [6698], [74597], [7994], [725], [2502]]]</t>
@@ -6821,10 +6821,10 @@
     <t>[5825, 256, 8192, 3375, 5647, 4119, 512, 5404, 7799, 45295, 9445, 6698, 74597, 7994, 725, 2502]</t>
   </si>
   <si>
-    <t>[[2913, 2912], [128, 128], [1366, 1366, 1365, 1365, 1365, 1365], [563, 1687, 1125], [942, 2823, 1882], [1, 1546, 1543, 1029], [95, 35, 382], [1, 1, 5402], [4120, 1, 3678], [45295], [1889, 2833, 3777, 945, 1], [1, -1115, 2790, 2232, 1674, 1116], [71852, 2745], [4922, 3072], [725], [2502]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp16_outfp16_fetch_6_ID581</t>
+    <t>[5365, 1, 7433, 202, 5495, 307, 9, 194, 206, 774, 1582, 312, 69144, 7474, 725, 2038]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp16_outfp16_ID581</t>
   </si>
   <si>
     <t>[[4096, 128], [[21940], [7406]]]</t>
@@ -6836,10 +6836,10 @@
     <t>[21940, 7406]</t>
   </si>
   <si>
-    <t>[[8022, 13918], [1, -1233, 3085, 2468, 1851, 1234]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outfp16_fetch_6_ID582</t>
+    <t>[2090, 7402]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outfp16_ID582</t>
   </si>
   <si>
     <t>[[32768, 256], [[2904], [39893], [61580], [9490]]]</t>
@@ -6848,10 +6848,10 @@
     <t>[2904, 39893, 61580, 9490]</t>
   </si>
   <si>
-    <t>[[2904], [19947, 19946], [1, -10259, 25656, 20525, 15394, 10263], [1581, 2371, 3161, 3951, -1575, 1]]</t>
-  </si>
-  <si>
-    <t>h3064_ws2_infp32_outfp32_fetch_2_ID583</t>
+    <t>[427, 39329, 58246, 901]</t>
+  </si>
+  <si>
+    <t>h3064_ws2_infp32_outfp32_ID583</t>
   </si>
   <si>
     <t>[[420913, 3064], [[2875], [3322]]]</t>
@@ -6869,10 +6869,10 @@
     <t>[2875, 3322]</t>
   </si>
   <si>
-    <t>[[1, 2874], [1, 3321]]</t>
-  </si>
-  <si>
-    <t>h5003_ws16_infp16_outfp16_fetch_5_ID584</t>
+    <t>[2690, 1824]</t>
+  </si>
+  <si>
+    <t>h5003_ws16_infp16_outfp16_ID584</t>
   </si>
   <si>
     <t>[[484983, 5003], [[5119], [610], [2948], [952], [8197], [65704], [35139], [48393], [7554], [1755], [8037], [9489], [1992], [6870], [256], [9998]]]</t>
@@ -6890,10 +6890,10 @@
     <t>[5119, 610, 2948, 952, 8197, 65704, 35139, 48393, 7554, 1755, 8037, 9489, 1992, 6870, 256, 9998]</t>
   </si>
   <si>
-    <t>[[1706, 2559, 854], [122, 122, 122, 122, 122], [2948], [1, 951], [1, 822, 3277, 2458, 1639], [17720, 47984], [35139], [48393], [1, 7553], [1755], [2010, 2009, 2009, 2009], [4745, 4744], [1992], [3706, 1, 1, 1, 3161], [256], [1782, 2376, 5840]]</t>
-  </si>
-  <si>
-    <t>h3171_ws16_infp16_outfp32_fetch_7_ID585</t>
+    <t>[152, 111, 2480, 67, 3766, 10989, 19625, 44757, 5060, 48, 82, 178, 87, 5748, 256, 1170]</t>
+  </si>
+  <si>
+    <t>h3171_ws16_infp16_outfp32_ID585</t>
   </si>
   <si>
     <t>[[494519, 3171], [[837], [78703], [34275], [9179], [1059], [5571], [24281], [286], [9586], [9818], [35927], [694], [80638], [7330], [5886], [7540]]]</t>
@@ -6911,10 +6911,10 @@
     <t>[837, 78703, 34275, 9179, 1059, 5571, 24281, 286, 9586, 9818, 35927, 694, 80638, 7330, 5886, 7540]</t>
   </si>
   <si>
-    <t>[[167, 250, 333, 86, 1], [11244, 11244, 11243, 11243, 11243, 11243, 11243], [17138, 17137], [1, 1, 1, 1, 9175], [1059], [5571], [1145, 23136], [286], [2397, 2397, 2396, 2396], [1, 3682, 3681, 2454], [17963, 17964], [138, 207, 276, 72, 1], [80638], [1466, 2199, 2932, 732, 1], [1471, 2206, 2208, 1], [1855, 529, 2315, 2841]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_inbf16_outfp16_fetch_1_ID586</t>
+    <t>[325, 39416, 31948, 1527, 569, 5070, 22930, 36, 4666, 9217, 33605, 66, 173, 7162, 392, 508]</t>
+  </si>
+  <si>
+    <t>h512_ws2_inbf16_outfp16_ID586</t>
   </si>
   <si>
     <t>[[476724, 512], [[17681], [49649]]]</t>
@@ -6929,10 +6929,10 @@
     <t>[17681, 49649]</t>
   </si>
   <si>
-    <t>[[17681], [49649]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_inbf16_outbf16_fetch_2_ID587</t>
+    <t>[1671, 46088]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_inbf16_outbf16_ID587</t>
   </si>
   <si>
     <t>[[4096, 4096], [[96993], [1699]]]</t>
@@ -6941,10 +6941,10 @@
     <t>[96993, 1699]</t>
   </si>
   <si>
-    <t>[[1, 96992], [1699]]</t>
-  </si>
-  <si>
-    <t>h1783_ws4_infp16_outbf16_fetch_5_ID588</t>
+    <t>[44869, 127]</t>
+  </si>
+  <si>
+    <t>h1783_ws4_infp16_outbf16_ID588</t>
   </si>
   <si>
     <t>[[603689, 1783], [[36334], [1423], [70978], [6708]]]</t>
@@ -6962,10 +6962,10 @@
     <t>[36334, 1423, 70978, 6708]</t>
   </si>
   <si>
-    <t>[[26242, 1, 10091], [1423], [35489, 35489], [1341, 2011, 2681, 674, 1]]</t>
-  </si>
-  <si>
-    <t>h3116_ws4_infp16_outfp16_fetch_6_ID589</t>
+    <t>[9676, 694, 1875, 5933]</t>
+  </si>
+  <si>
+    <t>h3116_ws4_infp16_outfp16_ID589</t>
   </si>
   <si>
     <t>[[210451, 3116], [[759], [7325], [9090], [15053]]]</t>
@@ -6983,10 +6983,10 @@
     <t>[759, 7325, 9090, 15053]</t>
   </si>
   <si>
-    <t>[[759], [3663, 3662], [1515, 1515, 1515, 1515, 1515, 1515], [15053]]</t>
-  </si>
-  <si>
-    <t>h4129_ws8_infp32_outfp16_fetch_7_ID590</t>
+    <t>[349, 6916, 4923, 10599]</t>
+  </si>
+  <si>
+    <t>h4129_ws8_infp32_outfp16_ID590</t>
   </si>
   <si>
     <t>[[72892, 4129], [[16], [7536], [6681], [83294], [81846], [7850], [21842], [4976]]]</t>
@@ -7004,10 +7004,10 @@
     <t>[16, 7536, 6681, 83294, 81846, 7850, 21842, 4976]</t>
   </si>
   <si>
-    <t>[[16], [1884, 2826, 2825, 1], [6681], [41647, 41647], [65518, 1, 1, 1, 1, 1, 16323], [1382, 6468], [21842], [1244, 1244, 1244, 1244]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp32_outfp16_fetch_3_ID591</t>
+    <t>[8, 7045, 3862, 44572, 75276, 7822, 20579, 2763]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp32_outfp16_ID591</t>
   </si>
   <si>
     <t>[[728352, 64], [[9298], [958], [281], [4245]]]</t>
@@ -7022,10 +7022,10 @@
     <t>[9298, 958, 281, 4245]</t>
   </si>
   <si>
-    <t>[[9122, 1, 175], [958], [281], [1415, 1415, 1415]]</t>
-  </si>
-  <si>
-    <t>h2978_ws2_infp32_outfp32_fetch_3_ID592</t>
+    <t>[2644, 905, 138, 2469]</t>
+  </si>
+  <si>
+    <t>h2978_ws2_infp32_outfp32_ID592</t>
   </si>
   <si>
     <t>[[262144, 2978], [[622], [251]]]</t>
@@ -7037,10 +7037,10 @@
     <t>[622, 251]</t>
   </si>
   <si>
-    <t>[[1, 1, 620], [251]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outfp16_fetch_6_ID593</t>
+    <t>[53, 2]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outfp16_ID593</t>
   </si>
   <si>
     <t>[[7367, 512], [[74051], [2383], [41983], [35296], [37353], [10332], [485], [67990], [36], [689], [16530], [10823], [67452], [3838], [1715], [94]]]</t>
@@ -7055,10 +7055,10 @@
     <t>[74051, 2383, 41983, 35296, 37353, 10332, 485, 67990, 36, 689, 16530, 10823, 67452, 3838, 1715, 94]</t>
   </si>
   <si>
-    <t>[[18513, 18513, 18513, 18512], [1192, 1191], [1, 15745, 15742, 10495], [35296], [22033, 15320], [10332], [121, 181, 182, 1], [1, 1, 1, 1, 1, 67985], [1, 1, 34], [570, 1, 118], [16530], [10823], [11242, 33726, 22484], [1919, 1919], [1715], [94]]</t>
-  </si>
-  <si>
-    <t>h1172_ws8_infp32_outfp16_fetch_6_ID594</t>
+    <t>[67514, 199, 24870, 32032, 35427, 8684, 206, 63781, 7, 87, 16105, 10289, 6437, 149, 128, 85]</t>
+  </si>
+  <si>
+    <t>h1172_ws8_infp32_outfp16_ID594</t>
   </si>
   <si>
     <t>[[58558, 1172], [[799], [29382], [859], [79604], [10435], [77], [155], [54]]]</t>
@@ -7076,10 +7076,10 @@
     <t>[799, 29382, 859, 79604, 10435, 77, 155, 54]</t>
   </si>
   <si>
-    <t>[[654, 1, 1, 1, 142], [14691, 14691], [430, 429], [1, -13263, 33166, 26533, 19900, 13267], [10435], [39, 38], [155], [54]]</t>
-  </si>
-  <si>
-    <t>h844_ws8_infp16_outfp16_fetch_7_ID595</t>
+    <t>[165, 12374, 853, 2331, 10178, 43, 83, 48]</t>
+  </si>
+  <si>
+    <t>h844_ws8_infp16_outfp16_ID595</t>
   </si>
   <si>
     <t>[[821200, 844], [[1024], [9367], [10628], [4096], [7720], [7734], [48674], [7828]]]</t>
@@ -7097,10 +7097,10 @@
     <t>[1024, 9367, 10628, 4096, 7720, 7734, 48674, 7828]</t>
   </si>
   <si>
-    <t>[[1024], [1, 1, 1, 1, 1, 1, 9361], [10628], [4096], [7720], [1933, 2899, 2901, 1], [16224, 24336, 8114], [1, 1, 1, 1, 1, 1, 7822]]</t>
-  </si>
-  <si>
-    <t>h927_ws16_infp32_outfp16_fetch_7_ID596</t>
+    <t>[951, 8676, 1458, 54, 7091, 330, 1325, 7331]</t>
+  </si>
+  <si>
+    <t>h927_ws16_infp32_outfp16_ID596</t>
   </si>
   <si>
     <t>[[8192, 927], [[3862], [21270], [25479], [1569], [49], [38686], [42289], [2399], [8208], [24556], [42], [7883], [52], [41030], [86], [6656]]]</t>
@@ -7112,10 +7112,10 @@
     <t>[3862, 21270, 25479, 1569, 49, 38686, 42289, 2399, 8208, 24556, 42, 7883, 52, 41030, 86, 6656]</t>
   </si>
   <si>
-    <t>[[3862], [10899, 10371], [12740, 12739], [1569], [3, 15, 31], [1, 38685], [20587, 10788, 10914], [2399], [1, -3513, 3516, 2930, 2344, 1758, 1172], [24556], [35, 7], [2466, 5417], [26, 26], [22424, 1, 1, 18604], [29, 29, 28], [3328, 3328]]</t>
-  </si>
-  <si>
-    <t>h1024_ws2_inbf16_outbf16_fetch_2_ID597</t>
+    <t>[1803, 12836, 20515, 1416, 22, 4634, 24110, 2376, 734, 20587, 12, 6507, 49, 21343, 79, 3750]</t>
+  </si>
+  <si>
+    <t>h1024_ws2_inbf16_outbf16_ID597</t>
   </si>
   <si>
     <t>[[524288, 1024], [[259], [2635]]]</t>
@@ -7124,10 +7124,10 @@
     <t>[259, 2635]</t>
   </si>
   <si>
-    <t>[[130, 129], [2635]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp16_outbf16_fetch_4_ID598</t>
+    <t>[254, 2451]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp16_outbf16_ID598</t>
   </si>
   <si>
     <t>[[8192, 4096], [[56519], [39678], [2594], [7072]]]</t>
@@ -7136,10 +7136,10 @@
     <t>[56519, 39678, 2594, 7072]</t>
   </si>
   <si>
-    <t>[[1, 21196, 21193, 14129], [13226, 19839, 6613], [1297, 1297], [7072]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_infp32_outfp32_fetch_9_ID599</t>
+    <t>[54330, 1603, 2335, 4727]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_infp32_outfp32_ID599</t>
   </si>
   <si>
     <t>[[377010, 2048], [[32427], [543], [91578], [5270], [53274], [834], [6260], [256]]]</t>
@@ -7154,10 +7154,10 @@
     <t>[32427, 543, 91578, 5270, 53274, 834, 6260, 256]</t>
   </si>
   <si>
-    <t>[[5405, 16213, 10809], [543], [26615, 6824, 16477, 2560, 3567, 10766, 7427, 5555, 11787], [4513, 1, 756], [53274], [139, 417, 278], [2894, 3366], [256]]</t>
-  </si>
-  <si>
-    <t>h3869_ws2_inbf16_outfp16_fetch_1_ID600</t>
+    <t>[15400, 321, 13308, 223, 3714, 36, 5947, 140]</t>
+  </si>
+  <si>
+    <t>h3869_ws2_inbf16_outfp16_ID600</t>
   </si>
   <si>
     <t>[[8192, 3869], [[72544], [19851]]]</t>
@@ -7169,10 +7169,10 @@
     <t>[72544, 19851]</t>
   </si>
   <si>
-    <t>[[72544], [19851]]</t>
-  </si>
-  <si>
-    <t>h1871_ws2_infp32_outfp16_fetch_4_ID601</t>
+    <t>[34795, 4567]</t>
+  </si>
+  <si>
+    <t>h1871_ws2_infp32_outfp16_ID601</t>
   </si>
   <si>
     <t>[[795401, 1871], [[680], [1598]]]</t>
@@ -7190,10 +7190,10 @@
     <t>[680, 1598]</t>
   </si>
   <si>
-    <t>[[1, 254, 255, 170], [1598]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp16_outfp16_fetch_6_ID602</t>
+    <t>[674, 133]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp16_outfp16_ID602</t>
   </si>
   <si>
     <t>[[32768, 64], [[6484], [5930], [8851], [2694]]]</t>
@@ -7202,10 +7202,10 @@
     <t>[6484, 5930, 8851, 2694]</t>
   </si>
   <si>
-    <t>[[2161, 3241, 1082], [4638, 1, 1, 1290], [4323, 1302, 433, 1137, 355, 1301], [1347, 1347]]</t>
-  </si>
-  <si>
-    <t>h3274_ws2_infp32_outfp32_fetch_5_ID603</t>
+    <t>[317, 5581, 4343, 2596]</t>
+  </si>
+  <si>
+    <t>h3274_ws2_infp32_outfp32_ID603</t>
   </si>
   <si>
     <t>[[8192, 3274], [[682], [1134]]]</t>
@@ -7220,10 +7220,10 @@
     <t>[682, 1134]</t>
   </si>
   <si>
-    <t>[[137, 137, 136, 136, 136], [1134]]</t>
-  </si>
-  <si>
-    <t>h1002_ws8_infp16_outfp16_fetch_7_ID604</t>
+    <t>[55, 1020]</t>
+  </si>
+  <si>
+    <t>h1002_ws8_infp16_outfp16_ID604</t>
   </si>
   <si>
     <t>[[8192, 1002], [[494], [34053], [47532], [7461], [69320], [22477], [83717], [6824]]]</t>
@@ -7235,10 +7235,10 @@
     <t>[494, 34053, 47532, 7461, 69320, 22477, 83717, 6824]</t>
   </si>
   <si>
-    <t>[[494], [17026, 17027], [23766, 23766], [1510, 1780, 820, 3351], [36788, 1, 32531], [22477], [11959, 17938, 23917, 29896, 35875, -35869, 1], [1, 6823]]</t>
-  </si>
-  <si>
-    <t>h128_ws16_inbf16_outfp16_fetch_8_ID605</t>
+    <t>[232, 31936, 7215, 3019, 64026, 789, 68037, 1076]</t>
+  </si>
+  <si>
+    <t>h128_ws16_inbf16_outfp16_ID605</t>
   </si>
   <si>
     <t>[[623517, 128], [[688], [85813], [1980], [8705], [49516], [1929], [2128], [554], [6152], [8980], [46898], [9993], [19602], [94419], [373], [4101]]]</t>
@@ -7253,10 +7253,10 @@
     <t>[688, 85813, 1980, 8705, 49516, 1929, 2128, 554, 6152, 8980, 46898, 9993, 19602, 94419, 373, 4101]</t>
   </si>
   <si>
-    <t>[[344, 344], [57494, 1, 1, 1, 1, 1, 28314], [1980], [1741, 2611, 3481, 871, 1], [8254, 24757, 16505], [1929], [1064, 1064], [536, 1, 17], [815, 5337], [2016, 439, 3185, 642, 820, 826, 86, 966], [4953, 41945], [1, 1001, 3996, 2997, 1998], [19602], [1, 35408, 35406, 23604], [373], [1, 1, 1, 4098]]</t>
-  </si>
-  <si>
-    <t>h128_ws4_infp32_outfp32_fetch_6_ID606</t>
+    <t>[608, 41618, 1482, 7619, 44948, 626, 88, 518, 5981, 8741, 2020, 5744, 6494, 26068, 241, 2016]</t>
+  </si>
+  <si>
+    <t>h128_ws4_infp32_outfp32_ID606</t>
   </si>
   <si>
     <t>[[548375, 128], [[13696], [8113], [18741], [8419]]]</t>
@@ -7271,10 +7271,10 @@
     <t>[13696, 8113, 18741, 8419]</t>
   </si>
   <si>
-    <t>[[13696], [324, 3100, 983, 3706], [18741], [2713, 957, 1959, 173, 1224, 1393]]</t>
-  </si>
-  <si>
-    <t>h166_ws8_infp32_outbf16_fetch_4_ID607</t>
+    <t>[8946, 8088, 8290, 1295]</t>
+  </si>
+  <si>
+    <t>h166_ws8_infp32_outbf16_ID607</t>
   </si>
   <si>
     <t>[[65536, 166], [[17257], [139], [60573], [1218], [18138], [8391], [80606], [47824]]]</t>
@@ -7286,10 +7286,10 @@
     <t>[17257, 139, 60573, 1218, 18138, 8391, 80606, 47824]</t>
   </si>
   <si>
-    <t>[[17257], [139], [60573], [1218], [18138], [1, 1, 1, 8388], [15974, 15771, 9089, 39772], [11956, 17934, 17933, 1]]</t>
-  </si>
-  <si>
-    <t>h1376_ws2_infp16_outfp16_fetch_3_ID608</t>
+    <t>[9115, 8, 34392, 38, 483, 507, 31948, 45313]</t>
+  </si>
+  <si>
+    <t>h1376_ws2_infp16_outfp16_ID608</t>
   </si>
   <si>
     <t>[[221844, 1376], [[309], [41770]]]</t>
@@ -7307,10 +7307,10 @@
     <t>[309, 41770]</t>
   </si>
   <si>
-    <t>[[309], [12123, 3051, 26596]]</t>
-  </si>
-  <si>
-    <t>h256_ws8_infp32_outfp16_fetch_3_ID609</t>
+    <t>[24, 24245]</t>
+  </si>
+  <si>
+    <t>h256_ws8_infp32_outfp16_ID609</t>
   </si>
   <si>
     <t>[[65536, 256], [[30272], [91], [25296], [70295], [13569], [8854], [8469], [245]]]</t>
@@ -7319,10 +7319,10 @@
     <t>[30272, 91, 25296, 70295, 13569, 8854, 8469, 245]</t>
   </si>
   <si>
-    <t>[[29481, 791], [16, 45, 30], [25296], [70295], [13569], [2952, 2951, 2951], [8469], [245]]</t>
-  </si>
-  <si>
-    <t>h3585_ws2_infp32_outbf16_fetch_3_ID610</t>
+    <t>[30082, 89, 25207, 26345, 12351, 876, 1310, 42]</t>
+  </si>
+  <si>
+    <t>h3585_ws2_infp32_outbf16_ID610</t>
   </si>
   <si>
     <t>[[131072, 3585], [[6032], [1024]]]</t>
@@ -7334,10 +7334,10 @@
     <t>[6032, 1024]</t>
   </si>
   <si>
-    <t>[[1007, 3015, 2010], [1024]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_infp16_outbf16_fetch_5_ID611</t>
+    <t>[414, 956]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_infp16_outbf16_ID611</t>
   </si>
   <si>
     <t>[[867261, 1024], [[6729], [32215], [8566], [673], [3701], [3201], [821], [732]]]</t>
@@ -7352,10 +7352,10 @@
     <t>[6729, 32215, 8566, 673, 3701, 3201, 821, 732]</t>
   </si>
   <si>
-    <t>[[2333, 1133, 3263], [10902, 10401, 10912], [1714, 1713, 1713, 1713, 1713], [134, 201, 268, 69, 1], [3701], [3201], [411, 410], [732]]</t>
-  </si>
-  <si>
-    <t>h4899_ws4_infp16_outfp32_fetch_2_ID612</t>
+    <t>[580, 9063, 4425, 334, 1552, 1536, 775, 242]</t>
+  </si>
+  <si>
+    <t>h4899_ws4_infp16_outfp32_ID612</t>
   </si>
   <si>
     <t>[[131072, 4899], [[24753], [4591], [73464], [21218]]]</t>
@@ -7364,10 +7364,10 @@
     <t>[24753, 4591, 73464, 21218]</t>
   </si>
   <si>
-    <t>[[24753], [1760, 2831], [73464], [2324, 18894]]</t>
-  </si>
-  <si>
-    <t>h5020_ws16_inbf16_outfp16_fetch_5_ID613</t>
+    <t>[21166, 3519, 39977, 10967]</t>
+  </si>
+  <si>
+    <t>h5020_ws16_inbf16_outfp16_ID613</t>
   </si>
   <si>
     <t>[[892213, 5020], [[3035], [39998], [2048], [256], [9253], [6454], [48470], [37677], [9322], [85], [45883], [12025], [81678], [83459], [541], [50212]]]</t>
@@ -7385,10 +7385,10 @@
     <t>[3035, 39998, 2048, 256, 9253, 6454, 48470, 37677, 9322, 85, 45883, 12025, 81678, 83459, 541, 50212]</t>
   </si>
   <si>
-    <t>[[1518, 1517], [5183, 34815], [1024, 1024], [208, 48], [4626, 4627], [3227, 3227], [1, 1, 1, 48467], [11399, 5895, 20383], [4661, 4661], [15, 42, 28], [9718, 134, 36031], [12025], [40733, 11760, 7244, 7994, 13947], [13912, 41728, 27819], [152, 389], [32219, 1, 17992]]</t>
-  </si>
-  <si>
-    <t>h2505_ws2_infp16_outbf16_fetch_2_ID614</t>
+    <t>[34, 38455, 189, 11, 8047, 523, 1462, 3275, 8526, 78, 22797, 249, 78741, 79259, 304, 29080]</t>
+  </si>
+  <si>
+    <t>h2505_ws2_infp16_outbf16_ID614</t>
   </si>
   <si>
     <t>[[8192, 2505], [[4178], [217]]]</t>
@@ -7403,10 +7403,10 @@
     <t>[4178, 217]</t>
   </si>
   <si>
-    <t>[[2654, 1524], [217]]</t>
-  </si>
-  <si>
-    <t>h64_ws16_inbf16_outbf16_fetch_8_ID615</t>
+    <t>[3712, 209]</t>
+  </si>
+  <si>
+    <t>h64_ws16_inbf16_outbf16_ID615</t>
   </si>
   <si>
     <t>[[32768, 64], [[2258], [21431], [395], [35240], [81], [22450], [8569], [20313], [7662], [6057], [4371], [1535], [12815], [60873], [1979], [76428]]]</t>
@@ -7415,10 +7415,10 @@
     <t>[2258, 21431, 395, 35240, 81, 22450, 8569, 20313, 7662, 6057, 4371, 1535, 12815, 60873, 1979, 76428]</t>
   </si>
   <si>
-    <t>[[1129, 1129], [16789, 4642], [186, 21, 188], [35240], [1, 80], [11225, 11225], [1072, 1071, 1071, 1071, 1071, 1071, 1071, 1071], [1, 20312], [1915, 2872, 2874, 1], [6057], [1092, 1638, 1640, 1], [1535], [12815], [30437, 30436], [1979], [19107, 19107, 19107, 19107]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_inbf16_outfp16_fetch_7_ID616</t>
+    <t>[165, 2108, 16, 14468, 9, 21471, 1696, 192, 7020, 3817, 405, 2, 773, 1828, 823, 33979]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_inbf16_outfp16_ID616</t>
   </si>
   <si>
     <t>[[212062, 2048], [[67], [9830], [632], [63026], [5677], [2100], [31972], [49600], [25757], [62602], [30445], [12391], [48724], [21], [188], [8824]]]</t>
@@ -7433,10 +7433,10 @@
     <t>[67, 9830, 632, 63026, 5677, 2100, 31972, 49600, 25757, 62602, 30445, 12391, 48724, 21, 188, 8824]</t>
   </si>
   <si>
-    <t>[[22, 33, 12], [3276, 4914, 1640], [126, 189, 252, 64, 1], [31513, 31513], [2838, 2839], [1050, 1050], [10657, 15985, 5330], [24800, 24800], [7710, 18047], [18196, 44406], [1, 1, 30443], [12391], [28830, 1, 19893], [1, 20], [188], [1261, 1261, 1261, 1261, 1260, 1260, 1260]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_inbf16_outfp32_fetch_8_ID617</t>
+    <t>[47, 8468, 19, 2981, 5475, 369, 31222, 45978, 18196, 44902, 4838, 3715, 24592, 17, 71, 521]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_inbf16_outfp32_ID617</t>
   </si>
   <si>
     <t>[[16384, 2048], [[39745], [70996], [34423], [66], [8976], [22849], [80629], [33378]]]</t>
@@ -7445,10 +7445,10 @@
     <t>[39745, 70996, 34423, 66, 8976, 22849, 80629, 33378]</t>
   </si>
   <si>
-    <t>[[1, 39744], [1, 1, 70994], [34423], [52, 1, 13], [1, 1, 1, 1, 1, 1, 1, 8969], [11424, 11425], [1, 30236, 30235, 20157], [9817, 23561]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_inbf16_outbf16_fetch_3_ID618</t>
+    <t>[38550, 4429, 1660, 3, 1098, 16649, 4002, 3565]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_inbf16_outbf16_ID618</t>
   </si>
   <si>
     <t>[[65536, 2048], [[3977], [6155], [14422], [60291]]]</t>
@@ -7457,10 +7457,10 @@
     <t>[3977, 6155, 14422, 60291]</t>
   </si>
   <si>
-    <t>[[1326, 1326, 1325], [1651, 447, 4057], [14422], [60291]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp16_outfp16_fetch_3_ID619</t>
+    <t>[1899, 3302, 7295, 578]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp16_outfp16_ID619</t>
   </si>
   <si>
     <t>[[803182, 1024], [[1106], [40984], [45395], [87215]]]</t>
@@ -7475,10 +7475,10 @@
     <t>[1106, 40984, 45395, 87215]</t>
   </si>
   <si>
-    <t>[[1106], [13661, 20491, 6832], [22643, 22752], [14485, 72730]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outbf16_fetch_5_ID620</t>
+    <t>[497, 2079, 15137, 12874]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outbf16_ID620</t>
   </si>
   <si>
     <t>[[152651, 512], [[9317], [2406], [41739], [1894], [142], [355], [2436], [1393], [3796], [48396], [58153], [42970], [831], [8962], [547], [2227]]]</t>
@@ -7493,10 +7493,10 @@
     <t>[9317, 2406, 41739, 1894, 142, 355, 2436, 1393, 3796, 48396, 58153, 42970, 831, 8962, 547, 2227]</t>
   </si>
   <si>
-    <t>[[8520, 797], [653, 1753], [41739], [1894], [142], [177, 178], [2436], [1393], [1898, 1898], [24198, 24198], [56147, 1, 1, 2004], [38651, 1, 4318], [1, 1, 1, 1, 827], [8962], [1, 206, 204, 136], [1340, 887]]</t>
-  </si>
-  <si>
-    <t>h1545_ws8_infp32_outfp16_fetch_5_ID621</t>
+    <t>[4199, 1339, 40460, 653, 31, 142, 1437, 110, 370, 1186, 26250, 21745, 463, 7638, 38, 2049]</t>
+  </si>
+  <si>
+    <t>h1545_ws8_infp32_outfp16_ID621</t>
   </si>
   <si>
     <t>[[955357, 1545], [[9489], [6652], [9531], [6100], [41939], [6602], [6315], [43821]]]</t>
@@ -7514,10 +7514,10 @@
     <t>[9489, 6652, 9531, 6100, 41939, 6602, 6315, 43821]</t>
   </si>
   <si>
-    <t>[[3163, 4744, 1582], [6652], [3177, 4765, 1589], [3527, 1, 2572], [6992, 20968, 13979], [1102, 3300, 2200], [1263, 1894, 2525, 632, 1], [43821]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_infp16_outbf16_fetch_8_ID622</t>
+    <t>[522, 2692, 8820, 5358, 38700, 454, 411, 17587]</t>
+  </si>
+  <si>
+    <t>h512_ws16_infp16_outbf16_ID622</t>
   </si>
   <si>
     <t>[[8192, 512], [[9123], [10971], [2048], [36562], [30708], [885], [1846], [42657], [22234], [12], [45759], [786], [424], [931], [2952], [5759]]]</t>
@@ -7526,10 +7526,10 @@
     <t>[9123, 10971, 2048, 36562, 30708, 885, 1846, 42657, 22234, 12, 45759, 786, 424, 931, 2952, 5759]</t>
   </si>
   <si>
-    <t>[[1, -6268, 3990, 3420, 2850, 2280, 1710, 1140], [10971], [2048], [36562], [1, 30707], [295, 295, 295], [1846], [14219, 14219, 14219], [553, 21681], [12], [13978, 10853, 20928], [393, 393], [141, 211, 72], [41, 890], [2952], [5759]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp16_outfp32_fetch_3_ID623</t>
+    <t>[8663, 311, 1884, 17039, 2294, 505, 1069, 6742, 1420, 6, 2212, 721, 35, 921, 2693, 382]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp16_outfp32_ID623</t>
   </si>
   <si>
     <t>[[633614, 4096], [[31], [34662]]]</t>
@@ -7544,10 +7544,10 @@
     <t>[31, 34662]</t>
   </si>
   <si>
-    <t>[[1, 1, 29], [17331, 17331]]</t>
-  </si>
-  <si>
-    <t>h4698_ws8_infp32_outfp32_fetch_8_ID624</t>
+    <t>[4, 17652]</t>
+  </si>
+  <si>
+    <t>h4698_ws8_infp32_outfp32_ID624</t>
   </si>
   <si>
     <t>[[798351, 4698], [[132], [5804], [5521], [9572], [1809], [70906], [8789], [28985]]]</t>
@@ -7565,10 +7565,10 @@
     <t>[132, 5804, 5521, 9572, 1809, 70906, 8789, 28985]</t>
   </si>
   <si>
-    <t>[[132], [1451, 2176, 2176, 1], [2073, 3448], [2976, 997, 1241, 523, 233, 3602], [1809], [70906], [1098, 1647, 2196, 2745, 3294, 3843, -6035, 1], [28985]]</t>
-  </si>
-  <si>
-    <t>h1228_ws8_inbf16_outfp16_fetch_4_ID625</t>
+    <t>[16, 202, 4146, 515, 63, 6684, 8255, 12254]</t>
+  </si>
+  <si>
+    <t>h1228_ws8_inbf16_outfp16_ID625</t>
   </si>
   <si>
     <t>[[820978, 1228], [[1024], [2474], [6272], [2749], [16459], [256], [45981], [2149]]]</t>
@@ -7586,10 +7586,10 @@
     <t>[1024, 2474, 6272, 2749, 16459, 256, 45981, 2149]</t>
   </si>
   <si>
-    <t>[[1024], [1237, 1237], [6126, 1, 1, 144], [1, 2748], [16459], [256], [45981], [1064, 1085]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp32_fetch_3_ID626</t>
+    <t>[33, 1320, 469, 2599, 2193, 10, 19430, 930]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp32_ID626</t>
   </si>
   <si>
     <t>[[674913, 256], [[2995], [3196], [31297], [7350]]]</t>
@@ -7604,10 +7604,10 @@
     <t>[2995, 3196, 31297, 7350]</t>
   </si>
   <si>
-    <t>[[2853, 142], [1065, 1597, 534], [31297], [7350]]</t>
-  </si>
-  <si>
-    <t>h2993_ws2_infp32_outbf16_fetch_6_ID627</t>
+    <t>[85, 3077, 488, 3]</t>
+  </si>
+  <si>
+    <t>h2993_ws2_infp32_outbf16_ID627</t>
   </si>
   <si>
     <t>[[8192, 2993], [[97965], [3072]]]</t>
@@ -7619,10 +7619,10 @@
     <t>[97965, 3072]</t>
   </si>
   <si>
-    <t>[[1, -16322, 40816, 32653, 24490, 16327], [1024, 1536, 512]]</t>
-  </si>
-  <si>
-    <t>h895_ws16_infp16_outfp16_fetch_7_ID628</t>
+    <t>[6615, 1076]</t>
+  </si>
+  <si>
+    <t>h895_ws16_infp16_outfp16_ID628</t>
   </si>
   <si>
     <t>[[4096, 895], [[56109], [2856], [3329], [46394], [38845], [75559], [40819], [369], [3165], [5898], [4100], [1124], [9287], [2530], [12954], [56]]]</t>
@@ -7634,10 +7634,10 @@
     <t>[56109, 2856, 3329, 46394, 38845, 75559, 40819, 369, 3165, 5898, 4100, 1124, 9287, 2530, 12954, 56]</t>
   </si>
   <si>
-    <t>[[56109], [1, 2855], [1664, 1665], [46394], [1, 1, 38843], [10794, 16191, 21588, 26985, 32382, -32382, 1], [40819], [369], [1582, 1583], [1180, 1180, 1180, 1179, 1179], [1025, 1025, 1025, 1025], [1124], [2942, 1375, 469, 1907, 2594], [2530], [12954], [18, 27, 11]]</t>
-  </si>
-  <si>
-    <t>h3838_ws8_infp32_outfp16_fetch_5_ID629</t>
+    <t>[31979, 127, 1904, 43866, 22467, 3662, 39887, 8, 713, 453, 264, 575, 3831, 2427, 5883, 2]</t>
+  </si>
+  <si>
+    <t>h3838_ws8_infp32_outfp16_ID629</t>
   </si>
   <si>
     <t>[[552418, 3838], [[601], [48063], [47], [69], [2197], [7507], [15038], [16136]]]</t>
@@ -7655,10 +7655,10 @@
     <t>[601, 48063, 47, 69, 2197, 7507, 15038, 16136]</t>
   </si>
   <si>
-    <t>[[1, 60, 240, 180, 120], [48063], [16, 16, 15], [69], [1099, 1098], [402, 1438, 630, 5037], [15038], [16136]]</t>
-  </si>
-  <si>
-    <t>h1788_ws16_infp32_outfp32_fetch_6_ID630</t>
+    <t>[461, 3206, 1, 65, 2091, 804, 315, 7485]</t>
+  </si>
+  <si>
+    <t>h1788_ws16_infp32_outfp32_ID630</t>
   </si>
   <si>
     <t>[[8192, 1788], [[512], [55223], [23880], [3709], [74910], [48309], [310], [2048], [5345], [20581], [1284], [37467], [4096], [5888], [21169], [18984]]]</t>
@@ -7670,10 +7670,10 @@
     <t>[512, 55223, 23880, 3709, 74910, 48309, 310, 2048, 5345, 20581, 1284, 37467, 4096, 5888, 21169, 18984]</t>
   </si>
   <si>
-    <t>[[512], [11044, 16566, 22088, 5524, 1], [23880], [788, 617, 2304], [29884, 6078, 4850, 16950, 3383, 13765], [8052, 24154, 16103], [155, 155], [2048], [3598, 1, 1, 1745], [20581], [1284], [18734, 18733], [4096], [1178, 1178, 1178, 1177, 1177], [10585, 10584], [18984]]</t>
-  </si>
-  <si>
-    <t>h3934_ws8_infp16_outfp32_fetch_9_ID631</t>
+    <t>[237, 45554, 618, 2841, 50431, 3736, 34, 846, 2605, 19791, 18, 1877, 3507, 1027, 1907, 5]</t>
+  </si>
+  <si>
+    <t>h3934_ws8_infp16_outfp32_ID631</t>
   </si>
   <si>
     <t>[[16384, 3934], [[32228], [21337], [49531], [9353], [96266], [3070], [470], [47409]]]</t>
@@ -7685,10 +7685,10 @@
     <t>[32228, 21337, 49531, 9353, 96266, 3070, 470, 47409]</t>
   </si>
   <si>
-    <t>[[32228], [21337], [12382, 18573, 18575, 1], [1337, 1336, 1336, 1336, 1336, 1336, 1336], [10697, 10697, 10696, 10696, 10696, 10696, 10696, 10696, 10696], [1024, 1023, 1023], [470], [47409]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_inbf16_outfp16_fetch_4_ID632</t>
+    <t>[15819, 3354, 3226, 5424, 11715, 1268, 43, 3960]</t>
+  </si>
+  <si>
+    <t>h512_ws4_inbf16_outfp16_ID632</t>
   </si>
   <si>
     <t>[[4096, 512], [[9716], [10], [2348], [6935]]]</t>
@@ -7697,10 +7697,10 @@
     <t>[9716, 10, 2348, 6935]</t>
   </si>
   <si>
-    <t>[[1070, 178, 1446, 7022], [10], [1174, 1174], [1158, 3466, 2311]]</t>
-  </si>
-  <si>
-    <t>h4620_ws16_inbf16_outbf16_fetch_5_ID633</t>
+    <t>[268, 4, 2297, 338]</t>
+  </si>
+  <si>
+    <t>h4620_ws16_inbf16_outbf16_ID633</t>
   </si>
   <si>
     <t>[[288910, 4620], [[16], [2284], [34], [21535], [43115], [9421], [15410], [16863], [53413], [1751], [11], [802], [809], [355], [36192], [755]]]</t>
@@ -7718,10 +7718,10 @@
     <t>[16, 2284, 34, 21535, 43115, 9421, 15410, 16863, 53413, 1751, 11, 802, 809, 355, 36192, 755]</t>
   </si>
   <si>
-    <t>[[16], [1142, 1142], [34], [2496, 19039], [21558, 21557], [9421], [15410], [16863], [35935, 1, 17477], [1751], [11], [802], [1, 1, 1, 1, 805], [113, 115, 127], [36192], [755]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_inbf16_outbf16_fetch_6_ID634</t>
+    <t>[13, 2278, 34, 1511, 24540, 7273, 2496, 14957, 25084, 30, 9, 40, 121, 141, 35090, 146]</t>
+  </si>
+  <si>
+    <t>h64_ws4_inbf16_outbf16_ID634</t>
   </si>
   <si>
     <t>[[524288, 64], [[764], [48873], [9664], [9914]]]</t>
@@ -7730,10 +7730,10 @@
     <t>[764, 48873, 9664, 9914]</t>
   </si>
   <si>
-    <t>[[764], [48873], [1611, 1611, 1611, 1611, 1610, 1610], [9049, 1, 1, 1, 1, 861]]</t>
-  </si>
-  <si>
-    <t>h432_ws8_inbf16_outfp16_fetch_3_ID635</t>
+    <t>[411, 24649, 770, 4625]</t>
+  </si>
+  <si>
+    <t>h432_ws8_inbf16_outfp16_ID635</t>
   </si>
   <si>
     <t>[[157621, 432], [[8651], [2079], [512], [4866], [1024], [1024], [256], [8192]]]</t>
@@ -7751,10 +7751,10 @@
     <t>[8651, 2079, 512, 4866, 1024, 1024, 256, 8192]</t>
   </si>
   <si>
-    <t>[[8081, 570], [1040, 1039], [87, 255, 170], [1622, 2433, 811], [1024], [1024], [128, 128], [2730, 4095, 1367]]</t>
-  </si>
-  <si>
-    <t>h3735_ws16_inbf16_outfp32_fetch_7_ID636</t>
+    <t>[3894, 1888, 480, 4511, 1008, 730, 10, 7506]</t>
+  </si>
+  <si>
+    <t>h3735_ws16_inbf16_outfp32_ID636</t>
   </si>
   <si>
     <t>[[131072, 3735], [[928], [97], [7247], [6256], [5461], [34439], [11694], [22655], [3401], [1299], [14066], [4096], [8005], [48], [26452], [2601]]]</t>
@@ -7766,10 +7766,10 @@
     <t>[928, 97, 7247, 6256, 5461, 34439, 11694, 22655, 3401, 1299, 14066, 4096, 8005, 48, 26452, 2601]</t>
   </si>
   <si>
-    <t>[[464, 464], [97], [1, 1, 1, 1, 1, 1, 7241], [1421, 988, 66, 1072, 2709], [1092, 1638, 2184, 546, 1], [17220, 17219], [11694], [11328, 11327], [3401], [1299], [14066], [4096], [4003, 4002], [24, 24], [1, 26451], [1713, 888]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_infp32_outfp32_fetch_3_ID637</t>
+    <t>[768, 17, 2841, 6137, 270, 14662, 5872, 21258, 2450, 70, 9721, 3932, 3368, 26, 1596, 71]</t>
+  </si>
+  <si>
+    <t>h512_ws4_infp32_outfp32_ID637</t>
   </si>
   <si>
     <t>[[755557, 512], [[5365], [53496], [2080], [832]]]</t>
@@ -7784,10 +7784,10 @@
     <t>[5365, 53496, 2080, 832]</t>
   </si>
   <si>
-    <t>[[1789, 1788, 1788], [2973, 50523], [1040, 1040], [199, 151, 482]]</t>
-  </si>
-  <si>
-    <t>h2074_ws4_infp16_outbf16_fetch_4_ID638</t>
+    <t>[126, 1487, 1981, 79]</t>
+  </si>
+  <si>
+    <t>h2074_ws4_infp16_outbf16_ID638</t>
   </si>
   <si>
     <t>[[524288, 2074], [[41004], [33277], [15507], [18339]]]</t>
@@ -7799,10 +7799,10 @@
     <t>[41004, 33277, 15507, 18339]</t>
   </si>
   <si>
-    <t>[[13555, 11492, 2148, 13809], [676, 15548, 17053], [15507], [18339]]</t>
-  </si>
-  <si>
-    <t>h4251_ws2_infp32_outfp16_fetch_1_ID639</t>
+    <t>[40291, 2805, 338, 7198]</t>
+  </si>
+  <si>
+    <t>h4251_ws2_infp32_outfp16_ID639</t>
   </si>
   <si>
     <t>[[4096, 4251], [[35632], [19606]]]</t>
@@ -7817,10 +7817,10 @@
     <t>[35632, 19606]</t>
   </si>
   <si>
-    <t>[[35632], [19606]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_infp32_outfp32_fetch_4_ID640</t>
+    <t>[19913, 9290]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_infp32_outfp32_ID640</t>
   </si>
   <si>
     <t>[[26913, 2048], [[68], [473], [22513], [1024], [7313], [3063], [36267], [2573]]]</t>
@@ -7835,10 +7835,10 @@
     <t>[68, 473, 22513, 1024, 7313, 3063, 36267, 2573]</t>
   </si>
   <si>
-    <t>[[22, 33, 13], [2, 78, 36, 357], [1, 22512], [1024], [7313], [3063], [18134, 18133], [1287, 1286]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_inbf16_outfp32_fetch_8_ID641</t>
+    <t>[43, 270, 16052, 13, 143, 2844, 951, 59]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_inbf16_outfp32_ID641</t>
   </si>
   <si>
     <t>[[65536, 2048], [[1207], [8028], [34475], [7522], [12347], [7978], [4096], [38592], [4158], [75812], [12], [47631], [143], [30472], [650], [2915]]]</t>
@@ -7847,10 +7847,10 @@
     <t>[1207, 8028, 34475, 7522, 12347, 7978, 4096, 38592, 4158, 75812, 12, 47631, 143, 30472, 650, 2915]</t>
   </si>
   <si>
-    <t>[[1207], [1004, 1004, 1004, 1004, 1003, 1003, 1003, 1003], [5748, 17236, 11491], [1908, 2139, 1252, 1033, 1190], [12347], [2659, 3988, 1331], [2048, 2048], [38592], [1040, 1040, 1039, 1039], [9748, 2400, 29962, 16662, 17040], [12], [15877, 15877, 15877], [143], [10158, 10157, 10157], [130, 130, 130, 130, 130], [1457, 1458]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp32_outfp32_fetch_8_ID642</t>
+    <t>[50, 7243, 33493, 3815, 10013, 5640, 3755, 1166, 2028, 32459, 7, 28303, 17, 1293, 610, 1114]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp32_outfp32_ID642</t>
   </si>
   <si>
     <t>[[8192, 256], [[26519], [83092], [80934], [97443], [531], [6950], [998], [1669], [7954], [830], [62369], [2024], [9502], [995], [385], [2857]]]</t>
@@ -7859,10 +7859,10 @@
     <t>[26519, 83092, 80934, 97443, 531, 6950, 998, 1669, 7954, 830, 62369, 2024, 9502, 995, 385, 2857]</t>
   </si>
   <si>
-    <t>[[14089, 12430], [30995, 20779, 647, 9294, 10662, 1226, 4236, 5253], [1, 1, 80932], [16241, 48721, 32481], [303, 1, 227], [4681, 1, 1, 1, 2266], [998], [1669], [5948, 1, 1, 1, 1, 2002], [1, 1, 1, 1, 826], [20790, 20790, 20789], [1756, 268], [846, 2907, 2681, 773, 196, 2099], [497, 498], [385], [1429, 1428]]</t>
-  </si>
-  <si>
-    <t>h2993_ws4_infp16_outbf16_fetch_7_ID643</t>
+    <t>[24808, 81853, 61990, 57562, 22, 301, 932, 1373, 1074, 38, 36122, 1829, 8943, 919, 76, 55]</t>
+  </si>
+  <si>
+    <t>h2993_ws4_infp16_outbf16_ID643</t>
   </si>
   <si>
     <t>[[397106, 2993], [[7352], [32348], [2476], [6785]]]</t>
@@ -7877,10 +7877,10 @@
     <t>[7352, 32348, 2476, 6785]</t>
   </si>
   <si>
-    <t>[[1050, 1575, 2100, 2625, 3150, -3149, 1], [5393, 16173, 10782], [2476], [1, 679, 2713, 2035, 1357]]</t>
-  </si>
-  <si>
-    <t>h64_ws8_inbf16_outfp32_fetch_8_ID644</t>
+    <t>[465, 19127, 1292, 6727]</t>
+  </si>
+  <si>
+    <t>h64_ws8_inbf16_outfp32_ID644</t>
   </si>
   <si>
     <t>[[352646, 64], [[8065], [90315], [9809], [134], [8937], [37840], [95398], [440]]]</t>
@@ -7895,10 +7895,10 @@
     <t>[8065, 90315, 9809, 134, 8937, 37840, 95398, 440]</t>
   </si>
   <si>
-    <t>[[1009, 1008, 1008, 1008, 1008, 1008, 1008, 1008], [90315], [9809], [134], [515, 725, 7697], [37840], [15901, 47698, 31799], [440]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_infp16_outbf16_fetch_5_ID645</t>
+    <t>[7926, 38042, 5800, 59, 282, 725, 43070, 434]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_infp16_outbf16_ID645</t>
   </si>
   <si>
     <t>[[131072, 4096], [[256], [2781], [8861], [512], [27576], [52], [5511], [659], [9470], [22038], [12657], [31466], [40969], [34456], [550], [1789]]]</t>
@@ -7907,10 +7907,10 @@
     <t>[256, 2781, 8861, 512, 27576, 52, 5511, 659, 9470, 22038, 12657, 31466, 40969, 34456, 550, 1789]</t>
   </si>
   <si>
-    <t>[[44, 212], [1391, 1390], [1, 1, 1, 1, 8857], [170, 255, 87], [27576], [17, 25, 10], [1377, 2065, 2068, 1], [659], [4795, 4675], [5019, 17019], [12657], [31466], [1, 40968], [5744, 17227, 11485], [550], [1789]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_infp16_outbf16_fetch_6_ID646</t>
+    <t>[17, 148, 8683, 287, 2818, 2, 5290, 633, 4695, 10005, 935, 16198, 20076, 33462, 264, 1769]</t>
+  </si>
+  <si>
+    <t>h512_ws8_infp16_outbf16_ID646</t>
   </si>
   <si>
     <t>[[54445, 512], [[6314], [23261], [44886], [7083], [7115], [7028], [9890], [19581]]]</t>
@@ -7925,10 +7925,10 @@
     <t>[6314, 23261, 44886, 7083, 7115, 7028, 9890, 19581]</t>
   </si>
   <si>
-    <t>[[1578, 2367, 2368, 1], [11631, 11630], [35801, 1, 9084], [6057, 1, 1, 1, 1023], [1, -1178, 2961, 2369, 1777, 1185], [2342, 3513, 1173], [4945, 4945], [19581]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_inbf16_outfp32_fetch_9_ID647</t>
+    <t>[5993, 22881, 1258, 481, 7042, 6880, 9191, 1400]</t>
+  </si>
+  <si>
+    <t>h512_ws8_inbf16_outfp32_ID647</t>
   </si>
   <si>
     <t>[[485253, 512], [[85409], [2146], [78242], [16184], [4705], [5049], [6637], [90240]]]</t>
@@ -7943,10 +7943,10 @@
     <t>[85409, 2146, 78242, 16184, 4705, 5049, 6637, 90240]</t>
   </si>
   <si>
-    <t>[[1, -58718, 37366, 32028, 26690, 21352, 16014, 10676], [1073, 1073], [78242], [16184], [3373, 1, 1, 1330], [1, 1, 1, 5046], [1093, 5544], [7820, 23924, 26224, 9910, 669, 1878, 1702, 1472, 16641]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outfp32_fetch_5_ID648</t>
+    <t>[84543, 108, 37215, 6717, 4570, 4294, 6120, 80929]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outfp32_ID648</t>
   </si>
   <si>
     <t>[[8192, 512], [[47389], [4783], [997], [32446], [9113], [16843], [256], [2700], [51215], [7806], [1352], [18660], [5400], [58], [11910], [5140]]]</t>
@@ -7955,10 +7955,10 @@
     <t>[47389, 4783, 997, 32446, 9113, 16843, 256, 2700, 51215, 7806, 1352, 18660, 5400, 58, 11910, 5140]</t>
   </si>
   <si>
-    <t>[[47389], [482, 377, 1184, 2740], [200, 200, 199, 199, 199], [16223, 16223], [1521, 4555, 3037], [16843], [256], [1350, 1350], [51215], [1952, 1952, 1951, 1951], [1352], [18660], [900, 2700, 1800], [29, 29], [11910], [4123, 1, 1016]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_infp32_outbf16_fetch_4_ID649</t>
+    <t>[26652, 4576, 421, 19636, 4210, 8850, 65, 2689, 1, 7173, 785, 10850, 4146, 38, 8543, 195]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_infp32_outbf16_ID649</t>
   </si>
   <si>
     <t>[[524288, 2048], [[4699], [2449]]]</t>
@@ -7967,10 +7967,10 @@
     <t>[4699, 2449]</t>
   </si>
   <si>
-    <t>[[1174, 1761, 1763, 1], [2449]]</t>
-  </si>
-  <si>
-    <t>h602_ws16_infp16_outfp16_fetch_8_ID650</t>
+    <t>[3573, 51]</t>
+  </si>
+  <si>
+    <t>h602_ws16_infp16_outfp16_ID650</t>
   </si>
   <si>
     <t>[[704185, 602], [[3760], [79418], [9128], [5305], [61029], [34142], [977], [1340], [4871], [4410], [168], [35830], [248], [69], [4265], [8201]]]</t>
@@ -7988,10 +7988,10 @@
     <t>[3760, 79418, 9128, 5305, 61029, 34142, 977, 1340, 4871, 4410, 168, 35830, 248, 69, 4265, 8201]</t>
   </si>
   <si>
-    <t>[[1880, 1880], [13238, 39708, 26472], [1223, 3650, 1230, 47, 510, 2468], [1768, 2652, 885], [61029], [34142], [300, 263, 414], [1340], [1465, 998, 1077, 1331], [1, 4409], [168], [1, 1, 35828], [248], [35, 34], [2330, 1935], [1026, 1025, 1025, 1025, 1025, 1025, 1025, 1025]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_inbf16_outbf16_fetch_1_ID651</t>
+    <t>[3415, 3100, 752, 1223, 187, 28172, 8, 90, 4789, 3824, 13, 23435, 239, 66, 4197, 679]</t>
+  </si>
+  <si>
+    <t>h512_ws4_inbf16_outbf16_ID651</t>
   </si>
   <si>
     <t>[[742690, 512], [[82], [135], [304], [41]]]</t>
@@ -8006,10 +8006,10 @@
     <t>[82, 135, 304, 41]</t>
   </si>
   <si>
-    <t>[[82], [135], [304], [41]]</t>
-  </si>
-  <si>
-    <t>h4058_ws2_infp16_outfp32_fetch_4_ID652</t>
+    <t>[41, 80, 6, 16]</t>
+  </si>
+  <si>
+    <t>h4058_ws2_infp16_outfp32_ID652</t>
   </si>
   <si>
     <t>[[524288, 4058], [[692], [42420]]]</t>
@@ -8021,10 +8021,10 @@
     <t>[692, 42420]</t>
   </si>
   <si>
-    <t>[[199, 86, 407], [34564, 1, 1, 7854]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_6_ID653</t>
+    <t>[50, 3923]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outbf16_ID653</t>
   </si>
   <si>
     <t>[[131072, 256], [[42330], [4096], [987], [7218], [7786], [8340], [3025], [5391], [4477], [801], [63329], [35355], [793], [30691], [41788], [5367]]]</t>
@@ -8033,10 +8033,10 @@
     <t>[42330, 4096, 987, 7218, 7786, 8340, 3025, 5391, 4477, 801, 63329, 35355, 793, 30691, 41788, 5367]</t>
   </si>
   <si>
-    <t>[[42330], [4096], [165, 493, 329], [3609, 3609], [3893, 3893], [1390, 1390, 1390, 1390, 1390, 1390], [1513, 1512], [3017, 1, 1, 2372], [890, 897, 94, 2596], [801], [63329], [35355], [396, 397], [30691], [27728, 14060], [2683, 2684]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp16_outfp32_fetch_5_ID654</t>
+    <t>[17942, 540, 963, 6706, 7232, 8273, 11, 109, 4466, 660, 61120, 28658, 438, 16848, 8233, 4843]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp16_outfp32_ID654</t>
   </si>
   <si>
     <t>[[524288, 256], [[35161], [16526], [42101], [66399], [40095], [5644], [310], [19133], [28128], [51], [5384], [38242], [2048], [512], [3086], [512]]]</t>
@@ -8048,10 +8048,10 @@
     <t>[35161, 16526, 42101, 66399, 40095, 5644, 310, 19133, 28128, 51, 5384, 38242, 2048, 512, 3086, 512]</t>
   </si>
   <si>
-    <t>[[35161], [16526], [1, 1, 42099], [16599, 24898, 24901, 1], [20048, 20047], [5644], [122, 59, 129], [19133], [1, 28127], [51], [5384], [38242], [1024, 1024], [14, 64, 191, 4, 239], [3086], [512]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_infp16_outfp32_fetch_1_ID655</t>
+    <t>[28777, 1234, 7988, 1382, 36418, 1040, 308, 1604, 26844, 3, 4547, 19978, 81, 56, 55, 34]</t>
+  </si>
+  <si>
+    <t>h256_ws2_infp16_outfp32_ID655</t>
   </si>
   <si>
     <t>[[16384, 256], [[22364], [1262]]]</t>
@@ -8063,10 +8063,10 @@
     <t>[22364, 1262]</t>
   </si>
   <si>
-    <t>[[22364], [1262]]</t>
-  </si>
-  <si>
-    <t>h3965_ws16_infp16_outfp16_fetch_8_ID656</t>
+    <t>[3469, 191]</t>
+  </si>
+  <si>
+    <t>h3965_ws16_infp16_outfp16_ID656</t>
   </si>
   <si>
     <t>[[262144, 3965], [[39398], [1784], [2048], [9984], [736], [4358], [15825], [512], [119], [19758], [9621], [652], [90], [7879], [2445], [7190]]]</t>
@@ -8078,10 +8078,10 @@
     <t>[39398, 1784, 2048, 9984, 736, 4358, 15825, 512, 119, 19758, 9621, 652, 90, 7879, 2445, 7190]</t>
   </si>
   <si>
-    <t>[[6568, 19698, 13132], [1784], [1024, 1024], [4356, 1948, 321, 957, 1132, 115, 285, 870], [1, 275, 276, 184], [4358], [15825], [1, 1, 1, 509], [119], [19758], [1, 1, 1, 1, 9617], [250, 11, 66, 51, 274], [15, 45, 30], [1, 2956, 2953, 1969], [2445], [1797, 2695, 2697, 1]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_inbf16_outbf16_fetch_4_ID657</t>
+    <t>[37538, 1072, 126, 9771, 415, 4356, 14562, 495, 55, 18711, 1977, 70, 87, 601, 211, 1674]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_inbf16_outbf16_ID657</t>
   </si>
   <si>
     <t>[[209862, 2048], [[5130], [5643]]]</t>
@@ -8096,10 +8096,10 @@
     <t>[5130, 5643]</t>
   </si>
   <si>
-    <t>[[1, 1924, 1923, 1282], [5643]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp32_outfp32_fetch_2_ID658</t>
+    <t>[5070, 3342]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp32_outfp32_ID658</t>
   </si>
   <si>
     <t>[[8192, 1024], [[164], [38467], [11317], [1519]]]</t>
@@ -8108,10 +8108,10 @@
     <t>[164, 38467, 11317, 1519]</t>
   </si>
   <si>
-    <t>[[164], [19234, 19233], [11317], [1519]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_infp16_outbf16_fetch_4_ID659</t>
+    <t>[158, 1679, 1350, 135]</t>
+  </si>
+  <si>
+    <t>h256_ws2_infp16_outbf16_ID659</t>
   </si>
   <si>
     <t>[[4096, 256], [[41436], [877]]]</t>
@@ -8123,10 +8123,10 @@
     <t>[41436, 877]</t>
   </si>
   <si>
-    <t>[[10359, 15538, 15538, 1], [1, 1, 875]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_inbf16_outbf16_fetch_1_ID660</t>
+    <t>[39439, 25]</t>
+  </si>
+  <si>
+    <t>h512_ws4_inbf16_outbf16_ID660</t>
   </si>
   <si>
     <t>[[200241, 512], [[92], [26519], [256], [243]]]</t>
@@ -8141,10 +8141,10 @@
     <t>[92, 26519, 256, 243]</t>
   </si>
   <si>
-    <t>[[92], [26519], [256], [243]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_infp32_outfp16_fetch_6_ID661</t>
+    <t>[43, 15790, 79, 218]</t>
+  </si>
+  <si>
+    <t>h512_ws16_infp32_outfp16_ID661</t>
   </si>
   <si>
     <t>[[524288, 512], [[77253], [2406], [21847], [8281], [4096], [34], [36393], [4096], [2020], [9507], [2649], [4096], [31092], [5296], [6011], [48664]]]</t>
@@ -8156,10 +8156,10 @@
     <t>[77253, 2406, 21847, 8281, 4096, 34, 36393, 4096, 2020, 9507, 2649, 4096, 31092, 5296, 6011, 48664]</t>
   </si>
   <si>
-    <t>[[19314, 19313, 19313, 19313], [2406], [5898, 15949], [879, 1008, 6394], [4096], [34], [18197, 18196], [1365, 2047, 684], [1919, 101], [1584, 2376, 3168, 3960, -1582, 1], [1324, 1325], [2048, 2048], [31092], [1765, 2647, 884], [6011], [8288, 40376]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_inbf16_outfp16_fetch_5_ID662</t>
+    <t>[75974, 1306, 3182, 7888, 2949, 1, 35567, 1875, 1838, 348, 74, 1653, 17456, 346, 5720, 47496]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_inbf16_outfp16_ID662</t>
   </si>
   <si>
     <t>[[8192, 1024], [[11775], [5167], [40302], [13915], [4096], [9968], [9255], [512], [1024], [855], [41040], [41388], [21006], [3864], [511], [308]]]</t>
@@ -8168,10 +8168,10 @@
     <t>[11775, 5167, 40302, 13915, 4096, 9968, 9255, 512, 1024, 855, 41040, 41388, 21006, 3864, 511, 308]</t>
   </si>
   <si>
-    <t>[[11775], [1722, 2583, 862], [1, 15114, 15112, 10075], [13915], [4096], [4984, 4984], [1, 926, 3701, 2776, 1851], [188, 23, 38, 263], [1024], [227, 628], [1, 41039], [20694, 20694], [10503, 10503], [3864], [255, 256], [192, 1, 115]]</t>
-  </si>
-  <si>
-    <t>h3016_ws16_infp16_outbf16_fetch_5_ID663</t>
+    <t>[1156, 337, 38048, 5787, 1844, 4886, 808, 502, 994, 378, 3735, 29034, 18068, 1969, 211, 7]</t>
+  </si>
+  <si>
+    <t>h3016_ws16_infp16_outbf16_ID663</t>
   </si>
   <si>
     <t>[[316759, 3016], [[90273], [203], [44299], [16447], [43229], [4096], [4312], [30101], [33918], [3692], [844], [538], [8682], [927], [3650], [713]]]</t>
@@ -8189,10 +8189,10 @@
     <t>[90273, 203, 44299, 16447, 43229, 4096, 4312, 30101, 33918, 3692, 844, 538, 8682, 927, 3650, 713]</t>
   </si>
   <si>
-    <t>[[45137, 45136], [101, 102], [1, 1, 44297], [16447], [21615, 21614], [1024, 1024, 1024, 1024], [1078, 1617, 1616, 1], [5019, 15049, 10033], [11306, 11306, 11306], [1230, 1845, 617], [844], [179, 268, 91], [8682], [1, 1, 1, 1, 923], [1825, 1825], [113, 90, 242, 108, 160]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_infp32_outfp16_fetch_4_ID664</t>
+    <t>[38451, 12, 1318, 12112, 41394, 2032, 347, 29478, 19333, 8, 344, 1, 4734, 81, 3542, 225]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_infp32_outfp16_ID664</t>
   </si>
   <si>
     <t>[[827092, 2048], [[43716], [91251], [18955], [3077]]]</t>
@@ -8207,10 +8207,10 @@
     <t>[43716, 91251, 18955, 3077]</t>
   </si>
   <si>
-    <t>[[10929, 16393, 16393, 1], [91251], [18955], [1025, 1537, 515]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_inbf16_outbf16_fetch_6_ID665</t>
+    <t>[41727, 53313, 18555, 68]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_inbf16_outbf16_ID665</t>
   </si>
   <si>
     <t>[[65536, 4096], [[4715], [7121], [5207], [78272], [26690], [308], [979], [715]]]</t>
@@ -8219,10 +8219,10 @@
     <t>[4715, 7121, 5207, 78272, 26690, 308, 979, 715]</t>
   </si>
   <si>
-    <t>[[1179, 1179, 1179, 1178], [1187, 1187, 1187, 1187, 1187, 1186], [105, 79, 5023], [78272], [26690], [133, 175], [326, 489, 164], [178, 267, 269, 1]]</t>
-  </si>
-  <si>
-    <t>h3990_ws8_infp16_outbf16_fetch_5_ID666</t>
+    <t>[3692, 4272, 2637, 3335, 11408, 283, 922, 530]</t>
+  </si>
+  <si>
+    <t>h3990_ws8_infp16_outbf16_ID666</t>
   </si>
   <si>
     <t>[[524288, 3990], [[7177], [9202], [80], [6458], [934], [744], [5087], [44]]]</t>
@@ -8237,10 +8237,10 @@
     <t>[7177, 9202, 80, 6458, 934, 744, 5087, 44]</t>
   </si>
   <si>
-    <t>[[934, 115, 2211, 739, 3178], [1841, 1841, 1840, 1840, 1840], [40, 40], [6458], [1, 1, 932], [287, 206, 61, 190], [1020, 1237, 445, 2385], [1, 1, 42]]</t>
-  </si>
-  <si>
-    <t>h661_ws16_infp16_outfp16_fetch_7_ID667</t>
+    <t>[7052, 3735, 43, 16, 43, 435, 108, 44]</t>
+  </si>
+  <si>
+    <t>h661_ws16_infp16_outfp16_ID667</t>
   </si>
   <si>
     <t>[[682459, 661], [[544], [33181], [3598], [748], [4700], [638], [7771], [240], [839], [15823], [38683], [42852], [9893], [1287], [4411], [37178]]]</t>
@@ -8258,10 +8258,10 @@
     <t>[544, 33181, 3598, 748, 4700, 638, 7771, 240, 839, 15823, 38683, 42852, 9893, 1287, 4411, 37178]</t>
   </si>
   <si>
-    <t>[[136, 204, 203, 1], [8505, 24676], [1200, 1199, 1199], [250, 249, 249], [4700], [127, 190, 253, 67, 1], [2590, 3885, 1296], [240], [224, 615], [15823], [38539, 144], [14284, 14284, 14284], [4112, 545, 782, 1407, 396, 800, 1851], [1287], [736, 2205, 1470], [18589, 18589]]</t>
-  </si>
-  <si>
-    <t>h2121_ws4_infp32_outfp16_fetch_4_ID668</t>
+    <t>[507, 31978, 296, 388, 2804, 128, 4205, 12, 10, 6864, 28617, 40021, 9080, 158, 2185, 32889]</t>
+  </si>
+  <si>
+    <t>h2121_ws4_infp32_outfp16_ID668</t>
   </si>
   <si>
     <t>[[131072, 2121], [[1302], [1564], [4096], [27]]]</t>
@@ -8273,10 +8273,10 @@
     <t>[1302, 1564, 4096, 27]</t>
   </si>
   <si>
-    <t>[[1302], [1564], [1024, 1536, 1535, 1], [16, 11]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp16_outbf16_fetch_8_ID669</t>
+    <t>[1156, 923, 428, 10]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp16_outbf16_ID669</t>
   </si>
   <si>
     <t>[[8192, 256], [[9524], [4178], [5892], [96469], [45133], [47611], [6725], [4014], [9374], [37265], [15102], [9624], [5000], [73391], [3494], [43014]]]</t>
@@ -8285,10 +8285,10 @@
     <t>[9524, 4178, 5892, 96469, 45133, 47611, 6725, 4014, 9374, 37265, 15102, 9624, 5000, 73391, 3494, 43014]</t>
   </si>
   <si>
-    <t>[[1030, 1027, 697, 6770], [1045, 1045, 1044, 1044], [5892], [16079, 48234, 32156], [7523, 22566, 15044], [47611], [1, 2522, 2521, 1681], [4014], [1, -6428, 4096, 3511, 2926, 2341, 1756, 1171], [37265], [15102], [9624], [1, 1874, 1875, 1250], [73391], [3494], [16122, 26892]]</t>
-  </si>
-  <si>
-    <t>h128_ws8_inbf16_outbf16_fetch_6_ID670</t>
+    <t>[1398, 734, 5630, 40749, 42090, 45906, 6147, 2034, 8517, 3626, 14894, 9493, 2029, 59813, 3398, 20420]</t>
+  </si>
+  <si>
+    <t>h128_ws8_inbf16_outbf16_ID670</t>
   </si>
   <si>
     <t>[[945311, 128], [[4144], [7191], [5410], [1780], [782], [80], [512], [70191]]]</t>
@@ -8303,10 +8303,10 @@
     <t>[4144, 7191, 5410, 1780, 782, 80, 512, 70191]</t>
   </si>
   <si>
-    <t>[[1, 1553, 1554, 1036], [1, 719, 2876, 2157, 1438], [2705, 2705], [1780], [1, 294, 292, 195], [2, 4, 74], [103, 103, 102, 102, 102], [11699, 11699, 11699, 11698, 11698, 11698]]</t>
-  </si>
-  <si>
-    <t>h128_ws16_inbf16_outfp16_fetch_6_ID671</t>
+    <t>[4142, 7029, 5014, 815, 62, 72, 275, 39045]</t>
+  </si>
+  <si>
+    <t>h128_ws16_inbf16_outfp16_ID671</t>
   </si>
   <si>
     <t>[[746330, 128], [[18925], [39776], [1238], [2878], [78], [79951], [2048], [4646], [47223], [6482], [78], [9583], [6322], [20419], [94], [52489]]]</t>
@@ -8321,10 +8321,10 @@
     <t>[18925, 39776, 1238, 2878, 78, 79951, 2048, 4646, 47223, 6482, 78, 9583, 6322, 20419, 94, 52489]</t>
   </si>
   <si>
-    <t>[[18925], [6631, 19887, 13258], [1238], [2878], [7, 32, 39], [26651, 26650, 26650], [542, 1506], [2323, 2323], [15741, 15741, 15741], [1062, 987, 1585, 132, 1171, 1545], [78], [4694, 1265, 904, 2720], [1265, 1265, 1264, 1264, 1264], [4978, 15441], [47, 47], [34907, 1, 1, 1, 17579]]</t>
-  </si>
-  <si>
-    <t>h3787_ws8_infp32_outbf16_fetch_3_ID672</t>
+    <t>[1648, 2489, 1165, 2852, 41, 12709, 1936, 2730, 4694, 6338, 65, 4248, 6227, 10854, 89, 9387]</t>
+  </si>
+  <si>
+    <t>h3787_ws8_infp32_outbf16_ID672</t>
   </si>
   <si>
     <t>[[524288, 3787], [[37], [46128], [66760], [119], [67383], [16], [858], [30720]]]</t>
@@ -8336,10 +8336,10 @@
     <t>[37, 46128, 66760, 119, 67383, 16, 858, 30720]</t>
   </si>
   <si>
-    <t>[[12, 18, 7], [17420, 28708], [66760], [119], [67383], [16], [286, 286, 286], [1, 30719]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_infp16_outbf16_fetch_5_ID673</t>
+    <t>[19, 533, 35188, 57, 37002, 7, 12, 28493]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_infp16_outbf16_ID673</t>
   </si>
   <si>
     <t>[[8192, 2048], [[8322], [1482]]]</t>
@@ -8348,10 +8348,10 @@
     <t>[8322, 1482]</t>
   </si>
   <si>
-    <t>[[1665, 1665, 1664, 1664, 1664], [1482]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_infp32_outbf16_fetch_8_ID674</t>
+    <t>[84, 34]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_infp32_outbf16_ID674</t>
   </si>
   <si>
     <t>[[32768, 4096], [[2336], [512], [21728], [2133], [7292], [4319], [9090], [943]]]</t>
@@ -8360,10 +8360,10 @@
     <t>[2336, 512, 21728, 2133, 7292, 4319, 9090, 943]</t>
   </si>
   <si>
-    <t>[[1168, 1168], [256, 256], [21728], [1067, 1066], [7292], [722, 2158, 1439], [1136, 1704, 2272, 2840, 3408, 3976, -6247, 1], [1, 942]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_inbf16_outfp32_fetch_3_ID675</t>
+    <t>[31, 428, 21210, 870, 722, 4121, 221, 178]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_inbf16_outfp32_ID675</t>
   </si>
   <si>
     <t>[[65536, 2048], [[6655], [5641]]]</t>
@@ -8372,10 +8372,10 @@
     <t>[6655, 5641]</t>
   </si>
   <si>
-    <t>[[1110, 3327, 2218], [5641]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_inbf16_outfp16_fetch_2_ID676</t>
+    <t>[446, 2763]</t>
+  </si>
+  <si>
+    <t>h512_ws2_inbf16_outfp16_ID676</t>
   </si>
   <si>
     <t>[[483058, 512], [[95], [46601]]]</t>
@@ -8390,10 +8390,10 @@
     <t>[95, 46601]</t>
   </si>
   <si>
-    <t>[[95], [23300, 23301]]</t>
-  </si>
-  <si>
-    <t>h3006_ws4_inbf16_outfp32_fetch_3_ID677</t>
+    <t>[38, 42857]</t>
+  </si>
+  <si>
+    <t>h3006_ws4_inbf16_outfp32_ID677</t>
   </si>
   <si>
     <t>[[502832, 3006], [[14299], [40767], [2761], [4243]]]</t>
@@ -8411,10 +8411,10 @@
     <t>[14299, 40767, 2761, 4243]</t>
   </si>
   <si>
-    <t>[[14299], [13589, 13589, 13589], [2761], [1415, 1414, 1414]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_inbf16_outfp32_fetch_3_ID678</t>
+    <t>[5595, 36502, 1180, 1920]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_inbf16_outfp32_ID678</t>
   </si>
   <si>
     <t>[[4096, 4096], [[426], [10]]]</t>
@@ -8423,10 +8423,10 @@
     <t>[426, 10]</t>
   </si>
   <si>
-    <t>[[92, 15, 319], [10]]</t>
-  </si>
-  <si>
-    <t>h3906_ws4_infp16_outfp32_fetch_2_ID679</t>
+    <t>[36, 1]</t>
+  </si>
+  <si>
+    <t>h3906_ws4_infp16_outfp32_ID679</t>
   </si>
   <si>
     <t>[[131072, 3906], [[89857], [7326], [15918], [6970]]]</t>
@@ -8438,10 +8438,10 @@
     <t>[89857, 7326, 15918, 6970]</t>
   </si>
   <si>
-    <t>[[52545, 37312], [3663, 3663], [15918], [6970]]</t>
-  </si>
-  <si>
-    <t>h64_ws16_infp16_outfp32_fetch_8_ID680</t>
+    <t>[42406, 391, 7305, 297]</t>
+  </si>
+  <si>
+    <t>h64_ws16_infp16_outfp32_ID680</t>
   </si>
   <si>
     <t>[[83456, 64], [[48541], [918], [45685], [6703], [44810], [39095], [498], [47837], [5376], [6381], [44806], [5545], [55785], [8192], [71532], [2307]]]</t>
@@ -8456,10 +8456,10 @@
     <t>[48541, 918, 45685, 6703, 44810, 39095, 498, 47837, 5376, 6381, 44806, 5545, 55785, 8192, 71532, 2307]</t>
   </si>
   <si>
-    <t>[[36534, 1, 12006], [918], [45685], [1117, 1675, 2233, 2791, -1114, 1], [44810], [19548, 19547], [249, 249], [16423, 15576, 15838], [5376], [6381], [9060, 35746], [1, 2079, 2079, 1386], [11157, 11157, 11157, 11157, 11157], [1, -5633, 3584, 3072, 2560, 2048, 1536, 1024], [7397, 11015, 6667, 46453], [207, 2100]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp32_outbf16_fetch_5_ID681</t>
+    <t>[1914, 71, 577, 616, 1695, 806, 30, 22836, 356, 4106, 20232, 2688, 6603, 8155, 2663, 1919]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp32_outbf16_ID681</t>
   </si>
   <si>
     <t>[[49029, 128], [[6168], [578]]]</t>
@@ -8474,10 +8474,10 @@
     <t>[6168, 578]</t>
   </si>
   <si>
-    <t>[[195, 603, 5370], [116, 116, 116, 115, 115]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_infp16_outfp32_fetch_4_ID682</t>
+    <t>[49, 95]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_infp16_outfp32_ID682</t>
   </si>
   <si>
     <t>[[723572, 1024], [[4277], [7482], [48128], [5747]]]</t>
@@ -8492,10 +8492,10 @@
     <t>[4277, 7482, 48128, 5747]</t>
   </si>
   <si>
-    <t>[[1425, 2137, 715], [3741, 3741], [8414, 19028, 3094, 17592], [1, 1, 1, 5744]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_inbf16_outbf16_fetch_1_ID683</t>
+    <t>[408, 234, 4475, 5707]</t>
+  </si>
+  <si>
+    <t>h64_ws2_inbf16_outbf16_ID683</t>
   </si>
   <si>
     <t>[[338096, 64], [[1538], [3225]]]</t>
@@ -8510,10 +8510,10 @@
     <t>[1538, 3225]</t>
   </si>
   <si>
-    <t>[[1538], [3225]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_infp16_outbf16_fetch_8_ID684</t>
+    <t>[624, 192]</t>
+  </si>
+  <si>
+    <t>h512_ws2_infp16_outbf16_ID684</t>
   </si>
   <si>
     <t>[[234595, 512], [[8144], [85363]]]</t>
@@ -8528,10 +8528,10 @@
     <t>[8144, 85363]</t>
   </si>
   <si>
-    <t>[[1018, 1018, 1018, 1018, 1018, 1018, 1018, 1018], [17072, 25608, 34144, 8538, 1]]</t>
-  </si>
-  <si>
-    <t>h4654_ws16_inbf16_outbf16_fetch_6_ID685</t>
+    <t>[7343, 34233]</t>
+  </si>
+  <si>
+    <t>h4654_ws16_inbf16_outbf16_ID685</t>
   </si>
   <si>
     <t>[[262144, 4654], [[2367], [5932], [19454], [30231], [3207], [43], [39784], [41706], [51], [296], [43209], [8462], [80450], [2627], [4739], [2876]]]</t>
@@ -8546,10 +8546,10 @@
     <t>[2367, 5932, 19454, 30231, 3207, 43, 39784, 41706, 51, 296, 43209, 8462, 80450, 2627, 4739, 2876]</t>
   </si>
   <si>
-    <t>[[2367], [1572, 274, 1127, 556, 2403], [19454], [30231], [1, 1, 3205], [14, 21, 8], [19892, 19892], [13902, 20853, 6951], [1, 50], [296], [43209], [8462], [24931, 5502, 10749, 16335, 7949, 14984], [1314, 1313], [1579, 2368, 792], [2876]]</t>
-  </si>
-  <si>
-    <t>h512_ws8_inbf16_outfp16_fetch_4_ID686</t>
+    <t>[609, 393, 10034, 610, 2951, 18, 24398, 40855, 51, 26, 3336, 1633, 39077, 1368, 2701, 182]</t>
+  </si>
+  <si>
+    <t>h512_ws8_inbf16_outfp16_ID686</t>
   </si>
   <si>
     <t>[[820340, 512], [[4096], [5806], [14225], [8776], [2844], [9592], [44022], [24807]]]</t>
@@ -8564,10 +8564,10 @@
     <t>[4096, 5806, 14225, 8776, 2844, 9592, 44022, 24807]</t>
   </si>
   <si>
-    <t>[[2048, 2048], [5806], [14225], [1, 1, 1, 8773], [2844], [3197, 4795, 1600], [11006, 11006, 11005, 11005], [12403, 12404]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_infp32_outfp16_fetch_3_ID687</t>
+    <t>[3780, 455, 8860, 8493, 1329, 8753, 40251, 1310]</t>
+  </si>
+  <si>
+    <t>h64_ws2_infp32_outfp16_ID687</t>
   </si>
   <si>
     <t>[[94548, 64], [[3263], [41586]]]</t>
@@ -8582,10 +8582,10 @@
     <t>[3263, 41586]</t>
   </si>
   <si>
-    <t>[[546, 1630, 1087], [41586]]</t>
-  </si>
-  <si>
-    <t>h64_ws4_infp16_outfp32_fetch_5_ID688</t>
+    <t>[2975, 39281]</t>
+  </si>
+  <si>
+    <t>h64_ws4_infp16_outfp32_ID688</t>
   </si>
   <si>
     <t>[[168214, 64], [[27553], [7456], [3469], [2176]]]</t>
@@ -8600,10 +8600,10 @@
     <t>[27553, 7456, 3469, 2176]</t>
   </si>
   <si>
-    <t>[[1, 27552], [1929, 164, 207, 692, 4464], [1032, 690, 1747], [2176]]</t>
-  </si>
-  <si>
-    <t>h2593_ws8_infp32_outbf16_fetch_7_ID689</t>
+    <t>[593, 4443, 3142, 956]</t>
+  </si>
+  <si>
+    <t>h2593_ws8_infp32_outbf16_ID689</t>
   </si>
   <si>
     <t>[[212188, 2593], [[31812], [71], [88767], [4374], [268], [2733], [2054], [76071]]]</t>
@@ -8618,10 +8618,10 @@
     <t>[31812, 71, 88767, 4374, 268, 2733, 2054, 76071]</t>
   </si>
   <si>
-    <t>[[13789, 8787, 9236], [23, 48], [1, -38039, 38041, 31701, 25361, 19021, 12681], [3627, 1, 746], [268], [2733], [1512, 542], [76071]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_inbf16_outfp16_fetch_2_ID690</t>
+    <t>[23966, 69, 8248, 201, 266, 1083, 2043, 6649]</t>
+  </si>
+  <si>
+    <t>h128_ws2_inbf16_outfp16_ID690</t>
   </si>
   <si>
     <t>[[226829, 128], [[8594], [2048]]]</t>
@@ -8636,10 +8636,10 @@
     <t>[8594, 2048]</t>
   </si>
   <si>
-    <t>[[3674, 4920], [2048]]</t>
-  </si>
-  <si>
-    <t>h1692_ws4_infp32_outfp16_fetch_3_ID691</t>
+    <t>[4465, 1998]</t>
+  </si>
+  <si>
+    <t>h1692_ws4_infp32_outfp16_ID691</t>
   </si>
   <si>
     <t>[[570623, 1692], [[18478], [394], [31261], [30152]]]</t>
@@ -8657,10 +8657,10 @@
     <t>[18478, 394, 31261, 30152]</t>
   </si>
   <si>
-    <t>[[18478], [67, 196, 131], [5211, 15630, 10420], [15076, 15076]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_infp16_outfp32_fetch_6_ID692</t>
+    <t>[917, 198, 29739, 1220]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_infp16_outfp32_ID692</t>
   </si>
   <si>
     <t>[[5251, 2048], [[92331], [58515], [9253], [922], [13], [25217], [24705], [8100]]]</t>
@@ -8675,10 +8675,10 @@
     <t>[92331, 58515, 9253, 922, 13, 25217, 24705, 8100]</t>
   </si>
   <si>
-    <t>[[80270, 1, 12060], [58515], [1543, 1542, 1542, 1542, 1542, 1542], [461, 461], [13], [6336, 18881], [24705], [4358, 1, 3741]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp32_outfp16_fetch_6_ID693</t>
+    <t>[11876, 56926, 4898, 5, 10, 12450, 12672, 3844]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp32_outfp16_ID693</t>
   </si>
   <si>
     <t>[[731004, 4096], [[6709], [470]]]</t>
@@ -8693,10 +8693,10 @@
     <t>[6709, 470]</t>
   </si>
   <si>
-    <t>[[4145, 1, 1, 1, 1, 2560], [1, 177, 175, 117]]</t>
-  </si>
-  <si>
-    <t>h175_ws2_infp32_outfp16_fetch_1_ID694</t>
+    <t>[5762, 389]</t>
+  </si>
+  <si>
+    <t>h175_ws2_infp32_outfp16_ID694</t>
   </si>
   <si>
     <t>[[262144, 175], [[28262], [16643]]]</t>
@@ -8708,10 +8708,10 @@
     <t>[28262, 16643]</t>
   </si>
   <si>
-    <t>[[28262], [16643]]</t>
-  </si>
-  <si>
-    <t>h1886_ws4_infp16_outfp32_fetch_4_ID695</t>
+    <t>[12413, 1472]</t>
+  </si>
+  <si>
+    <t>h1886_ws4_infp16_outfp32_ID695</t>
   </si>
   <si>
     <t>[[131072, 1886], [[5026], [7034], [5108], [20029]]]</t>
@@ -8723,10 +8723,10 @@
     <t>[5026, 7034, 5108, 20029]</t>
   </si>
   <si>
-    <t>[[5026], [319, 232, 194, 6289], [1702, 2553, 853], [10015, 10014]]</t>
-  </si>
-  <si>
-    <t>h1881_ws8_infp16_outfp16_fetch_4_ID696</t>
+    <t>[2972, 3981, 638, 8204]</t>
+  </si>
+  <si>
+    <t>h1881_ws8_infp16_outfp16_ID696</t>
   </si>
   <si>
     <t>[[524288, 1881], [[341], [42491], [8204], [972], [6425], [2832], [781], [1527]]]</t>
@@ -8738,10 +8738,10 @@
     <t>[341, 42491, 8204, 972, 6425, 2832, 781, 1527]</t>
   </si>
   <si>
-    <t>[[341], [38787, 1, 1, 3702], [1, 3076, 3076, 2051], [243, 243, 243, 243], [2142, 2142, 2141], [1416, 1416], [390, 391], [1527]]</t>
-  </si>
-  <si>
-    <t>h64_ws8_inbf16_outfp16_fetch_2_ID697</t>
+    <t>[159, 39888, 4475, 965, 772, 1449, 412, 39]</t>
+  </si>
+  <si>
+    <t>h64_ws8_inbf16_outfp16_ID697</t>
   </si>
   <si>
     <t>[[524288, 64], [[157], [2385], [5099], [14571], [42900], [8648], [1400], [4078]]]</t>
@@ -8750,10 +8750,10 @@
     <t>[157, 2385, 5099, 14571, 42900, 8648, 1400, 4078]</t>
   </si>
   <si>
-    <t>[[157], [2385], [2550, 2549], [14571], [27720, 15180], [8648], [1400], [4078]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outfp32_fetch_7_ID698</t>
+    <t>[8, 1240, 4152, 13798, 40639, 4627, 599, 116]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outfp32_ID698</t>
   </si>
   <si>
     <t>[[636019, 512], [[73693], [2048], [9761], [58540], [9648], [19862], [4786], [9741], [32462], [20763], [24467], [5500], [493], [16456], [65], [5847]]]</t>
@@ -8768,10 +8768,10 @@
     <t>[73693, 2048, 9761, 58540, 9648, 19862, 4786, 9741, 32462, 20763, 24467, 5500, 493, 16456, 65, 5847]</t>
   </si>
   <si>
-    <t>[[1, 1, 1, 73690], [2048], [2115, 7646], [58540], [1, -4133, 4134, 3445, 2756, 2067, 1378], [19862], [2393, 2393], [2111, 7630], [32462], [10382, 10381], [5587, 18880], [5500], [493], [16456], [65], [2923, 2924]]</t>
-  </si>
-  <si>
-    <t>h827_ws2_inbf16_outbf16_fetch_1_ID699</t>
+    <t>[67634, 34, 9597, 32421, 90, 9553, 4730, 3657, 26849, 8444, 3440, 4572, 471, 1233, 2, 2549]</t>
+  </si>
+  <si>
+    <t>h827_ws2_inbf16_outbf16_ID699</t>
   </si>
   <si>
     <t>[[80346, 827], [[1789], [3545]]]</t>
@@ -8789,10 +8789,10 @@
     <t>[1789, 3545]</t>
   </si>
   <si>
-    <t>[[1789], [3545]]</t>
-  </si>
-  <si>
-    <t>h1517_ws8_infp32_outbf16_fetch_7_ID700</t>
+    <t>[103, 645]</t>
+  </si>
+  <si>
+    <t>h1517_ws8_infp32_outbf16_ID700</t>
   </si>
   <si>
     <t>[[32768, 1517], [[296], [4521], [31221], [89768], [15792], [4951], [28897], [727]]]</t>
@@ -8804,10 +8804,10 @@
     <t>[296, 4521, 31221, 89768, 15792, 4951, 28897, 727]</t>
   </si>
   <si>
-    <t>[[183, 113], [4521], [14332, 16889], [74003, 1, 1, 1, 1, 1, 15760], [15792], [1651, 1650, 1650], [28897], [134, 593]]</t>
-  </si>
-  <si>
-    <t>h2381_ws16_infp16_outbf16_fetch_6_ID701</t>
+    <t>[270, 4265, 28270, 52903, 14452, 4753, 2714, 337]</t>
+  </si>
+  <si>
+    <t>h2381_ws16_infp16_outbf16_ID701</t>
   </si>
   <si>
     <t>[[16384, 2381], [[42725], [905], [4961], [64635], [4096], [5713], [223], [487], [1024], [6413], [1024], [891], [20242], [9453], [256], [8067]]]</t>
@@ -8819,10 +8819,10 @@
     <t>[42725, 905, 4961, 64635, 4096, 5713, 223, 487, 1024, 6413, 1024, 891, 20242, 9453, 256, 8067]</t>
   </si>
   <si>
-    <t>[[1, 16022, 16021, 10681], [1, 339, 339, 226], [4961], [32318, 32317], [332, 3764], [1566, 733, 3414], [223], [224, 263], [1024], [5652, 761], [1024], [1, 1, 1, 888], [1, 20241], [2363, 3544, 3545, 1], [256], [6838, 1, 1, 1, 1, 1225]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_inbf16_outfp32_fetch_3_ID702</t>
+    <t>[41535, 875, 865, 55713, 1328, 392, 188, 107, 373, 1738, 971, 30, 18584, 4277, 253, 481]</t>
+  </si>
+  <si>
+    <t>h512_ws2_inbf16_outfp32_ID702</t>
   </si>
   <si>
     <t>[[739195, 512], [[17090], [889]]]</t>
@@ -8837,10 +8837,10 @@
     <t>[17090, 889]</t>
   </si>
   <si>
-    <t>[[17090], [1, 1, 887]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_inbf16_outfp32_fetch_3_ID703</t>
+    <t>[15776, 23]</t>
+  </si>
+  <si>
+    <t>h512_ws4_inbf16_outfp32_ID703</t>
   </si>
   <si>
     <t>[[815424, 512], [[258], [5082], [6611], [639]]]</t>
@@ -8855,10 +8855,10 @@
     <t>[258, 5082, 6611, 639]</t>
   </si>
   <si>
-    <t>[[129, 129], [3518, 1564], [2204, 2204, 2203], [27, 147, 465]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_infp32_outfp16_fetch_4_ID704</t>
+    <t>[205, 5004, 5996, 100]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_infp32_outfp16_ID704</t>
   </si>
   <si>
     <t>[[588535, 4096], [[34441], [47130], [7284], [3661], [6928], [469], [34], [819]]]</t>
@@ -8873,10 +8873,10 @@
     <t>[34441, 47130, 7284, 3661, 6928, 469, 34, 819]</t>
   </si>
   <si>
-    <t>[[1, 1, 34439], [1, 1, 1, 47127], [3642, 3642], [1156, 589, 1916], [6928], [118, 117, 117, 117], [34], [819]]</t>
-  </si>
-  <si>
-    <t>h3611_ws16_inbf16_outfp16_fetch_8_ID705</t>
+    <t>[14901, 6910, 5686, 3361, 6672, 459, 19, 335]</t>
+  </si>
+  <si>
+    <t>h3611_ws16_inbf16_outfp16_ID705</t>
   </si>
   <si>
     <t>[[872278, 3611], [[10513], [8075], [4634], [8192], [97819], [36745], [15793], [6080], [7603], [4096], [26920], [6632], [42], [345], [44657], [608]]]</t>
@@ -8894,10 +8894,10 @@
     <t>[10513, 8075, 4634, 8192, 97819, 36745, 15793, 6080, 7603, 4096, 26920, 6632, 42, 345, 44657, 608]</t>
   </si>
   <si>
-    <t>[[10513], [3642, 334, 5, 862, 1605, 761, 287, 579], [4634], [6002, 1, 1, 1, 1, 1, 2185], [48144, 4370, 45305], [36745], [15793], [2035, 478, 3567], [2535, 2534, 2534], [4096], [26920], [853, 1958, 3821], [42], [190, 155], [22329, 22328], [23, 53, 133, 145, 254]]</t>
-  </si>
-  <si>
-    <t>h512_ws16_inbf16_outfp16_fetch_7_ID706</t>
+    <t>[1543, 4245, 667, 4137, 73142, 6333, 14448, 5726, 4187, 3752, 24072, 6411, 21, 179, 32552, 116]</t>
+  </si>
+  <si>
+    <t>h512_ws16_inbf16_outfp16_ID706</t>
   </si>
   <si>
     <t>[[32768, 512], [[27295], [42899], [8802], [663], [1586], [7076], [65014], [933], [42], [50875], [1215], [45134], [8384], [693], [257], [45303]]]</t>
@@ -8906,10 +8906,10 @@
     <t>[27295, 42899, 8802, 663, 1586, 7076, 65014, 933, 42, 50875, 1215, 45134, 8384, 693, 257, 45303]</t>
   </si>
   <si>
-    <t>[[7740, 19555], [42899], [1, -1465, 3666, 2933, 2200, 1467], [1, 250, 247, 165], [1586], [1010, 1515, 2020, 2525, 3030, -3025, 1], [65014], [187, 187, 187, 186, 186], [4, 16, 22], [8480, 25437, 16958], [1215], [45134], [1, -1393, 3491, 2793, 2095, 1397], [490, 1, 202], [257], [11296, 9764, 24243]]</t>
-  </si>
-  <si>
-    <t>h1767_ws8_inbf16_outfp32_fetch_3_ID707</t>
+    <t>[26976, 38648, 330, 653, 1537, 6152, 555, 151, 25, 7413, 1210, 4053, 8373, 295, 124, 43375]</t>
+  </si>
+  <si>
+    <t>h1767_ws8_inbf16_outfp32_ID707</t>
   </si>
   <si>
     <t>[[733890, 1767], [[90], [83731], [40387], [43180], [84568], [6009], [578], [18]]]</t>
@@ -8927,10 +8927,10 @@
     <t>[90, 83731, 40387, 43180, 84568, 6009, 578, 18]</t>
   </si>
   <si>
-    <t>[[90], [83731], [40387], [4198, 38982], [28189, 42283, 14096], [2003, 3004, 1002], [289, 289], [18]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_infp32_outbf16_fetch_6_ID708</t>
+    <t>[1, 76876, 5267, 36642, 9781, 202, 573, 14]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_infp32_outbf16_ID708</t>
   </si>
   <si>
     <t>[[32768, 4096], [[964], [32908], [6782], [49170], [4439], [6139], [75849], [63]]]</t>
@@ -8939,10 +8939,10 @@
     <t>[964, 32908, 6782, 49170, 4439, 6139, 75849, 63]</t>
   </si>
   <si>
-    <t>[[322, 321, 321], [16454, 16454], [1130, 1695, 2260, 2825, -1129, 1], [49170], [2219, 2220], [1, 1, 1, 6136], [1, 1, 75847], [63]]</t>
-  </si>
-  <si>
-    <t>h423_ws8_inbf16_outbf16_fetch_5_ID709</t>
+    <t>[15, 29678, 39, 47700, 4001, 753, 13736, 24]</t>
+  </si>
+  <si>
+    <t>h423_ws8_inbf16_outbf16_ID709</t>
   </si>
   <si>
     <t>[[412715, 423], [[5409], [209], [608], [2004], [79], [7008], [369], [54504]]]</t>
@@ -8960,10 +8960,10 @@
     <t>[5409, 209, 608, 2004, 79, 7008, 369, 54504]</t>
   </si>
   <si>
-    <t>[[1082, 1082, 1082, 1082, 1081], [105, 104], [608], [2004], [1, 1, 77], [7008], [185, 184], [27252, 27252]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_infp16_outbf16_fetch_7_ID710</t>
+    <t>[509, 117, 249, 291, 75, 30, 311, 1228]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_infp16_outbf16_ID710</t>
   </si>
   <si>
     <t>[[8192, 2048], [[8337], [38812], [1638], [7945], [1197], [83127], [7153], [49455], [2882], [7751], [92246], [3018], [6781], [42], [184], [30707]]]</t>
@@ -8972,10 +8972,10 @@
     <t>[8337, 38812, 1638, 7945, 1197, 83127, 7153, 49455, 2882, 7751, 92246, 3018, 6781, 42, 184, 30707]</t>
   </si>
   <si>
-    <t>[[482, 3191, 2089, 267, 1123, 432, 753], [1, 1, 38810], [1638], [1, 1, 7943], [1197], [41564, 41563], [7153], [16485, 24727, 8243], [2882], [2915, 553, 161, 1393, 761, 1968], [18449, 27673, 36897, 9226, 1], [174, 485, 2359], [1695, 2542, 2543, 1], [42], [184], [30707]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp16_outfp32_fetch_5_ID711</t>
+    <t>[8117, 21905, 1551, 863, 304, 58869, 3386, 5035, 426, 6986, 10547, 2766, 3758, 9, 94, 2871]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp16_outfp32_ID711</t>
   </si>
   <si>
     <t>[[551784, 256], [[35740], [33086], [5036], [5439]]]</t>
@@ -8990,10 +8990,10 @@
     <t>[35740, 33086, 5036, 5439]</t>
   </si>
   <si>
-    <t>[[17870, 17870], [11029, 11029, 11028], [1198, 3838], [1087, 1630, 2173, 548, 1]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp16_outbf16_fetch_8_ID712</t>
+    <t>[33386, 4883, 911, 2830]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp16_outbf16_ID712</t>
   </si>
   <si>
     <t>[[148803, 128], [[9185], [7978]]]</t>
@@ -9008,10 +9008,10 @@
     <t>[9185, 7978]</t>
   </si>
   <si>
-    <t>[[8688, 1, 1, 1, 1, 1, 1, 491], [1596, 1596, 1596, 1595, 1595]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_infp32_outbf16_fetch_7_ID713</t>
+    <t>[8116, 7406]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_infp32_outbf16_ID713</t>
   </si>
   <si>
     <t>[[4096, 4096], [[5655], [7603], [27235], [78894], [8192], [932], [1647], [4049], [22670], [213], [1620], [36431], [2570], [44777], [39317], [32752]]]</t>
@@ -9020,10 +9020,10 @@
     <t>[5655, 7603, 27235, 78894, 8192, 932, 1647, 4049, 22670, 213, 1620, 36431, 2570, 44777, 39317, 32752]</t>
   </si>
   <si>
-    <t>[[4559, 1, 1095], [1086, 1629, 2172, 2715, 3258, -3258, 1], [27235], [31573, 4406, 42915], [2730, 4095, 1367], [187, 187, 186, 186, 186], [1647], [1, 1518, 1518, 1012], [22670], [213], [1620], [18215, 18216], [2570], [44777], [19659, 19658], [10917, 16375, 5460]]</t>
-  </si>
-  <si>
-    <t>h128_ws16_inbf16_outfp32_fetch_6_ID714</t>
+    <t>[214, 6601, 2318, 63146, 7648, 421, 224, 3685, 2398, 15, 1526, 19980, 74, 27116, 20074, 2057]</t>
+  </si>
+  <si>
+    <t>h128_ws16_inbf16_outfp32_ID714</t>
   </si>
   <si>
     <t>[[868902, 128], [[14584], [256], [2267], [1951], [3315], [8192], [7810], [3860], [23], [22], [2676], [839], [79], [71], [85161], [23530]]]</t>
@@ -9038,10 +9038,10 @@
     <t>[14584, 256, 2267, 1951, 3315, 8192, 7810, 3860, 23, 22, 2676, 839, 79, 71, 85161, 23530]</t>
   </si>
   <si>
-    <t>[[14584], [128, 128], [1134, 1133], [1951], [3315], [1, -1361, 3411, 2729, 2047, 1365], [7810], [502, 3358], [23], [22], [1338, 1338], [836, 1, 1, 1], [27, 26, 26], [49, 22], [14194, 14194, 14194, 14193, 14193, 14193], [23530]]</t>
-  </si>
-  <si>
-    <t>h3268_ws4_infp32_outbf16_fetch_5_ID715</t>
+    <t>[13158, 138, 206, 115, 1697, 756, 7060, 229, 8, 9, 533, 761, 73, 10, 42606, 20688]</t>
+  </si>
+  <si>
+    <t>h3268_ws4_infp32_outbf16_ID715</t>
   </si>
   <si>
     <t>[[305551, 3268], [[3444], [65364], [722], [834]]]</t>
@@ -9059,10 +9059,10 @@
     <t>[3444, 65364, 722, 834]</t>
   </si>
   <si>
-    <t>[[1666, 244, 1534], [13073, 13073, 13073, 13073, 13072], [722], [1, 1, 1, 831]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_infp32_outfp32_fetch_1_ID716</t>
+    <t>[3288, 53304, 18, 833]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_infp32_outfp32_ID716</t>
   </si>
   <si>
     <t>[[665108, 2048], [[859], [18935]]]</t>
@@ -9077,10 +9077,10 @@
     <t>[859, 18935]</t>
   </si>
   <si>
-    <t>[[859], [18935]]</t>
-  </si>
-  <si>
-    <t>h421_ws8_inbf16_outbf16_fetch_4_ID717</t>
+    <t>[367, 1556]</t>
+  </si>
+  <si>
+    <t>h421_ws8_inbf16_outbf16_ID717</t>
   </si>
   <si>
     <t>[[421631, 421], [[3509], [88929], [9048], [256], [54], [452], [47032], [1394]]]</t>
@@ -9098,10 +9098,10 @@
     <t>[3509, 88929, 9048, 256, 54, 452, 47032, 1394]</t>
   </si>
   <si>
-    <t>[[3509], [22233, 22232, 22232, 22232], [9048], [256], [54], [115, 114, 223], [1, 1, 47030], [1394]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_infp16_outfp32_fetch_6_ID718</t>
+    <t>[3029, 37074, 3654, 75, 19, 230, 45286, 242]</t>
+  </si>
+  <si>
+    <t>h512_ws2_infp16_outfp32_ID718</t>
   </si>
   <si>
     <t>[[196054, 512], [[4684], [78587]]]</t>
@@ -9116,10 +9116,10 @@
     <t>[4684, 78587]</t>
   </si>
   <si>
-    <t>[[768, 131, 1295, 2490], [13097, 19645, 26193, 32741, -13090, 1]]</t>
-  </si>
-  <si>
-    <t>h1902_ws8_infp16_outbf16_fetch_6_ID719</t>
+    <t>[4622, 24549]</t>
+  </si>
+  <si>
+    <t>h1902_ws8_infp16_outbf16_ID719</t>
   </si>
   <si>
     <t>[[152391, 1902], [[2831], [43290], [7892], [37698], [45716], [95101], [4096], [36691]]]</t>
@@ -9137,10 +9137,10 @@
     <t>[2831, 43290, 7892, 37698, 45716, 95101, 4096, 36691]</t>
   </si>
   <si>
-    <t>[[1416, 1415], [7562, 16904, 18824], [1316, 1316, 1315, 1315, 1315, 1315], [12566, 12566, 12566], [45716], [15851, 15850, 15850, 15850, 15850, 15850], [1024, 1024, 1024, 1024], [18346, 18345]]</t>
-  </si>
-  <si>
-    <t>h64_ws8_inbf16_outbf16_fetch_5_ID720</t>
+    <t>[1628, 25740, 644, 15124, 3210, 12991, 155, 2742]</t>
+  </si>
+  <si>
+    <t>h64_ws8_inbf16_outbf16_ID720</t>
   </si>
   <si>
     <t>[[653038, 64], [[20186], [34], [78924], [8739], [87], [99889], [29562], [6885]]]</t>
@@ -9155,10 +9155,10 @@
     <t>[20186, 34, 78924, 8739, 87, 99889, 29562, 6885]</t>
   </si>
   <si>
-    <t>[[10093, 10093], [11, 9, 14], [44690, 1, 1, 34232], [1747, 2620, 3493, 878, 1], [87], [19978, 19978, 19978, 19978, 19977], [29562], [2295, 2295, 2295]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_infp16_outfp16_fetch_8_ID721</t>
+    <t>[955, 22, 57489, 7154, 6, 43221, 131, 227]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_infp16_outfp16_ID721</t>
   </si>
   <si>
     <t>[[434157, 1024], [[523], [833], [7870], [3332], [65793], [4120], [8292], [46384], [1576], [6344], [30], [2581], [58326], [97], [1139], [135]]]</t>
@@ -9173,10 +9173,10 @@
     <t>[523, 833, 7870, 3332, 65793, 4120, 8292, 46384, 1576, 6344, 30, 2581, 58326, 97, 1139, 135]</t>
   </si>
   <si>
-    <t>[[262, 261], [412, 39, 56, 326], [2624, 2623, 2623], [1111, 1111, 1110], [1, 24672, 24672, 16448], [1030, 1030, 1030, 1030], [2577, 2799, 1320, 618, 482, 121, 150, 225], [1, 17393, 17394, 11596], [1576], [2115, 2115, 2114], [15, 15], [1291, 1290], [11665, 17497, 23329, 5834, 1], [97], [1139], [135]]</t>
-  </si>
-  <si>
-    <t>h2952_ws16_inbf16_outbf16_fetch_7_ID722</t>
+    <t>[500, 827, 7793, 1421, 64650, 4117, 7546, 46126, 645, 3854, 27, 2526, 3293, 2, 35, 11]</t>
+  </si>
+  <si>
+    <t>h2952_ws16_inbf16_outbf16_ID722</t>
   </si>
   <si>
     <t>[[197215, 2952], [[19935], [645], [3422], [9906], [3746], [8728], [15199], [11965], [444], [4096], [25351], [24531], [56705], [12409], [6498], [9415]]]</t>
@@ -9194,10 +9194,10 @@
     <t>[19935, 645, 3422, 9906, 3746, 8728, 15199, 11965, 444, 4096, 25351, 24531, 56705, 12409, 6498, 9415]</t>
   </si>
   <si>
-    <t>[[19935], [129, 193, 257, 65, 1], [1, 3421], [1, -4240, 4243, 3536, 2829, 2122, 1415], [3746], [2432, 6296], [15199], [11965], [222, 222], [1366, 1365, 1365], [25351], [24531], [28352, 28353], [12409], [1, -1081, 2706, 2165, 1624, 1083], [7218, 1, 1, 1, 1, 2193]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp16_outfp16_fetch_4_ID723</t>
+    <t>[18768, 313, 107, 6973, 3488, 541, 8383, 4864, 217, 3484, 12689, 11220, 26701, 11639, 286, 5105]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp16_outfp16_ID723</t>
   </si>
   <si>
     <t>[[998376, 4096], [[4348], [5174], [3385], [9016]]]</t>
@@ -9212,10 +9212,10 @@
     <t>[4348, 5174, 3385, 9016]</t>
   </si>
   <si>
-    <t>[[3643, 1, 704], [1725, 1725, 1724], [1128, 1692, 565], [1, 3380, 3381, 2254]]</t>
-  </si>
-  <si>
-    <t>h512_ws4_infp32_outfp16_fetch_5_ID724</t>
+    <t>[369, 4873, 20, 238]</t>
+  </si>
+  <si>
+    <t>h512_ws4_infp32_outfp16_ID724</t>
   </si>
   <si>
     <t>[[32768, 512], [[69037], [17302], [23265], [6502]]]</t>
@@ -9224,10 +9224,10 @@
     <t>[69037, 17302, 23265, 6502]</t>
   </si>
   <si>
-    <t>[[69037], [17302], [23265], [1301, 1301, 1300, 1300, 1300]]</t>
-  </si>
-  <si>
-    <t>h2940_ws2_infp32_outfp16_fetch_1_ID725</t>
+    <t>[35039, 16888, 11270, 42]</t>
+  </si>
+  <si>
+    <t>h2940_ws2_infp32_outfp16_ID725</t>
   </si>
   <si>
     <t>[[131072, 2940], [[150], [79]]]</t>
@@ -9239,10 +9239,10 @@
     <t>[150, 79]</t>
   </si>
   <si>
-    <t>[[150], [79]]</t>
-  </si>
-  <si>
-    <t>h4096_ws2_infp16_outfp32_fetch_2_ID726</t>
+    <t>[12, 31]</t>
+  </si>
+  <si>
+    <t>h4096_ws2_infp16_outfp32_ID726</t>
   </si>
   <si>
     <t>[[4096, 4096], [[6839], [2048]]]</t>
@@ -9254,10 +9254,10 @@
     <t>[6839, 2048]</t>
   </si>
   <si>
-    <t>[[3419, 3420], [1024, 1024]]</t>
-  </si>
-  <si>
-    <t>h2595_ws16_infp32_outfp16_fetch_7_ID727</t>
+    <t>[6041, 1940]</t>
+  </si>
+  <si>
+    <t>h2595_ws16_infp32_outfp16_ID727</t>
   </si>
   <si>
     <t>[[65536, 2595], [[61144], [8705], [723], [5701], [512], [24356], [17122], [271], [72804], [1092], [80], [6809], [5416], [41507], [60166], [1519]]]</t>
@@ -9269,10 +9269,10 @@
     <t>[61144, 8705, 723, 5701, 512, 24356, 17122, 271, 72804, 1092, 80, 6809, 5416, 41507, 60166, 1519]</t>
   </si>
   <si>
-    <t>[[10191, 10191, 10191, 10191, 10190, 10190], [2901, 4351, 1453], [221, 60, 94, 155, 193], [5701], [171, 171, 170], [12178, 12178], [17122], [136, 135], [15703, 13959, 10683, 8559, 9379, 4897, 9624], [1092], [15, 39, 26], [6809], [1805, 2707, 904], [10377, 10377, 10377, 10376], [15042, 15042, 15041, 15041], [1519]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_infp32_outfp32_fetch_8_ID728</t>
+    <t>[35909, 2455, 72, 5367, 39, 12656, 136, 11, 30173, 55, 31, 6461, 4690, 30743, 6324, 740]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_infp32_outfp32_ID728</t>
   </si>
   <si>
     <t>[[131072, 4096], [[78870], [96595], [91549], [103], [6390], [33298], [457], [671], [9074], [8548], [12596], [8937], [4886], [648], [972], [11922]]]</t>
@@ -9281,10 +9281,10 @@
     <t>[78870, 96595, 91549, 103, 6390, 33298, 457, 671, 9074, 8548, 12596, 8937, 4886, 648, 972, 11922]</t>
   </si>
   <si>
-    <t>[[19718, 19718, 19717, 19717], [23681, 1723, 19665, 15623, 8743, 1160, 4089, 21911], [91549], [103], [1065, 1597, 2129, 2661, -1063, 1], [10093, 4301, 18904], [115, 114, 114, 114], [87, 115, 121, 89, 259], [9074], [8548], [12596], [1788, 1788, 1787, 1787, 1787], [4886], [207, 441], [486, 486], [11922]]</t>
-  </si>
-  <si>
-    <t>h1072_ws8_infp16_outfp16_fetch_7_ID729</t>
+    <t>[71390, 95813, 431, 8, 73, 28977, 412, 40, 558, 7725, 11678, 2762, 864, 3, 7, 737]</t>
+  </si>
+  <si>
+    <t>h1072_ws8_infp16_outfp16_ID729</t>
   </si>
   <si>
     <t>[[61372, 1072], [[31448], [87857], [48486], [3609], [881], [62669], [17324], [687]]]</t>
@@ -9302,10 +9302,10 @@
     <t>[31448, 87857, 48486, 3609, 881, 62669, 17324, 687]</t>
   </si>
   <si>
-    <t>[[10483, 10483, 10482], [29998, 5560, 21864, 954, 2991, 4788, 21702], [16162, 24243, 8081], [3609], [1, 88, 352, 264, 176], [62669], [17324], [171, 256, 259, 1]]</t>
-  </si>
-  <si>
-    <t>h4096_ws4_infp32_outbf16_fetch_2_ID730</t>
+    <t>[15944, 59995, 2991, 267, 37, 2557, 16376, 390]</t>
+  </si>
+  <si>
+    <t>h4096_ws4_infp32_outbf16_ID730</t>
   </si>
   <si>
     <t>[[951055, 4096], [[5733], [4096], [20410], [394]]]</t>
@@ -9320,10 +9320,10 @@
     <t>[5733, 4096, 20410, 394]</t>
   </si>
   <si>
-    <t>[[2866, 2867], [1621, 2475], [10205, 10205], [394]]</t>
-  </si>
-  <si>
-    <t>h389_ws16_inbf16_outfp16_fetch_8_ID731</t>
+    <t>[375, 3278, 8436, 84]</t>
+  </si>
+  <si>
+    <t>h389_ws16_inbf16_outfp16_ID731</t>
   </si>
   <si>
     <t>[[98391, 389], [[45115], [56907], [256], [2650], [43378], [5334], [9997], [3010], [36341], [68], [23863], [6543], [7887], [9194], [2978], [5328]]]</t>
@@ -9341,10 +9341,10 @@
     <t>[45115, 56907, 256, 2650, 43378, 5334, 9997, 3010, 36341, 68, 23863, 6543, 7887, 9194, 2978, 5328]</t>
   </si>
   <si>
-    <t>[[11279, 11279, 11279, 11278], [14227, 14227, 14227, 14226], [256], [1, 2649], [10845, 10845, 10844, 10844], [3357, 1, 1, 1, 1974], [4710, 1622, 973, 617, 518, 275, 376, 906], [69, 376, 2565], [36341], [34, 34], [23863], [6543], [7413, 1, 1, 1, 1, 470], [3065, 3065, 3064], [1489, 1489], [1066, 1066, 1066, 1065, 1065]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_inbf16_outfp16_fetch_5_ID732</t>
+    <t>[41532, 51712, 115, 1656, 7855, 2586, 731, 589, 34651, 10, 1100, 636, 3529, 5328, 215, 2274]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_inbf16_outfp16_ID732</t>
   </si>
   <si>
     <t>[[420232, 1024], [[35290], [26343], [842], [514], [782], [15902], [463], [22198], [3652], [71], [98], [7096], [3770], [8613], [8358], [1381]]]</t>
@@ -9359,10 +9359,10 @@
     <t>[35290, 26343, 842, 514, 782, 15902, 463, 22198, 3652, 71, 98, 7096, 3770, 8613, 8358, 1381]</t>
   </si>
   <si>
-    <t>[[35290], [13171, 13172], [1, 316, 315, 210], [347, 1, 1, 1, 164], [260, 390, 132], [15902], [463], [22198], [3652], [35, 36], [49, 49], [7096], [670, 3100], [8613], [2487, 2297, 3574], [1381]]</t>
-  </si>
-  <si>
-    <t>h2322_ws4_inbf16_outfp16_fetch_5_ID733</t>
+    <t>[30753, 1643, 834, 456, 42, 15124, 10, 10756, 85, 64, 98, 2920, 246, 5355, 155, 618]</t>
+  </si>
+  <si>
+    <t>h2322_ws4_inbf16_outfp16_ID733</t>
   </si>
   <si>
     <t>[[275432, 2322], [[8397], [657], [749], [18044]]]</t>
@@ -9380,10 +9380,10 @@
     <t>[8397, 657, 749, 18044]</t>
   </si>
   <si>
-    <t>[[153, 413, 7831], [657], [149, 223, 297, 79, 1], [18044]]</t>
-  </si>
-  <si>
-    <t>h1024_ws4_inbf16_outfp16_fetch_6_ID734</t>
+    <t>[39, 272, 36, 10123]</t>
+  </si>
+  <si>
+    <t>h1024_ws4_inbf16_outfp16_ID734</t>
   </si>
   <si>
     <t>[[131072, 1024], [[27164], [94248], [33187], [3910]]]</t>
@@ -9392,10 +9392,10 @@
     <t>[27164, 94248, 33187, 3910]</t>
   </si>
   <si>
-    <t>[[27164], [87059, 1, 1, 1, 1, 7185], [11062, 16593, 5532], [3910]]</t>
-  </si>
-  <si>
-    <t>h2048_ws2_infp32_outfp32_fetch_2_ID735</t>
+    <t>[13941, 2860, 31040, 3650]</t>
+  </si>
+  <si>
+    <t>h2048_ws2_infp32_outfp32_ID735</t>
   </si>
   <si>
     <t>[[131072, 2048], [[3130], [72]]]</t>
@@ -9404,10 +9404,10 @@
     <t>[3130, 72]</t>
   </si>
   <si>
-    <t>[[1565, 1565], [36, 36]]</t>
-  </si>
-  <si>
-    <t>h952_ws8_infp16_outbf16_fetch_5_ID736</t>
+    <t>[3020, 65]</t>
+  </si>
+  <si>
+    <t>h952_ws8_infp16_outbf16_ID736</t>
   </si>
   <si>
     <t>[[262144, 952], [[2163], [73], [636], [616], [5977], [13392], [39076], [713]]]</t>
@@ -9419,10 +9419,10 @@
     <t>[2163, 73, 636, 616, 5977, 13392, 39076, 713]</t>
   </si>
   <si>
-    <t>[[2163], [73], [318, 318], [124, 123, 123, 123, 123], [1, 1, 1, 5974], [13392], [19203, 19873], [131, 196, 125, 95, 166]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_infp16_outbf16_fetch_5_ID737</t>
+    <t>[1219, 4, 181, 310, 3339, 764, 32452, 617]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_infp16_outbf16_ID737</t>
   </si>
   <si>
     <t>[[32768, 2048], [[34], [34], [98045], [9185], [56288], [2089], [4932], [4520]]]</t>
@@ -9431,10 +9431,10 @@
     <t>[34, 34, 98045, 9185, 56288, 2089, 4932, 4520]</t>
   </si>
   <si>
-    <t>[[34], [34], [1, 9805, 39217, 29413, 19609], [9185], [14072, 21108, 21107, 1], [1045, 1044], [2466, 2466], [755, 2259, 1506]]</t>
-  </si>
-  <si>
-    <t>h4154_ws2_infp32_outfp32_fetch_5_ID738</t>
+    <t>[4, 19, 6893, 5333, 42124, 2089, 135, 4166]</t>
+  </si>
+  <si>
+    <t>h4154_ws2_infp32_outfp32_ID738</t>
   </si>
   <si>
     <t>[[524288, 4154], [[56063], [3605]]]</t>
@@ -9446,10 +9446,10 @@
     <t>[56063, 3605]</t>
   </si>
   <si>
-    <t>[[11213, 11213, 11213, 11212, 11212], [1, 3604]]</t>
-  </si>
-  <si>
-    <t>h3883_ws8_inbf16_outfp32_fetch_6_ID739</t>
+    <t>[8021, 3361]</t>
+  </si>
+  <si>
+    <t>h3883_ws8_inbf16_outfp32_ID739</t>
   </si>
   <si>
     <t>[[522010, 3883], [[808], [4044], [12336], [512], [7897], [99251], [31256], [2595]]]</t>
@@ -9467,10 +9467,10 @@
     <t>[808, 4044, 12336, 512, 7897, 99251, 31256, 2595]</t>
   </si>
   <si>
-    <t>[[404, 404], [1, 1, 1, 4041], [12336], [128, 192, 191, 1], [1, 1, 1, 1, 7893], [32562, 14845, 20248, 10003, 677, 20916], [31256], [2595]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_infp32_outbf16_fetch_6_ID740</t>
+    <t>[685, 655, 11666, 476, 1110, 50217, 16281, 928]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_infp32_outbf16_ID740</t>
   </si>
   <si>
     <t>[[262144, 1024], [[1722], [28646], [2187], [26200], [3659], [6917], [20582], [3387], [30115], [45042], [1412], [164], [562], [2048], [40030], [9205]]]</t>
@@ -9479,10 +9479,10 @@
     <t>[1722, 28646, 2187, 26200, 3659, 6917, 20582, 3387, 30115, 45042, 1412, 164, 562, 2048, 40030, 9205]</t>
   </si>
   <si>
-    <t>[[1722], [28646], [2187], [13100, 13100], [1725, 106, 1828], [6635, 1, 1, 1, 1, 278], [20582], [1693, 1694], [24498, 1, 5616], [45042], [1412], [164], [119, 443], [1024, 1024], [10007, 15010, 15012, 1], [4603, 4602]]</t>
-  </si>
-  <si>
-    <t>h2047_ws4_infp16_outbf16_fetch_4_ID741</t>
+    <t>[93, 16248, 1132, 9497, 2131, 6899, 9672, 131, 13231, 4114, 1405, 94, 353, 172, 2998, 1528]</t>
+  </si>
+  <si>
+    <t>h2047_ws4_infp16_outbf16_ID741</t>
   </si>
   <si>
     <t>[[262144, 2047], [[9616], [11339], [80107], [2287]]]</t>
@@ -9494,10 +9494,10 @@
     <t>[9616, 11339, 80107, 2287]</t>
   </si>
   <si>
-    <t>[[1208, 2248, 6160], [11339], [20027, 20027, 20027, 20026], [2287]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_infp32_outbf16_fetch_5_ID742</t>
+    <t>[1534, 2003, 15670, 1173]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_infp32_outbf16_ID742</t>
   </si>
   <si>
     <t>[[4096, 4096], [[6099], [696], [998], [1820], [5550], [2335], [72802], [23526], [19446], [5958], [1953], [845], [11960], [50656], [4612], [82318]]]</t>
@@ -9506,10 +9506,10 @@
     <t>[6099, 696, 998, 1820, 5550, 2335, 72802, 23526, 19446, 5958, 1953, 845, 11960, 50656, 4612, 82318]</t>
   </si>
   <si>
-    <t>[[6099], [232, 348, 116], [333, 333, 332], [1820], [2775, 2775], [2335], [72802], [11763, 11763], [19446], [486, 2124, 448, 685, 2215], [1953], [282, 282, 281], [11960], [13344, 9078, 4072, 24162], [770, 2305, 1537], [17630, 3340, 3543, 57805]]</t>
-  </si>
-  <si>
-    <t>h3614_ws2_infp32_outbf16_fetch_1_ID743</t>
+    <t>[3409, 40, 16, 302, 1284, 1387, 31139, 13936, 769, 3319, 157, 837, 6907, 44426, 2948, 45794]</t>
+  </si>
+  <si>
+    <t>h3614_ws2_infp32_outbf16_ID743</t>
   </si>
   <si>
     <t>[[524288, 3614], [[28614], [1666]]]</t>
@@ -9521,10 +9521,10 @@
     <t>[28614, 1666]</t>
   </si>
   <si>
-    <t>[[28614], [1666]]</t>
-  </si>
-  <si>
-    <t>h2048_ws4_inbf16_outfp16_fetch_5_ID744</t>
+    <t>[890, 919]</t>
+  </si>
+  <si>
+    <t>h2048_ws4_inbf16_outfp16_ID744</t>
   </si>
   <si>
     <t>[[524288, 2048], [[9803], [44087], [102], [6324]]]</t>
@@ -9533,10 +9533,10 @@
     <t>[9803, 44087, 102, 6324]</t>
   </si>
   <si>
-    <t>[[1, 982, 3920, 2940, 1960], [6450, 37637], [102], [1, 6323]]</t>
-  </si>
-  <si>
-    <t>h512_ws2_infp32_outfp32_fetch_5_ID745</t>
+    <t>[456, 13888, 26, 2053]</t>
+  </si>
+  <si>
+    <t>h512_ws2_infp32_outfp32_ID745</t>
   </si>
   <si>
     <t>[[369507, 512], [[9982], [3585]]]</t>
@@ -9551,10 +9551,10 @@
     <t>[9982, 3585]</t>
   </si>
   <si>
-    <t>[[1996, 2994, 3992, 999, 1], [1195, 1792, 598]]</t>
-  </si>
-  <si>
-    <t>h128_ws2_infp32_outfp16_fetch_7_ID746</t>
+    <t>[373, 128]</t>
+  </si>
+  <si>
+    <t>h128_ws2_infp32_outfp16_ID746</t>
   </si>
   <si>
     <t>[[262144, 128], [[3580], [8574]]]</t>
@@ -9563,10 +9563,10 @@
     <t>[3580, 8574]</t>
   </si>
   <si>
-    <t>[[3580], [6085, 1, 1, 1, 1, 1, 2484]]</t>
-  </si>
-  <si>
-    <t>h4139_ws8_infp32_outbf16_fetch_5_ID747</t>
+    <t>[3064, 8475]</t>
+  </si>
+  <si>
+    <t>h4139_ws8_infp32_outbf16_ID747</t>
   </si>
   <si>
     <t>[[524288, 4139], [[2940], [27766], [9452], [4162], [15125], [77878], [9677], [7149]]]</t>
@@ -9578,10 +9578,10 @@
     <t>[2940, 27766, 9452, 4162, 15125, 77878, 9677, 7149]</t>
   </si>
   <si>
-    <t>[[1470, 1470], [24517, 3249], [8704, 1, 747], [2081, 2081], [15125], [66133, 1, 1, 11743], [1935, 2902, 3869, 970, 1], [7149]]</t>
-  </si>
-  <si>
-    <t>h64_ws2_infp32_outbf16_fetch_7_ID748</t>
+    <t>[2836, 25586, 743, 3826, 14786, 4282, 8910, 3853]</t>
+  </si>
+  <si>
+    <t>h64_ws2_infp32_outbf16_ID748</t>
   </si>
   <si>
     <t>[[65536, 64], [[431], [7311]]]</t>
@@ -9590,10 +9590,10 @@
     <t>[431, 7311]</t>
   </si>
   <si>
-    <t>[[1, 163, 160, 107], [1045, 1045, 1045, 1044, 1044, 1044, 1044]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_infp32_outfp32_fetch_8_ID749</t>
+    <t>[200, 6676]</t>
+  </si>
+  <si>
+    <t>h256_ws16_infp32_outfp32_ID749</t>
   </si>
   <si>
     <t>[[243911, 256], [[39269], [21258], [1320], [4096], [8192], [51502], [36810], [90], [9343], [8985], [5454], [1248], [41710], [1024], [16415], [672]]]</t>
@@ -9608,10 +9608,10 @@
     <t>[39269, 21258, 1320, 4096, 8192, 51502, 36810, 90, 9343, 8985, 5454, 1248, 41710, 1024, 16415, 672]</t>
   </si>
   <si>
-    <t>[[39269], [10629, 10629], [1320], [1365, 2047, 684], [1024, 1536, 2048, 2560, 3072, 3584, -5633, 1], [25751, 25751], [36810], [90], [1, -3998, 4002, 3335, 2668, 2001, 1334], [2247, 2246, 2246, 2246], [1818, 1818, 1818], [1248], [41710], [1024], [16415], [1, 68, 268, 201, 134]]</t>
-  </si>
-  <si>
-    <t>h3422_ws2_infp32_outfp32_fetch_2_ID750</t>
+    <t>[7708, 20694, 671, 141, 7755, 43131, 33124, 75, 8250, 394, 5186, 91, 19618, 178, 741, 45]</t>
+  </si>
+  <si>
+    <t>h3422_ws2_infp32_outfp32_ID750</t>
   </si>
   <si>
     <t>[[65536, 3422], [[3273], [2048]]]</t>
@@ -9623,10 +9623,10 @@
     <t>[3273, 2048]</t>
   </si>
   <si>
-    <t>[[1636, 1637], [2048]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outbf16_fetch_4_ID701</t>
+    <t>[156, 958]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outbf16_ID701</t>
   </si>
   <si>
     <t>[[262144, 1024], [[42725], [905], [4961], [64635], [4096], [5713], [223], [487]]]</t>
@@ -9635,10 +9635,10 @@
     <t>[42725, 905, 4961, 64635, 4096, 5713, 223, 487]</t>
   </si>
   <si>
-    <t>[[10682, 10681, 10681, 10681], [227, 226, 226, 226], [1241, 1240, 1240, 1240], [16159, 16159, 16159, 16158], [4096], [2857, 2856], [223], [487]]</t>
-  </si>
-  <si>
-    <t>h2048_ws8_inbf16_outbf16_fetch_4_ID702</t>
+    <t>[25148, 457, 2459, 33665, 2244, 2500, 103, 214]</t>
+  </si>
+  <si>
+    <t>h2048_ws8_inbf16_outbf16_ID702</t>
   </si>
   <si>
     <t>[[262144, 2048], [[17090], [889], [22834], [29019], [47658], [2276], [5016], [21720]]]</t>
@@ -9647,10 +9647,10 @@
     <t>[17090, 889, 22834, 29019, 47658, 2276, 5016, 21720]</t>
   </si>
   <si>
-    <t>[[17090], [445, 444], [11417, 11417], [29019], [23829, 23829], [2276], [1254, 1254, 1254, 1254], [10860, 10860]]</t>
-  </si>
-  <si>
-    <t>h4096_ws8_inbf16_outbf16_fetch_6_ID703</t>
+    <t>[8554, 404, 11455, 13030, 21172, 941, 2415, 11602]</t>
+  </si>
+  <si>
+    <t>h4096_ws8_inbf16_outbf16_ID703</t>
   </si>
   <si>
     <t>[[262144, 4096], [[258], [5082], [6611], [639], [512], [32234], [5107], [19471]]]</t>
@@ -9659,10 +9659,10 @@
     <t>[258, 5082, 6611, 639, 512, 32234, 5107, 19471]</t>
   </si>
   <si>
-    <t>[[129, 129], [1271, 1271, 1270, 1270], [1102, 1102, 1102, 1102, 1102, 1101], [320, 319], [256, 256], [32234], [1703, 1702, 1702], [19471]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_8_ID704</t>
+    <t>[136, 2441, 3439, 305, 233, 12995, 2396, 8764]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outbf16_ID704</t>
   </si>
   <si>
     <t>[[65536, 256], [[34441], [47130], [7284], [3661], [6928], [469], [34], [819], [33559], [6565], [1024], [2048], [94531], [9095], [6888], [600]]]</t>
@@ -9671,16 +9671,16 @@
     <t>[34441, 47130, 7284, 3661, 6928, 469, 34, 819, 33559, 6565, 1024, 2048, 94531, 9095, 6888, 600]</t>
   </si>
   <si>
-    <t>[[11481, 11480, 11480], [23565, 23565], [1457, 1457, 1457, 1457, 1456], [3661], [1386, 1386, 1386, 1385, 1385], [118, 117, 117, 117], [34], [410, 409], [33559], [6565], [1024], [2048], [94531], [1137, 1137, 1137, 1137, 1137, 1137, 1137, 1136], [6888], [600]]</t>
-  </si>
-  <si>
-    <t>h1024_ws16_inbf16_outbf16_fetch_8_ID705</t>
+    <t>[18081, 22577, 4145, 1570, 4036, 275, 19, 360, 14758, 3104, 437, 1101, 56699, 4792, 3343, 251]</t>
+  </si>
+  <si>
+    <t>h1024_ws16_inbf16_outbf16_ID705</t>
   </si>
   <si>
     <t>[[262144, 1024], [[10513], [8075], [4634], [8192], [97819], [36745], [15793], [6080], [7603], [4096], [26920], [6632], [42], [345], [44657], [608]]]</t>
   </si>
   <si>
-    <t>h256_ws8_inbf16_outbf16_fetch_6_ID706</t>
+    <t>h256_ws8_inbf16_outbf16_ID706</t>
   </si>
   <si>
     <t>[[524288, 256], [[27295], [42899], [8802], [663], [1586], [7076], [65014], [933]]]</t>
@@ -9689,19 +9689,19 @@
     <t>[27295, 42899, 8802, 663, 1586, 7076, 65014, 933]</t>
   </si>
   <si>
-    <t>[[13648, 13647], [10725, 10725, 10725, 10724], [8802], [221, 221, 221], [1586], [1180, 1180, 1179, 1179, 1179, 1179], [16254, 16254, 16253, 16253], [234, 233, 233, 233]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outbf16_fetch_5_ID707</t>
+    <t>[14611, 24898, 5023, 265, 786, 3489, 38148, 491]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outbf16_ID707</t>
   </si>
   <si>
     <t>[[524288, 1024], [[90], [83731], [40387], [43180], [84568], [6009], [578], [18]]]</t>
   </si>
   <si>
-    <t>[[90], [41866, 41865], [40387], [43180], [28190, 28189, 28189], [3005, 3004], [116, 116, 116, 115, 115], [18]]</t>
-  </si>
-  <si>
-    <t>h2048_ws16_inbf16_outbf16_fetch_5_ID708</t>
+    <t>[41, 37398, 23664, 17610, 36460, 2705, 249, 8]</t>
+  </si>
+  <si>
+    <t>h2048_ws16_inbf16_outbf16_ID708</t>
   </si>
   <si>
     <t>[[524288, 2048], [[964], [32908], [6782], [49170], [4439], [6139], [75849], [63], [570], [4758], [35950], [783], [387], [7679], [193], [2747]]]</t>
@@ -9710,10 +9710,10 @@
     <t>[964, 32908, 6782, 49170, 4439, 6139, 75849, 63, 570, 4758, 35950, 783, 387, 7679, 193, 2747]</t>
   </si>
   <si>
-    <t>[[322, 321, 321], [32908], [1696, 1696, 1695, 1695], [49170], [1480, 1480, 1479], [6139], [15170, 15170, 15170, 15170, 15169], [21, 21, 21], [285, 285], [1586, 1586, 1586], [17975, 17975], [392, 391], [194, 193], [2560, 2560, 2559], [193], [2747]]</t>
-  </si>
-  <si>
-    <t>h4096_ws16_inbf16_outbf16_fetch_7_ID709</t>
+    <t>[465, 14092, 3612, 19914, 2425, 3089, 30954, 33, 336, 2648, 15966, 387, 210, 4449, 91, 1430]</t>
+  </si>
+  <si>
+    <t>h4096_ws16_inbf16_outbf16_ID709</t>
   </si>
   <si>
     <t>[[524288, 4096], [[5409], [209], [608], [2004], [79], [7008], [369], [54504], [84301], [1129], [79506], [15234], [4630], [33773], [659], [221]]]</t>
@@ -9722,10 +9722,10 @@
     <t>[5409, 209, 608, 2004, 79, 7008, 369, 54504, 84301, 1129, 79506, 15234, 4630, 33773, 659, 221]</t>
   </si>
   <si>
-    <t>[[1082, 1082, 1082, 1082, 1081], [209], [122, 122, 122, 121, 121], [1002, 1002], [79], [7008], [123, 123, 123], [10901, 10901, 10901, 10901, 10900], [28101, 28100, 28100], [1129], [11358, 11358, 11358, 11358, 11358, 11358, 11358], [15234], [2315, 2315], [16887, 16886], [659], [221]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_inbf16_outbf16_fetch_7_ID710</t>
+    <t>[2290, 120, 301, 821, 32, 4164, 218, 24126, 50455, 643, 46704, 8477, 1991, 20009, 266, 97]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_inbf16_outbf16_ID710</t>
   </si>
   <si>
     <t>[[262144, 1024], [[8337], [38812], [1638], [7945], [1197], [83127], [7153], [49455]]]</t>
@@ -9734,10 +9734,10 @@
     <t>[8337, 38812, 1638, 7945, 1197, 83127, 7153, 49455]</t>
   </si>
   <si>
-    <t>[[1191, 1191, 1191, 1191, 1191, 1191, 1191], [12938, 12937, 12937], [1638], [1135, 1135, 1135, 1135, 1135, 1135, 1135], [1197], [11876, 11876, 11875, 11875, 11875, 11875, 11875], [1431, 1431, 1431, 1430, 1430], [24728, 24727]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_infp16_outfp16_fetch_5_ID711</t>
+    <t>[4126, 20439, 685, 4524, 696, 37514, 3982, 26677]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_infp16_outfp16_ID711</t>
   </si>
   <si>
     <t>[[262144, 1024], [[35740], [33086], [5036], [5439], [6429], [256], [36447], [65]]]</t>
@@ -9746,10 +9746,10 @@
     <t>[35740, 33086, 5036, 5439, 6429, 256, 36447, 65]</t>
   </si>
   <si>
-    <t>[[17870, 17870], [16543, 16543], [1008, 1007, 1007, 1007, 1007], [5439], [3215, 3214], [128, 128], [12149, 12149, 12149], [33, 32]]</t>
-  </si>
-  <si>
-    <t>h1024_ws8_infp32_outfp32_fetch_8_ID712</t>
+    <t>[20603, 17236, 2319, 2327, 3025, 138, 16972, 37]</t>
+  </si>
+  <si>
+    <t>h1024_ws8_infp32_outfp32_ID712</t>
   </si>
   <si>
     <t>[[262144, 1024], [[9185], [7978], [761], [5453], [1182], [575], [51987], [2007]]]</t>
@@ -9758,10 +9758,10 @@
     <t>[9185, 7978, 761, 5453, 1182, 575, 51987, 2007]</t>
   </si>
   <si>
-    <t>[[1149, 1148, 1148, 1148, 1148, 1148, 1148, 1148], [3989, 3989], [381, 380], [1091, 1091, 1091, 1090, 1090], [1182], [288, 287], [51987], [1004, 1003]]</t>
-  </si>
-  <si>
-    <t>h32_ws2_inbf16_outbf16_fetch_5_ID901</t>
+    <t>[5172, 4252, 429, 2535, 506, 342, 28987, 1113]</t>
+  </si>
+  <si>
+    <t>h32_ws2_inbf16_outbf16_ID901</t>
   </si>
   <si>
     <t>[[4096, 32], [[5826], [259]]]</t>
@@ -9773,10 +9773,10 @@
     <t>[5826, 259]</t>
   </si>
   <si>
-    <t>[[1166, 1165, 1165, 1165, 1165], [259]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outbf16_fetch_1_ID902</t>
+    <t>[3404, 148]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outbf16_ID902</t>
   </si>
   <si>
     <t>[[1024, 256], [[8192], [41519]]]</t>
@@ -9788,10 +9788,10 @@
     <t>[8192, 41519]</t>
   </si>
   <si>
-    <t>[[8192], [41519]]</t>
-  </si>
-  <si>
-    <t>h256_ws2_inbf16_outbf16_fetch_3_ID903</t>
+    <t>[3336, 17579]</t>
+  </si>
+  <si>
+    <t>h256_ws2_inbf16_outbf16_ID903</t>
   </si>
   <si>
     <t>[[65536, 256], [[93], [556]]]</t>
@@ -9800,10 +9800,10 @@
     <t>[93, 556]</t>
   </si>
   <si>
-    <t>[[31, 31, 31], [278, 278]]</t>
-  </si>
-  <si>
-    <t>h256_ws16_inbf16_outbf16_fetch_5_ID904</t>
+    <t>[41, 259]</t>
+  </si>
+  <si>
+    <t>h256_ws16_inbf16_outbf16_ID904</t>
   </si>
   <si>
     <t>[[65536, 256], [[49450], [7500], [13568], [9361], [20], [8850], [587], [41876], [5613], [66780], [87], [2239], [13059], [314], [36546], [83]]]</t>
@@ -9812,10 +9812,10 @@
     <t>[49450, 7500, 13568, 9361, 20, 8850, 587, 41876, 5613, 66780, 87, 2239, 13059, 314, 36546, 83]</t>
   </si>
   <si>
-    <t>[[12363, 12363, 12362, 12362], [1875, 1875, 1875, 1875], [13568], [3121, 3120, 3120], [10, 10], [2950, 2950, 2950], [587], [20938, 20938], [1123, 1123, 1123, 1122, 1122], [66780], [87], [2239], [13059], [314], [18273, 18273], [83]]</t>
-  </si>
-  <si>
-    <t>h5120_ws4_inbf16_outbf16_fetch_1_ID905</t>
+    <t>[27687, 3866, 5961, 5520, 9, 4919, 272, 18903, 2320, 36158, 39, 1176, 5567, 131, 14654, 45]</t>
+  </si>
+  <si>
+    <t>h5120_ws4_inbf16_outbf16_ID905</t>
   </si>
   <si>
     <t>[[65536, 5120], [[32742], [41561], [18928], [1657]]]</t>
@@ -9827,10 +9827,10 @@
     <t>[32742, 41561, 18928, 1657]</t>
   </si>
   <si>
-    <t>[[32742], [41561], [18928], [1657]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_3_ID906</t>
+    <t>[13953, 16655, 7594, 770]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID906</t>
   </si>
   <si>
     <t>[[1000000, 256], [[84], [14876], [28120], [6516]]]</t>
@@ -9845,10 +9845,10 @@
     <t>[84, 14876, 28120, 6516]</t>
   </si>
   <si>
-    <t>[[84], [14876], [28120], [2172, 2172, 2172]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_1_ID907</t>
+    <t>[39, 7649, 12793, 3272]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID907</t>
   </si>
   <si>
     <t>[[65536, 256], [[1], [1], [1], [1]]]</t>
@@ -9857,10 +9857,7 @@
     <t>[1, 1, 1, 1]</t>
   </si>
   <si>
-    <t>[[1], [1], [1], [1]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outfp32_fetch_5_ID908</t>
+    <t>h256_ws4_inbf16_outfp32_ID908</t>
   </si>
   <si>
     <t>[[65536, 256], [[35742], [146], [6881], [39686]]]</t>
@@ -9869,10 +9866,10 @@
     <t>[35742, 146, 6881, 39686]</t>
   </si>
   <si>
-    <t>[[35742], [146], [1377, 1376, 1376, 1376, 1376], [39686]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_infp32_outbf16_fetch_3_ID909</t>
+    <t>[16024, 84, 4080, 19739]</t>
+  </si>
+  <si>
+    <t>h256_ws4_infp32_outbf16_ID909</t>
   </si>
   <si>
     <t>[[65536, 256], [[7511], [23955], [5738], [8192]]]</t>
@@ -9881,10 +9878,10 @@
     <t>[7511, 23955, 5738, 8192]</t>
   </si>
   <si>
-    <t>[[2504, 2504, 2503], [23955], [2869, 2869], [2731, 2731, 2730]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_4_ID910</t>
+    <t>[3554, 10705, 2715, 3637]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID910</t>
   </si>
   <si>
     <t>[[65536, 256], [[39621], [15691], [27884], [8204]]]</t>
@@ -9893,10 +9890,10 @@
     <t>[39621, 15691, 27884, 8204]</t>
   </si>
   <si>
-    <t>[[39621], [15691], [27884], [2051, 2051, 2051, 2051]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_5_ID911</t>
+    <t>[16357, 8291, 16359, 4914]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID911</t>
   </si>
   <si>
     <t>[[65536, 256], [[7495], [279], [99250], [9092]]]</t>
@@ -9905,10 +9902,10 @@
     <t>[7495, 279, 99250, 9092]</t>
   </si>
   <si>
-    <t>[[2499, 2498, 2498], [279], [19850, 19850, 19850, 19850, 19850], [2273, 2273, 2273, 2273]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_5_ID912</t>
+    <t>[3714, 153, 56140, 3644]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID912</t>
   </si>
   <si>
     <t>[[65536, 256], [[6089], [523], [44867], [1593]]]</t>
@@ -9917,10 +9914,10 @@
     <t>[6089, 523, 44867, 1593]</t>
   </si>
   <si>
-    <t>[[6089], [105, 105, 105, 104, 104], [14956, 14956, 14955], [1593]]</t>
-  </si>
-  <si>
-    <t>h256_ws4_inbf16_outbf16_fetch_7_ID913</t>
+    <t>[2533, 301, 22610, 928]</t>
+  </si>
+  <si>
+    <t>h256_ws4_inbf16_outbf16_ID913</t>
   </si>
   <si>
     <t>[[65536, 256], [[588], [88643], [31885], [75596]]]</t>
@@ -9929,7 +9926,7 @@
     <t>[588, 88643, 31885, 75596]</t>
   </si>
   <si>
-    <t>[[118, 118, 118, 117, 117], [12664, 12664, 12663, 12663, 12663, 12663, 12663], [31885], [37798, 37798]]</t>
+    <t>[299, 48771, 14036, 32520]</t>
   </si>
 </sst>
 </file>
@@ -10901,9 +10898,8 @@
   <dimension ref="A1:J43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="30.5765765765766" customWidth="1"/>
-    <col min="8" max="8" width="38.5225225225225" customWidth="1"/>
-    <col min="9" max="9" width="73.8198198198198" customWidth="1"/>
+    <col min="8" max="8" width="34.1261261261261" customWidth="1"/>
+    <col min="9" max="9" width="46.009009009009" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -30616,7 +30612,7 @@
         <v>3274</v>
       </c>
       <c r="I8" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -30624,10 +30620,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B9" t="s">
         <v>3276</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3277</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -30645,10 +30641,10 @@
         <v>16</v>
       </c>
       <c r="H9" t="s">
+        <v>3277</v>
+      </c>
+      <c r="I9" t="s">
         <v>3278</v>
-      </c>
-      <c r="I9" t="s">
-        <v>3279</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -30656,10 +30652,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B10" t="s">
         <v>3280</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3281</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
@@ -30677,10 +30673,10 @@
         <v>16</v>
       </c>
       <c r="H10" t="s">
+        <v>3281</v>
+      </c>
+      <c r="I10" t="s">
         <v>3282</v>
-      </c>
-      <c r="I10" t="s">
-        <v>3283</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -30688,10 +30684,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B11" t="s">
         <v>3284</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3285</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -30709,10 +30705,10 @@
         <v>16</v>
       </c>
       <c r="H11" t="s">
+        <v>3285</v>
+      </c>
+      <c r="I11" t="s">
         <v>3286</v>
-      </c>
-      <c r="I11" t="s">
-        <v>3287</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -30720,10 +30716,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B12" t="s">
         <v>3288</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3289</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -30741,10 +30737,10 @@
         <v>16</v>
       </c>
       <c r="H12" t="s">
+        <v>3289</v>
+      </c>
+      <c r="I12" t="s">
         <v>3290</v>
-      </c>
-      <c r="I12" t="s">
-        <v>3291</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -30752,10 +30748,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B13" t="s">
         <v>3292</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3293</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -30773,10 +30769,10 @@
         <v>16</v>
       </c>
       <c r="H13" t="s">
+        <v>3293</v>
+      </c>
+      <c r="I13" t="s">
         <v>3294</v>
-      </c>
-      <c r="I13" t="s">
-        <v>3295</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -30784,10 +30780,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B14" t="s">
         <v>3296</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3297</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -30805,10 +30801,10 @@
         <v>16</v>
       </c>
       <c r="H14" t="s">
+        <v>3297</v>
+      </c>
+      <c r="I14" t="s">
         <v>3298</v>
-      </c>
-      <c r="I14" t="s">
-        <v>3299</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
